--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="711">
   <si>
     <t>Наименование</t>
   </si>
@@ -221,6 +221,9 @@
     <t>Boxing Wizard - Straight Run (APA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Boxing Wizard - Suckin' Diesel (Helles), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Brew Division - 600 (Triple IPA),  РОЗЛИВ ,Россия</t>
   </si>
   <si>
@@ -1368,6 +1371,9 @@
   </si>
   <si>
     <t>вынос_Boxing Wizard - Straight Run (APA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Boxing Wizard - Suckin' Diesel (Helles), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Brew Division - 600 (Triple IPA),  РОЗЛИВ ,Россия</t>
@@ -2495,7 +2501,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B708"/>
+  <dimension ref="A1:B710"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -3043,7 +3049,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -3051,7 +3057,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -3059,7 +3065,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -3067,7 +3073,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -3075,7 +3081,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -3083,7 +3089,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -3091,7 +3097,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -3099,7 +3105,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3107,7 +3113,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -3115,7 +3121,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -3123,7 +3129,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -3139,7 +3145,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -3147,7 +3153,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -3155,7 +3161,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -3163,7 +3169,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -3171,7 +3177,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>540</v>
+        <v>560</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -3179,7 +3185,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>860</v>
+        <v>540</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -3187,7 +3193,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -3195,7 +3201,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>440</v>
+        <v>720</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -3203,7 +3209,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3211,7 +3217,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>460</v>
+        <v>560</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3227,7 +3233,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>960</v>
+        <v>460</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3235,7 +3241,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>940</v>
+        <v>960</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3243,7 +3249,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3251,7 +3257,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>660</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3259,7 +3265,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>480</v>
+        <v>660</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3267,7 +3273,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>400</v>
+        <v>480</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3275,7 +3281,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>720</v>
+        <v>400</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3283,7 +3289,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3291,7 +3297,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>500</v>
+        <v>560</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3299,7 +3305,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3307,7 +3313,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>500</v>
+        <v>760</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3315,7 +3321,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>920</v>
+        <v>500</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3323,7 +3329,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3331,7 +3337,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>420</v>
+        <v>600</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3339,7 +3345,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3347,7 +3353,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3355,7 +3361,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -3363,7 +3369,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3371,7 +3377,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3379,7 +3385,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>580</v>
+        <v>740</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3387,7 +3393,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3395,7 +3401,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3403,7 +3409,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3411,7 +3417,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3419,7 +3425,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3427,7 +3433,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3435,7 +3441,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3443,7 +3449,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3451,7 +3457,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3459,7 +3465,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>500</v>
+        <v>780</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3467,7 +3473,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>580</v>
+        <v>500</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3475,7 +3481,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -3483,7 +3489,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -3491,7 +3497,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -3499,7 +3505,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>420</v>
+        <v>560</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -3507,7 +3513,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>520</v>
+        <v>420</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -3515,7 +3521,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -3523,7 +3529,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>460</v>
+        <v>720</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -3531,7 +3537,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>560</v>
+        <v>460</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -3539,7 +3545,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -3547,7 +3553,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -3555,7 +3561,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -3563,7 +3569,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -3571,7 +3577,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>980</v>
+        <v>520</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -3579,7 +3585,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>540</v>
+        <v>980</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -3587,7 +3593,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -3595,7 +3601,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -3603,7 +3609,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -3611,7 +3617,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -3627,7 +3633,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -3635,7 +3641,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -3643,7 +3649,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -3667,7 +3673,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -3675,7 +3681,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3683,7 +3689,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -3691,7 +3697,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -3699,7 +3705,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -3707,7 +3713,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>460</v>
+        <v>700</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3715,7 +3721,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3723,7 +3729,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3731,7 +3737,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -3739,7 +3745,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -3747,7 +3753,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -3763,7 +3769,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -3779,7 +3785,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -3787,7 +3793,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -3795,7 +3801,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -3803,7 +3809,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -3811,7 +3817,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -3819,7 +3825,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>740</v>
+        <v>400</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -3827,7 +3833,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -3835,7 +3841,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -3843,7 +3849,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -3851,7 +3857,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -3859,7 +3865,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -3867,7 +3873,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -3883,7 +3889,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -3891,7 +3897,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -3899,7 +3905,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -3915,7 +3921,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -3923,7 +3929,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -3931,7 +3937,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -3939,7 +3945,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -3947,7 +3953,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -3955,7 +3961,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -3963,7 +3969,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -3971,7 +3977,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -3979,7 +3985,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -3987,7 +3993,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -3995,7 +4001,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4003,7 +4009,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4011,7 +4017,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>480</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4019,7 +4025,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4027,7 +4033,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4035,7 +4041,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4043,7 +4049,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4051,7 +4057,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4059,7 +4065,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4067,7 +4073,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4075,7 +4081,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4083,7 +4089,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4091,7 +4097,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4099,7 +4105,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4107,7 +4113,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4123,7 +4129,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4139,7 +4145,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4147,7 +4153,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4179,7 +4185,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4187,7 +4193,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4203,7 +4209,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4211,7 +4217,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4219,7 +4225,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4235,7 +4241,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4243,7 +4249,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4251,7 +4257,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>758</v>
+        <v>500</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4259,7 +4265,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>2273</v>
+        <v>758</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4267,7 +4273,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>1515</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4275,7 +4281,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>520</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4283,7 +4289,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4291,7 +4297,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4299,7 +4305,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4307,7 +4313,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4323,7 +4329,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4331,7 +4337,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4339,7 +4345,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4347,7 +4353,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4355,7 +4361,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4363,7 +4369,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4371,7 +4377,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4379,7 +4385,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4387,7 +4393,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4395,7 +4401,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4403,7 +4409,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4411,7 +4417,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4419,7 +4425,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4427,7 +4433,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4435,7 +4441,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>460</v>
+        <v>580</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4443,7 +4449,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4451,7 +4457,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4459,7 +4465,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4475,7 +4481,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4491,7 +4497,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>1000</v>
+        <v>560</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4499,7 +4505,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4507,7 +4513,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4515,7 +4521,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4523,7 +4529,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4531,7 +4537,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4539,7 +4545,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -4547,7 +4553,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4555,7 +4561,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4563,7 +4569,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4571,7 +4577,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4579,7 +4585,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4587,7 +4593,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4595,7 +4601,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4603,7 +4609,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4611,7 +4617,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4619,7 +4625,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4627,7 +4633,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4635,7 +4641,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4643,7 +4649,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4651,7 +4657,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4659,7 +4665,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>520</v>
+        <v>880</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4667,7 +4673,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4675,7 +4681,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4683,7 +4689,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4691,7 +4697,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4699,7 +4705,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4707,7 +4713,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4715,7 +4721,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>320</v>
+        <v>520</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4723,7 +4729,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>540</v>
+        <v>320</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4731,7 +4737,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4739,7 +4745,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4755,7 +4761,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4763,7 +4769,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4771,7 +4777,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>640</v>
+        <v>500</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4779,7 +4785,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>480</v>
+        <v>640</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4787,7 +4793,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>740</v>
+        <v>480</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4795,7 +4801,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>520</v>
+        <v>740</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4803,7 +4809,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4811,7 +4817,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4819,7 +4825,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -4835,7 +4841,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -4843,7 +4849,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -4851,7 +4857,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -4859,7 +4865,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -4867,7 +4873,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -4875,7 +4881,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -4883,7 +4889,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -4891,7 +4897,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -4899,7 +4905,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -4907,7 +4913,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -4923,7 +4929,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -4931,7 +4937,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -4939,7 +4945,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -4947,7 +4953,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -4955,7 +4961,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -4963,7 +4969,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -4979,7 +4985,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -4987,7 +4993,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -4995,7 +5001,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>640</v>
+        <v>480</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5003,7 +5009,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5011,7 +5017,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5019,7 +5025,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5027,7 +5033,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>520</v>
+        <v>860</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5035,7 +5041,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5043,7 +5049,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5059,7 +5065,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5067,7 +5073,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>700</v>
+        <v>420</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5075,7 +5081,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5083,7 +5089,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5091,7 +5097,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5099,7 +5105,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5107,7 +5113,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5115,7 +5121,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5123,7 +5129,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5131,7 +5137,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5139,7 +5145,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>440</v>
+        <v>620</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5147,7 +5153,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>320</v>
+        <v>440</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5163,7 +5169,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>820</v>
+        <v>320</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5171,7 +5177,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5179,7 +5185,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5195,7 +5201,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5203,7 +5209,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5219,7 +5225,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5227,7 +5233,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5235,7 +5241,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5243,7 +5249,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5251,7 +5257,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5259,7 +5265,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5267,7 +5273,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5275,7 +5281,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5283,7 +5289,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5291,7 +5297,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5299,7 +5305,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5307,7 +5313,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5315,7 +5321,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5323,7 +5329,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5331,7 +5337,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5339,7 +5345,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5347,7 +5353,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5355,7 +5361,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5363,7 +5369,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5371,7 +5377,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5379,7 +5385,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5387,7 +5393,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5395,7 +5401,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5403,7 +5409,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5411,7 +5417,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5427,7 +5433,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5435,7 +5441,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5443,7 +5449,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5451,7 +5457,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5459,7 +5465,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5475,7 +5481,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5483,7 +5489,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5491,7 +5497,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5499,7 +5505,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5507,7 +5513,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5515,7 +5521,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5523,7 +5529,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5539,7 +5545,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5547,7 +5553,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5555,7 +5561,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="1">
-        <v>640</v>
+        <v>920</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5563,7 +5569,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5571,7 +5577,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5579,7 +5585,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5587,7 +5593,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5595,7 +5601,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5603,7 +5609,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5611,7 +5617,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>860</v>
+        <v>640</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5619,7 +5625,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5627,7 +5633,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5635,7 +5641,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5643,7 +5649,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5651,7 +5657,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5659,7 +5665,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5667,7 +5673,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5675,7 +5681,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5683,7 +5689,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>620</v>
+        <v>480</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5691,7 +5697,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5699,7 +5705,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5707,7 +5713,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5715,7 +5721,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5723,7 +5729,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5731,7 +5737,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5739,7 +5745,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5747,7 +5753,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5755,7 +5761,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>840</v>
+        <v>480</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5763,7 +5769,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5771,7 +5777,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5779,7 +5785,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5795,7 +5801,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5803,7 +5809,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5819,7 +5825,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5827,7 +5833,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5835,7 +5841,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5843,7 +5849,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>1100</v>
+        <v>660</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5851,7 +5857,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5859,7 +5865,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5875,7 +5881,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -5883,7 +5889,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -5899,7 +5905,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -5907,7 +5913,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -5931,7 +5937,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -5939,7 +5945,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -5955,7 +5961,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -5963,7 +5969,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -5971,7 +5977,7 @@
         <v>434</v>
       </c>
       <c r="B434" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -5979,7 +5985,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -5987,7 +5993,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>880</v>
+        <v>620</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -5995,7 +6001,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6011,7 +6017,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6019,7 +6025,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6027,7 +6033,7 @@
         <v>441</v>
       </c>
       <c r="B441" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6035,7 +6041,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6043,7 +6049,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6051,7 +6057,7 @@
         <v>444</v>
       </c>
       <c r="B444" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6059,7 +6065,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6067,7 +6073,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6083,7 +6089,7 @@
         <v>448</v>
       </c>
       <c r="B448" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6091,7 +6097,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6099,7 +6105,7 @@
         <v>450</v>
       </c>
       <c r="B450" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6107,7 +6113,7 @@
         <v>451</v>
       </c>
       <c r="B451" s="1">
-        <v>920</v>
+        <v>820</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6115,7 +6121,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6123,7 +6129,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6131,7 +6137,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>640</v>
+        <v>600</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6139,7 +6145,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>700</v>
+        <v>880</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6147,7 +6153,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6155,7 +6161,7 @@
         <v>457</v>
       </c>
       <c r="B457" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6163,7 +6169,7 @@
         <v>458</v>
       </c>
       <c r="B458" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6171,7 +6177,7 @@
         <v>459</v>
       </c>
       <c r="B459" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6179,7 +6185,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6187,7 +6193,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6195,7 +6201,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6203,7 +6209,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6211,7 +6217,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6219,7 +6225,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>600</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6227,7 +6233,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>580</v>
+        <v>920</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6235,7 +6241,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6243,7 +6249,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6251,7 +6257,7 @@
         <v>469</v>
       </c>
       <c r="B469" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6259,7 +6265,7 @@
         <v>470</v>
       </c>
       <c r="B470" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6267,7 +6273,7 @@
         <v>471</v>
       </c>
       <c r="B471" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6275,7 +6281,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6283,7 +6289,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6291,7 +6297,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>720</v>
+        <v>960</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6299,7 +6305,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6307,7 +6313,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>540</v>
+        <v>720</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6315,7 +6321,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6323,7 +6329,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6331,7 +6337,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6339,7 +6345,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6347,7 +6353,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6355,7 +6361,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>980</v>
+        <v>620</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6363,7 +6369,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6371,7 +6377,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>720</v>
+        <v>980</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6379,7 +6385,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6387,7 +6393,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>920</v>
+        <v>720</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6395,7 +6401,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6403,7 +6409,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6411,7 +6417,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6427,7 +6433,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6435,7 +6441,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6443,7 +6449,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6451,7 +6457,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6467,7 +6473,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6475,7 +6481,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6491,7 +6497,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6499,7 +6505,7 @@
         <v>500</v>
       </c>
       <c r="B500" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6507,7 +6513,7 @@
         <v>501</v>
       </c>
       <c r="B501" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6515,7 +6521,7 @@
         <v>502</v>
       </c>
       <c r="B502" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6523,7 +6529,7 @@
         <v>503</v>
       </c>
       <c r="B503" s="1">
-        <v>1400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6539,7 +6545,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>660</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6547,7 +6553,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6555,7 +6561,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6563,7 +6569,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6571,7 +6577,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6579,7 +6585,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6587,7 +6593,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6595,7 +6601,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6611,7 +6617,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6619,7 +6625,7 @@
         <v>515</v>
       </c>
       <c r="B515" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6627,7 +6633,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6635,7 +6641,7 @@
         <v>517</v>
       </c>
       <c r="B517" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6643,7 +6649,7 @@
         <v>518</v>
       </c>
       <c r="B518" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6651,7 +6657,7 @@
         <v>519</v>
       </c>
       <c r="B519" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6659,7 +6665,7 @@
         <v>520</v>
       </c>
       <c r="B520" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6667,7 +6673,7 @@
         <v>521</v>
       </c>
       <c r="B521" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6683,7 +6689,7 @@
         <v>523</v>
       </c>
       <c r="B523" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6691,7 +6697,7 @@
         <v>524</v>
       </c>
       <c r="B524" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6699,7 +6705,7 @@
         <v>525</v>
       </c>
       <c r="B525" s="1">
-        <v>680</v>
+        <v>600</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6707,7 +6713,7 @@
         <v>526</v>
       </c>
       <c r="B526" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6715,7 +6721,7 @@
         <v>527</v>
       </c>
       <c r="B527" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6723,7 +6729,7 @@
         <v>528</v>
       </c>
       <c r="B528" s="1">
-        <v>540</v>
+        <v>640</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6739,7 +6745,7 @@
         <v>530</v>
       </c>
       <c r="B530" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6747,7 +6753,7 @@
         <v>531</v>
       </c>
       <c r="B531" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6755,7 +6761,7 @@
         <v>532</v>
       </c>
       <c r="B532" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6763,7 +6769,7 @@
         <v>533</v>
       </c>
       <c r="B533" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6771,7 +6777,7 @@
         <v>534</v>
       </c>
       <c r="B534" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6779,7 +6785,7 @@
         <v>535</v>
       </c>
       <c r="B535" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -6787,7 +6793,7 @@
         <v>536</v>
       </c>
       <c r="B536" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -6795,7 +6801,7 @@
         <v>537</v>
       </c>
       <c r="B537" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -6803,7 +6809,7 @@
         <v>538</v>
       </c>
       <c r="B538" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -6819,7 +6825,7 @@
         <v>540</v>
       </c>
       <c r="B540" s="1">
-        <v>800</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -6827,7 +6833,7 @@
         <v>541</v>
       </c>
       <c r="B541" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -6835,7 +6841,7 @@
         <v>542</v>
       </c>
       <c r="B542" s="1">
-        <v>640</v>
+        <v>800</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -6843,7 +6849,7 @@
         <v>543</v>
       </c>
       <c r="B543" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -6851,7 +6857,7 @@
         <v>544</v>
       </c>
       <c r="B544" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -6859,7 +6865,7 @@
         <v>545</v>
       </c>
       <c r="B545" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -6875,7 +6881,7 @@
         <v>547</v>
       </c>
       <c r="B547" s="1">
-        <v>880</v>
+        <v>640</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -6883,7 +6889,7 @@
         <v>548</v>
       </c>
       <c r="B548" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -6891,7 +6897,7 @@
         <v>549</v>
       </c>
       <c r="B549" s="1">
-        <v>600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -6899,7 +6905,7 @@
         <v>550</v>
       </c>
       <c r="B550" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -6915,7 +6921,7 @@
         <v>552</v>
       </c>
       <c r="B552" s="1">
-        <v>640</v>
+        <v>820</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -6923,7 +6929,7 @@
         <v>553</v>
       </c>
       <c r="B553" s="1">
-        <v>740</v>
+        <v>600</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -6931,7 +6937,7 @@
         <v>554</v>
       </c>
       <c r="B554" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -6939,7 +6945,7 @@
         <v>555</v>
       </c>
       <c r="B555" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -6947,7 +6953,7 @@
         <v>556</v>
       </c>
       <c r="B556" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -6955,7 +6961,7 @@
         <v>557</v>
       </c>
       <c r="B557" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -6963,7 +6969,7 @@
         <v>558</v>
       </c>
       <c r="B558" s="1">
-        <v>1020</v>
+        <v>720</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -6971,7 +6977,7 @@
         <v>559</v>
       </c>
       <c r="B559" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -6979,7 +6985,7 @@
         <v>560</v>
       </c>
       <c r="B560" s="1">
-        <v>700</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -6987,7 +6993,7 @@
         <v>561</v>
       </c>
       <c r="B561" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -6995,7 +7001,7 @@
         <v>562</v>
       </c>
       <c r="B562" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7003,7 +7009,7 @@
         <v>563</v>
       </c>
       <c r="B563" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7019,7 +7025,7 @@
         <v>565</v>
       </c>
       <c r="B565" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7027,7 +7033,7 @@
         <v>566</v>
       </c>
       <c r="B566" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7035,7 +7041,7 @@
         <v>567</v>
       </c>
       <c r="B567" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7043,7 +7049,7 @@
         <v>568</v>
       </c>
       <c r="B568" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7051,7 +7057,7 @@
         <v>569</v>
       </c>
       <c r="B569" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7059,7 +7065,7 @@
         <v>570</v>
       </c>
       <c r="B570" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7075,7 +7081,7 @@
         <v>572</v>
       </c>
       <c r="B572" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7091,7 +7097,7 @@
         <v>574</v>
       </c>
       <c r="B574" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7099,7 +7105,7 @@
         <v>575</v>
       </c>
       <c r="B575" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7107,7 +7113,7 @@
         <v>576</v>
       </c>
       <c r="B576" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7115,7 +7121,7 @@
         <v>577</v>
       </c>
       <c r="B577" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7123,7 +7129,7 @@
         <v>578</v>
       </c>
       <c r="B578" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7139,7 +7145,7 @@
         <v>580</v>
       </c>
       <c r="B580" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7147,7 +7153,7 @@
         <v>581</v>
       </c>
       <c r="B581" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7155,7 +7161,7 @@
         <v>582</v>
       </c>
       <c r="B582" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7163,7 +7169,7 @@
         <v>583</v>
       </c>
       <c r="B583" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7171,7 +7177,7 @@
         <v>584</v>
       </c>
       <c r="B584" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7179,7 +7185,7 @@
         <v>585</v>
       </c>
       <c r="B585" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7187,7 +7193,7 @@
         <v>586</v>
       </c>
       <c r="B586" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7195,7 +7201,7 @@
         <v>587</v>
       </c>
       <c r="B587" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7203,7 +7209,7 @@
         <v>588</v>
       </c>
       <c r="B588" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7219,7 +7225,7 @@
         <v>590</v>
       </c>
       <c r="B590" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7227,7 +7233,7 @@
         <v>591</v>
       </c>
       <c r="B591" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7235,7 +7241,7 @@
         <v>592</v>
       </c>
       <c r="B592" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7243,7 +7249,7 @@
         <v>593</v>
       </c>
       <c r="B593" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7251,7 +7257,7 @@
         <v>594</v>
       </c>
       <c r="B594" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7259,7 +7265,7 @@
         <v>595</v>
       </c>
       <c r="B595" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7267,7 +7273,7 @@
         <v>596</v>
       </c>
       <c r="B596" s="1">
-        <v>440</v>
+        <v>680</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7275,7 +7281,7 @@
         <v>597</v>
       </c>
       <c r="B597" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7283,7 +7289,7 @@
         <v>598</v>
       </c>
       <c r="B598" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7291,7 +7297,7 @@
         <v>599</v>
       </c>
       <c r="B599" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7299,7 +7305,7 @@
         <v>600</v>
       </c>
       <c r="B600" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7307,7 +7313,7 @@
         <v>601</v>
       </c>
       <c r="B601" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7315,7 +7321,7 @@
         <v>602</v>
       </c>
       <c r="B602" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7323,7 +7329,7 @@
         <v>603</v>
       </c>
       <c r="B603" s="1">
-        <v>800</v>
+        <v>560</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7331,7 +7337,7 @@
         <v>604</v>
       </c>
       <c r="B604" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7339,7 +7345,7 @@
         <v>605</v>
       </c>
       <c r="B605" s="1">
-        <v>920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7347,7 +7353,7 @@
         <v>606</v>
       </c>
       <c r="B606" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7355,7 +7361,7 @@
         <v>607</v>
       </c>
       <c r="B607" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7363,7 +7369,7 @@
         <v>608</v>
       </c>
       <c r="B608" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7371,7 +7377,7 @@
         <v>609</v>
       </c>
       <c r="B609" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7379,7 +7385,7 @@
         <v>610</v>
       </c>
       <c r="B610" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7387,7 +7393,7 @@
         <v>611</v>
       </c>
       <c r="B611" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7395,7 +7401,7 @@
         <v>612</v>
       </c>
       <c r="B612" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7403,7 +7409,7 @@
         <v>613</v>
       </c>
       <c r="B613" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7411,7 +7417,7 @@
         <v>614</v>
       </c>
       <c r="B614" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7419,7 +7425,7 @@
         <v>615</v>
       </c>
       <c r="B615" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7427,7 +7433,7 @@
         <v>616</v>
       </c>
       <c r="B616" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -7435,7 +7441,7 @@
         <v>617</v>
       </c>
       <c r="B617" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -7443,7 +7449,7 @@
         <v>618</v>
       </c>
       <c r="B618" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -7451,7 +7457,7 @@
         <v>619</v>
       </c>
       <c r="B619" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7459,7 +7465,7 @@
         <v>620</v>
       </c>
       <c r="B620" s="1">
-        <v>660</v>
+        <v>860</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7467,7 +7473,7 @@
         <v>621</v>
       </c>
       <c r="B621" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -7475,7 +7481,7 @@
         <v>622</v>
       </c>
       <c r="B622" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -7483,7 +7489,7 @@
         <v>623</v>
       </c>
       <c r="B623" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -7491,7 +7497,7 @@
         <v>624</v>
       </c>
       <c r="B624" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -7499,7 +7505,7 @@
         <v>625</v>
       </c>
       <c r="B625" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -7507,7 +7513,7 @@
         <v>626</v>
       </c>
       <c r="B626" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -7515,7 +7521,7 @@
         <v>627</v>
       </c>
       <c r="B627" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -7523,7 +7529,7 @@
         <v>628</v>
       </c>
       <c r="B628" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -7531,7 +7537,7 @@
         <v>629</v>
       </c>
       <c r="B629" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -7539,7 +7545,7 @@
         <v>630</v>
       </c>
       <c r="B630" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -7547,7 +7553,7 @@
         <v>631</v>
       </c>
       <c r="B631" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -7555,7 +7561,7 @@
         <v>632</v>
       </c>
       <c r="B632" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -7563,7 +7569,7 @@
         <v>633</v>
       </c>
       <c r="B633" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -7571,7 +7577,7 @@
         <v>634</v>
       </c>
       <c r="B634" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -7579,7 +7585,7 @@
         <v>635</v>
       </c>
       <c r="B635" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -7587,7 +7593,7 @@
         <v>636</v>
       </c>
       <c r="B636" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -7595,7 +7601,7 @@
         <v>637</v>
       </c>
       <c r="B637" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -7603,7 +7609,7 @@
         <v>638</v>
       </c>
       <c r="B638" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -7611,7 +7617,7 @@
         <v>639</v>
       </c>
       <c r="B639" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -7619,7 +7625,7 @@
         <v>640</v>
       </c>
       <c r="B640" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -7635,7 +7641,7 @@
         <v>642</v>
       </c>
       <c r="B642" s="1">
-        <v>920</v>
+        <v>500</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -7643,7 +7649,7 @@
         <v>643</v>
       </c>
       <c r="B643" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -7651,7 +7657,7 @@
         <v>644</v>
       </c>
       <c r="B644" s="1">
-        <v>1040</v>
+        <v>920</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -7659,7 +7665,7 @@
         <v>645</v>
       </c>
       <c r="B645" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -7667,7 +7673,7 @@
         <v>646</v>
       </c>
       <c r="B646" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -7675,7 +7681,7 @@
         <v>647</v>
       </c>
       <c r="B647" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -7683,7 +7689,7 @@
         <v>648</v>
       </c>
       <c r="B648" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -7691,7 +7697,7 @@
         <v>649</v>
       </c>
       <c r="B649" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -7699,7 +7705,7 @@
         <v>650</v>
       </c>
       <c r="B650" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -7715,7 +7721,7 @@
         <v>652</v>
       </c>
       <c r="B652" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -7723,7 +7729,7 @@
         <v>653</v>
       </c>
       <c r="B653" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -7731,7 +7737,7 @@
         <v>654</v>
       </c>
       <c r="B654" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -7739,7 +7745,7 @@
         <v>655</v>
       </c>
       <c r="B655" s="1">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -7747,7 +7753,7 @@
         <v>656</v>
       </c>
       <c r="B656" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -7755,7 +7761,7 @@
         <v>657</v>
       </c>
       <c r="B657" s="1">
-        <v>400</v>
+        <v>700</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -7763,7 +7769,7 @@
         <v>658</v>
       </c>
       <c r="B658" s="1">
-        <v>400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -7771,7 +7777,7 @@
         <v>659</v>
       </c>
       <c r="B659" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -7779,7 +7785,7 @@
         <v>660</v>
       </c>
       <c r="B660" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -7795,7 +7801,7 @@
         <v>662</v>
       </c>
       <c r="B662" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -7803,7 +7809,7 @@
         <v>663</v>
       </c>
       <c r="B663" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -7811,7 +7817,7 @@
         <v>664</v>
       </c>
       <c r="B664" s="1">
-        <v>860</v>
+        <v>520</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -7819,7 +7825,7 @@
         <v>665</v>
       </c>
       <c r="B665" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -7827,7 +7833,7 @@
         <v>666</v>
       </c>
       <c r="B666" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -7835,7 +7841,7 @@
         <v>667</v>
       </c>
       <c r="B667" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -7843,7 +7849,7 @@
         <v>668</v>
       </c>
       <c r="B668" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -7851,7 +7857,7 @@
         <v>669</v>
       </c>
       <c r="B669" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -7859,7 +7865,7 @@
         <v>670</v>
       </c>
       <c r="B670" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -7867,7 +7873,7 @@
         <v>671</v>
       </c>
       <c r="B671" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -7883,7 +7889,7 @@
         <v>673</v>
       </c>
       <c r="B673" s="1">
-        <v>840</v>
+        <v>500</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -7891,7 +7897,7 @@
         <v>674</v>
       </c>
       <c r="B674" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -7899,7 +7905,7 @@
         <v>675</v>
       </c>
       <c r="B675" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -7907,7 +7913,7 @@
         <v>676</v>
       </c>
       <c r="B676" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -7915,7 +7921,7 @@
         <v>677</v>
       </c>
       <c r="B677" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -7923,7 +7929,7 @@
         <v>678</v>
       </c>
       <c r="B678" s="1">
-        <v>1040</v>
+        <v>920</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -7931,7 +7937,7 @@
         <v>679</v>
       </c>
       <c r="B679" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -7939,7 +7945,7 @@
         <v>680</v>
       </c>
       <c r="B680" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -7947,7 +7953,7 @@
         <v>681</v>
       </c>
       <c r="B681" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -7955,7 +7961,7 @@
         <v>682</v>
       </c>
       <c r="B682" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -7963,7 +7969,7 @@
         <v>683</v>
       </c>
       <c r="B683" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -7971,7 +7977,7 @@
         <v>684</v>
       </c>
       <c r="B684" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -7987,7 +7993,7 @@
         <v>686</v>
       </c>
       <c r="B686" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -7995,7 +8001,7 @@
         <v>687</v>
       </c>
       <c r="B687" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8003,7 +8009,7 @@
         <v>688</v>
       </c>
       <c r="B688" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8011,7 +8017,7 @@
         <v>689</v>
       </c>
       <c r="B689" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8019,7 +8025,7 @@
         <v>690</v>
       </c>
       <c r="B690" s="1">
-        <v>380</v>
+        <v>740</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8035,7 +8041,7 @@
         <v>692</v>
       </c>
       <c r="B692" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8043,7 +8049,7 @@
         <v>693</v>
       </c>
       <c r="B693" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8059,7 +8065,7 @@
         <v>695</v>
       </c>
       <c r="B695" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8067,7 +8073,7 @@
         <v>696</v>
       </c>
       <c r="B696" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8075,7 +8081,7 @@
         <v>697</v>
       </c>
       <c r="B697" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8083,7 +8089,7 @@
         <v>698</v>
       </c>
       <c r="B698" s="1">
-        <v>420</v>
+        <v>520</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8091,7 +8097,7 @@
         <v>699</v>
       </c>
       <c r="B699" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8099,7 +8105,7 @@
         <v>700</v>
       </c>
       <c r="B700" s="1">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8107,7 +8113,7 @@
         <v>701</v>
       </c>
       <c r="B701" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8123,7 +8129,7 @@
         <v>703</v>
       </c>
       <c r="B703" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8131,7 +8137,7 @@
         <v>704</v>
       </c>
       <c r="B704" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8147,7 +8153,7 @@
         <v>706</v>
       </c>
       <c r="B706" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8155,7 +8161,7 @@
         <v>707</v>
       </c>
       <c r="B707" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8163,6 +8169,22 @@
         <v>708</v>
       </c>
       <c r="B708" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2">
+      <c r="A709" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="B709" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2">
+      <c r="A710" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B710" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -7761,7 +7761,7 @@
         <v>657</v>
       </c>
       <c r="B657" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -8129,7 +8129,7 @@
         <v>703</v>
       </c>
       <c r="B703" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="704" spans="1:2">

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="717">
   <si>
     <t>Наименование</t>
   </si>
@@ -665,6 +665,9 @@
     <t>Rakovar, РОЗЛИВ, Чехия</t>
   </si>
   <si>
+    <t>Red Button - Farout Faded Fantasy Super Grand Sale (Lager), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Red Button - Fondue fountain (Milk stout), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -761,6 +764,9 @@
     <t>Saint Loony - NICE (Sour), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Saint Loony - Strobe (Sour), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Saldens - Citra &amp; Galaxy Double IPA, РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1577,6 +1583,9 @@
     <t>вынос_Plan B - Ковбой Мальборо (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Red Button - Farout Faded Fantasy Super Grand Sale (Lager), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Red Button - Fondue fountain (Milk stout), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1622,6 +1631,9 @@
     <t>вынос_Saint Loony - NICE (Sour), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Saint Loony - Strobe (Sour), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Saliwa - Death by a 1000 Cats (Triple IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1931,6 +1943,9 @@
     <t>вынос_Одна тонна - Sunday Draft: Enigma + Idaho 7 (NE Pale Ale), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Одна тонна - Коник (Kolsch), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Одна тонна - Огниво: Cascade &amp; Simcoe, РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -2022,6 +2037,9 @@
   </si>
   <si>
     <t>Одна тонна - Sunday Draft: Enigma + Idaho 7 (NE Pale Ale), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>Одна тонна - Коник (Kolsch), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>Одна тонна - Огниво: Cascade &amp; Simcoe, РОЗЛИВ, Россия</t>
@@ -2501,7 +2519,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B710"/>
+  <dimension ref="A1:B716"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -4233,7 +4251,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4249,7 +4267,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4257,7 +4275,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4265,7 +4283,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>758</v>
+        <v>500</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4273,7 +4291,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>2273</v>
+        <v>758</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4281,7 +4299,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>1515</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4289,7 +4307,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>520</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4297,7 +4315,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4305,7 +4323,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4313,7 +4331,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4321,7 +4339,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4337,7 +4355,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4345,7 +4363,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4353,7 +4371,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4361,7 +4379,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4369,7 +4387,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4377,7 +4395,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4385,7 +4403,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4393,7 +4411,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4401,7 +4419,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4409,7 +4427,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4417,7 +4435,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4425,7 +4443,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4433,7 +4451,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4441,7 +4459,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4449,7 +4467,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>460</v>
+        <v>580</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4457,7 +4475,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4465,7 +4483,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4473,7 +4491,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4489,7 +4507,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4497,7 +4515,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4505,7 +4523,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>1000</v>
+        <v>560</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4513,7 +4531,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4521,7 +4539,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4529,7 +4547,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4537,7 +4555,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>840</v>
+        <v>680</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4553,7 +4571,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>1020</v>
+        <v>840</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4569,7 +4587,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>680</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4577,7 +4595,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>520</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4585,7 +4603,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4593,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4601,7 +4619,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4609,7 +4627,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4617,7 +4635,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4625,7 +4643,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4633,7 +4651,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4641,7 +4659,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4649,7 +4667,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4665,7 +4683,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>880</v>
+        <v>640</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4673,7 +4691,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>520</v>
+        <v>720</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4681,7 +4699,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4689,7 +4707,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4697,7 +4715,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4713,7 +4731,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4721,7 +4739,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>520</v>
+        <v>600</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4729,7 +4747,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>320</v>
+        <v>380</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4737,7 +4755,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4745,7 +4763,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>560</v>
+        <v>320</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4753,7 +4771,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>480</v>
+        <v>540</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4761,7 +4779,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4769,7 +4787,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4777,7 +4795,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>500</v>
+        <v>480</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4785,7 +4803,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4793,7 +4811,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4801,7 +4819,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4809,7 +4827,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4817,7 +4835,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>380</v>
+        <v>780</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4825,7 +4843,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -4833,7 +4851,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>900</v>
+        <v>380</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -4841,7 +4859,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -4849,7 +4867,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -4857,7 +4875,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -4865,7 +4883,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>1020</v>
+        <v>720</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -4873,7 +4891,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -4881,7 +4899,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>700</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -4889,7 +4907,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -4897,7 +4915,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -4905,7 +4923,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -4921,7 +4939,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -4929,7 +4947,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -4937,7 +4955,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -4945,7 +4963,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -4953,7 +4971,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -4961,7 +4979,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -4977,7 +4995,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -4985,7 +5003,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -4993,7 +5011,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5001,7 +5019,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>480</v>
+        <v>740</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5009,7 +5027,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5017,7 +5035,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>1000</v>
+        <v>480</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5025,7 +5043,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>920</v>
+        <v>640</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5033,7 +5051,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5041,7 +5059,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>520</v>
+        <v>920</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5049,7 +5067,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>540</v>
+        <v>860</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5057,7 +5075,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>700</v>
+        <v>520</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5065,7 +5083,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5073,7 +5091,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5089,7 +5107,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>720</v>
+        <v>420</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5097,7 +5115,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5105,7 +5123,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5113,7 +5131,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5121,7 +5139,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5129,7 +5147,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5137,7 +5155,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5145,7 +5163,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5153,7 +5171,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>440</v>
+        <v>720</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5161,7 +5179,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>320</v>
+        <v>620</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5169,7 +5187,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>320</v>
+        <v>440</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5177,7 +5195,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>820</v>
+        <v>320</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5185,7 +5203,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>1000</v>
+        <v>320</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5193,7 +5211,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5201,7 +5219,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5209,7 +5227,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5225,7 +5243,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5233,7 +5251,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5241,7 +5259,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5249,7 +5267,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>1000</v>
+        <v>620</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5257,7 +5275,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5265,7 +5283,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5281,7 +5299,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5289,7 +5307,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5297,7 +5315,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5305,7 +5323,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5313,7 +5331,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5321,7 +5339,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5329,7 +5347,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>440</v>
+        <v>680</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5337,7 +5355,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5345,7 +5363,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5353,7 +5371,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5361,7 +5379,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5369,7 +5387,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5377,7 +5395,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5385,7 +5403,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5393,7 +5411,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5401,7 +5419,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5409,7 +5427,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5417,7 +5435,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>680</v>
+        <v>620</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5425,7 +5443,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>480</v>
+        <v>720</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5433,7 +5451,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5441,7 +5459,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5449,7 +5467,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5457,7 +5475,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5465,7 +5483,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5473,7 +5491,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5481,7 +5499,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5489,7 +5507,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5497,7 +5515,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5505,7 +5523,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5513,7 +5531,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="1">
-        <v>600</v>
+        <v>980</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5521,7 +5539,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>760</v>
+        <v>920</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5529,7 +5547,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5537,7 +5555,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>620</v>
+        <v>760</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5545,7 +5563,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5553,7 +5571,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5561,7 +5579,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5569,7 +5587,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="1">
-        <v>640</v>
+        <v>860</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5577,7 +5595,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5585,7 +5603,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>820</v>
+        <v>640</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5593,7 +5611,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5601,7 +5619,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5609,7 +5627,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5617,7 +5635,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5625,7 +5643,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5633,7 +5651,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5641,7 +5659,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5649,7 +5667,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5657,7 +5675,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5665,7 +5683,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5673,7 +5691,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>840</v>
+        <v>640</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5681,7 +5699,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5689,7 +5707,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>480</v>
+        <v>840</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5697,7 +5715,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5705,7 +5723,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>780</v>
+        <v>480</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5713,7 +5731,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5721,7 +5739,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5729,7 +5747,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5737,7 +5755,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5745,7 +5763,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5753,7 +5771,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5761,7 +5779,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>480</v>
+        <v>780</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5769,7 +5787,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5777,7 +5795,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>660</v>
+        <v>480</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5785,7 +5803,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5793,7 +5811,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5801,7 +5819,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5809,7 +5827,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5817,7 +5835,7 @@
         <v>414</v>
       </c>
       <c r="B414" s="1">
-        <v>880</v>
+        <v>440</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5825,7 +5843,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5833,7 +5851,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5841,7 +5859,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5849,7 +5867,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5857,7 +5875,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5865,7 +5883,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5873,7 +5891,7 @@
         <v>421</v>
       </c>
       <c r="B421" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -5881,7 +5899,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -5889,7 +5907,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -5897,7 +5915,7 @@
         <v>424</v>
       </c>
       <c r="B424" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -5905,7 +5923,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -5913,7 +5931,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -5921,7 +5939,7 @@
         <v>427</v>
       </c>
       <c r="B427" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -5929,7 +5947,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -5945,7 +5963,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -5953,7 +5971,7 @@
         <v>431</v>
       </c>
       <c r="B431" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -5961,7 +5979,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -5969,7 +5987,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -5977,7 +5995,7 @@
         <v>434</v>
       </c>
       <c r="B434" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -5985,7 +6003,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -5993,7 +6011,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6001,7 +6019,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6009,7 +6027,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6017,7 +6035,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6025,7 +6043,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6033,7 +6051,7 @@
         <v>441</v>
       </c>
       <c r="B441" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6041,7 +6059,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6049,7 +6067,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6057,7 +6075,7 @@
         <v>444</v>
       </c>
       <c r="B444" s="1">
-        <v>640</v>
+        <v>900</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6065,7 +6083,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>800</v>
+        <v>740</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6073,7 +6091,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6081,7 +6099,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6089,7 +6107,7 @@
         <v>448</v>
       </c>
       <c r="B448" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6097,7 +6115,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6105,7 +6123,7 @@
         <v>450</v>
       </c>
       <c r="B450" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6129,7 +6147,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>920</v>
+        <v>820</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6137,7 +6155,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6145,7 +6163,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6153,7 +6171,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>640</v>
+        <v>600</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6161,7 +6179,7 @@
         <v>457</v>
       </c>
       <c r="B457" s="1">
-        <v>700</v>
+        <v>880</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6169,7 +6187,7 @@
         <v>458</v>
       </c>
       <c r="B458" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6177,7 +6195,7 @@
         <v>459</v>
       </c>
       <c r="B459" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6185,7 +6203,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6193,7 +6211,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6201,7 +6219,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6209,7 +6227,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6217,7 +6235,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6225,7 +6243,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6233,7 +6251,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6241,7 +6259,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>600</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6249,7 +6267,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>580</v>
+        <v>920</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6257,7 +6275,7 @@
         <v>469</v>
       </c>
       <c r="B469" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6265,7 +6283,7 @@
         <v>470</v>
       </c>
       <c r="B470" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6273,7 +6291,7 @@
         <v>471</v>
       </c>
       <c r="B471" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6281,7 +6299,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6289,7 +6307,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6297,7 +6315,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6305,7 +6323,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6313,7 +6331,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>720</v>
+        <v>960</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6321,7 +6339,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6329,7 +6347,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>540</v>
+        <v>720</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6337,7 +6355,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6345,7 +6363,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6353,7 +6371,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6361,7 +6379,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6369,7 +6387,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6377,7 +6395,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>980</v>
+        <v>620</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6385,7 +6403,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6393,7 +6411,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>720</v>
+        <v>980</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6401,7 +6419,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6409,7 +6427,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>920</v>
+        <v>720</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6417,7 +6435,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6425,7 +6443,7 @@
         <v>490</v>
       </c>
       <c r="B490" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6433,7 +6451,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6449,7 +6467,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6457,7 +6475,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6465,7 +6483,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6473,7 +6491,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6489,7 +6507,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6497,7 +6515,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6513,7 +6531,7 @@
         <v>501</v>
       </c>
       <c r="B501" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6521,7 +6539,7 @@
         <v>502</v>
       </c>
       <c r="B502" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6529,7 +6547,7 @@
         <v>503</v>
       </c>
       <c r="B503" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6537,7 +6555,7 @@
         <v>504</v>
       </c>
       <c r="B504" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6545,7 +6563,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>1400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6561,7 +6579,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>660</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6569,7 +6587,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6577,7 +6595,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6585,7 +6603,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6593,7 +6611,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6601,7 +6619,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6609,7 +6627,7 @@
         <v>513</v>
       </c>
       <c r="B513" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6617,7 +6635,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6633,7 +6651,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6641,7 +6659,7 @@
         <v>517</v>
       </c>
       <c r="B517" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6649,7 +6667,7 @@
         <v>518</v>
       </c>
       <c r="B518" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6657,7 +6675,7 @@
         <v>519</v>
       </c>
       <c r="B519" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6665,7 +6683,7 @@
         <v>520</v>
       </c>
       <c r="B520" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6673,7 +6691,7 @@
         <v>521</v>
       </c>
       <c r="B521" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6681,7 +6699,7 @@
         <v>522</v>
       </c>
       <c r="B522" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -6689,7 +6707,7 @@
         <v>523</v>
       </c>
       <c r="B523" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6697,7 +6715,7 @@
         <v>524</v>
       </c>
       <c r="B524" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6705,7 +6723,7 @@
         <v>525</v>
       </c>
       <c r="B525" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6713,7 +6731,7 @@
         <v>526</v>
       </c>
       <c r="B526" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6721,7 +6739,7 @@
         <v>527</v>
       </c>
       <c r="B527" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6729,7 +6747,7 @@
         <v>528</v>
       </c>
       <c r="B528" s="1">
-        <v>640</v>
+        <v>600</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6737,7 +6755,7 @@
         <v>529</v>
       </c>
       <c r="B529" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6745,7 +6763,7 @@
         <v>530</v>
       </c>
       <c r="B530" s="1">
-        <v>540</v>
+        <v>680</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6753,7 +6771,7 @@
         <v>531</v>
       </c>
       <c r="B531" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6761,7 +6779,7 @@
         <v>532</v>
       </c>
       <c r="B532" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6769,7 +6787,7 @@
         <v>533</v>
       </c>
       <c r="B533" s="1">
-        <v>860</v>
+        <v>540</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6777,7 +6795,7 @@
         <v>534</v>
       </c>
       <c r="B534" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6785,7 +6803,7 @@
         <v>535</v>
       </c>
       <c r="B535" s="1">
-        <v>1000</v>
+        <v>580</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -6793,7 +6811,7 @@
         <v>536</v>
       </c>
       <c r="B536" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -6801,7 +6819,7 @@
         <v>537</v>
       </c>
       <c r="B537" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -6809,7 +6827,7 @@
         <v>538</v>
       </c>
       <c r="B538" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -6825,7 +6843,7 @@
         <v>540</v>
       </c>
       <c r="B540" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -6833,7 +6851,7 @@
         <v>541</v>
       </c>
       <c r="B541" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -6841,7 +6859,7 @@
         <v>542</v>
       </c>
       <c r="B542" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -6849,7 +6867,7 @@
         <v>543</v>
       </c>
       <c r="B543" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -6857,7 +6875,7 @@
         <v>544</v>
       </c>
       <c r="B544" s="1">
-        <v>640</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -6865,7 +6883,7 @@
         <v>545</v>
       </c>
       <c r="B545" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -6873,7 +6891,7 @@
         <v>546</v>
       </c>
       <c r="B546" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -6881,7 +6899,7 @@
         <v>547</v>
       </c>
       <c r="B547" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -6889,7 +6907,7 @@
         <v>548</v>
       </c>
       <c r="B548" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -6897,7 +6915,7 @@
         <v>549</v>
       </c>
       <c r="B549" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -6905,7 +6923,7 @@
         <v>550</v>
       </c>
       <c r="B550" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -6913,7 +6931,7 @@
         <v>551</v>
       </c>
       <c r="B551" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -6921,7 +6939,7 @@
         <v>552</v>
       </c>
       <c r="B552" s="1">
-        <v>820</v>
+        <v>720</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -6929,7 +6947,7 @@
         <v>553</v>
       </c>
       <c r="B553" s="1">
-        <v>600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -6937,7 +6955,7 @@
         <v>554</v>
       </c>
       <c r="B554" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -6945,7 +6963,7 @@
         <v>555</v>
       </c>
       <c r="B555" s="1">
-        <v>740</v>
+        <v>600</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -6953,7 +6971,7 @@
         <v>556</v>
       </c>
       <c r="B556" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -6961,7 +6979,7 @@
         <v>557</v>
       </c>
       <c r="B557" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -6969,7 +6987,7 @@
         <v>558</v>
       </c>
       <c r="B558" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -6977,7 +6995,7 @@
         <v>559</v>
       </c>
       <c r="B559" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -6985,7 +7003,7 @@
         <v>560</v>
       </c>
       <c r="B560" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -6993,7 +7011,7 @@
         <v>561</v>
       </c>
       <c r="B561" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7001,7 +7019,7 @@
         <v>562</v>
       </c>
       <c r="B562" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7009,7 +7027,7 @@
         <v>563</v>
       </c>
       <c r="B563" s="1">
-        <v>640</v>
+        <v>960</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7017,7 +7035,7 @@
         <v>564</v>
       </c>
       <c r="B564" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7025,7 +7043,7 @@
         <v>565</v>
       </c>
       <c r="B565" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7033,7 +7051,7 @@
         <v>566</v>
       </c>
       <c r="B566" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7041,7 +7059,7 @@
         <v>567</v>
       </c>
       <c r="B567" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7049,7 +7067,7 @@
         <v>568</v>
       </c>
       <c r="B568" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7057,7 +7075,7 @@
         <v>569</v>
       </c>
       <c r="B569" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7065,7 +7083,7 @@
         <v>570</v>
       </c>
       <c r="B570" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7073,7 +7091,7 @@
         <v>571</v>
       </c>
       <c r="B571" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7081,7 +7099,7 @@
         <v>572</v>
       </c>
       <c r="B572" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7089,7 +7107,7 @@
         <v>573</v>
       </c>
       <c r="B573" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7097,7 +7115,7 @@
         <v>574</v>
       </c>
       <c r="B574" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7113,7 +7131,7 @@
         <v>576</v>
       </c>
       <c r="B576" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7121,7 +7139,7 @@
         <v>577</v>
       </c>
       <c r="B577" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7129,7 +7147,7 @@
         <v>578</v>
       </c>
       <c r="B578" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7137,7 +7155,7 @@
         <v>579</v>
       </c>
       <c r="B579" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7145,7 +7163,7 @@
         <v>580</v>
       </c>
       <c r="B580" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7153,7 +7171,7 @@
         <v>581</v>
       </c>
       <c r="B581" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7161,7 +7179,7 @@
         <v>582</v>
       </c>
       <c r="B582" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7169,7 +7187,7 @@
         <v>583</v>
       </c>
       <c r="B583" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7177,7 +7195,7 @@
         <v>584</v>
       </c>
       <c r="B584" s="1">
-        <v>820</v>
+        <v>900</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7185,7 +7203,7 @@
         <v>585</v>
       </c>
       <c r="B585" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7193,7 +7211,7 @@
         <v>586</v>
       </c>
       <c r="B586" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7201,7 +7219,7 @@
         <v>587</v>
       </c>
       <c r="B587" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7209,7 +7227,7 @@
         <v>588</v>
       </c>
       <c r="B588" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7217,7 +7235,7 @@
         <v>589</v>
       </c>
       <c r="B589" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7225,7 +7243,7 @@
         <v>590</v>
       </c>
       <c r="B590" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7233,7 +7251,7 @@
         <v>591</v>
       </c>
       <c r="B591" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7241,7 +7259,7 @@
         <v>592</v>
       </c>
       <c r="B592" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7249,7 +7267,7 @@
         <v>593</v>
       </c>
       <c r="B593" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7257,7 +7275,7 @@
         <v>594</v>
       </c>
       <c r="B594" s="1">
-        <v>660</v>
+        <v>880</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7265,7 +7283,7 @@
         <v>595</v>
       </c>
       <c r="B595" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7273,7 +7291,7 @@
         <v>596</v>
       </c>
       <c r="B596" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7281,7 +7299,7 @@
         <v>597</v>
       </c>
       <c r="B597" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7289,7 +7307,7 @@
         <v>598</v>
       </c>
       <c r="B598" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7305,7 +7323,7 @@
         <v>600</v>
       </c>
       <c r="B600" s="1">
-        <v>800</v>
+        <v>680</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7313,7 +7331,7 @@
         <v>601</v>
       </c>
       <c r="B601" s="1">
-        <v>720</v>
+        <v>660</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7321,7 +7339,7 @@
         <v>602</v>
       </c>
       <c r="B602" s="1">
-        <v>600</v>
+        <v>440</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7329,7 +7347,7 @@
         <v>603</v>
       </c>
       <c r="B603" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7337,7 +7355,7 @@
         <v>604</v>
       </c>
       <c r="B604" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7345,7 +7363,7 @@
         <v>605</v>
       </c>
       <c r="B605" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7353,7 +7371,7 @@
         <v>606</v>
       </c>
       <c r="B606" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7361,7 +7379,7 @@
         <v>607</v>
       </c>
       <c r="B607" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7369,7 +7387,7 @@
         <v>608</v>
       </c>
       <c r="B608" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7377,7 +7395,7 @@
         <v>609</v>
       </c>
       <c r="B609" s="1">
-        <v>940</v>
+        <v>800</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7385,7 +7403,7 @@
         <v>610</v>
       </c>
       <c r="B610" s="1">
-        <v>980</v>
+        <v>780</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7401,7 +7419,7 @@
         <v>612</v>
       </c>
       <c r="B612" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7409,7 +7427,7 @@
         <v>613</v>
       </c>
       <c r="B613" s="1">
-        <v>860</v>
+        <v>940</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7417,7 +7435,7 @@
         <v>614</v>
       </c>
       <c r="B614" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7425,7 +7443,7 @@
         <v>615</v>
       </c>
       <c r="B615" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7433,7 +7451,7 @@
         <v>616</v>
       </c>
       <c r="B616" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -7441,7 +7459,7 @@
         <v>617</v>
       </c>
       <c r="B617" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -7449,7 +7467,7 @@
         <v>618</v>
       </c>
       <c r="B618" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -7457,7 +7475,7 @@
         <v>619</v>
       </c>
       <c r="B619" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7465,7 +7483,7 @@
         <v>620</v>
       </c>
       <c r="B620" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7473,7 +7491,7 @@
         <v>621</v>
       </c>
       <c r="B621" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -7481,7 +7499,7 @@
         <v>622</v>
       </c>
       <c r="B622" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -7489,7 +7507,7 @@
         <v>623</v>
       </c>
       <c r="B623" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -7497,7 +7515,7 @@
         <v>624</v>
       </c>
       <c r="B624" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -7505,7 +7523,7 @@
         <v>625</v>
       </c>
       <c r="B625" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -7513,7 +7531,7 @@
         <v>626</v>
       </c>
       <c r="B626" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -7521,7 +7539,7 @@
         <v>627</v>
       </c>
       <c r="B627" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -7537,7 +7555,7 @@
         <v>629</v>
       </c>
       <c r="B629" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -7545,7 +7563,7 @@
         <v>630</v>
       </c>
       <c r="B630" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -7553,7 +7571,7 @@
         <v>631</v>
       </c>
       <c r="B631" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -7561,7 +7579,7 @@
         <v>632</v>
       </c>
       <c r="B632" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -7569,7 +7587,7 @@
         <v>633</v>
       </c>
       <c r="B633" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -7577,7 +7595,7 @@
         <v>634</v>
       </c>
       <c r="B634" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -7585,7 +7603,7 @@
         <v>635</v>
       </c>
       <c r="B635" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -7593,7 +7611,7 @@
         <v>636</v>
       </c>
       <c r="B636" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -7601,7 +7619,7 @@
         <v>637</v>
       </c>
       <c r="B637" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -7609,7 +7627,7 @@
         <v>638</v>
       </c>
       <c r="B638" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -7617,7 +7635,7 @@
         <v>639</v>
       </c>
       <c r="B639" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -7625,7 +7643,7 @@
         <v>640</v>
       </c>
       <c r="B640" s="1">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -7633,7 +7651,7 @@
         <v>641</v>
       </c>
       <c r="B641" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -7641,7 +7659,7 @@
         <v>642</v>
       </c>
       <c r="B642" s="1">
-        <v>500</v>
+        <v>780</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -7649,7 +7667,7 @@
         <v>643</v>
       </c>
       <c r="B643" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -7657,7 +7675,7 @@
         <v>644</v>
       </c>
       <c r="B644" s="1">
-        <v>920</v>
+        <v>720</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -7665,7 +7683,7 @@
         <v>645</v>
       </c>
       <c r="B645" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -7673,7 +7691,7 @@
         <v>646</v>
       </c>
       <c r="B646" s="1">
-        <v>1040</v>
+        <v>600</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -7681,7 +7699,7 @@
         <v>647</v>
       </c>
       <c r="B647" s="1">
-        <v>940</v>
+        <v>500</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -7689,7 +7707,7 @@
         <v>648</v>
       </c>
       <c r="B648" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -7697,7 +7715,7 @@
         <v>649</v>
       </c>
       <c r="B649" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -7705,7 +7723,7 @@
         <v>650</v>
       </c>
       <c r="B650" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -7713,7 +7731,7 @@
         <v>651</v>
       </c>
       <c r="B651" s="1">
-        <v>440</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -7721,7 +7739,7 @@
         <v>652</v>
       </c>
       <c r="B652" s="1">
-        <v>500</v>
+        <v>940</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -7729,7 +7747,7 @@
         <v>653</v>
       </c>
       <c r="B653" s="1">
-        <v>440</v>
+        <v>900</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -7737,7 +7755,7 @@
         <v>654</v>
       </c>
       <c r="B654" s="1">
-        <v>560</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -7745,7 +7763,7 @@
         <v>655</v>
       </c>
       <c r="B655" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -7753,7 +7771,7 @@
         <v>656</v>
       </c>
       <c r="B656" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -7761,7 +7779,7 @@
         <v>657</v>
       </c>
       <c r="B657" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -7769,7 +7787,7 @@
         <v>658</v>
       </c>
       <c r="B658" s="1">
-        <v>760</v>
+        <v>440</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -7777,7 +7795,7 @@
         <v>659</v>
       </c>
       <c r="B659" s="1">
-        <v>400</v>
+        <v>560</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -7785,7 +7803,7 @@
         <v>660</v>
       </c>
       <c r="B660" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -7793,7 +7811,7 @@
         <v>661</v>
       </c>
       <c r="B661" s="1">
-        <v>380</v>
+        <v>740</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -7801,7 +7819,7 @@
         <v>662</v>
       </c>
       <c r="B662" s="1">
-        <v>380</v>
+        <v>760</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -7809,7 +7827,7 @@
         <v>663</v>
       </c>
       <c r="B663" s="1">
-        <v>380</v>
+        <v>760</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -7817,7 +7835,7 @@
         <v>664</v>
       </c>
       <c r="B664" s="1">
-        <v>520</v>
+        <v>400</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -7825,7 +7843,7 @@
         <v>665</v>
       </c>
       <c r="B665" s="1">
-        <v>700</v>
+        <v>400</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -7833,7 +7851,7 @@
         <v>666</v>
       </c>
       <c r="B666" s="1">
-        <v>860</v>
+        <v>380</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -7841,7 +7859,7 @@
         <v>667</v>
       </c>
       <c r="B667" s="1">
-        <v>680</v>
+        <v>380</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -7849,7 +7867,7 @@
         <v>668</v>
       </c>
       <c r="B668" s="1">
-        <v>740</v>
+        <v>380</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -7857,7 +7875,7 @@
         <v>669</v>
       </c>
       <c r="B669" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -7865,7 +7883,7 @@
         <v>670</v>
       </c>
       <c r="B670" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -7873,7 +7891,7 @@
         <v>671</v>
       </c>
       <c r="B671" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -7881,7 +7899,7 @@
         <v>672</v>
       </c>
       <c r="B672" s="1">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -7889,7 +7907,7 @@
         <v>673</v>
       </c>
       <c r="B673" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -7897,7 +7915,7 @@
         <v>674</v>
       </c>
       <c r="B674" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -7905,7 +7923,7 @@
         <v>675</v>
       </c>
       <c r="B675" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -7913,7 +7931,7 @@
         <v>676</v>
       </c>
       <c r="B676" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -7921,7 +7939,7 @@
         <v>677</v>
       </c>
       <c r="B677" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -7929,7 +7947,7 @@
         <v>678</v>
       </c>
       <c r="B678" s="1">
-        <v>920</v>
+        <v>600</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -7937,7 +7955,7 @@
         <v>679</v>
       </c>
       <c r="B679" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -7945,7 +7963,7 @@
         <v>680</v>
       </c>
       <c r="B680" s="1">
-        <v>1040</v>
+        <v>760</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -7953,7 +7971,7 @@
         <v>681</v>
       </c>
       <c r="B681" s="1">
-        <v>940</v>
+        <v>840</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -7969,7 +7987,7 @@
         <v>683</v>
       </c>
       <c r="B683" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -7977,7 +7995,7 @@
         <v>684</v>
       </c>
       <c r="B684" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -7985,7 +8003,7 @@
         <v>685</v>
       </c>
       <c r="B685" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -7993,7 +8011,7 @@
         <v>686</v>
       </c>
       <c r="B686" s="1">
-        <v>500</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8001,7 +8019,7 @@
         <v>687</v>
       </c>
       <c r="B687" s="1">
-        <v>440</v>
+        <v>940</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8009,7 +8027,7 @@
         <v>688</v>
       </c>
       <c r="B688" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8017,7 +8035,7 @@
         <v>689</v>
       </c>
       <c r="B689" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8033,7 +8051,7 @@
         <v>691</v>
       </c>
       <c r="B691" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8041,7 +8059,7 @@
         <v>692</v>
       </c>
       <c r="B692" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8049,7 +8067,7 @@
         <v>693</v>
       </c>
       <c r="B693" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8057,7 +8075,7 @@
         <v>694</v>
       </c>
       <c r="B694" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8065,7 +8083,7 @@
         <v>695</v>
       </c>
       <c r="B695" s="1">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8073,7 +8091,7 @@
         <v>696</v>
       </c>
       <c r="B696" s="1">
-        <v>480</v>
+        <v>740</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8081,7 +8099,7 @@
         <v>697</v>
       </c>
       <c r="B697" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8089,7 +8107,7 @@
         <v>698</v>
       </c>
       <c r="B698" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8097,7 +8115,7 @@
         <v>699</v>
       </c>
       <c r="B699" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8105,7 +8123,7 @@
         <v>700</v>
       </c>
       <c r="B700" s="1">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8113,7 +8131,7 @@
         <v>701</v>
       </c>
       <c r="B701" s="1">
-        <v>380</v>
+        <v>480</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8121,7 +8139,7 @@
         <v>702</v>
       </c>
       <c r="B702" s="1">
-        <v>600</v>
+        <v>480</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8129,7 +8147,7 @@
         <v>703</v>
       </c>
       <c r="B703" s="1">
-        <v>760</v>
+        <v>520</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8137,7 +8155,7 @@
         <v>704</v>
       </c>
       <c r="B704" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8145,7 +8163,7 @@
         <v>705</v>
       </c>
       <c r="B705" s="1">
-        <v>580</v>
+        <v>440</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8153,7 +8171,7 @@
         <v>706</v>
       </c>
       <c r="B706" s="1">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8161,7 +8179,7 @@
         <v>707</v>
       </c>
       <c r="B707" s="1">
-        <v>580</v>
+        <v>380</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8169,7 +8187,7 @@
         <v>708</v>
       </c>
       <c r="B708" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8177,7 +8195,7 @@
         <v>709</v>
       </c>
       <c r="B709" s="1">
-        <v>560</v>
+        <v>760</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8185,6 +8203,54 @@
         <v>710</v>
       </c>
       <c r="B710" s="1">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2">
+      <c r="A711" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="B711" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2">
+      <c r="A712" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B712" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2">
+      <c r="A713" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="B713" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2">
+      <c r="A714" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B714" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2">
+      <c r="A715" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B715" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2">
+      <c r="A716" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B716" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="719">
   <si>
     <t>Наименование</t>
   </si>
@@ -779,6 +779,9 @@
     <t>Saliwa - Massive Hops Attack (NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Saliwa - Вечный Спор (DDH NEIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Saliwa - Виталити (NZ Pils), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1638,6 +1641,9 @@
   </si>
   <si>
     <t>вынос_Saliwa - Massive Hops Attack (NEIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Saliwa - Вечный Спор (DDH NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Saliwa - Виталити (NZ Pils), РОЗЛИВ, Россия</t>
@@ -2519,7 +2525,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B716"/>
+  <dimension ref="A1:B718"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -2771,7 +2777,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3635,7 +3641,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -4187,7 +4193,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4555,7 +4561,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4563,7 +4569,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -4571,7 +4577,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4579,7 +4585,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4587,7 +4593,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4595,7 +4601,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4603,7 +4609,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4611,7 +4617,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4619,7 +4625,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4627,7 +4633,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4635,7 +4641,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4643,7 +4649,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4651,7 +4657,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4659,7 +4665,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4667,7 +4673,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4675,7 +4681,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4683,7 +4689,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4691,7 +4697,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4699,7 +4705,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4707,7 +4713,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>520</v>
+        <v>880</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4715,7 +4721,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4723,7 +4729,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4731,7 +4737,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4739,7 +4745,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4747,7 +4753,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4755,7 +4761,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4763,7 +4769,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>320</v>
+        <v>520</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4771,7 +4777,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>540</v>
+        <v>320</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4779,7 +4785,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4787,7 +4793,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4803,7 +4809,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4811,7 +4817,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4819,7 +4825,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>640</v>
+        <v>500</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4827,7 +4833,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>480</v>
+        <v>640</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4835,7 +4841,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>780</v>
+        <v>480</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4843,7 +4849,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -4851,7 +4857,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -4859,7 +4865,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -4867,7 +4873,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -4883,7 +4889,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -4891,7 +4897,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -4899,7 +4905,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -4907,7 +4913,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -4915,7 +4921,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -4923,7 +4929,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -4931,7 +4937,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -4939,7 +4945,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -4947,7 +4953,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -4955,7 +4961,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -4971,7 +4977,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -4979,7 +4985,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -4987,7 +4993,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -4995,7 +5001,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5003,7 +5009,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5011,7 +5017,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5027,7 +5033,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5035,7 +5041,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5043,7 +5049,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>640</v>
+        <v>480</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5051,7 +5057,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5059,7 +5065,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5067,7 +5073,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5075,7 +5081,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>520</v>
+        <v>860</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5083,7 +5089,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5091,7 +5097,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5107,7 +5113,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5115,7 +5121,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>700</v>
+        <v>420</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5123,7 +5129,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5131,7 +5137,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5139,7 +5145,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5147,7 +5153,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5155,7 +5161,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5163,7 +5169,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5171,7 +5177,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5179,7 +5185,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5187,7 +5193,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>440</v>
+        <v>620</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5195,7 +5201,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>320</v>
+        <v>440</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5211,7 +5217,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>820</v>
+        <v>320</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5219,7 +5225,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5227,7 +5233,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5243,7 +5249,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5251,7 +5257,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5267,7 +5273,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5275,7 +5281,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5283,7 +5289,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5291,7 +5297,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5299,7 +5305,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5307,7 +5313,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5315,7 +5321,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5323,7 +5329,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5331,7 +5337,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5339,7 +5345,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5347,7 +5353,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5355,7 +5361,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5363,7 +5369,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5371,7 +5377,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5379,7 +5385,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5387,7 +5393,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5395,7 +5401,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5403,7 +5409,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5411,7 +5417,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5419,7 +5425,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5427,7 +5433,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5435,7 +5441,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5443,7 +5449,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5451,7 +5457,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5459,7 +5465,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5475,7 +5481,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5483,7 +5489,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5491,7 +5497,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5499,7 +5505,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5507,7 +5513,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5523,7 +5529,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5531,7 +5537,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="1">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5539,7 +5545,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5547,7 +5553,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5555,7 +5561,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5563,7 +5569,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5571,7 +5577,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5587,7 +5593,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5595,7 +5601,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5603,7 +5609,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>640</v>
+        <v>920</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5611,7 +5617,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5619,7 +5625,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5627,7 +5633,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5635,7 +5641,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5643,7 +5649,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5651,7 +5657,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5659,7 +5665,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>860</v>
+        <v>640</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5667,7 +5673,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5675,7 +5681,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5683,7 +5689,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5691,7 +5697,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5699,7 +5705,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5707,7 +5713,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5715,7 +5721,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5723,7 +5729,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5731,7 +5737,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>620</v>
+        <v>480</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5739,7 +5745,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5747,7 +5753,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5755,7 +5761,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5763,7 +5769,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5771,7 +5777,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5779,7 +5785,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5787,7 +5793,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5795,7 +5801,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5803,7 +5809,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>840</v>
+        <v>480</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5811,7 +5817,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5819,7 +5825,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5827,7 +5833,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5843,7 +5849,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5851,7 +5857,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5867,7 +5873,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5875,7 +5881,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5883,7 +5889,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5891,7 +5897,7 @@
         <v>421</v>
       </c>
       <c r="B421" s="1">
-        <v>1100</v>
+        <v>660</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -5899,7 +5905,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -5907,7 +5913,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -5923,7 +5929,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -5931,7 +5937,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -5947,7 +5953,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -5955,7 +5961,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -5971,7 +5977,7 @@
         <v>431</v>
       </c>
       <c r="B431" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -5979,7 +5985,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -5987,7 +5993,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6003,7 +6009,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6011,7 +6017,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6019,7 +6025,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6027,7 +6033,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6035,7 +6041,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>880</v>
+        <v>620</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6043,7 +6049,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6059,7 +6065,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6067,7 +6073,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6075,7 +6081,7 @@
         <v>444</v>
       </c>
       <c r="B444" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6083,7 +6089,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6091,7 +6097,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6099,7 +6105,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6107,7 +6113,7 @@
         <v>448</v>
       </c>
       <c r="B448" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6115,7 +6121,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6131,7 +6137,7 @@
         <v>451</v>
       </c>
       <c r="B451" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6139,7 +6145,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6147,7 +6153,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6155,7 +6161,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6163,7 +6169,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6171,7 +6177,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6179,7 +6185,7 @@
         <v>457</v>
       </c>
       <c r="B457" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6187,7 +6193,7 @@
         <v>458</v>
       </c>
       <c r="B458" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6195,7 +6201,7 @@
         <v>459</v>
       </c>
       <c r="B459" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6203,7 +6209,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6211,7 +6217,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6227,7 +6233,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6235,7 +6241,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6243,7 +6249,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6251,7 +6257,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>940</v>
+        <v>960</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6259,7 +6265,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6267,7 +6273,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>920</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6275,7 +6281,7 @@
         <v>469</v>
       </c>
       <c r="B469" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6283,7 +6289,7 @@
         <v>470</v>
       </c>
       <c r="B470" s="1">
-        <v>580</v>
+        <v>600</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6291,7 +6297,7 @@
         <v>471</v>
       </c>
       <c r="B471" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6299,7 +6305,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6307,7 +6313,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6315,7 +6321,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6323,7 +6329,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6331,7 +6337,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6339,7 +6345,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6347,7 +6353,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6355,7 +6361,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6363,7 +6369,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>540</v>
+        <v>780</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6371,7 +6377,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>720</v>
+        <v>540</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6379,7 +6385,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6387,7 +6393,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6395,7 +6401,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6403,7 +6409,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6411,7 +6417,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>980</v>
+        <v>860</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6419,7 +6425,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>740</v>
+        <v>980</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6427,7 +6433,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6435,7 +6441,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6451,7 +6457,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6459,7 +6465,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6467,7 +6473,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6475,7 +6481,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6483,7 +6489,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6491,7 +6497,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6499,7 +6505,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6507,7 +6513,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6515,7 +6521,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6523,7 +6529,7 @@
         <v>500</v>
       </c>
       <c r="B500" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6531,7 +6537,7 @@
         <v>501</v>
       </c>
       <c r="B501" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6539,7 +6545,7 @@
         <v>502</v>
       </c>
       <c r="B502" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6547,7 +6553,7 @@
         <v>503</v>
       </c>
       <c r="B503" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6555,7 +6561,7 @@
         <v>504</v>
       </c>
       <c r="B504" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6563,7 +6569,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6571,7 +6577,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6579,7 +6585,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>1400</v>
+        <v>720</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6587,7 +6593,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>720</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6595,7 +6601,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6603,7 +6609,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6611,7 +6617,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6619,7 +6625,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6627,7 +6633,7 @@
         <v>513</v>
       </c>
       <c r="B513" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6635,7 +6641,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6643,7 +6649,7 @@
         <v>515</v>
       </c>
       <c r="B515" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6651,7 +6657,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6667,7 +6673,7 @@
         <v>518</v>
       </c>
       <c r="B518" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6675,7 +6681,7 @@
         <v>519</v>
       </c>
       <c r="B519" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6691,7 +6697,7 @@
         <v>521</v>
       </c>
       <c r="B521" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6699,7 +6705,7 @@
         <v>522</v>
       </c>
       <c r="B522" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -6707,7 +6713,7 @@
         <v>523</v>
       </c>
       <c r="B523" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6723,7 +6729,7 @@
         <v>525</v>
       </c>
       <c r="B525" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6747,7 +6753,7 @@
         <v>528</v>
       </c>
       <c r="B528" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6755,7 +6761,7 @@
         <v>529</v>
       </c>
       <c r="B529" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6763,7 +6769,7 @@
         <v>530</v>
       </c>
       <c r="B530" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6771,7 +6777,7 @@
         <v>531</v>
       </c>
       <c r="B531" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6779,7 +6785,7 @@
         <v>532</v>
       </c>
       <c r="B532" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6787,7 +6793,7 @@
         <v>533</v>
       </c>
       <c r="B533" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6795,7 +6801,7 @@
         <v>534</v>
       </c>
       <c r="B534" s="1">
-        <v>660</v>
+        <v>540</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6803,7 +6809,7 @@
         <v>535</v>
       </c>
       <c r="B535" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -6811,7 +6817,7 @@
         <v>536</v>
       </c>
       <c r="B536" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -6827,7 +6833,7 @@
         <v>538</v>
       </c>
       <c r="B538" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -6835,7 +6841,7 @@
         <v>539</v>
       </c>
       <c r="B539" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -6843,7 +6849,7 @@
         <v>540</v>
       </c>
       <c r="B540" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -6851,7 +6857,7 @@
         <v>541</v>
       </c>
       <c r="B541" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -6859,7 +6865,7 @@
         <v>542</v>
       </c>
       <c r="B542" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -6867,7 +6873,7 @@
         <v>543</v>
       </c>
       <c r="B543" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -6875,7 +6881,7 @@
         <v>544</v>
       </c>
       <c r="B544" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -6891,7 +6897,7 @@
         <v>546</v>
       </c>
       <c r="B546" s="1">
-        <v>800</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -6899,7 +6905,7 @@
         <v>547</v>
       </c>
       <c r="B547" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -6907,7 +6913,7 @@
         <v>548</v>
       </c>
       <c r="B548" s="1">
-        <v>640</v>
+        <v>800</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -6915,7 +6921,7 @@
         <v>549</v>
       </c>
       <c r="B549" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -6923,7 +6929,7 @@
         <v>550</v>
       </c>
       <c r="B550" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -6931,7 +6937,7 @@
         <v>551</v>
       </c>
       <c r="B551" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -6947,7 +6953,7 @@
         <v>553</v>
       </c>
       <c r="B553" s="1">
-        <v>880</v>
+        <v>640</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -6955,7 +6961,7 @@
         <v>554</v>
       </c>
       <c r="B554" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -6963,7 +6969,7 @@
         <v>555</v>
       </c>
       <c r="B555" s="1">
-        <v>600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -6971,7 +6977,7 @@
         <v>556</v>
       </c>
       <c r="B556" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -6987,7 +6993,7 @@
         <v>558</v>
       </c>
       <c r="B558" s="1">
-        <v>640</v>
+        <v>820</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -6995,7 +7001,7 @@
         <v>559</v>
       </c>
       <c r="B559" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7003,7 +7009,7 @@
         <v>560</v>
       </c>
       <c r="B560" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7011,7 +7017,7 @@
         <v>561</v>
       </c>
       <c r="B561" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7019,7 +7025,7 @@
         <v>562</v>
       </c>
       <c r="B562" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7027,7 +7033,7 @@
         <v>563</v>
       </c>
       <c r="B563" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7035,7 +7041,7 @@
         <v>564</v>
       </c>
       <c r="B564" s="1">
-        <v>1020</v>
+        <v>720</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7043,7 +7049,7 @@
         <v>565</v>
       </c>
       <c r="B565" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7051,7 +7057,7 @@
         <v>566</v>
       </c>
       <c r="B566" s="1">
-        <v>700</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7059,7 +7065,7 @@
         <v>567</v>
       </c>
       <c r="B567" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7067,7 +7073,7 @@
         <v>568</v>
       </c>
       <c r="B568" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7075,7 +7081,7 @@
         <v>569</v>
       </c>
       <c r="B569" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7091,7 +7097,7 @@
         <v>571</v>
       </c>
       <c r="B571" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7099,7 +7105,7 @@
         <v>572</v>
       </c>
       <c r="B572" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7107,7 +7113,7 @@
         <v>573</v>
       </c>
       <c r="B573" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7115,7 +7121,7 @@
         <v>574</v>
       </c>
       <c r="B574" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7123,7 +7129,7 @@
         <v>575</v>
       </c>
       <c r="B575" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7131,7 +7137,7 @@
         <v>576</v>
       </c>
       <c r="B576" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7147,7 +7153,7 @@
         <v>578</v>
       </c>
       <c r="B578" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7163,7 +7169,7 @@
         <v>580</v>
       </c>
       <c r="B580" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7171,7 +7177,7 @@
         <v>581</v>
       </c>
       <c r="B581" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7179,7 +7185,7 @@
         <v>582</v>
       </c>
       <c r="B582" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7187,7 +7193,7 @@
         <v>583</v>
       </c>
       <c r="B583" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7195,7 +7201,7 @@
         <v>584</v>
       </c>
       <c r="B584" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7211,7 +7217,7 @@
         <v>586</v>
       </c>
       <c r="B586" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7219,7 +7225,7 @@
         <v>587</v>
       </c>
       <c r="B587" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7227,7 +7233,7 @@
         <v>588</v>
       </c>
       <c r="B588" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7235,7 +7241,7 @@
         <v>589</v>
       </c>
       <c r="B589" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7243,7 +7249,7 @@
         <v>590</v>
       </c>
       <c r="B590" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7251,7 +7257,7 @@
         <v>591</v>
       </c>
       <c r="B591" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7259,7 +7265,7 @@
         <v>592</v>
       </c>
       <c r="B592" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7267,7 +7273,7 @@
         <v>593</v>
       </c>
       <c r="B593" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7275,7 +7281,7 @@
         <v>594</v>
       </c>
       <c r="B594" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7291,7 +7297,7 @@
         <v>596</v>
       </c>
       <c r="B596" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7299,7 +7305,7 @@
         <v>597</v>
       </c>
       <c r="B597" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7307,7 +7313,7 @@
         <v>598</v>
       </c>
       <c r="B598" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7315,7 +7321,7 @@
         <v>599</v>
       </c>
       <c r="B599" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7323,7 +7329,7 @@
         <v>600</v>
       </c>
       <c r="B600" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7331,7 +7337,7 @@
         <v>601</v>
       </c>
       <c r="B601" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7339,7 +7345,7 @@
         <v>602</v>
       </c>
       <c r="B602" s="1">
-        <v>440</v>
+        <v>680</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7347,7 +7353,7 @@
         <v>603</v>
       </c>
       <c r="B603" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7355,7 +7361,7 @@
         <v>604</v>
       </c>
       <c r="B604" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7363,7 +7369,7 @@
         <v>605</v>
       </c>
       <c r="B605" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7371,7 +7377,7 @@
         <v>606</v>
       </c>
       <c r="B606" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7379,7 +7385,7 @@
         <v>607</v>
       </c>
       <c r="B607" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7387,7 +7393,7 @@
         <v>608</v>
       </c>
       <c r="B608" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7395,7 +7401,7 @@
         <v>609</v>
       </c>
       <c r="B609" s="1">
-        <v>800</v>
+        <v>560</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7403,7 +7409,7 @@
         <v>610</v>
       </c>
       <c r="B610" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7411,7 +7417,7 @@
         <v>611</v>
       </c>
       <c r="B611" s="1">
-        <v>920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7419,7 +7425,7 @@
         <v>612</v>
       </c>
       <c r="B612" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7427,7 +7433,7 @@
         <v>613</v>
       </c>
       <c r="B613" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7435,7 +7441,7 @@
         <v>614</v>
       </c>
       <c r="B614" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7443,7 +7449,7 @@
         <v>615</v>
       </c>
       <c r="B615" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7451,7 +7457,7 @@
         <v>616</v>
       </c>
       <c r="B616" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -7459,7 +7465,7 @@
         <v>617</v>
       </c>
       <c r="B617" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -7467,7 +7473,7 @@
         <v>618</v>
       </c>
       <c r="B618" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -7475,7 +7481,7 @@
         <v>619</v>
       </c>
       <c r="B619" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7483,7 +7489,7 @@
         <v>620</v>
       </c>
       <c r="B620" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7491,7 +7497,7 @@
         <v>621</v>
       </c>
       <c r="B621" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -7499,7 +7505,7 @@
         <v>622</v>
       </c>
       <c r="B622" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -7507,7 +7513,7 @@
         <v>623</v>
       </c>
       <c r="B623" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -7515,7 +7521,7 @@
         <v>624</v>
       </c>
       <c r="B624" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -7523,7 +7529,7 @@
         <v>625</v>
       </c>
       <c r="B625" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -7531,7 +7537,7 @@
         <v>626</v>
       </c>
       <c r="B626" s="1">
-        <v>660</v>
+        <v>860</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -7539,7 +7545,7 @@
         <v>627</v>
       </c>
       <c r="B627" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -7547,7 +7553,7 @@
         <v>628</v>
       </c>
       <c r="B628" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -7555,7 +7561,7 @@
         <v>629</v>
       </c>
       <c r="B629" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -7563,7 +7569,7 @@
         <v>630</v>
       </c>
       <c r="B630" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -7571,7 +7577,7 @@
         <v>631</v>
       </c>
       <c r="B631" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -7579,7 +7585,7 @@
         <v>632</v>
       </c>
       <c r="B632" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -7587,7 +7593,7 @@
         <v>633</v>
       </c>
       <c r="B633" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -7595,7 +7601,7 @@
         <v>634</v>
       </c>
       <c r="B634" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -7603,7 +7609,7 @@
         <v>635</v>
       </c>
       <c r="B635" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -7611,7 +7617,7 @@
         <v>636</v>
       </c>
       <c r="B636" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -7619,7 +7625,7 @@
         <v>637</v>
       </c>
       <c r="B637" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -7627,7 +7633,7 @@
         <v>638</v>
       </c>
       <c r="B638" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -7635,7 +7641,7 @@
         <v>639</v>
       </c>
       <c r="B639" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -7643,7 +7649,7 @@
         <v>640</v>
       </c>
       <c r="B640" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -7651,7 +7657,7 @@
         <v>641</v>
       </c>
       <c r="B641" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -7659,7 +7665,7 @@
         <v>642</v>
       </c>
       <c r="B642" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -7667,7 +7673,7 @@
         <v>643</v>
       </c>
       <c r="B643" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -7675,7 +7681,7 @@
         <v>644</v>
       </c>
       <c r="B644" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -7683,7 +7689,7 @@
         <v>645</v>
       </c>
       <c r="B645" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -7691,7 +7697,7 @@
         <v>646</v>
       </c>
       <c r="B646" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -7699,7 +7705,7 @@
         <v>647</v>
       </c>
       <c r="B647" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -7707,7 +7713,7 @@
         <v>648</v>
       </c>
       <c r="B648" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -7715,7 +7721,7 @@
         <v>649</v>
       </c>
       <c r="B649" s="1">
-        <v>920</v>
+        <v>500</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -7723,7 +7729,7 @@
         <v>650</v>
       </c>
       <c r="B650" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -7731,7 +7737,7 @@
         <v>651</v>
       </c>
       <c r="B651" s="1">
-        <v>1040</v>
+        <v>920</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -7739,7 +7745,7 @@
         <v>652</v>
       </c>
       <c r="B652" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -7747,7 +7753,7 @@
         <v>653</v>
       </c>
       <c r="B653" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -7755,7 +7761,7 @@
         <v>654</v>
       </c>
       <c r="B654" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -7763,7 +7769,7 @@
         <v>655</v>
       </c>
       <c r="B655" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -7771,7 +7777,7 @@
         <v>656</v>
       </c>
       <c r="B656" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -7779,7 +7785,7 @@
         <v>657</v>
       </c>
       <c r="B657" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -7795,7 +7801,7 @@
         <v>659</v>
       </c>
       <c r="B659" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -7803,7 +7809,7 @@
         <v>660</v>
       </c>
       <c r="B660" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -7811,7 +7817,7 @@
         <v>661</v>
       </c>
       <c r="B661" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -7819,7 +7825,7 @@
         <v>662</v>
       </c>
       <c r="B662" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -7827,7 +7833,7 @@
         <v>663</v>
       </c>
       <c r="B663" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -7835,7 +7841,7 @@
         <v>664</v>
       </c>
       <c r="B664" s="1">
-        <v>400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -7843,7 +7849,7 @@
         <v>665</v>
       </c>
       <c r="B665" s="1">
-        <v>400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -7851,7 +7857,7 @@
         <v>666</v>
       </c>
       <c r="B666" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -7859,7 +7865,7 @@
         <v>667</v>
       </c>
       <c r="B667" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -7875,7 +7881,7 @@
         <v>669</v>
       </c>
       <c r="B669" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -7883,7 +7889,7 @@
         <v>670</v>
       </c>
       <c r="B670" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -7891,7 +7897,7 @@
         <v>671</v>
       </c>
       <c r="B671" s="1">
-        <v>860</v>
+        <v>520</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -7899,7 +7905,7 @@
         <v>672</v>
       </c>
       <c r="B672" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -7907,7 +7913,7 @@
         <v>673</v>
       </c>
       <c r="B673" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -7915,7 +7921,7 @@
         <v>674</v>
       </c>
       <c r="B674" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -7923,7 +7929,7 @@
         <v>675</v>
       </c>
       <c r="B675" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -7931,7 +7937,7 @@
         <v>676</v>
       </c>
       <c r="B676" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -7939,7 +7945,7 @@
         <v>677</v>
       </c>
       <c r="B677" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -7947,7 +7953,7 @@
         <v>678</v>
       </c>
       <c r="B678" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -7955,7 +7961,7 @@
         <v>679</v>
       </c>
       <c r="B679" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -7963,7 +7969,7 @@
         <v>680</v>
       </c>
       <c r="B680" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -7971,7 +7977,7 @@
         <v>681</v>
       </c>
       <c r="B681" s="1">
-        <v>840</v>
+        <v>500</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -7979,7 +7985,7 @@
         <v>682</v>
       </c>
       <c r="B682" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -7987,7 +7993,7 @@
         <v>683</v>
       </c>
       <c r="B683" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -7995,7 +8001,7 @@
         <v>684</v>
       </c>
       <c r="B684" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8003,7 +8009,7 @@
         <v>685</v>
       </c>
       <c r="B685" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8011,7 +8017,7 @@
         <v>686</v>
       </c>
       <c r="B686" s="1">
-        <v>1040</v>
+        <v>920</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8019,7 +8025,7 @@
         <v>687</v>
       </c>
       <c r="B687" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8027,7 +8033,7 @@
         <v>688</v>
       </c>
       <c r="B688" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8035,7 +8041,7 @@
         <v>689</v>
       </c>
       <c r="B689" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8043,7 +8049,7 @@
         <v>690</v>
       </c>
       <c r="B690" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8051,7 +8057,7 @@
         <v>691</v>
       </c>
       <c r="B691" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8059,7 +8065,7 @@
         <v>692</v>
       </c>
       <c r="B692" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8075,7 +8081,7 @@
         <v>694</v>
       </c>
       <c r="B694" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8083,7 +8089,7 @@
         <v>695</v>
       </c>
       <c r="B695" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8091,7 +8097,7 @@
         <v>696</v>
       </c>
       <c r="B696" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8099,7 +8105,7 @@
         <v>697</v>
       </c>
       <c r="B697" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8107,7 +8113,7 @@
         <v>698</v>
       </c>
       <c r="B698" s="1">
-        <v>380</v>
+        <v>780</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8123,7 +8129,7 @@
         <v>700</v>
       </c>
       <c r="B700" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8131,7 +8137,7 @@
         <v>701</v>
       </c>
       <c r="B701" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8147,7 +8153,7 @@
         <v>703</v>
       </c>
       <c r="B703" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8155,7 +8161,7 @@
         <v>704</v>
       </c>
       <c r="B704" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8163,7 +8169,7 @@
         <v>705</v>
       </c>
       <c r="B705" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8171,7 +8177,7 @@
         <v>706</v>
       </c>
       <c r="B706" s="1">
-        <v>420</v>
+        <v>520</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8179,7 +8185,7 @@
         <v>707</v>
       </c>
       <c r="B707" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8187,7 +8193,7 @@
         <v>708</v>
       </c>
       <c r="B708" s="1">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8195,7 +8201,7 @@
         <v>709</v>
       </c>
       <c r="B709" s="1">
-        <v>760</v>
+        <v>380</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8211,7 +8217,7 @@
         <v>711</v>
       </c>
       <c r="B711" s="1">
-        <v>580</v>
+        <v>760</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8219,7 +8225,7 @@
         <v>712</v>
       </c>
       <c r="B712" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8235,7 +8241,7 @@
         <v>714</v>
       </c>
       <c r="B714" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8243,7 +8249,7 @@
         <v>715</v>
       </c>
       <c r="B715" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8251,6 +8257,22 @@
         <v>716</v>
       </c>
       <c r="B716" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2">
+      <c r="A717" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="B717" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2">
+      <c r="A718" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B718" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="723">
   <si>
     <t>Наименование</t>
   </si>
@@ -440,6 +440,12 @@
     <t>Maisel`S Weisse ORIGINAL, Розлив, Германия</t>
   </si>
   <si>
+    <t>Malanka - Zaltum: Simcoe (Black IPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>Malanka - Znicka: Mosaic (NEIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Manfas - Let’s party together (Sour), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1485,6 +1491,12 @@
   </si>
   <si>
     <t>вынос_Magic Mess - Понедельник (Lager), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Malanka - Zaltum: Simcoe (Black IPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Malanka - Znicka: Mosaic (NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Midnight Project - Cyberpunk Shotgun (DIPA), РОЗЛИВ, Россия</t>
@@ -2525,7 +2537,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B718"/>
+  <dimension ref="A1:B722"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -2969,7 +2981,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -3657,7 +3669,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -3665,7 +3677,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>640</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -3681,7 +3693,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>920</v>
+        <v>640</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -3689,7 +3701,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -3705,7 +3717,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3713,7 +3725,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -3721,7 +3733,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -3729,7 +3741,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -3737,7 +3749,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3745,7 +3757,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>460</v>
+        <v>840</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3753,7 +3765,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3761,7 +3773,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>720</v>
+        <v>460</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -3769,7 +3781,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>660</v>
+        <v>580</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -3777,7 +3789,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -3785,7 +3797,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>260</v>
+        <v>660</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -3793,7 +3805,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -3801,7 +3813,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -3809,7 +3821,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -3817,7 +3829,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -3825,7 +3837,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -3833,7 +3845,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -3841,7 +3853,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -3849,7 +3861,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>400</v>
+        <v>720</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -3857,7 +3869,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>740</v>
+        <v>500</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -3865,7 +3877,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>680</v>
+        <v>400</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -3873,7 +3885,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -3881,7 +3893,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -3889,7 +3901,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -3897,7 +3909,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>680</v>
+        <v>620</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -3905,7 +3917,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -3913,7 +3925,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -3921,7 +3933,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -3929,7 +3941,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -3937,7 +3949,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>580</v>
+        <v>620</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -3945,7 +3957,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -3953,7 +3965,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -3961,7 +3973,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -3969,7 +3981,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -3977,7 +3989,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -3985,7 +3997,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -3993,7 +4005,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4001,7 +4013,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>700</v>
+        <v>580</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4009,7 +4021,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>820</v>
+        <v>540</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4017,7 +4029,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4025,7 +4037,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4033,7 +4045,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4041,7 +4053,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>1400</v>
+        <v>720</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4049,7 +4061,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4057,7 +4069,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>720</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4065,7 +4077,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>660</v>
+        <v>480</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4073,7 +4085,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4081,7 +4093,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4089,7 +4101,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>740</v>
+        <v>600</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4097,7 +4109,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4105,7 +4117,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4113,7 +4125,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>520</v>
+        <v>720</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4121,7 +4133,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4129,7 +4141,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4137,7 +4149,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4153,7 +4165,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4161,7 +4173,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4169,7 +4181,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4177,7 +4189,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4185,7 +4197,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4193,7 +4205,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4209,7 +4221,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4217,7 +4229,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4225,7 +4237,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4233,7 +4245,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4241,7 +4253,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4249,7 +4261,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4257,7 +4269,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4265,7 +4277,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4273,7 +4285,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4281,7 +4293,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4289,7 +4301,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>500</v>
+        <v>640</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4297,7 +4309,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>758</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4305,7 +4317,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>2273</v>
+        <v>500</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4313,7 +4325,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>1515</v>
+        <v>758</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4321,7 +4333,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>520</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4329,7 +4341,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>720</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4337,7 +4349,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4345,7 +4357,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>480</v>
+        <v>720</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4353,7 +4365,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4361,7 +4373,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4369,7 +4381,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4377,7 +4389,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4385,7 +4397,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>580</v>
+        <v>600</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4393,7 +4405,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>520</v>
+        <v>700</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4401,7 +4413,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>680</v>
+        <v>580</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4409,7 +4421,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4417,7 +4429,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4425,7 +4437,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4433,7 +4445,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>380</v>
+        <v>580</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4441,7 +4453,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4449,7 +4461,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>540</v>
+        <v>380</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4457,7 +4469,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>520</v>
+        <v>660</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4465,7 +4477,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>660</v>
+        <v>540</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4473,7 +4485,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4481,7 +4493,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>460</v>
+        <v>660</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4489,7 +4501,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4497,7 +4509,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4505,7 +4517,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>860</v>
+        <v>520</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4513,7 +4525,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4521,7 +4533,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4529,7 +4541,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4537,7 +4549,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4545,7 +4557,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>1000</v>
+        <v>560</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4553,7 +4565,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4561,7 +4573,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4569,7 +4581,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -4577,7 +4589,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4585,7 +4597,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>840</v>
+        <v>680</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4601,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>1020</v>
+        <v>840</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4617,7 +4629,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>680</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4625,7 +4637,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>520</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4633,7 +4645,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4641,7 +4653,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4649,7 +4661,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4657,7 +4669,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4665,7 +4677,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4673,7 +4685,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4681,7 +4693,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4689,7 +4701,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4697,7 +4709,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4713,7 +4725,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>880</v>
+        <v>640</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4721,7 +4733,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>520</v>
+        <v>720</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4729,7 +4741,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4737,7 +4749,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4745,7 +4757,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4761,7 +4773,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4769,7 +4781,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>520</v>
+        <v>600</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4777,7 +4789,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>320</v>
+        <v>380</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4785,7 +4797,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4793,7 +4805,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>560</v>
+        <v>320</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4801,7 +4813,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>480</v>
+        <v>540</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4809,7 +4821,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4817,7 +4829,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4825,7 +4837,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>500</v>
+        <v>480</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4833,7 +4845,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4841,7 +4853,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4849,7 +4861,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -4857,7 +4869,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -4865,7 +4877,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>380</v>
+        <v>780</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -4873,7 +4885,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -4881,7 +4893,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>900</v>
+        <v>380</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -4889,7 +4901,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -4897,7 +4909,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -4905,7 +4917,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -4913,7 +4925,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>1020</v>
+        <v>720</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -4921,7 +4933,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -4929,7 +4941,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>700</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -4937,7 +4949,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -4945,7 +4957,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -4953,7 +4965,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -4969,7 +4981,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -4977,7 +4989,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -4985,7 +4997,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -4993,7 +5005,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5001,7 +5013,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5009,7 +5021,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5025,7 +5037,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5033,7 +5045,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5041,7 +5053,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5049,7 +5061,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>480</v>
+        <v>740</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5057,7 +5069,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5065,7 +5077,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>1000</v>
+        <v>480</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5073,7 +5085,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>920</v>
+        <v>640</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5081,7 +5093,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5089,7 +5101,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>520</v>
+        <v>920</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5097,7 +5109,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>540</v>
+        <v>860</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5105,7 +5117,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>700</v>
+        <v>520</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5113,7 +5125,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5121,7 +5133,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5137,7 +5149,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>720</v>
+        <v>420</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5145,7 +5157,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5153,7 +5165,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5161,7 +5173,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5169,7 +5181,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5177,7 +5189,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5185,7 +5197,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5193,7 +5205,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5201,7 +5213,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>440</v>
+        <v>720</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5209,7 +5221,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>320</v>
+        <v>620</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5217,7 +5229,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>320</v>
+        <v>440</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5225,7 +5237,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>820</v>
+        <v>320</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5233,7 +5245,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>1000</v>
+        <v>320</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5241,7 +5253,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5249,7 +5261,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5257,7 +5269,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5273,7 +5285,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5281,7 +5293,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5289,7 +5301,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5297,7 +5309,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>1000</v>
+        <v>620</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5305,7 +5317,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5313,7 +5325,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5329,7 +5341,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5337,7 +5349,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5345,7 +5357,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5353,7 +5365,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5361,7 +5373,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5369,7 +5381,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5377,7 +5389,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>440</v>
+        <v>680</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5385,7 +5397,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5393,7 +5405,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5401,7 +5413,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5409,7 +5421,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5417,7 +5429,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5425,7 +5437,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5433,7 +5445,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5441,7 +5453,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5449,7 +5461,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5457,7 +5469,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5465,7 +5477,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>680</v>
+        <v>620</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5473,7 +5485,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>480</v>
+        <v>720</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5481,7 +5493,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5489,7 +5501,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5497,7 +5509,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5505,7 +5517,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5513,7 +5525,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5521,7 +5533,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5529,7 +5541,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5537,7 +5549,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5545,7 +5557,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5553,7 +5565,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5561,7 +5573,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>600</v>
+        <v>980</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5569,7 +5581,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>760</v>
+        <v>920</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5577,7 +5589,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5585,7 +5597,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="1">
-        <v>620</v>
+        <v>760</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5593,7 +5605,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5601,7 +5613,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5609,7 +5621,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5617,7 +5629,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>640</v>
+        <v>860</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5625,7 +5637,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5633,7 +5645,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>820</v>
+        <v>640</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5641,7 +5653,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5649,7 +5661,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5657,7 +5669,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5665,7 +5677,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5673,7 +5685,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5681,7 +5693,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5689,7 +5701,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5697,7 +5709,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5705,7 +5717,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5713,7 +5725,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5721,7 +5733,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>840</v>
+        <v>640</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5729,7 +5741,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5737,7 +5749,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>480</v>
+        <v>840</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5745,7 +5757,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5753,7 +5765,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>780</v>
+        <v>480</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5761,7 +5773,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5769,7 +5781,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5777,7 +5789,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5785,7 +5797,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5793,7 +5805,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5801,7 +5813,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5809,7 +5821,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>480</v>
+        <v>780</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5817,7 +5829,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5825,7 +5837,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>660</v>
+        <v>480</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5833,7 +5845,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5841,7 +5853,7 @@
         <v>414</v>
       </c>
       <c r="B414" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5849,7 +5861,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5857,7 +5869,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5865,7 +5877,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>880</v>
+        <v>440</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5873,7 +5885,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5881,7 +5893,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5889,7 +5901,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5897,7 +5909,7 @@
         <v>421</v>
       </c>
       <c r="B421" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -5905,7 +5917,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -5913,7 +5925,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -5921,7 +5933,7 @@
         <v>424</v>
       </c>
       <c r="B424" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -5929,7 +5941,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -5937,7 +5949,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -5945,7 +5957,7 @@
         <v>427</v>
       </c>
       <c r="B427" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -5953,7 +5965,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -5961,7 +5973,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -5969,7 +5981,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -5977,7 +5989,7 @@
         <v>431</v>
       </c>
       <c r="B431" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -5993,7 +6005,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6001,7 +6013,7 @@
         <v>434</v>
       </c>
       <c r="B434" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6009,7 +6021,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6017,7 +6029,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6025,7 +6037,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6033,7 +6045,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6041,7 +6053,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6049,7 +6061,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6057,7 +6069,7 @@
         <v>441</v>
       </c>
       <c r="B441" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6065,7 +6077,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6073,7 +6085,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6081,7 +6093,7 @@
         <v>444</v>
       </c>
       <c r="B444" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6089,7 +6101,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6097,7 +6109,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6105,7 +6117,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>640</v>
+        <v>900</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6113,7 +6125,7 @@
         <v>448</v>
       </c>
       <c r="B448" s="1">
-        <v>800</v>
+        <v>790</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6121,7 +6133,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6129,7 +6141,7 @@
         <v>450</v>
       </c>
       <c r="B450" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6137,7 +6149,7 @@
         <v>451</v>
       </c>
       <c r="B451" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6145,7 +6157,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6153,7 +6165,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6177,7 +6189,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>920</v>
+        <v>820</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6185,7 +6197,7 @@
         <v>457</v>
       </c>
       <c r="B457" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6193,7 +6205,7 @@
         <v>458</v>
       </c>
       <c r="B458" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6201,7 +6213,7 @@
         <v>459</v>
       </c>
       <c r="B459" s="1">
-        <v>640</v>
+        <v>600</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6209,7 +6221,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>700</v>
+        <v>880</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6217,7 +6229,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6225,7 +6237,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6233,7 +6245,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6241,7 +6253,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6249,7 +6261,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6257,7 +6269,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6265,7 +6277,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6273,7 +6285,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6281,7 +6293,7 @@
         <v>469</v>
       </c>
       <c r="B469" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6289,7 +6301,7 @@
         <v>470</v>
       </c>
       <c r="B470" s="1">
-        <v>600</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6297,7 +6309,7 @@
         <v>471</v>
       </c>
       <c r="B471" s="1">
-        <v>580</v>
+        <v>920</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6305,7 +6317,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6313,7 +6325,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6321,7 +6333,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6329,7 +6341,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6337,7 +6349,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6345,7 +6357,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6353,7 +6365,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6361,7 +6373,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>720</v>
+        <v>960</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6369,7 +6381,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6377,7 +6389,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>540</v>
+        <v>720</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6385,7 +6397,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6393,7 +6405,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6401,7 +6413,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6409,7 +6421,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6417,7 +6429,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6425,7 +6437,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>980</v>
+        <v>620</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6433,7 +6445,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6441,7 +6453,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>760</v>
+        <v>980</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6449,7 +6461,7 @@
         <v>490</v>
       </c>
       <c r="B490" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6457,7 +6469,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6465,7 +6477,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6473,7 +6485,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6481,7 +6493,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6489,7 +6501,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6505,7 +6517,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6513,7 +6525,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6521,7 +6533,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6529,7 +6541,7 @@
         <v>500</v>
       </c>
       <c r="B500" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6537,7 +6549,7 @@
         <v>501</v>
       </c>
       <c r="B501" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6545,7 +6557,7 @@
         <v>502</v>
       </c>
       <c r="B502" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6553,7 +6565,7 @@
         <v>503</v>
       </c>
       <c r="B503" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6561,7 +6573,7 @@
         <v>504</v>
       </c>
       <c r="B504" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6569,7 +6581,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6577,7 +6589,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6585,7 +6597,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6593,7 +6605,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>1400</v>
+        <v>700</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6601,7 +6613,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6609,7 +6621,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6617,7 +6629,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6625,7 +6637,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>740</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6641,7 +6653,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6649,7 +6661,7 @@
         <v>515</v>
       </c>
       <c r="B515" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6657,7 +6669,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6673,7 +6685,7 @@
         <v>518</v>
       </c>
       <c r="B518" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6681,7 +6693,7 @@
         <v>519</v>
       </c>
       <c r="B519" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6689,7 +6701,7 @@
         <v>520</v>
       </c>
       <c r="B520" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6697,7 +6709,7 @@
         <v>521</v>
       </c>
       <c r="B521" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6713,7 +6725,7 @@
         <v>523</v>
       </c>
       <c r="B523" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6721,7 +6733,7 @@
         <v>524</v>
       </c>
       <c r="B524" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6729,7 +6741,7 @@
         <v>525</v>
       </c>
       <c r="B525" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6745,7 +6757,7 @@
         <v>527</v>
       </c>
       <c r="B527" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6753,7 +6765,7 @@
         <v>528</v>
       </c>
       <c r="B528" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6761,7 +6773,7 @@
         <v>529</v>
       </c>
       <c r="B529" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6769,7 +6781,7 @@
         <v>530</v>
       </c>
       <c r="B530" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6777,7 +6789,7 @@
         <v>531</v>
       </c>
       <c r="B531" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6785,7 +6797,7 @@
         <v>532</v>
       </c>
       <c r="B532" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6793,7 +6805,7 @@
         <v>533</v>
       </c>
       <c r="B533" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6801,7 +6813,7 @@
         <v>534</v>
       </c>
       <c r="B534" s="1">
-        <v>540</v>
+        <v>700</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6809,7 +6821,7 @@
         <v>535</v>
       </c>
       <c r="B535" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -6817,7 +6829,7 @@
         <v>536</v>
       </c>
       <c r="B536" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -6825,7 +6837,7 @@
         <v>537</v>
       </c>
       <c r="B537" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -6833,7 +6845,7 @@
         <v>538</v>
       </c>
       <c r="B538" s="1">
-        <v>860</v>
+        <v>540</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -6841,7 +6853,7 @@
         <v>539</v>
       </c>
       <c r="B539" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -6849,7 +6861,7 @@
         <v>540</v>
       </c>
       <c r="B540" s="1">
-        <v>1000</v>
+        <v>580</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -6857,7 +6869,7 @@
         <v>541</v>
       </c>
       <c r="B541" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -6865,7 +6877,7 @@
         <v>542</v>
       </c>
       <c r="B542" s="1">
-        <v>1040</v>
+        <v>860</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -6873,7 +6885,7 @@
         <v>543</v>
       </c>
       <c r="B543" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -6889,7 +6901,7 @@
         <v>545</v>
       </c>
       <c r="B545" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -6897,7 +6909,7 @@
         <v>546</v>
       </c>
       <c r="B546" s="1">
-        <v>1020</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -6905,7 +6917,7 @@
         <v>547</v>
       </c>
       <c r="B547" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -6913,7 +6925,7 @@
         <v>548</v>
       </c>
       <c r="B548" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -6921,7 +6933,7 @@
         <v>549</v>
       </c>
       <c r="B549" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -6929,7 +6941,7 @@
         <v>550</v>
       </c>
       <c r="B550" s="1">
-        <v>640</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -6937,7 +6949,7 @@
         <v>551</v>
       </c>
       <c r="B551" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -6945,7 +6957,7 @@
         <v>552</v>
       </c>
       <c r="B552" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -6953,7 +6965,7 @@
         <v>553</v>
       </c>
       <c r="B553" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -6961,7 +6973,7 @@
         <v>554</v>
       </c>
       <c r="B554" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -6969,7 +6981,7 @@
         <v>555</v>
       </c>
       <c r="B555" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -6977,7 +6989,7 @@
         <v>556</v>
       </c>
       <c r="B556" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -6985,7 +6997,7 @@
         <v>557</v>
       </c>
       <c r="B557" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -6993,7 +7005,7 @@
         <v>558</v>
       </c>
       <c r="B558" s="1">
-        <v>820</v>
+        <v>720</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7001,7 +7013,7 @@
         <v>559</v>
       </c>
       <c r="B559" s="1">
-        <v>600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7009,7 +7021,7 @@
         <v>560</v>
       </c>
       <c r="B560" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7017,7 +7029,7 @@
         <v>561</v>
       </c>
       <c r="B561" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7025,7 +7037,7 @@
         <v>562</v>
       </c>
       <c r="B562" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7033,7 +7045,7 @@
         <v>563</v>
       </c>
       <c r="B563" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7041,7 +7053,7 @@
         <v>564</v>
       </c>
       <c r="B564" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7049,7 +7061,7 @@
         <v>565</v>
       </c>
       <c r="B565" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7057,7 +7069,7 @@
         <v>566</v>
       </c>
       <c r="B566" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7065,7 +7077,7 @@
         <v>567</v>
       </c>
       <c r="B567" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7073,7 +7085,7 @@
         <v>568</v>
       </c>
       <c r="B568" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7081,7 +7093,7 @@
         <v>569</v>
       </c>
       <c r="B569" s="1">
-        <v>640</v>
+        <v>960</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7089,7 +7101,7 @@
         <v>570</v>
       </c>
       <c r="B570" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7097,7 +7109,7 @@
         <v>571</v>
       </c>
       <c r="B571" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7105,7 +7117,7 @@
         <v>572</v>
       </c>
       <c r="B572" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7113,7 +7125,7 @@
         <v>573</v>
       </c>
       <c r="B573" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7121,7 +7133,7 @@
         <v>574</v>
       </c>
       <c r="B574" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7129,7 +7141,7 @@
         <v>575</v>
       </c>
       <c r="B575" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7137,7 +7149,7 @@
         <v>576</v>
       </c>
       <c r="B576" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7145,7 +7157,7 @@
         <v>577</v>
       </c>
       <c r="B577" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7153,7 +7165,7 @@
         <v>578</v>
       </c>
       <c r="B578" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7161,7 +7173,7 @@
         <v>579</v>
       </c>
       <c r="B579" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7169,7 +7181,7 @@
         <v>580</v>
       </c>
       <c r="B580" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7185,7 +7197,7 @@
         <v>582</v>
       </c>
       <c r="B582" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7193,7 +7205,7 @@
         <v>583</v>
       </c>
       <c r="B583" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7201,7 +7213,7 @@
         <v>584</v>
       </c>
       <c r="B584" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7209,7 +7221,7 @@
         <v>585</v>
       </c>
       <c r="B585" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7217,7 +7229,7 @@
         <v>586</v>
       </c>
       <c r="B586" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7225,7 +7237,7 @@
         <v>587</v>
       </c>
       <c r="B587" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7233,7 +7245,7 @@
         <v>588</v>
       </c>
       <c r="B588" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7241,7 +7253,7 @@
         <v>589</v>
       </c>
       <c r="B589" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7249,7 +7261,7 @@
         <v>590</v>
       </c>
       <c r="B590" s="1">
-        <v>820</v>
+        <v>900</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7257,7 +7269,7 @@
         <v>591</v>
       </c>
       <c r="B591" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7265,7 +7277,7 @@
         <v>592</v>
       </c>
       <c r="B592" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7273,7 +7285,7 @@
         <v>593</v>
       </c>
       <c r="B593" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7281,7 +7293,7 @@
         <v>594</v>
       </c>
       <c r="B594" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7289,7 +7301,7 @@
         <v>595</v>
       </c>
       <c r="B595" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7297,7 +7309,7 @@
         <v>596</v>
       </c>
       <c r="B596" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7305,7 +7317,7 @@
         <v>597</v>
       </c>
       <c r="B597" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7313,7 +7325,7 @@
         <v>598</v>
       </c>
       <c r="B598" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7321,7 +7333,7 @@
         <v>599</v>
       </c>
       <c r="B599" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7329,7 +7341,7 @@
         <v>600</v>
       </c>
       <c r="B600" s="1">
-        <v>660</v>
+        <v>880</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7337,7 +7349,7 @@
         <v>601</v>
       </c>
       <c r="B601" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7345,7 +7357,7 @@
         <v>602</v>
       </c>
       <c r="B602" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7353,7 +7365,7 @@
         <v>603</v>
       </c>
       <c r="B603" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7361,7 +7373,7 @@
         <v>604</v>
       </c>
       <c r="B604" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7377,7 +7389,7 @@
         <v>606</v>
       </c>
       <c r="B606" s="1">
-        <v>800</v>
+        <v>680</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7385,7 +7397,7 @@
         <v>607</v>
       </c>
       <c r="B607" s="1">
-        <v>720</v>
+        <v>660</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7393,7 +7405,7 @@
         <v>608</v>
       </c>
       <c r="B608" s="1">
-        <v>600</v>
+        <v>440</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7401,7 +7413,7 @@
         <v>609</v>
       </c>
       <c r="B609" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7409,7 +7421,7 @@
         <v>610</v>
       </c>
       <c r="B610" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7417,7 +7429,7 @@
         <v>611</v>
       </c>
       <c r="B611" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7425,7 +7437,7 @@
         <v>612</v>
       </c>
       <c r="B612" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7433,7 +7445,7 @@
         <v>613</v>
       </c>
       <c r="B613" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7441,7 +7453,7 @@
         <v>614</v>
       </c>
       <c r="B614" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7449,7 +7461,7 @@
         <v>615</v>
       </c>
       <c r="B615" s="1">
-        <v>940</v>
+        <v>800</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7457,7 +7469,7 @@
         <v>616</v>
       </c>
       <c r="B616" s="1">
-        <v>980</v>
+        <v>780</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -7473,7 +7485,7 @@
         <v>618</v>
       </c>
       <c r="B618" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -7481,7 +7493,7 @@
         <v>619</v>
       </c>
       <c r="B619" s="1">
-        <v>860</v>
+        <v>940</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7489,7 +7501,7 @@
         <v>620</v>
       </c>
       <c r="B620" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7497,7 +7509,7 @@
         <v>621</v>
       </c>
       <c r="B621" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -7505,7 +7517,7 @@
         <v>622</v>
       </c>
       <c r="B622" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -7513,7 +7525,7 @@
         <v>623</v>
       </c>
       <c r="B623" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -7521,7 +7533,7 @@
         <v>624</v>
       </c>
       <c r="B624" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -7529,7 +7541,7 @@
         <v>625</v>
       </c>
       <c r="B625" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -7537,7 +7549,7 @@
         <v>626</v>
       </c>
       <c r="B626" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -7545,7 +7557,7 @@
         <v>627</v>
       </c>
       <c r="B627" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -7553,7 +7565,7 @@
         <v>628</v>
       </c>
       <c r="B628" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -7561,7 +7573,7 @@
         <v>629</v>
       </c>
       <c r="B629" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -7569,7 +7581,7 @@
         <v>630</v>
       </c>
       <c r="B630" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -7577,7 +7589,7 @@
         <v>631</v>
       </c>
       <c r="B631" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -7585,7 +7597,7 @@
         <v>632</v>
       </c>
       <c r="B632" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -7593,7 +7605,7 @@
         <v>633</v>
       </c>
       <c r="B633" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -7609,7 +7621,7 @@
         <v>635</v>
       </c>
       <c r="B635" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -7617,7 +7629,7 @@
         <v>636</v>
       </c>
       <c r="B636" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -7625,7 +7637,7 @@
         <v>637</v>
       </c>
       <c r="B637" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -7633,7 +7645,7 @@
         <v>638</v>
       </c>
       <c r="B638" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -7641,7 +7653,7 @@
         <v>639</v>
       </c>
       <c r="B639" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -7649,7 +7661,7 @@
         <v>640</v>
       </c>
       <c r="B640" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -7657,7 +7669,7 @@
         <v>641</v>
       </c>
       <c r="B641" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -7665,7 +7677,7 @@
         <v>642</v>
       </c>
       <c r="B642" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -7673,7 +7685,7 @@
         <v>643</v>
       </c>
       <c r="B643" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -7681,7 +7693,7 @@
         <v>644</v>
       </c>
       <c r="B644" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -7689,7 +7701,7 @@
         <v>645</v>
       </c>
       <c r="B645" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -7697,7 +7709,7 @@
         <v>646</v>
       </c>
       <c r="B646" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -7705,7 +7717,7 @@
         <v>647</v>
       </c>
       <c r="B647" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -7713,7 +7725,7 @@
         <v>648</v>
       </c>
       <c r="B648" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -7721,7 +7733,7 @@
         <v>649</v>
       </c>
       <c r="B649" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -7729,7 +7741,7 @@
         <v>650</v>
       </c>
       <c r="B650" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -7737,7 +7749,7 @@
         <v>651</v>
       </c>
       <c r="B651" s="1">
-        <v>920</v>
+        <v>600</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -7745,7 +7757,7 @@
         <v>652</v>
       </c>
       <c r="B652" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -7753,7 +7765,7 @@
         <v>653</v>
       </c>
       <c r="B653" s="1">
-        <v>1040</v>
+        <v>500</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -7761,7 +7773,7 @@
         <v>654</v>
       </c>
       <c r="B654" s="1">
-        <v>940</v>
+        <v>760</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -7769,7 +7781,7 @@
         <v>655</v>
       </c>
       <c r="B655" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -7785,7 +7797,7 @@
         <v>657</v>
       </c>
       <c r="B657" s="1">
-        <v>740</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -7793,7 +7805,7 @@
         <v>658</v>
       </c>
       <c r="B658" s="1">
-        <v>440</v>
+        <v>940</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -7801,7 +7813,7 @@
         <v>659</v>
       </c>
       <c r="B659" s="1">
-        <v>500</v>
+        <v>900</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -7809,7 +7821,7 @@
         <v>660</v>
       </c>
       <c r="B660" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -7817,7 +7829,7 @@
         <v>661</v>
       </c>
       <c r="B661" s="1">
-        <v>560</v>
+        <v>740</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -7825,7 +7837,7 @@
         <v>662</v>
       </c>
       <c r="B662" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -7833,7 +7845,7 @@
         <v>663</v>
       </c>
       <c r="B663" s="1">
-        <v>780</v>
+        <v>500</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -7841,7 +7853,7 @@
         <v>664</v>
       </c>
       <c r="B664" s="1">
-        <v>760</v>
+        <v>440</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -7849,7 +7861,7 @@
         <v>665</v>
       </c>
       <c r="B665" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -7857,7 +7869,7 @@
         <v>666</v>
       </c>
       <c r="B666" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -7865,7 +7877,7 @@
         <v>667</v>
       </c>
       <c r="B667" s="1">
-        <v>400</v>
+        <v>780</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -7873,7 +7885,7 @@
         <v>668</v>
       </c>
       <c r="B668" s="1">
-        <v>380</v>
+        <v>760</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -7881,7 +7893,7 @@
         <v>669</v>
       </c>
       <c r="B669" s="1">
-        <v>380</v>
+        <v>760</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -7889,7 +7901,7 @@
         <v>670</v>
       </c>
       <c r="B670" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -7897,7 +7909,7 @@
         <v>671</v>
       </c>
       <c r="B671" s="1">
-        <v>520</v>
+        <v>400</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -7905,7 +7917,7 @@
         <v>672</v>
       </c>
       <c r="B672" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -7913,7 +7925,7 @@
         <v>673</v>
       </c>
       <c r="B673" s="1">
-        <v>860</v>
+        <v>380</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -7921,7 +7933,7 @@
         <v>674</v>
       </c>
       <c r="B674" s="1">
-        <v>680</v>
+        <v>380</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -7929,7 +7941,7 @@
         <v>675</v>
       </c>
       <c r="B675" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -7937,7 +7949,7 @@
         <v>676</v>
       </c>
       <c r="B676" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -7945,7 +7957,7 @@
         <v>677</v>
       </c>
       <c r="B677" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -7953,7 +7965,7 @@
         <v>678</v>
       </c>
       <c r="B678" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -7961,7 +7973,7 @@
         <v>679</v>
       </c>
       <c r="B679" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -7969,7 +7981,7 @@
         <v>680</v>
       </c>
       <c r="B680" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -7977,7 +7989,7 @@
         <v>681</v>
       </c>
       <c r="B681" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -7985,7 +7997,7 @@
         <v>682</v>
       </c>
       <c r="B682" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -7993,7 +8005,7 @@
         <v>683</v>
       </c>
       <c r="B683" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8001,7 +8013,7 @@
         <v>684</v>
       </c>
       <c r="B684" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8009,7 +8021,7 @@
         <v>685</v>
       </c>
       <c r="B685" s="1">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8017,7 +8029,7 @@
         <v>686</v>
       </c>
       <c r="B686" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8025,7 +8037,7 @@
         <v>687</v>
       </c>
       <c r="B687" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8033,7 +8045,7 @@
         <v>688</v>
       </c>
       <c r="B688" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8041,7 +8053,7 @@
         <v>689</v>
       </c>
       <c r="B689" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8049,7 +8061,7 @@
         <v>690</v>
       </c>
       <c r="B690" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8065,7 +8077,7 @@
         <v>692</v>
       </c>
       <c r="B692" s="1">
-        <v>740</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8073,7 +8085,7 @@
         <v>693</v>
       </c>
       <c r="B693" s="1">
-        <v>440</v>
+        <v>940</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8081,7 +8093,7 @@
         <v>694</v>
       </c>
       <c r="B694" s="1">
-        <v>500</v>
+        <v>900</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8089,7 +8101,7 @@
         <v>695</v>
       </c>
       <c r="B695" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8097,7 +8109,7 @@
         <v>696</v>
       </c>
       <c r="B696" s="1">
-        <v>560</v>
+        <v>740</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8105,7 +8117,7 @@
         <v>697</v>
       </c>
       <c r="B697" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8113,7 +8125,7 @@
         <v>698</v>
       </c>
       <c r="B698" s="1">
-        <v>780</v>
+        <v>500</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8121,7 +8133,7 @@
         <v>699</v>
       </c>
       <c r="B699" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8129,7 +8141,7 @@
         <v>700</v>
       </c>
       <c r="B700" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8137,7 +8149,7 @@
         <v>701</v>
       </c>
       <c r="B701" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8145,7 +8157,7 @@
         <v>702</v>
       </c>
       <c r="B702" s="1">
-        <v>480</v>
+        <v>780</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8153,7 +8165,7 @@
         <v>703</v>
       </c>
       <c r="B703" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8161,7 +8173,7 @@
         <v>704</v>
       </c>
       <c r="B704" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8169,7 +8181,7 @@
         <v>705</v>
       </c>
       <c r="B705" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8177,7 +8189,7 @@
         <v>706</v>
       </c>
       <c r="B706" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8185,7 +8197,7 @@
         <v>707</v>
       </c>
       <c r="B707" s="1">
-        <v>440</v>
+        <v>480</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8193,7 +8205,7 @@
         <v>708</v>
       </c>
       <c r="B708" s="1">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8201,7 +8213,7 @@
         <v>709</v>
       </c>
       <c r="B709" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8209,7 +8221,7 @@
         <v>710</v>
       </c>
       <c r="B710" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8217,7 +8229,7 @@
         <v>711</v>
       </c>
       <c r="B711" s="1">
-        <v>760</v>
+        <v>440</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8225,7 +8237,7 @@
         <v>712</v>
       </c>
       <c r="B712" s="1">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8233,7 +8245,7 @@
         <v>713</v>
       </c>
       <c r="B713" s="1">
-        <v>580</v>
+        <v>380</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8241,7 +8253,7 @@
         <v>714</v>
       </c>
       <c r="B714" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8249,7 +8261,7 @@
         <v>715</v>
       </c>
       <c r="B715" s="1">
-        <v>580</v>
+        <v>760</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8257,7 +8269,7 @@
         <v>716</v>
       </c>
       <c r="B716" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8265,7 +8277,7 @@
         <v>717</v>
       </c>
       <c r="B717" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8273,6 +8285,38 @@
         <v>718</v>
       </c>
       <c r="B718" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2">
+      <c r="A719" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B719" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2">
+      <c r="A720" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B720" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2">
+      <c r="A721" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="B721" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2">
+      <c r="A722" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B722" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -4541,7 +4541,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>860</v>
+        <v>900</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -6877,7 +6877,7 @@
         <v>542</v>
       </c>
       <c r="B542" s="1">
-        <v>860</v>
+        <v>900</v>
       </c>
     </row>
     <row r="543" spans="1:2">

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -4861,7 +4861,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>640</v>
+        <v>800</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -7053,7 +7053,7 @@
         <v>564</v>
       </c>
       <c r="B564" s="1">
-        <v>640</v>
+        <v>800</v>
       </c>
     </row>
     <row r="565" spans="1:2">

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="727">
   <si>
     <t>Наименование</t>
   </si>
@@ -392,6 +392,9 @@
     <t>Jaws, APA, Розлив, Россия</t>
   </si>
   <si>
+    <t>Jungle - Body Flow (IPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Jungle - The Rush (AIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -440,6 +443,9 @@
     <t>Maisel`S Weisse ORIGINAL, Розлив, Германия</t>
   </si>
   <si>
+    <t>Malanka - Imhla: Galaxy (NEIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Malanka - Zaltum: Simcoe (Black IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1469,6 +1475,9 @@
     <t>вынос_Jaws - Nitro Stout, РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Jungle - Body Flow (IPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_KRIEKENBIER (Cherry Lager), Розлив, Бельгия</t>
   </si>
   <si>
@@ -1491,6 +1500,9 @@
   </si>
   <si>
     <t>вынос_Magic Mess - Понедельник (Lager), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Malanka - Imhla: Galaxy (NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Malanka - Zaltum: Simcoe (Black IPA), РОЗЛИВ, Россия</t>
@@ -2537,7 +2549,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B722"/>
+  <dimension ref="A1:B726"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -3541,7 +3553,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -3549,7 +3561,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>420</v>
+        <v>560</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -3557,7 +3569,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>520</v>
+        <v>420</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -3565,7 +3577,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -3573,7 +3585,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>460</v>
+        <v>720</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -3581,7 +3593,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>560</v>
+        <v>460</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -3589,7 +3601,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -3597,7 +3609,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -3605,7 +3617,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -3613,7 +3625,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -3621,7 +3633,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>980</v>
+        <v>520</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -3629,7 +3641,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>540</v>
+        <v>980</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -3637,7 +3649,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -3645,7 +3657,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -3653,7 +3665,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -3661,7 +3673,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>560</v>
+        <v>760</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -3669,7 +3681,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -3685,7 +3697,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -3693,7 +3705,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>640</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -3709,7 +3721,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>920</v>
+        <v>640</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -3717,7 +3729,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3733,7 +3745,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -3741,7 +3753,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -3749,7 +3761,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3757,7 +3769,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3765,7 +3777,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3773,7 +3785,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>460</v>
+        <v>840</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -3781,7 +3793,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -3789,7 +3801,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>720</v>
+        <v>460</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -3797,7 +3809,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>660</v>
+        <v>580</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -3805,7 +3817,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -3813,7 +3825,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>260</v>
+        <v>660</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -3821,7 +3833,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -3829,7 +3841,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -3837,7 +3849,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -3845,7 +3857,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -3853,7 +3865,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -3861,7 +3873,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -3869,7 +3881,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -3877,7 +3889,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>400</v>
+        <v>720</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -3885,7 +3897,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>740</v>
+        <v>500</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -3893,7 +3905,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>680</v>
+        <v>400</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -3901,7 +3913,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -3909,7 +3921,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -3917,7 +3929,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -3925,7 +3937,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>680</v>
+        <v>620</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -3933,7 +3945,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -3941,7 +3953,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -3949,7 +3961,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -3957,7 +3969,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -3965,7 +3977,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>580</v>
+        <v>620</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -3973,7 +3985,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -3981,7 +3993,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -3989,7 +4001,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -3997,7 +4009,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4005,7 +4017,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4013,7 +4025,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4021,7 +4033,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4029,7 +4041,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>700</v>
+        <v>580</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4037,7 +4049,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>820</v>
+        <v>540</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4045,7 +4057,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4053,7 +4065,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4061,7 +4073,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4069,7 +4081,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>1400</v>
+        <v>720</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4077,7 +4089,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4085,7 +4097,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>720</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4093,7 +4105,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>660</v>
+        <v>480</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4101,7 +4113,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4109,7 +4121,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4117,7 +4129,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>740</v>
+        <v>600</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4125,7 +4137,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4133,7 +4145,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4141,7 +4153,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>520</v>
+        <v>720</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4149,7 +4161,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4157,7 +4169,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4165,7 +4177,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4181,7 +4193,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4189,7 +4201,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4197,7 +4209,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4205,7 +4217,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4213,7 +4225,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4221,7 +4233,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4237,7 +4249,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4245,7 +4257,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4253,7 +4265,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4261,7 +4273,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4269,7 +4281,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4277,7 +4289,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4285,7 +4297,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4293,7 +4305,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4301,7 +4313,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4309,7 +4321,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4317,7 +4329,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>500</v>
+        <v>640</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4325,7 +4337,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>758</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4333,7 +4345,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>2273</v>
+        <v>500</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4341,7 +4353,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>1515</v>
+        <v>758</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4349,7 +4361,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>520</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4357,7 +4369,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>720</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4365,7 +4377,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4373,7 +4385,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>480</v>
+        <v>720</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4381,7 +4393,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4389,7 +4401,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4397,7 +4409,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4405,7 +4417,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4413,7 +4425,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>580</v>
+        <v>600</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4421,7 +4433,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>520</v>
+        <v>700</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4429,7 +4441,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>680</v>
+        <v>580</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4437,7 +4449,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4445,7 +4457,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4453,7 +4465,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4461,7 +4473,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>380</v>
+        <v>580</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4469,7 +4481,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4477,7 +4489,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>540</v>
+        <v>380</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4485,7 +4497,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>520</v>
+        <v>660</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4493,7 +4505,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>660</v>
+        <v>540</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4501,7 +4513,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4509,7 +4521,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>460</v>
+        <v>660</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4517,7 +4529,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4525,7 +4537,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4533,7 +4545,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>860</v>
+        <v>520</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4541,7 +4553,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4549,7 +4561,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4557,7 +4569,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4565,7 +4577,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4573,7 +4585,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>1000</v>
+        <v>560</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4581,7 +4593,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -4589,7 +4601,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4597,7 +4609,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4605,7 +4617,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4613,7 +4625,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>840</v>
+        <v>680</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4629,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>1020</v>
+        <v>840</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4645,7 +4657,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>680</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4653,7 +4665,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>520</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4661,7 +4673,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4669,7 +4681,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4677,7 +4689,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4685,7 +4697,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4693,7 +4705,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4701,7 +4713,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4709,7 +4721,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4717,7 +4729,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4725,7 +4737,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4741,7 +4753,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>880</v>
+        <v>640</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4749,7 +4761,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>520</v>
+        <v>720</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4757,7 +4769,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4765,7 +4777,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4773,7 +4785,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4789,7 +4801,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4797,7 +4809,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>520</v>
+        <v>600</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4805,7 +4817,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>320</v>
+        <v>380</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4813,7 +4825,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4821,7 +4833,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>560</v>
+        <v>320</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4829,7 +4841,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>480</v>
+        <v>540</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4837,7 +4849,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4845,7 +4857,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4853,7 +4865,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>500</v>
+        <v>480</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4861,7 +4873,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -4869,7 +4881,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -4877,7 +4889,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -4885,7 +4897,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -4893,7 +4905,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>380</v>
+        <v>780</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -4901,7 +4913,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -4909,7 +4921,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>900</v>
+        <v>380</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -4917,7 +4929,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -4925,7 +4937,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -4933,7 +4945,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -4941,7 +4953,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>1020</v>
+        <v>720</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -4949,7 +4961,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -4957,7 +4969,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>700</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -4965,7 +4977,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -4973,7 +4985,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -4981,7 +4993,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -4997,7 +5009,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5005,7 +5017,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5013,7 +5025,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5021,7 +5033,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5029,7 +5041,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5037,7 +5049,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5053,7 +5065,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5061,7 +5073,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5069,7 +5081,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5077,7 +5089,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>480</v>
+        <v>740</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5085,7 +5097,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5093,7 +5105,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>1000</v>
+        <v>480</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5101,7 +5113,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>920</v>
+        <v>640</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5109,7 +5121,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5117,7 +5129,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>520</v>
+        <v>920</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5125,7 +5137,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>540</v>
+        <v>860</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5133,7 +5145,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>700</v>
+        <v>520</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5141,7 +5153,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5149,7 +5161,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5165,7 +5177,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>720</v>
+        <v>420</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5173,7 +5185,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5181,7 +5193,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5189,7 +5201,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5197,7 +5209,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5205,7 +5217,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5213,7 +5225,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5221,7 +5233,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5229,7 +5241,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>440</v>
+        <v>720</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5237,7 +5249,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>320</v>
+        <v>620</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5245,7 +5257,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>320</v>
+        <v>440</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5253,7 +5265,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>820</v>
+        <v>320</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5261,7 +5273,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>1000</v>
+        <v>320</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5269,7 +5281,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5277,7 +5289,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5285,7 +5297,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5301,7 +5313,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5309,7 +5321,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5317,7 +5329,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5325,7 +5337,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>1000</v>
+        <v>620</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5333,7 +5345,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5341,7 +5353,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5357,7 +5369,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5365,7 +5377,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5373,7 +5385,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5381,7 +5393,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5389,7 +5401,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5397,7 +5409,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5405,7 +5417,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>440</v>
+        <v>680</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5413,7 +5425,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5421,7 +5433,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5429,7 +5441,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5437,7 +5449,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5445,7 +5457,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5453,7 +5465,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5461,7 +5473,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5469,7 +5481,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5477,7 +5489,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5485,7 +5497,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5493,7 +5505,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>680</v>
+        <v>620</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5501,7 +5513,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>480</v>
+        <v>720</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5509,7 +5521,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5517,7 +5529,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5525,7 +5537,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5533,7 +5545,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5541,7 +5553,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5549,7 +5561,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5557,7 +5569,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5565,7 +5577,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5573,7 +5585,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5581,7 +5593,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5589,7 +5601,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>600</v>
+        <v>980</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5597,7 +5609,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="1">
-        <v>760</v>
+        <v>920</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5605,7 +5617,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5613,7 +5625,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="1">
-        <v>620</v>
+        <v>760</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5621,7 +5633,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5629,7 +5641,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5637,7 +5649,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5645,7 +5657,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>640</v>
+        <v>860</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5653,7 +5665,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5661,7 +5673,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>820</v>
+        <v>640</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5669,7 +5681,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5677,7 +5689,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5685,7 +5697,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5693,7 +5705,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5701,7 +5713,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5709,7 +5721,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5717,7 +5729,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5725,7 +5737,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5733,7 +5745,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5741,7 +5753,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5749,7 +5761,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>840</v>
+        <v>640</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5757,7 +5769,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5765,7 +5777,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>480</v>
+        <v>840</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5773,7 +5785,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5781,7 +5793,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>780</v>
+        <v>480</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5789,7 +5801,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5797,7 +5809,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5805,7 +5817,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5813,7 +5825,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5821,7 +5833,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5829,7 +5841,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5837,7 +5849,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>480</v>
+        <v>780</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5845,7 +5857,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5853,7 +5865,7 @@
         <v>414</v>
       </c>
       <c r="B414" s="1">
-        <v>660</v>
+        <v>480</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5861,7 +5873,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5869,7 +5881,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5877,7 +5889,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5885,7 +5897,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5893,7 +5905,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>880</v>
+        <v>440</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5901,7 +5913,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5909,7 +5921,7 @@
         <v>421</v>
       </c>
       <c r="B421" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -5917,7 +5929,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -5925,7 +5937,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -5933,7 +5945,7 @@
         <v>424</v>
       </c>
       <c r="B424" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -5941,7 +5953,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -5949,7 +5961,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -5957,7 +5969,7 @@
         <v>427</v>
       </c>
       <c r="B427" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -5965,7 +5977,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -5973,7 +5985,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -5981,7 +5993,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -5989,7 +6001,7 @@
         <v>431</v>
       </c>
       <c r="B431" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -5997,7 +6009,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6005,7 +6017,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6021,7 +6033,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6029,7 +6041,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6037,7 +6049,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6045,7 +6057,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6053,7 +6065,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6061,7 +6073,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6069,7 +6081,7 @@
         <v>441</v>
       </c>
       <c r="B441" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6077,7 +6089,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6085,7 +6097,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6093,7 +6105,7 @@
         <v>444</v>
       </c>
       <c r="B444" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6101,7 +6113,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6109,7 +6121,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6117,7 +6129,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6125,7 +6137,7 @@
         <v>448</v>
       </c>
       <c r="B448" s="1">
-        <v>790</v>
+        <v>720</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6133,7 +6145,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>640</v>
+        <v>900</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6141,7 +6153,7 @@
         <v>450</v>
       </c>
       <c r="B450" s="1">
-        <v>800</v>
+        <v>790</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6149,7 +6161,7 @@
         <v>451</v>
       </c>
       <c r="B451" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6157,7 +6169,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6165,7 +6177,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6173,7 +6185,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6181,7 +6193,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6205,7 +6217,7 @@
         <v>458</v>
       </c>
       <c r="B458" s="1">
-        <v>920</v>
+        <v>820</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6213,7 +6225,7 @@
         <v>459</v>
       </c>
       <c r="B459" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6221,7 +6233,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6229,7 +6241,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>640</v>
+        <v>600</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6237,7 +6249,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>700</v>
+        <v>880</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6245,7 +6257,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6253,7 +6265,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6261,7 +6273,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6269,7 +6281,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6277,7 +6289,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6285,7 +6297,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6293,7 +6305,7 @@
         <v>469</v>
       </c>
       <c r="B469" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6301,7 +6313,7 @@
         <v>470</v>
       </c>
       <c r="B470" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6309,7 +6321,7 @@
         <v>471</v>
       </c>
       <c r="B471" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6317,7 +6329,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>600</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6325,7 +6337,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>580</v>
+        <v>920</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6333,7 +6345,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6341,7 +6353,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6349,7 +6361,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6357,7 +6369,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6365,7 +6377,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6373,7 +6385,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6381,7 +6393,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6389,7 +6401,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>720</v>
+        <v>960</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6397,7 +6409,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6405,7 +6417,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>540</v>
+        <v>720</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6413,7 +6425,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6421,7 +6433,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6429,7 +6441,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>740</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6437,7 +6449,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6445,7 +6457,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6453,7 +6465,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6461,7 +6473,7 @@
         <v>490</v>
       </c>
       <c r="B490" s="1">
-        <v>740</v>
+        <v>620</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6469,7 +6481,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6477,7 +6489,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>1100</v>
+        <v>980</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6485,7 +6497,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6493,7 +6505,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6501,7 +6513,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6509,7 +6521,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6517,7 +6529,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6525,7 +6537,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6533,7 +6545,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6549,7 +6561,7 @@
         <v>501</v>
       </c>
       <c r="B501" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6557,7 +6569,7 @@
         <v>502</v>
       </c>
       <c r="B502" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6565,7 +6577,7 @@
         <v>503</v>
       </c>
       <c r="B503" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6573,7 +6585,7 @@
         <v>504</v>
       </c>
       <c r="B504" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6581,7 +6593,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6589,7 +6601,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6597,7 +6609,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6605,7 +6617,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6613,7 +6625,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6621,7 +6633,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6629,7 +6641,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6637,7 +6649,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>1400</v>
+        <v>700</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6645,7 +6657,7 @@
         <v>513</v>
       </c>
       <c r="B513" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6653,7 +6665,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6661,7 +6673,7 @@
         <v>515</v>
       </c>
       <c r="B515" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6669,7 +6681,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>740</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6685,7 +6697,7 @@
         <v>518</v>
       </c>
       <c r="B518" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6693,7 +6705,7 @@
         <v>519</v>
       </c>
       <c r="B519" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6701,7 +6713,7 @@
         <v>520</v>
       </c>
       <c r="B520" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6717,7 +6729,7 @@
         <v>522</v>
       </c>
       <c r="B522" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -6725,7 +6737,7 @@
         <v>523</v>
       </c>
       <c r="B523" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6733,7 +6745,7 @@
         <v>524</v>
       </c>
       <c r="B524" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6741,7 +6753,7 @@
         <v>525</v>
       </c>
       <c r="B525" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6757,7 +6769,7 @@
         <v>527</v>
       </c>
       <c r="B527" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6765,7 +6777,7 @@
         <v>528</v>
       </c>
       <c r="B528" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6773,7 +6785,7 @@
         <v>529</v>
       </c>
       <c r="B529" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6789,7 +6801,7 @@
         <v>531</v>
       </c>
       <c r="B531" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6797,7 +6809,7 @@
         <v>532</v>
       </c>
       <c r="B532" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6805,7 +6817,7 @@
         <v>533</v>
       </c>
       <c r="B533" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6813,7 +6825,7 @@
         <v>534</v>
       </c>
       <c r="B534" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6821,7 +6833,7 @@
         <v>535</v>
       </c>
       <c r="B535" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -6829,7 +6841,7 @@
         <v>536</v>
       </c>
       <c r="B536" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -6837,7 +6849,7 @@
         <v>537</v>
       </c>
       <c r="B537" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -6845,7 +6857,7 @@
         <v>538</v>
       </c>
       <c r="B538" s="1">
-        <v>540</v>
+        <v>700</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -6853,7 +6865,7 @@
         <v>539</v>
       </c>
       <c r="B539" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -6861,7 +6873,7 @@
         <v>540</v>
       </c>
       <c r="B540" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -6869,7 +6881,7 @@
         <v>541</v>
       </c>
       <c r="B541" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -6877,7 +6889,7 @@
         <v>542</v>
       </c>
       <c r="B542" s="1">
-        <v>900</v>
+        <v>540</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -6885,7 +6897,7 @@
         <v>543</v>
       </c>
       <c r="B543" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -6893,7 +6905,7 @@
         <v>544</v>
       </c>
       <c r="B544" s="1">
-        <v>1000</v>
+        <v>580</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -6901,7 +6913,7 @@
         <v>545</v>
       </c>
       <c r="B545" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -6909,7 +6921,7 @@
         <v>546</v>
       </c>
       <c r="B546" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -6917,7 +6929,7 @@
         <v>547</v>
       </c>
       <c r="B547" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -6933,7 +6945,7 @@
         <v>549</v>
       </c>
       <c r="B549" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -6941,7 +6953,7 @@
         <v>550</v>
       </c>
       <c r="B550" s="1">
-        <v>1020</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -6949,7 +6961,7 @@
         <v>551</v>
       </c>
       <c r="B551" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -6957,7 +6969,7 @@
         <v>552</v>
       </c>
       <c r="B552" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -6965,7 +6977,7 @@
         <v>553</v>
       </c>
       <c r="B553" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -6973,7 +6985,7 @@
         <v>554</v>
       </c>
       <c r="B554" s="1">
-        <v>640</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -6981,7 +6993,7 @@
         <v>555</v>
       </c>
       <c r="B555" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -6989,7 +7001,7 @@
         <v>556</v>
       </c>
       <c r="B556" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -6997,7 +7009,7 @@
         <v>557</v>
       </c>
       <c r="B557" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7005,7 +7017,7 @@
         <v>558</v>
       </c>
       <c r="B558" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7013,7 +7025,7 @@
         <v>559</v>
       </c>
       <c r="B559" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7021,7 +7033,7 @@
         <v>560</v>
       </c>
       <c r="B560" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7029,7 +7041,7 @@
         <v>561</v>
       </c>
       <c r="B561" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7037,7 +7049,7 @@
         <v>562</v>
       </c>
       <c r="B562" s="1">
-        <v>820</v>
+        <v>720</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7045,7 +7057,7 @@
         <v>563</v>
       </c>
       <c r="B563" s="1">
-        <v>600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7053,7 +7065,7 @@
         <v>564</v>
       </c>
       <c r="B564" s="1">
-        <v>800</v>
+        <v>740</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7061,7 +7073,7 @@
         <v>565</v>
       </c>
       <c r="B565" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7069,7 +7081,7 @@
         <v>566</v>
       </c>
       <c r="B566" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7077,7 +7089,7 @@
         <v>567</v>
       </c>
       <c r="B567" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7085,7 +7097,7 @@
         <v>568</v>
       </c>
       <c r="B568" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7093,7 +7105,7 @@
         <v>569</v>
       </c>
       <c r="B569" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7101,7 +7113,7 @@
         <v>570</v>
       </c>
       <c r="B570" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7109,7 +7121,7 @@
         <v>571</v>
       </c>
       <c r="B571" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7117,7 +7129,7 @@
         <v>572</v>
       </c>
       <c r="B572" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7125,7 +7137,7 @@
         <v>573</v>
       </c>
       <c r="B573" s="1">
-        <v>640</v>
+        <v>960</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7133,7 +7145,7 @@
         <v>574</v>
       </c>
       <c r="B574" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7141,7 +7153,7 @@
         <v>575</v>
       </c>
       <c r="B575" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7149,7 +7161,7 @@
         <v>576</v>
       </c>
       <c r="B576" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7157,7 +7169,7 @@
         <v>577</v>
       </c>
       <c r="B577" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7165,7 +7177,7 @@
         <v>578</v>
       </c>
       <c r="B578" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7173,7 +7185,7 @@
         <v>579</v>
       </c>
       <c r="B579" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7181,7 +7193,7 @@
         <v>580</v>
       </c>
       <c r="B580" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7189,7 +7201,7 @@
         <v>581</v>
       </c>
       <c r="B581" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7197,7 +7209,7 @@
         <v>582</v>
       </c>
       <c r="B582" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7205,7 +7217,7 @@
         <v>583</v>
       </c>
       <c r="B583" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7213,7 +7225,7 @@
         <v>584</v>
       </c>
       <c r="B584" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7229,7 +7241,7 @@
         <v>586</v>
       </c>
       <c r="B586" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7237,7 +7249,7 @@
         <v>587</v>
       </c>
       <c r="B587" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7245,7 +7257,7 @@
         <v>588</v>
       </c>
       <c r="B588" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7253,7 +7265,7 @@
         <v>589</v>
       </c>
       <c r="B589" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7261,7 +7273,7 @@
         <v>590</v>
       </c>
       <c r="B590" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7269,7 +7281,7 @@
         <v>591</v>
       </c>
       <c r="B591" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7277,7 +7289,7 @@
         <v>592</v>
       </c>
       <c r="B592" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7285,7 +7297,7 @@
         <v>593</v>
       </c>
       <c r="B593" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7293,7 +7305,7 @@
         <v>594</v>
       </c>
       <c r="B594" s="1">
-        <v>820</v>
+        <v>900</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7301,7 +7313,7 @@
         <v>595</v>
       </c>
       <c r="B595" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7309,7 +7321,7 @@
         <v>596</v>
       </c>
       <c r="B596" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7317,7 +7329,7 @@
         <v>597</v>
       </c>
       <c r="B597" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7325,7 +7337,7 @@
         <v>598</v>
       </c>
       <c r="B598" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7333,7 +7345,7 @@
         <v>599</v>
       </c>
       <c r="B599" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7341,7 +7353,7 @@
         <v>600</v>
       </c>
       <c r="B600" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7349,7 +7361,7 @@
         <v>601</v>
       </c>
       <c r="B601" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7357,7 +7369,7 @@
         <v>602</v>
       </c>
       <c r="B602" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7365,7 +7377,7 @@
         <v>603</v>
       </c>
       <c r="B603" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7373,7 +7385,7 @@
         <v>604</v>
       </c>
       <c r="B604" s="1">
-        <v>660</v>
+        <v>880</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7381,7 +7393,7 @@
         <v>605</v>
       </c>
       <c r="B605" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7389,7 +7401,7 @@
         <v>606</v>
       </c>
       <c r="B606" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7397,7 +7409,7 @@
         <v>607</v>
       </c>
       <c r="B607" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7405,7 +7417,7 @@
         <v>608</v>
       </c>
       <c r="B608" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7421,7 +7433,7 @@
         <v>610</v>
       </c>
       <c r="B610" s="1">
-        <v>800</v>
+        <v>680</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7429,7 +7441,7 @@
         <v>611</v>
       </c>
       <c r="B611" s="1">
-        <v>720</v>
+        <v>660</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7437,7 +7449,7 @@
         <v>612</v>
       </c>
       <c r="B612" s="1">
-        <v>600</v>
+        <v>440</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7445,7 +7457,7 @@
         <v>613</v>
       </c>
       <c r="B613" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7453,7 +7465,7 @@
         <v>614</v>
       </c>
       <c r="B614" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7461,7 +7473,7 @@
         <v>615</v>
       </c>
       <c r="B615" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7469,7 +7481,7 @@
         <v>616</v>
       </c>
       <c r="B616" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -7477,7 +7489,7 @@
         <v>617</v>
       </c>
       <c r="B617" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -7485,7 +7497,7 @@
         <v>618</v>
       </c>
       <c r="B618" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -7493,7 +7505,7 @@
         <v>619</v>
       </c>
       <c r="B619" s="1">
-        <v>940</v>
+        <v>800</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7501,7 +7513,7 @@
         <v>620</v>
       </c>
       <c r="B620" s="1">
-        <v>980</v>
+        <v>780</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7517,7 +7529,7 @@
         <v>622</v>
       </c>
       <c r="B622" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -7525,7 +7537,7 @@
         <v>623</v>
       </c>
       <c r="B623" s="1">
-        <v>860</v>
+        <v>940</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -7533,7 +7545,7 @@
         <v>624</v>
       </c>
       <c r="B624" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -7541,7 +7553,7 @@
         <v>625</v>
       </c>
       <c r="B625" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -7549,7 +7561,7 @@
         <v>626</v>
       </c>
       <c r="B626" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -7557,7 +7569,7 @@
         <v>627</v>
       </c>
       <c r="B627" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -7565,7 +7577,7 @@
         <v>628</v>
       </c>
       <c r="B628" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -7573,7 +7585,7 @@
         <v>629</v>
       </c>
       <c r="B629" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -7581,7 +7593,7 @@
         <v>630</v>
       </c>
       <c r="B630" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -7589,7 +7601,7 @@
         <v>631</v>
       </c>
       <c r="B631" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -7597,7 +7609,7 @@
         <v>632</v>
       </c>
       <c r="B632" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -7605,7 +7617,7 @@
         <v>633</v>
       </c>
       <c r="B633" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -7613,7 +7625,7 @@
         <v>634</v>
       </c>
       <c r="B634" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -7621,7 +7633,7 @@
         <v>635</v>
       </c>
       <c r="B635" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -7629,7 +7641,7 @@
         <v>636</v>
       </c>
       <c r="B636" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -7637,7 +7649,7 @@
         <v>637</v>
       </c>
       <c r="B637" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -7653,7 +7665,7 @@
         <v>639</v>
       </c>
       <c r="B639" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -7661,7 +7673,7 @@
         <v>640</v>
       </c>
       <c r="B640" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -7669,7 +7681,7 @@
         <v>641</v>
       </c>
       <c r="B641" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -7677,7 +7689,7 @@
         <v>642</v>
       </c>
       <c r="B642" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -7685,7 +7697,7 @@
         <v>643</v>
       </c>
       <c r="B643" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -7693,7 +7705,7 @@
         <v>644</v>
       </c>
       <c r="B644" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -7701,7 +7713,7 @@
         <v>645</v>
       </c>
       <c r="B645" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -7709,7 +7721,7 @@
         <v>646</v>
       </c>
       <c r="B646" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -7717,7 +7729,7 @@
         <v>647</v>
       </c>
       <c r="B647" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -7725,7 +7737,7 @@
         <v>648</v>
       </c>
       <c r="B648" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -7733,7 +7745,7 @@
         <v>649</v>
       </c>
       <c r="B649" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -7741,7 +7753,7 @@
         <v>650</v>
       </c>
       <c r="B650" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -7749,7 +7761,7 @@
         <v>651</v>
       </c>
       <c r="B651" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -7757,7 +7769,7 @@
         <v>652</v>
       </c>
       <c r="B652" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -7765,7 +7777,7 @@
         <v>653</v>
       </c>
       <c r="B653" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -7773,7 +7785,7 @@
         <v>654</v>
       </c>
       <c r="B654" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -7781,7 +7793,7 @@
         <v>655</v>
       </c>
       <c r="B655" s="1">
-        <v>920</v>
+        <v>600</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -7789,7 +7801,7 @@
         <v>656</v>
       </c>
       <c r="B656" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -7797,7 +7809,7 @@
         <v>657</v>
       </c>
       <c r="B657" s="1">
-        <v>1040</v>
+        <v>500</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -7805,7 +7817,7 @@
         <v>658</v>
       </c>
       <c r="B658" s="1">
-        <v>940</v>
+        <v>760</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -7813,7 +7825,7 @@
         <v>659</v>
       </c>
       <c r="B659" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -7829,7 +7841,7 @@
         <v>661</v>
       </c>
       <c r="B661" s="1">
-        <v>740</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -7837,7 +7849,7 @@
         <v>662</v>
       </c>
       <c r="B662" s="1">
-        <v>440</v>
+        <v>940</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -7845,7 +7857,7 @@
         <v>663</v>
       </c>
       <c r="B663" s="1">
-        <v>500</v>
+        <v>900</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -7853,7 +7865,7 @@
         <v>664</v>
       </c>
       <c r="B664" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -7861,7 +7873,7 @@
         <v>665</v>
       </c>
       <c r="B665" s="1">
-        <v>560</v>
+        <v>740</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -7869,7 +7881,7 @@
         <v>666</v>
       </c>
       <c r="B666" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -7877,7 +7889,7 @@
         <v>667</v>
       </c>
       <c r="B667" s="1">
-        <v>780</v>
+        <v>500</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -7885,7 +7897,7 @@
         <v>668</v>
       </c>
       <c r="B668" s="1">
-        <v>760</v>
+        <v>440</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -7893,7 +7905,7 @@
         <v>669</v>
       </c>
       <c r="B669" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -7901,7 +7913,7 @@
         <v>670</v>
       </c>
       <c r="B670" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -7909,7 +7921,7 @@
         <v>671</v>
       </c>
       <c r="B671" s="1">
-        <v>400</v>
+        <v>780</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -7917,7 +7929,7 @@
         <v>672</v>
       </c>
       <c r="B672" s="1">
-        <v>380</v>
+        <v>760</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -7925,7 +7937,7 @@
         <v>673</v>
       </c>
       <c r="B673" s="1">
-        <v>380</v>
+        <v>760</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -7933,7 +7945,7 @@
         <v>674</v>
       </c>
       <c r="B674" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -7941,7 +7953,7 @@
         <v>675</v>
       </c>
       <c r="B675" s="1">
-        <v>520</v>
+        <v>400</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -7949,7 +7961,7 @@
         <v>676</v>
       </c>
       <c r="B676" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -7957,7 +7969,7 @@
         <v>677</v>
       </c>
       <c r="B677" s="1">
-        <v>860</v>
+        <v>380</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -7965,7 +7977,7 @@
         <v>678</v>
       </c>
       <c r="B678" s="1">
-        <v>680</v>
+        <v>380</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -7973,7 +7985,7 @@
         <v>679</v>
       </c>
       <c r="B679" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -7981,7 +7993,7 @@
         <v>680</v>
       </c>
       <c r="B680" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -7989,7 +8001,7 @@
         <v>681</v>
       </c>
       <c r="B681" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -7997,7 +8009,7 @@
         <v>682</v>
       </c>
       <c r="B682" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8005,7 +8017,7 @@
         <v>683</v>
       </c>
       <c r="B683" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8013,7 +8025,7 @@
         <v>684</v>
       </c>
       <c r="B684" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8021,7 +8033,7 @@
         <v>685</v>
       </c>
       <c r="B685" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8029,7 +8041,7 @@
         <v>686</v>
       </c>
       <c r="B686" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8037,7 +8049,7 @@
         <v>687</v>
       </c>
       <c r="B687" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8045,7 +8057,7 @@
         <v>688</v>
       </c>
       <c r="B688" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8053,7 +8065,7 @@
         <v>689</v>
       </c>
       <c r="B689" s="1">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8061,7 +8073,7 @@
         <v>690</v>
       </c>
       <c r="B690" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8069,7 +8081,7 @@
         <v>691</v>
       </c>
       <c r="B691" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8077,7 +8089,7 @@
         <v>692</v>
       </c>
       <c r="B692" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8085,7 +8097,7 @@
         <v>693</v>
       </c>
       <c r="B693" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8093,7 +8105,7 @@
         <v>694</v>
       </c>
       <c r="B694" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8109,7 +8121,7 @@
         <v>696</v>
       </c>
       <c r="B696" s="1">
-        <v>740</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8117,7 +8129,7 @@
         <v>697</v>
       </c>
       <c r="B697" s="1">
-        <v>440</v>
+        <v>940</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8125,7 +8137,7 @@
         <v>698</v>
       </c>
       <c r="B698" s="1">
-        <v>500</v>
+        <v>900</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8133,7 +8145,7 @@
         <v>699</v>
       </c>
       <c r="B699" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8141,7 +8153,7 @@
         <v>700</v>
       </c>
       <c r="B700" s="1">
-        <v>560</v>
+        <v>740</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8149,7 +8161,7 @@
         <v>701</v>
       </c>
       <c r="B701" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8157,7 +8169,7 @@
         <v>702</v>
       </c>
       <c r="B702" s="1">
-        <v>780</v>
+        <v>500</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8165,7 +8177,7 @@
         <v>703</v>
       </c>
       <c r="B703" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8173,7 +8185,7 @@
         <v>704</v>
       </c>
       <c r="B704" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8181,7 +8193,7 @@
         <v>705</v>
       </c>
       <c r="B705" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8189,7 +8201,7 @@
         <v>706</v>
       </c>
       <c r="B706" s="1">
-        <v>480</v>
+        <v>780</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8197,7 +8209,7 @@
         <v>707</v>
       </c>
       <c r="B707" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8205,7 +8217,7 @@
         <v>708</v>
       </c>
       <c r="B708" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8213,7 +8225,7 @@
         <v>709</v>
       </c>
       <c r="B709" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8221,7 +8233,7 @@
         <v>710</v>
       </c>
       <c r="B710" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8229,7 +8241,7 @@
         <v>711</v>
       </c>
       <c r="B711" s="1">
-        <v>440</v>
+        <v>480</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8237,7 +8249,7 @@
         <v>712</v>
       </c>
       <c r="B712" s="1">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8245,7 +8257,7 @@
         <v>713</v>
       </c>
       <c r="B713" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8253,7 +8265,7 @@
         <v>714</v>
       </c>
       <c r="B714" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8261,7 +8273,7 @@
         <v>715</v>
       </c>
       <c r="B715" s="1">
-        <v>760</v>
+        <v>440</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8269,7 +8281,7 @@
         <v>716</v>
       </c>
       <c r="B716" s="1">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8277,7 +8289,7 @@
         <v>717</v>
       </c>
       <c r="B717" s="1">
-        <v>580</v>
+        <v>380</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8285,7 +8297,7 @@
         <v>718</v>
       </c>
       <c r="B718" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8293,7 +8305,7 @@
         <v>719</v>
       </c>
       <c r="B719" s="1">
-        <v>580</v>
+        <v>760</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8301,7 +8313,7 @@
         <v>720</v>
       </c>
       <c r="B720" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8309,7 +8321,7 @@
         <v>721</v>
       </c>
       <c r="B721" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8317,6 +8329,38 @@
         <v>722</v>
       </c>
       <c r="B722" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2">
+      <c r="A723" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="B723" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2">
+      <c r="A724" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B724" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2">
+      <c r="A725" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="B725" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2">
+      <c r="A726" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B726" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="731">
   <si>
     <t>Наименование</t>
   </si>
@@ -302,6 +302,9 @@
     <t>Dieta  - В собственном соку: Вишня, РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Dieta  - Властелины Лапулина (DIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Dieta - Feei the Best! (NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -776,6 +779,9 @@
     <t>Saint Loony - NICE (Sour), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Saint Loony - Out Of Space (Sour), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Saint Loony - Strobe (Sour), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1436,6 +1442,9 @@
     <t>вынос_Dieta  - В собственном соку: Вишня, РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Dieta  - Властелины Лапулина (DIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Ganza - Белое солнце (NEDIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1656,6 +1665,9 @@
   </si>
   <si>
     <t>вынос_Saint Loony - NICE (Sour), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Saint Loony - Out Of Space (Sour), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Saint Loony - Strobe (Sour), РОЗЛИВ, Россия</t>
@@ -2549,7 +2561,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B726"/>
+  <dimension ref="A1:B730"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -2753,7 +2765,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3313,7 +3325,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>660</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3321,7 +3333,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>480</v>
+        <v>660</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3329,7 +3341,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>400</v>
+        <v>480</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3337,7 +3349,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>720</v>
+        <v>400</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3345,7 +3357,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3353,7 +3365,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>500</v>
+        <v>560</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3361,7 +3373,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3369,7 +3381,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>500</v>
+        <v>760</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3377,7 +3389,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>920</v>
+        <v>500</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3385,7 +3397,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3393,7 +3405,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>420</v>
+        <v>600</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3401,7 +3413,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3409,7 +3421,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -3417,7 +3429,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3425,7 +3437,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3433,7 +3445,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3441,7 +3453,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>580</v>
+        <v>740</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3449,7 +3461,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3457,7 +3469,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3465,7 +3477,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3473,7 +3485,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3481,7 +3493,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3489,7 +3501,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3497,7 +3509,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3505,7 +3517,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3513,7 +3525,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3521,7 +3533,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>500</v>
+        <v>780</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3529,7 +3541,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>580</v>
+        <v>500</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -3537,7 +3549,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -3545,7 +3557,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -3553,7 +3565,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>1100</v>
+        <v>520</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -3561,7 +3573,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -3569,7 +3581,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>420</v>
+        <v>560</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -3577,7 +3589,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>520</v>
+        <v>420</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -3585,7 +3597,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -3593,7 +3605,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>460</v>
+        <v>720</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -3601,7 +3613,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>560</v>
+        <v>460</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -3609,7 +3621,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -3617,7 +3629,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -3625,7 +3637,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -3633,7 +3645,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -3641,7 +3653,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>980</v>
+        <v>520</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -3649,7 +3661,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>540</v>
+        <v>980</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -3657,7 +3669,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -3665,7 +3677,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -3673,7 +3685,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -3681,7 +3693,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>560</v>
+        <v>760</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -3689,7 +3701,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -3713,7 +3725,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -3721,7 +3733,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -3729,7 +3741,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3737,7 +3749,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -3761,7 +3773,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3769,7 +3781,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3777,7 +3789,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3785,7 +3797,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -3793,7 +3805,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -3801,7 +3813,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>460</v>
+        <v>700</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -3809,7 +3821,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -3817,7 +3829,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -3825,7 +3837,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -3833,7 +3845,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -3841,7 +3853,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -3857,7 +3869,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -3873,7 +3885,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -3881,7 +3893,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -3889,7 +3901,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -3897,7 +3909,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -3905,7 +3917,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -3913,7 +3925,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>740</v>
+        <v>400</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -3921,7 +3933,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -3929,7 +3941,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -3937,7 +3949,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -3945,7 +3957,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -3953,7 +3965,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -3961,7 +3973,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -3977,7 +3989,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -3985,7 +3997,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -3993,7 +4005,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4009,7 +4021,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4017,7 +4029,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4025,7 +4037,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4033,7 +4045,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4041,7 +4053,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4049,7 +4061,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4057,7 +4069,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4065,7 +4077,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4073,7 +4085,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4081,7 +4093,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4089,7 +4101,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4097,7 +4109,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4105,7 +4117,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>480</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4113,7 +4125,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4121,7 +4133,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4129,7 +4141,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4137,7 +4149,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4145,7 +4157,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4153,7 +4165,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4161,7 +4173,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4169,7 +4181,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4177,7 +4189,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4185,7 +4197,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4193,7 +4205,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4201,7 +4213,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4217,7 +4229,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4233,7 +4245,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4241,7 +4253,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4249,7 +4261,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4257,7 +4269,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4273,7 +4285,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4281,7 +4293,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4297,7 +4309,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4305,7 +4317,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4313,7 +4325,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4321,7 +4333,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4337,7 +4349,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4345,7 +4357,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4353,7 +4365,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>758</v>
+        <v>500</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4361,7 +4373,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>2273</v>
+        <v>758</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4369,7 +4381,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>1515</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4377,7 +4389,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>520</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4385,7 +4397,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4393,7 +4405,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4401,7 +4413,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4409,7 +4421,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4425,7 +4437,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4433,7 +4445,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4441,7 +4453,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4449,7 +4461,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4457,7 +4469,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4465,7 +4477,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4473,7 +4485,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4481,7 +4493,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4489,7 +4501,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4497,7 +4509,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4505,7 +4517,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4513,7 +4525,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4521,7 +4533,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4529,7 +4541,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4537,7 +4549,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>460</v>
+        <v>580</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4545,7 +4557,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4553,7 +4565,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4561,7 +4573,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4569,7 +4581,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4585,7 +4597,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4593,7 +4605,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -4601,7 +4613,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>1000</v>
+        <v>560</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4609,7 +4621,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4617,7 +4629,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4625,7 +4637,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4633,7 +4645,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4641,7 +4653,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>840</v>
+        <v>680</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4657,7 +4669,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>1020</v>
+        <v>840</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4673,7 +4685,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>680</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4681,7 +4693,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>520</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4689,7 +4701,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4697,7 +4709,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4705,7 +4717,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4713,7 +4725,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4721,7 +4733,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4729,7 +4741,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4737,7 +4749,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4745,7 +4757,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4753,7 +4765,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4769,7 +4781,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>880</v>
+        <v>640</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4777,7 +4789,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>520</v>
+        <v>720</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4785,7 +4797,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4793,7 +4805,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4801,7 +4813,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4817,7 +4829,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4825,7 +4837,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>520</v>
+        <v>600</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4833,7 +4845,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>320</v>
+        <v>380</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4841,7 +4853,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4849,7 +4861,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>560</v>
+        <v>320</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4857,7 +4869,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>480</v>
+        <v>540</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4865,7 +4877,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4873,7 +4885,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -4881,7 +4893,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>500</v>
+        <v>480</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -4889,7 +4901,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -4897,7 +4909,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -4905,7 +4917,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -4913,7 +4925,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -4921,7 +4933,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>380</v>
+        <v>780</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -4929,7 +4941,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -4937,7 +4949,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>900</v>
+        <v>380</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -4945,7 +4957,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -4953,7 +4965,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -4961,7 +4973,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -4969,7 +4981,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>1020</v>
+        <v>720</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -4977,7 +4989,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -4985,7 +4997,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>700</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -4993,7 +5005,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5001,7 +5013,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5009,7 +5021,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5025,7 +5037,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5033,7 +5045,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5041,7 +5053,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5049,7 +5061,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5057,7 +5069,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5065,7 +5077,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5081,7 +5093,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5089,7 +5101,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5097,7 +5109,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5105,7 +5117,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>480</v>
+        <v>740</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5113,7 +5125,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5121,7 +5133,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>1000</v>
+        <v>480</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5129,7 +5141,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>920</v>
+        <v>640</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5137,7 +5149,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5145,7 +5157,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>520</v>
+        <v>920</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5153,7 +5165,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>540</v>
+        <v>860</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5161,7 +5173,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>700</v>
+        <v>520</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5169,7 +5181,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5177,7 +5189,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5193,7 +5205,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>720</v>
+        <v>420</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5201,7 +5213,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5209,7 +5221,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5217,7 +5229,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5225,7 +5237,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5233,7 +5245,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5241,7 +5253,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5249,7 +5261,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5257,7 +5269,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>440</v>
+        <v>720</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5265,7 +5277,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>320</v>
+        <v>620</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5273,7 +5285,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>320</v>
+        <v>440</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5281,7 +5293,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>820</v>
+        <v>320</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5289,7 +5301,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>1000</v>
+        <v>320</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5297,7 +5309,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5305,7 +5317,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5313,7 +5325,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5329,7 +5341,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5337,7 +5349,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5345,7 +5357,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5353,7 +5365,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>1000</v>
+        <v>620</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5361,7 +5373,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5369,7 +5381,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5385,7 +5397,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5393,7 +5405,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5401,7 +5413,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5409,7 +5421,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5417,7 +5429,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5425,7 +5437,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5433,7 +5445,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>440</v>
+        <v>680</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5441,7 +5453,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5449,7 +5461,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5457,7 +5469,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5465,7 +5477,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5473,7 +5485,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5481,7 +5493,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5489,7 +5501,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5497,7 +5509,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5505,7 +5517,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5513,7 +5525,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5521,7 +5533,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>680</v>
+        <v>620</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5529,7 +5541,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>480</v>
+        <v>720</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5537,7 +5549,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5545,7 +5557,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5553,7 +5565,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5561,7 +5573,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5569,7 +5581,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5577,7 +5589,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5585,7 +5597,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5593,7 +5605,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5601,7 +5613,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5609,7 +5621,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5617,7 +5629,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="1">
-        <v>600</v>
+        <v>980</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5625,7 +5637,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="1">
-        <v>760</v>
+        <v>920</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5633,7 +5645,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5641,7 +5653,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>620</v>
+        <v>760</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5649,7 +5661,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5657,7 +5669,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5665,7 +5677,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5673,7 +5685,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>640</v>
+        <v>860</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5681,7 +5693,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5689,7 +5701,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>820</v>
+        <v>640</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5697,7 +5709,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5705,7 +5717,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5713,7 +5725,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5721,7 +5733,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5729,7 +5741,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5737,7 +5749,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5745,7 +5757,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5753,7 +5765,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5761,7 +5773,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5769,7 +5781,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5777,7 +5789,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>840</v>
+        <v>640</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5785,7 +5797,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5793,7 +5805,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>480</v>
+        <v>840</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5801,7 +5813,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5809,7 +5821,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>780</v>
+        <v>480</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5817,7 +5829,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5825,7 +5837,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5833,7 +5845,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5841,7 +5853,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5849,7 +5861,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5857,7 +5869,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5865,7 +5877,7 @@
         <v>414</v>
       </c>
       <c r="B414" s="1">
-        <v>480</v>
+        <v>780</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5873,7 +5885,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5881,7 +5893,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>660</v>
+        <v>480</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5889,7 +5901,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5897,7 +5909,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5905,7 +5917,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5913,7 +5925,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5921,7 +5933,7 @@
         <v>421</v>
       </c>
       <c r="B421" s="1">
-        <v>880</v>
+        <v>440</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -5929,7 +5941,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -5937,7 +5949,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -5945,7 +5957,7 @@
         <v>424</v>
       </c>
       <c r="B424" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -5953,7 +5965,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -5961,7 +5973,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -5969,7 +5981,7 @@
         <v>427</v>
       </c>
       <c r="B427" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -5977,7 +5989,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -5985,7 +5997,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -5993,7 +6005,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6001,7 +6013,7 @@
         <v>431</v>
       </c>
       <c r="B431" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6009,7 +6021,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6017,7 +6029,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6025,7 +6037,7 @@
         <v>434</v>
       </c>
       <c r="B434" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6033,7 +6045,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6049,7 +6061,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6057,7 +6069,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6065,7 +6077,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6073,7 +6085,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6081,7 +6093,7 @@
         <v>441</v>
       </c>
       <c r="B441" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6089,7 +6101,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6097,7 +6109,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6105,7 +6117,7 @@
         <v>444</v>
       </c>
       <c r="B444" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6113,7 +6125,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6121,7 +6133,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6129,7 +6141,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6137,7 +6149,7 @@
         <v>448</v>
       </c>
       <c r="B448" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6145,7 +6157,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6153,7 +6165,7 @@
         <v>450</v>
       </c>
       <c r="B450" s="1">
-        <v>790</v>
+        <v>720</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6161,7 +6173,7 @@
         <v>451</v>
       </c>
       <c r="B451" s="1">
-        <v>640</v>
+        <v>900</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6169,7 +6181,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>800</v>
+        <v>790</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6177,7 +6189,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6185,7 +6197,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6193,7 +6205,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6201,7 +6213,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6209,7 +6221,7 @@
         <v>457</v>
       </c>
       <c r="B457" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6233,7 +6245,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>920</v>
+        <v>820</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6241,7 +6253,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6249,7 +6261,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6257,7 +6269,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>640</v>
+        <v>600</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6265,7 +6277,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>700</v>
+        <v>880</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6273,7 +6285,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6281,7 +6293,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6289,7 +6301,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6297,7 +6309,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6305,7 +6317,7 @@
         <v>469</v>
       </c>
       <c r="B469" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6313,7 +6325,7 @@
         <v>470</v>
       </c>
       <c r="B470" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6321,7 +6333,7 @@
         <v>471</v>
       </c>
       <c r="B471" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6329,7 +6341,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6337,7 +6349,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6345,7 +6357,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>600</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6353,7 +6365,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>580</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6361,7 +6373,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6369,7 +6381,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6377,7 +6389,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6385,7 +6397,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6393,7 +6405,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>700</v>
+        <v>620</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6401,7 +6413,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6409,7 +6421,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6417,7 +6429,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6425,7 +6437,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6433,7 +6445,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>540</v>
+        <v>600</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6441,7 +6453,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6449,7 +6461,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6457,7 +6469,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6465,7 +6477,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>740</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6473,7 +6485,7 @@
         <v>490</v>
       </c>
       <c r="B490" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6481,7 +6493,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6489,7 +6501,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6497,7 +6509,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>740</v>
+        <v>620</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6505,7 +6517,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6513,7 +6525,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>1100</v>
+        <v>980</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6521,7 +6533,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6529,7 +6541,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6537,7 +6549,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6545,7 +6557,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6553,7 +6565,7 @@
         <v>500</v>
       </c>
       <c r="B500" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6561,7 +6573,7 @@
         <v>501</v>
       </c>
       <c r="B501" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6569,7 +6581,7 @@
         <v>502</v>
       </c>
       <c r="B502" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6577,7 +6589,7 @@
         <v>503</v>
       </c>
       <c r="B503" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6585,7 +6597,7 @@
         <v>504</v>
       </c>
       <c r="B504" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6593,7 +6605,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6601,7 +6613,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6617,7 +6629,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6625,7 +6637,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6641,7 +6653,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6649,7 +6661,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6657,7 +6669,7 @@
         <v>513</v>
       </c>
       <c r="B513" s="1">
-        <v>820</v>
+        <v>720</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6665,7 +6677,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6673,7 +6685,7 @@
         <v>515</v>
       </c>
       <c r="B515" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6681,7 +6693,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>1400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6689,7 +6701,7 @@
         <v>517</v>
       </c>
       <c r="B517" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6697,7 +6709,7 @@
         <v>518</v>
       </c>
       <c r="B518" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6705,7 +6717,7 @@
         <v>519</v>
       </c>
       <c r="B519" s="1">
-        <v>700</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6713,7 +6725,7 @@
         <v>520</v>
       </c>
       <c r="B520" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6721,7 +6733,7 @@
         <v>521</v>
       </c>
       <c r="B521" s="1">
-        <v>720</v>
+        <v>660</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6729,7 +6741,7 @@
         <v>522</v>
       </c>
       <c r="B522" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -6737,7 +6749,7 @@
         <v>523</v>
       </c>
       <c r="B523" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6745,7 +6757,7 @@
         <v>524</v>
       </c>
       <c r="B524" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6753,7 +6765,7 @@
         <v>525</v>
       </c>
       <c r="B525" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6761,7 +6773,7 @@
         <v>526</v>
       </c>
       <c r="B526" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6769,7 +6781,7 @@
         <v>527</v>
       </c>
       <c r="B527" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6777,7 +6789,7 @@
         <v>528</v>
       </c>
       <c r="B528" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6785,7 +6797,7 @@
         <v>529</v>
       </c>
       <c r="B529" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6793,7 +6805,7 @@
         <v>530</v>
       </c>
       <c r="B530" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6809,7 +6821,7 @@
         <v>532</v>
       </c>
       <c r="B532" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6817,7 +6829,7 @@
         <v>533</v>
       </c>
       <c r="B533" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6825,7 +6837,7 @@
         <v>534</v>
       </c>
       <c r="B534" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6833,7 +6845,7 @@
         <v>535</v>
       </c>
       <c r="B535" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -6841,7 +6853,7 @@
         <v>536</v>
       </c>
       <c r="B536" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -6849,7 +6861,7 @@
         <v>537</v>
       </c>
       <c r="B537" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -6857,7 +6869,7 @@
         <v>538</v>
       </c>
       <c r="B538" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -6865,7 +6877,7 @@
         <v>539</v>
       </c>
       <c r="B539" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -6873,7 +6885,7 @@
         <v>540</v>
       </c>
       <c r="B540" s="1">
-        <v>640</v>
+        <v>600</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -6881,7 +6893,7 @@
         <v>541</v>
       </c>
       <c r="B541" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -6889,7 +6901,7 @@
         <v>542</v>
       </c>
       <c r="B542" s="1">
-        <v>540</v>
+        <v>680</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -6897,7 +6909,7 @@
         <v>543</v>
       </c>
       <c r="B543" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -6905,7 +6917,7 @@
         <v>544</v>
       </c>
       <c r="B544" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -6913,7 +6925,7 @@
         <v>545</v>
       </c>
       <c r="B545" s="1">
-        <v>860</v>
+        <v>540</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -6921,7 +6933,7 @@
         <v>546</v>
       </c>
       <c r="B546" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -6929,7 +6941,7 @@
         <v>547</v>
       </c>
       <c r="B547" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -6937,7 +6949,7 @@
         <v>548</v>
       </c>
       <c r="B548" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -6953,7 +6965,7 @@
         <v>550</v>
       </c>
       <c r="B550" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -6961,7 +6973,7 @@
         <v>551</v>
       </c>
       <c r="B551" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -6977,7 +6989,7 @@
         <v>553</v>
       </c>
       <c r="B553" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -6985,7 +6997,7 @@
         <v>554</v>
       </c>
       <c r="B554" s="1">
-        <v>1020</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -6993,7 +7005,7 @@
         <v>555</v>
       </c>
       <c r="B555" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7001,7 +7013,7 @@
         <v>556</v>
       </c>
       <c r="B556" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7009,7 +7021,7 @@
         <v>557</v>
       </c>
       <c r="B557" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7017,7 +7029,7 @@
         <v>558</v>
       </c>
       <c r="B558" s="1">
-        <v>640</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7025,7 +7037,7 @@
         <v>559</v>
       </c>
       <c r="B559" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7033,7 +7045,7 @@
         <v>560</v>
       </c>
       <c r="B560" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7041,7 +7053,7 @@
         <v>561</v>
       </c>
       <c r="B561" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7049,7 +7061,7 @@
         <v>562</v>
       </c>
       <c r="B562" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7057,7 +7069,7 @@
         <v>563</v>
       </c>
       <c r="B563" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7065,7 +7077,7 @@
         <v>564</v>
       </c>
       <c r="B564" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7073,7 +7085,7 @@
         <v>565</v>
       </c>
       <c r="B565" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7081,7 +7093,7 @@
         <v>566</v>
       </c>
       <c r="B566" s="1">
-        <v>820</v>
+        <v>720</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7089,7 +7101,7 @@
         <v>567</v>
       </c>
       <c r="B567" s="1">
-        <v>600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7097,7 +7109,7 @@
         <v>568</v>
       </c>
       <c r="B568" s="1">
-        <v>800</v>
+        <v>740</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7105,7 +7117,7 @@
         <v>569</v>
       </c>
       <c r="B569" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7113,7 +7125,7 @@
         <v>570</v>
       </c>
       <c r="B570" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7121,7 +7133,7 @@
         <v>571</v>
       </c>
       <c r="B571" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7129,7 +7141,7 @@
         <v>572</v>
       </c>
       <c r="B572" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7137,7 +7149,7 @@
         <v>573</v>
       </c>
       <c r="B573" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7145,7 +7157,7 @@
         <v>574</v>
       </c>
       <c r="B574" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7153,7 +7165,7 @@
         <v>575</v>
       </c>
       <c r="B575" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7161,7 +7173,7 @@
         <v>576</v>
       </c>
       <c r="B576" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7169,7 +7181,7 @@
         <v>577</v>
       </c>
       <c r="B577" s="1">
-        <v>640</v>
+        <v>960</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7177,7 +7189,7 @@
         <v>578</v>
       </c>
       <c r="B578" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7185,7 +7197,7 @@
         <v>579</v>
       </c>
       <c r="B579" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7193,7 +7205,7 @@
         <v>580</v>
       </c>
       <c r="B580" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7201,7 +7213,7 @@
         <v>581</v>
       </c>
       <c r="B581" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7209,7 +7221,7 @@
         <v>582</v>
       </c>
       <c r="B582" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7217,7 +7229,7 @@
         <v>583</v>
       </c>
       <c r="B583" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7225,7 +7237,7 @@
         <v>584</v>
       </c>
       <c r="B584" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7233,7 +7245,7 @@
         <v>585</v>
       </c>
       <c r="B585" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7241,7 +7253,7 @@
         <v>586</v>
       </c>
       <c r="B586" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7249,7 +7261,7 @@
         <v>587</v>
       </c>
       <c r="B587" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7257,7 +7269,7 @@
         <v>588</v>
       </c>
       <c r="B588" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7273,7 +7285,7 @@
         <v>590</v>
       </c>
       <c r="B590" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7281,7 +7293,7 @@
         <v>591</v>
       </c>
       <c r="B591" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7289,7 +7301,7 @@
         <v>592</v>
       </c>
       <c r="B592" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7297,7 +7309,7 @@
         <v>593</v>
       </c>
       <c r="B593" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7305,7 +7317,7 @@
         <v>594</v>
       </c>
       <c r="B594" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7313,7 +7325,7 @@
         <v>595</v>
       </c>
       <c r="B595" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7321,7 +7333,7 @@
         <v>596</v>
       </c>
       <c r="B596" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7329,7 +7341,7 @@
         <v>597</v>
       </c>
       <c r="B597" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7337,7 +7349,7 @@
         <v>598</v>
       </c>
       <c r="B598" s="1">
-        <v>820</v>
+        <v>900</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7345,7 +7357,7 @@
         <v>599</v>
       </c>
       <c r="B599" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7353,7 +7365,7 @@
         <v>600</v>
       </c>
       <c r="B600" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7361,7 +7373,7 @@
         <v>601</v>
       </c>
       <c r="B601" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7369,7 +7381,7 @@
         <v>602</v>
       </c>
       <c r="B602" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7377,7 +7389,7 @@
         <v>603</v>
       </c>
       <c r="B603" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7385,7 +7397,7 @@
         <v>604</v>
       </c>
       <c r="B604" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7393,7 +7405,7 @@
         <v>605</v>
       </c>
       <c r="B605" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7401,7 +7413,7 @@
         <v>606</v>
       </c>
       <c r="B606" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7409,7 +7421,7 @@
         <v>607</v>
       </c>
       <c r="B607" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7417,7 +7429,7 @@
         <v>608</v>
       </c>
       <c r="B608" s="1">
-        <v>660</v>
+        <v>880</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7425,7 +7437,7 @@
         <v>609</v>
       </c>
       <c r="B609" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7433,7 +7445,7 @@
         <v>610</v>
       </c>
       <c r="B610" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7441,7 +7453,7 @@
         <v>611</v>
       </c>
       <c r="B611" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7449,7 +7461,7 @@
         <v>612</v>
       </c>
       <c r="B612" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7465,7 +7477,7 @@
         <v>614</v>
       </c>
       <c r="B614" s="1">
-        <v>800</v>
+        <v>680</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7473,7 +7485,7 @@
         <v>615</v>
       </c>
       <c r="B615" s="1">
-        <v>720</v>
+        <v>660</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7481,7 +7493,7 @@
         <v>616</v>
       </c>
       <c r="B616" s="1">
-        <v>600</v>
+        <v>440</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -7489,7 +7501,7 @@
         <v>617</v>
       </c>
       <c r="B617" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -7497,7 +7509,7 @@
         <v>618</v>
       </c>
       <c r="B618" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -7505,7 +7517,7 @@
         <v>619</v>
       </c>
       <c r="B619" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7513,7 +7525,7 @@
         <v>620</v>
       </c>
       <c r="B620" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7521,7 +7533,7 @@
         <v>621</v>
       </c>
       <c r="B621" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -7529,7 +7541,7 @@
         <v>622</v>
       </c>
       <c r="B622" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -7537,7 +7549,7 @@
         <v>623</v>
       </c>
       <c r="B623" s="1">
-        <v>940</v>
+        <v>800</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -7545,7 +7557,7 @@
         <v>624</v>
       </c>
       <c r="B624" s="1">
-        <v>980</v>
+        <v>780</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -7561,7 +7573,7 @@
         <v>626</v>
       </c>
       <c r="B626" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -7569,7 +7581,7 @@
         <v>627</v>
       </c>
       <c r="B627" s="1">
-        <v>860</v>
+        <v>940</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -7577,7 +7589,7 @@
         <v>628</v>
       </c>
       <c r="B628" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -7585,7 +7597,7 @@
         <v>629</v>
       </c>
       <c r="B629" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -7593,7 +7605,7 @@
         <v>630</v>
       </c>
       <c r="B630" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -7601,7 +7613,7 @@
         <v>631</v>
       </c>
       <c r="B631" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -7609,7 +7621,7 @@
         <v>632</v>
       </c>
       <c r="B632" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -7617,7 +7629,7 @@
         <v>633</v>
       </c>
       <c r="B633" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -7625,7 +7637,7 @@
         <v>634</v>
       </c>
       <c r="B634" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -7633,7 +7645,7 @@
         <v>635</v>
       </c>
       <c r="B635" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -7641,7 +7653,7 @@
         <v>636</v>
       </c>
       <c r="B636" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -7649,7 +7661,7 @@
         <v>637</v>
       </c>
       <c r="B637" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -7657,7 +7669,7 @@
         <v>638</v>
       </c>
       <c r="B638" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -7665,7 +7677,7 @@
         <v>639</v>
       </c>
       <c r="B639" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -7673,7 +7685,7 @@
         <v>640</v>
       </c>
       <c r="B640" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -7681,7 +7693,7 @@
         <v>641</v>
       </c>
       <c r="B641" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -7697,7 +7709,7 @@
         <v>643</v>
       </c>
       <c r="B643" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -7705,7 +7717,7 @@
         <v>644</v>
       </c>
       <c r="B644" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -7713,7 +7725,7 @@
         <v>645</v>
       </c>
       <c r="B645" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -7721,7 +7733,7 @@
         <v>646</v>
       </c>
       <c r="B646" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -7729,7 +7741,7 @@
         <v>647</v>
       </c>
       <c r="B647" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -7737,7 +7749,7 @@
         <v>648</v>
       </c>
       <c r="B648" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -7745,7 +7757,7 @@
         <v>649</v>
       </c>
       <c r="B649" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -7753,7 +7765,7 @@
         <v>650</v>
       </c>
       <c r="B650" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -7761,7 +7773,7 @@
         <v>651</v>
       </c>
       <c r="B651" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -7769,7 +7781,7 @@
         <v>652</v>
       </c>
       <c r="B652" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -7777,7 +7789,7 @@
         <v>653</v>
       </c>
       <c r="B653" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -7785,7 +7797,7 @@
         <v>654</v>
       </c>
       <c r="B654" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -7793,7 +7805,7 @@
         <v>655</v>
       </c>
       <c r="B655" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -7801,7 +7813,7 @@
         <v>656</v>
       </c>
       <c r="B656" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -7809,7 +7821,7 @@
         <v>657</v>
       </c>
       <c r="B657" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -7817,7 +7829,7 @@
         <v>658</v>
       </c>
       <c r="B658" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -7825,7 +7837,7 @@
         <v>659</v>
       </c>
       <c r="B659" s="1">
-        <v>920</v>
+        <v>600</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -7833,7 +7845,7 @@
         <v>660</v>
       </c>
       <c r="B660" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -7841,7 +7853,7 @@
         <v>661</v>
       </c>
       <c r="B661" s="1">
-        <v>1040</v>
+        <v>500</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -7849,7 +7861,7 @@
         <v>662</v>
       </c>
       <c r="B662" s="1">
-        <v>940</v>
+        <v>760</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -7857,7 +7869,7 @@
         <v>663</v>
       </c>
       <c r="B663" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -7873,7 +7885,7 @@
         <v>665</v>
       </c>
       <c r="B665" s="1">
-        <v>740</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -7881,7 +7893,7 @@
         <v>666</v>
       </c>
       <c r="B666" s="1">
-        <v>440</v>
+        <v>940</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -7889,7 +7901,7 @@
         <v>667</v>
       </c>
       <c r="B667" s="1">
-        <v>500</v>
+        <v>900</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -7897,7 +7909,7 @@
         <v>668</v>
       </c>
       <c r="B668" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -7905,7 +7917,7 @@
         <v>669</v>
       </c>
       <c r="B669" s="1">
-        <v>560</v>
+        <v>740</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -7913,7 +7925,7 @@
         <v>670</v>
       </c>
       <c r="B670" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -7921,7 +7933,7 @@
         <v>671</v>
       </c>
       <c r="B671" s="1">
-        <v>780</v>
+        <v>500</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -7929,7 +7941,7 @@
         <v>672</v>
       </c>
       <c r="B672" s="1">
-        <v>760</v>
+        <v>440</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -7937,7 +7949,7 @@
         <v>673</v>
       </c>
       <c r="B673" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -7945,7 +7957,7 @@
         <v>674</v>
       </c>
       <c r="B674" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -7953,7 +7965,7 @@
         <v>675</v>
       </c>
       <c r="B675" s="1">
-        <v>400</v>
+        <v>780</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -7961,7 +7973,7 @@
         <v>676</v>
       </c>
       <c r="B676" s="1">
-        <v>380</v>
+        <v>760</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -7969,7 +7981,7 @@
         <v>677</v>
       </c>
       <c r="B677" s="1">
-        <v>380</v>
+        <v>760</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -7977,7 +7989,7 @@
         <v>678</v>
       </c>
       <c r="B678" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -7985,7 +7997,7 @@
         <v>679</v>
       </c>
       <c r="B679" s="1">
-        <v>520</v>
+        <v>400</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -7993,7 +8005,7 @@
         <v>680</v>
       </c>
       <c r="B680" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8001,7 +8013,7 @@
         <v>681</v>
       </c>
       <c r="B681" s="1">
-        <v>860</v>
+        <v>380</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8009,7 +8021,7 @@
         <v>682</v>
       </c>
       <c r="B682" s="1">
-        <v>680</v>
+        <v>380</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8017,7 +8029,7 @@
         <v>683</v>
       </c>
       <c r="B683" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8025,7 +8037,7 @@
         <v>684</v>
       </c>
       <c r="B684" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8033,7 +8045,7 @@
         <v>685</v>
       </c>
       <c r="B685" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8041,7 +8053,7 @@
         <v>686</v>
       </c>
       <c r="B686" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8049,7 +8061,7 @@
         <v>687</v>
       </c>
       <c r="B687" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8057,7 +8069,7 @@
         <v>688</v>
       </c>
       <c r="B688" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8065,7 +8077,7 @@
         <v>689</v>
       </c>
       <c r="B689" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8073,7 +8085,7 @@
         <v>690</v>
       </c>
       <c r="B690" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8081,7 +8093,7 @@
         <v>691</v>
       </c>
       <c r="B691" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8089,7 +8101,7 @@
         <v>692</v>
       </c>
       <c r="B692" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8097,7 +8109,7 @@
         <v>693</v>
       </c>
       <c r="B693" s="1">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8105,7 +8117,7 @@
         <v>694</v>
       </c>
       <c r="B694" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8113,7 +8125,7 @@
         <v>695</v>
       </c>
       <c r="B695" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8121,7 +8133,7 @@
         <v>696</v>
       </c>
       <c r="B696" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8129,7 +8141,7 @@
         <v>697</v>
       </c>
       <c r="B697" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8137,7 +8149,7 @@
         <v>698</v>
       </c>
       <c r="B698" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8153,7 +8165,7 @@
         <v>700</v>
       </c>
       <c r="B700" s="1">
-        <v>740</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8161,7 +8173,7 @@
         <v>701</v>
       </c>
       <c r="B701" s="1">
-        <v>440</v>
+        <v>940</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8169,7 +8181,7 @@
         <v>702</v>
       </c>
       <c r="B702" s="1">
-        <v>500</v>
+        <v>900</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8177,7 +8189,7 @@
         <v>703</v>
       </c>
       <c r="B703" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8185,7 +8197,7 @@
         <v>704</v>
       </c>
       <c r="B704" s="1">
-        <v>560</v>
+        <v>740</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8193,7 +8205,7 @@
         <v>705</v>
       </c>
       <c r="B705" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8201,7 +8213,7 @@
         <v>706</v>
       </c>
       <c r="B706" s="1">
-        <v>780</v>
+        <v>500</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8209,7 +8221,7 @@
         <v>707</v>
       </c>
       <c r="B707" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8217,7 +8229,7 @@
         <v>708</v>
       </c>
       <c r="B708" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8225,7 +8237,7 @@
         <v>709</v>
       </c>
       <c r="B709" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8233,7 +8245,7 @@
         <v>710</v>
       </c>
       <c r="B710" s="1">
-        <v>480</v>
+        <v>780</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8241,7 +8253,7 @@
         <v>711</v>
       </c>
       <c r="B711" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8249,7 +8261,7 @@
         <v>712</v>
       </c>
       <c r="B712" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8257,7 +8269,7 @@
         <v>713</v>
       </c>
       <c r="B713" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8265,7 +8277,7 @@
         <v>714</v>
       </c>
       <c r="B714" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8273,7 +8285,7 @@
         <v>715</v>
       </c>
       <c r="B715" s="1">
-        <v>440</v>
+        <v>480</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8281,7 +8293,7 @@
         <v>716</v>
       </c>
       <c r="B716" s="1">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8289,7 +8301,7 @@
         <v>717</v>
       </c>
       <c r="B717" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8297,7 +8309,7 @@
         <v>718</v>
       </c>
       <c r="B718" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8305,7 +8317,7 @@
         <v>719</v>
       </c>
       <c r="B719" s="1">
-        <v>760</v>
+        <v>440</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8313,7 +8325,7 @@
         <v>720</v>
       </c>
       <c r="B720" s="1">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8321,7 +8333,7 @@
         <v>721</v>
       </c>
       <c r="B721" s="1">
-        <v>580</v>
+        <v>380</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8329,7 +8341,7 @@
         <v>722</v>
       </c>
       <c r="B722" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8337,7 +8349,7 @@
         <v>723</v>
       </c>
       <c r="B723" s="1">
-        <v>580</v>
+        <v>760</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8345,7 +8357,7 @@
         <v>724</v>
       </c>
       <c r="B724" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8353,7 +8365,7 @@
         <v>725</v>
       </c>
       <c r="B725" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8361,6 +8373,38 @@
         <v>726</v>
       </c>
       <c r="B726" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2">
+      <c r="A727" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B727" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2">
+      <c r="A728" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="B728" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2">
+      <c r="A729" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B729" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2">
+      <c r="A730" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="B730" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -2797,7 +2797,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2805,7 +2805,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3405,7 +3405,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -4285,7 +4285,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4317,7 +4317,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -5093,7 +5093,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5413,7 +5413,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -6045,7 +6045,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6053,7 +6053,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6381,7 +6381,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6797,7 +6797,7 @@
         <v>529</v>
       </c>
       <c r="B529" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6829,7 +6829,7 @@
         <v>533</v>
       </c>
       <c r="B533" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -7285,7 +7285,7 @@
         <v>590</v>
       </c>
       <c r="B590" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7445,7 +7445,7 @@
         <v>610</v>
       </c>
       <c r="B610" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7965,7 +7965,7 @@
         <v>675</v>
       </c>
       <c r="B675" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8245,7 +8245,7 @@
         <v>710</v>
       </c>
       <c r="B710" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="711" spans="1:2">

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -3053,7 +3053,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -4445,7 +4445,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -6885,7 +6885,7 @@
         <v>540</v>
       </c>
       <c r="B540" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -8357,7 +8357,7 @@
         <v>724</v>
       </c>
       <c r="B724" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="725" spans="1:2">

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="733">
   <si>
     <t>Наименование</t>
   </si>
@@ -1073,6 +1073,9 @@
     <t>White Stone  - The Great Eight (DIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>White Stone  - Верный Путь (IPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>White Stone  - Экземпляр 2 (NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1833,6 +1836,9 @@
   </si>
   <si>
     <t>вынос_White Stone  - The Great Eight (DIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_White Stone  - Верный Путь (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_White Stone  - Экземпляр 2 (NEIPA), РОЗЛИВ, Россия</t>
@@ -2561,7 +2567,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B730"/>
+  <dimension ref="A1:B732"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -5381,7 +5387,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5389,7 +5395,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5397,7 +5403,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5405,7 +5411,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5421,7 +5427,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5429,7 +5435,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5437,7 +5443,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5445,7 +5451,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5453,7 +5459,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5461,7 +5467,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5469,7 +5475,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5477,7 +5483,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5485,7 +5491,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5493,7 +5499,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5501,7 +5507,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5509,7 +5515,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5517,7 +5523,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5525,7 +5531,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5533,7 +5539,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5541,7 +5547,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5549,7 +5555,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5557,7 +5563,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5573,7 +5579,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5581,7 +5587,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5589,7 +5595,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5597,7 +5603,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5605,7 +5611,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5621,7 +5627,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5629,7 +5635,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="1">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5637,7 +5643,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5645,7 +5651,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5653,7 +5659,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5661,7 +5667,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5669,7 +5675,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5685,7 +5691,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5693,7 +5699,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5701,7 +5707,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>640</v>
+        <v>920</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5709,7 +5715,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5717,7 +5723,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5725,7 +5731,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5733,7 +5739,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5741,7 +5747,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5749,7 +5755,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5757,7 +5763,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>860</v>
+        <v>640</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5765,7 +5771,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5773,7 +5779,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5781,7 +5787,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5789,7 +5795,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5797,7 +5803,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5805,7 +5811,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5813,7 +5819,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5821,7 +5827,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5829,7 +5835,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>620</v>
+        <v>480</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5837,7 +5843,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5845,7 +5851,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5853,7 +5859,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5861,7 +5867,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5869,7 +5875,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5877,7 +5883,7 @@
         <v>414</v>
       </c>
       <c r="B414" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5885,7 +5891,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5893,7 +5899,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5901,7 +5907,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>840</v>
+        <v>480</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5909,7 +5915,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5917,7 +5923,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5925,7 +5931,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5941,7 +5947,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -5949,7 +5955,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -5965,7 +5971,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -5973,7 +5979,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -5981,7 +5987,7 @@
         <v>427</v>
       </c>
       <c r="B427" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -5989,7 +5995,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>1100</v>
+        <v>660</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -5997,7 +6003,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6005,7 +6011,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6013,7 +6019,7 @@
         <v>431</v>
       </c>
       <c r="B431" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6021,7 +6027,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>800</v>
+        <v>760</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6029,7 +6035,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6045,7 +6051,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6053,7 +6059,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6061,7 +6067,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6069,7 +6075,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6077,7 +6083,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6085,7 +6091,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6101,7 +6107,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6109,7 +6115,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6117,7 +6123,7 @@
         <v>444</v>
       </c>
       <c r="B444" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6125,7 +6131,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6133,7 +6139,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>880</v>
+        <v>620</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6141,7 +6147,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6157,7 +6163,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6165,7 +6171,7 @@
         <v>450</v>
       </c>
       <c r="B450" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6173,7 +6179,7 @@
         <v>451</v>
       </c>
       <c r="B451" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6181,7 +6187,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>790</v>
+        <v>900</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6189,7 +6195,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>640</v>
+        <v>790</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6197,7 +6203,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6205,7 +6211,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6213,7 +6219,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6229,7 +6235,7 @@
         <v>458</v>
       </c>
       <c r="B458" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6237,7 +6243,7 @@
         <v>459</v>
       </c>
       <c r="B459" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6245,7 +6251,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6253,7 +6259,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6261,7 +6267,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6269,7 +6275,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6277,7 +6283,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6285,7 +6291,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6293,7 +6299,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6301,7 +6307,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6309,7 +6315,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6325,7 +6331,7 @@
         <v>470</v>
       </c>
       <c r="B470" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6333,7 +6339,7 @@
         <v>471</v>
       </c>
       <c r="B471" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6341,7 +6347,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6349,7 +6355,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>940</v>
+        <v>960</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6357,7 +6363,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6373,7 +6379,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>920</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6381,7 +6387,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6389,7 +6395,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6397,7 +6403,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6405,7 +6411,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6413,7 +6419,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6421,7 +6427,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6429,7 +6435,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6437,7 +6443,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6445,7 +6451,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6453,7 +6459,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6461,7 +6467,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6469,7 +6475,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>540</v>
+        <v>780</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6477,7 +6483,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>1100</v>
+        <v>540</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6485,7 +6491,7 @@
         <v>490</v>
       </c>
       <c r="B490" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6493,7 +6499,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6501,7 +6507,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6509,7 +6515,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6517,7 +6523,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6525,7 +6531,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>980</v>
+        <v>860</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6533,7 +6539,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>740</v>
+        <v>980</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6541,7 +6547,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6549,7 +6555,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6573,7 +6579,7 @@
         <v>501</v>
       </c>
       <c r="B501" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6589,7 +6595,7 @@
         <v>503</v>
       </c>
       <c r="B503" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6597,7 +6603,7 @@
         <v>504</v>
       </c>
       <c r="B504" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6605,7 +6611,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6613,7 +6619,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6621,7 +6627,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6629,7 +6635,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6637,7 +6643,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6645,7 +6651,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6653,7 +6659,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6661,7 +6667,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6669,7 +6675,7 @@
         <v>513</v>
       </c>
       <c r="B513" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6677,7 +6683,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6685,7 +6691,7 @@
         <v>515</v>
       </c>
       <c r="B515" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6693,7 +6699,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6701,7 +6707,7 @@
         <v>517</v>
       </c>
       <c r="B517" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6709,7 +6715,7 @@
         <v>518</v>
       </c>
       <c r="B518" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6717,7 +6723,7 @@
         <v>519</v>
       </c>
       <c r="B519" s="1">
-        <v>1400</v>
+        <v>720</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6725,7 +6731,7 @@
         <v>520</v>
       </c>
       <c r="B520" s="1">
-        <v>720</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6733,7 +6739,7 @@
         <v>521</v>
       </c>
       <c r="B521" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6741,7 +6747,7 @@
         <v>522</v>
       </c>
       <c r="B522" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -6749,7 +6755,7 @@
         <v>523</v>
       </c>
       <c r="B523" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6757,7 +6763,7 @@
         <v>524</v>
       </c>
       <c r="B524" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6765,7 +6771,7 @@
         <v>525</v>
       </c>
       <c r="B525" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6773,7 +6779,7 @@
         <v>526</v>
       </c>
       <c r="B526" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6781,7 +6787,7 @@
         <v>527</v>
       </c>
       <c r="B527" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6789,7 +6795,7 @@
         <v>528</v>
       </c>
       <c r="B528" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6797,7 +6803,7 @@
         <v>529</v>
       </c>
       <c r="B529" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6805,7 +6811,7 @@
         <v>530</v>
       </c>
       <c r="B530" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6813,7 +6819,7 @@
         <v>531</v>
       </c>
       <c r="B531" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6845,7 +6851,7 @@
         <v>535</v>
       </c>
       <c r="B535" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -6861,7 +6867,7 @@
         <v>537</v>
       </c>
       <c r="B537" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -6885,7 +6891,7 @@
         <v>540</v>
       </c>
       <c r="B540" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -6893,7 +6899,7 @@
         <v>541</v>
       </c>
       <c r="B541" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -6901,7 +6907,7 @@
         <v>542</v>
       </c>
       <c r="B542" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -6909,7 +6915,7 @@
         <v>543</v>
       </c>
       <c r="B543" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -6917,7 +6923,7 @@
         <v>544</v>
       </c>
       <c r="B544" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -6925,7 +6931,7 @@
         <v>545</v>
       </c>
       <c r="B545" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -6933,7 +6939,7 @@
         <v>546</v>
       </c>
       <c r="B546" s="1">
-        <v>660</v>
+        <v>540</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -6941,7 +6947,7 @@
         <v>547</v>
       </c>
       <c r="B547" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -6949,7 +6955,7 @@
         <v>548</v>
       </c>
       <c r="B548" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -6957,7 +6963,7 @@
         <v>549</v>
       </c>
       <c r="B549" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -6981,7 +6987,7 @@
         <v>552</v>
       </c>
       <c r="B552" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -6989,7 +6995,7 @@
         <v>553</v>
       </c>
       <c r="B553" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -6997,7 +7003,7 @@
         <v>554</v>
       </c>
       <c r="B554" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7005,7 +7011,7 @@
         <v>555</v>
       </c>
       <c r="B555" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7013,7 +7019,7 @@
         <v>556</v>
       </c>
       <c r="B556" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7029,7 +7035,7 @@
         <v>558</v>
       </c>
       <c r="B558" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7037,7 +7043,7 @@
         <v>559</v>
       </c>
       <c r="B559" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7045,7 +7051,7 @@
         <v>560</v>
       </c>
       <c r="B560" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7053,7 +7059,7 @@
         <v>561</v>
       </c>
       <c r="B561" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7061,7 +7067,7 @@
         <v>562</v>
       </c>
       <c r="B562" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7069,7 +7075,7 @@
         <v>563</v>
       </c>
       <c r="B563" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7077,7 +7083,7 @@
         <v>564</v>
       </c>
       <c r="B564" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7085,7 +7091,7 @@
         <v>565</v>
       </c>
       <c r="B565" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7093,7 +7099,7 @@
         <v>566</v>
       </c>
       <c r="B566" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7101,7 +7107,7 @@
         <v>567</v>
       </c>
       <c r="B567" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7109,7 +7115,7 @@
         <v>568</v>
       </c>
       <c r="B568" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7117,7 +7123,7 @@
         <v>569</v>
       </c>
       <c r="B569" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7125,7 +7131,7 @@
         <v>570</v>
       </c>
       <c r="B570" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7133,7 +7139,7 @@
         <v>571</v>
       </c>
       <c r="B571" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7141,7 +7147,7 @@
         <v>572</v>
       </c>
       <c r="B572" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7149,7 +7155,7 @@
         <v>573</v>
       </c>
       <c r="B573" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7157,7 +7163,7 @@
         <v>574</v>
       </c>
       <c r="B574" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7173,7 +7179,7 @@
         <v>576</v>
       </c>
       <c r="B576" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7181,7 +7187,7 @@
         <v>577</v>
       </c>
       <c r="B577" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7189,7 +7195,7 @@
         <v>578</v>
       </c>
       <c r="B578" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7197,7 +7203,7 @@
         <v>579</v>
       </c>
       <c r="B579" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7205,7 +7211,7 @@
         <v>580</v>
       </c>
       <c r="B580" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7213,7 +7219,7 @@
         <v>581</v>
       </c>
       <c r="B581" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7221,7 +7227,7 @@
         <v>582</v>
       </c>
       <c r="B582" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7229,7 +7235,7 @@
         <v>583</v>
       </c>
       <c r="B583" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7237,7 +7243,7 @@
         <v>584</v>
       </c>
       <c r="B584" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7245,7 +7251,7 @@
         <v>585</v>
       </c>
       <c r="B585" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7261,7 +7267,7 @@
         <v>587</v>
       </c>
       <c r="B587" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7269,7 +7275,7 @@
         <v>588</v>
       </c>
       <c r="B588" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7277,7 +7283,7 @@
         <v>589</v>
       </c>
       <c r="B589" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7285,7 +7291,7 @@
         <v>590</v>
       </c>
       <c r="B590" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7293,7 +7299,7 @@
         <v>591</v>
       </c>
       <c r="B591" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7301,7 +7307,7 @@
         <v>592</v>
       </c>
       <c r="B592" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7309,7 +7315,7 @@
         <v>593</v>
       </c>
       <c r="B593" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7317,7 +7323,7 @@
         <v>594</v>
       </c>
       <c r="B594" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7325,7 +7331,7 @@
         <v>595</v>
       </c>
       <c r="B595" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7333,7 +7339,7 @@
         <v>596</v>
       </c>
       <c r="B596" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7341,7 +7347,7 @@
         <v>597</v>
       </c>
       <c r="B597" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7349,7 +7355,7 @@
         <v>598</v>
       </c>
       <c r="B598" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7357,7 +7363,7 @@
         <v>599</v>
       </c>
       <c r="B599" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7365,7 +7371,7 @@
         <v>600</v>
       </c>
       <c r="B600" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7373,7 +7379,7 @@
         <v>601</v>
       </c>
       <c r="B601" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7381,7 +7387,7 @@
         <v>602</v>
       </c>
       <c r="B602" s="1">
-        <v>820</v>
+        <v>720</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7389,7 +7395,7 @@
         <v>603</v>
       </c>
       <c r="B603" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7397,7 +7403,7 @@
         <v>604</v>
       </c>
       <c r="B604" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7413,7 +7419,7 @@
         <v>606</v>
       </c>
       <c r="B606" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7421,7 +7427,7 @@
         <v>607</v>
       </c>
       <c r="B607" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7429,7 +7435,7 @@
         <v>608</v>
       </c>
       <c r="B608" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7445,7 +7451,7 @@
         <v>610</v>
       </c>
       <c r="B610" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7453,7 +7459,7 @@
         <v>611</v>
       </c>
       <c r="B611" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7461,7 +7467,7 @@
         <v>612</v>
       </c>
       <c r="B612" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7469,7 +7475,7 @@
         <v>613</v>
       </c>
       <c r="B613" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7477,7 +7483,7 @@
         <v>614</v>
       </c>
       <c r="B614" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7485,7 +7491,7 @@
         <v>615</v>
       </c>
       <c r="B615" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7493,7 +7499,7 @@
         <v>616</v>
       </c>
       <c r="B616" s="1">
-        <v>440</v>
+        <v>680</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -7501,7 +7507,7 @@
         <v>617</v>
       </c>
       <c r="B617" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -7509,7 +7515,7 @@
         <v>618</v>
       </c>
       <c r="B618" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -7517,7 +7523,7 @@
         <v>619</v>
       </c>
       <c r="B619" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7525,7 +7531,7 @@
         <v>620</v>
       </c>
       <c r="B620" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7533,7 +7539,7 @@
         <v>621</v>
       </c>
       <c r="B621" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -7541,7 +7547,7 @@
         <v>622</v>
       </c>
       <c r="B622" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -7549,7 +7555,7 @@
         <v>623</v>
       </c>
       <c r="B623" s="1">
-        <v>800</v>
+        <v>560</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -7557,7 +7563,7 @@
         <v>624</v>
       </c>
       <c r="B624" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -7565,7 +7571,7 @@
         <v>625</v>
       </c>
       <c r="B625" s="1">
-        <v>920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -7573,7 +7579,7 @@
         <v>626</v>
       </c>
       <c r="B626" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -7581,7 +7587,7 @@
         <v>627</v>
       </c>
       <c r="B627" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -7589,7 +7595,7 @@
         <v>628</v>
       </c>
       <c r="B628" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -7597,7 +7603,7 @@
         <v>629</v>
       </c>
       <c r="B629" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -7605,7 +7611,7 @@
         <v>630</v>
       </c>
       <c r="B630" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -7613,7 +7619,7 @@
         <v>631</v>
       </c>
       <c r="B631" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -7621,7 +7627,7 @@
         <v>632</v>
       </c>
       <c r="B632" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -7629,7 +7635,7 @@
         <v>633</v>
       </c>
       <c r="B633" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -7637,7 +7643,7 @@
         <v>634</v>
       </c>
       <c r="B634" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -7645,7 +7651,7 @@
         <v>635</v>
       </c>
       <c r="B635" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -7653,7 +7659,7 @@
         <v>636</v>
       </c>
       <c r="B636" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -7661,7 +7667,7 @@
         <v>637</v>
       </c>
       <c r="B637" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -7669,7 +7675,7 @@
         <v>638</v>
       </c>
       <c r="B638" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -7677,7 +7683,7 @@
         <v>639</v>
       </c>
       <c r="B639" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -7685,7 +7691,7 @@
         <v>640</v>
       </c>
       <c r="B640" s="1">
-        <v>660</v>
+        <v>860</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -7693,7 +7699,7 @@
         <v>641</v>
       </c>
       <c r="B641" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -7701,7 +7707,7 @@
         <v>642</v>
       </c>
       <c r="B642" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -7709,7 +7715,7 @@
         <v>643</v>
       </c>
       <c r="B643" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -7717,7 +7723,7 @@
         <v>644</v>
       </c>
       <c r="B644" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -7725,7 +7731,7 @@
         <v>645</v>
       </c>
       <c r="B645" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -7733,7 +7739,7 @@
         <v>646</v>
       </c>
       <c r="B646" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -7741,7 +7747,7 @@
         <v>647</v>
       </c>
       <c r="B647" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -7749,7 +7755,7 @@
         <v>648</v>
       </c>
       <c r="B648" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -7757,7 +7763,7 @@
         <v>649</v>
       </c>
       <c r="B649" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -7765,7 +7771,7 @@
         <v>650</v>
       </c>
       <c r="B650" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -7773,7 +7779,7 @@
         <v>651</v>
       </c>
       <c r="B651" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -7781,7 +7787,7 @@
         <v>652</v>
       </c>
       <c r="B652" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -7789,7 +7795,7 @@
         <v>653</v>
       </c>
       <c r="B653" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -7797,7 +7803,7 @@
         <v>654</v>
       </c>
       <c r="B654" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -7805,7 +7811,7 @@
         <v>655</v>
       </c>
       <c r="B655" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -7813,7 +7819,7 @@
         <v>656</v>
       </c>
       <c r="B656" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -7821,7 +7827,7 @@
         <v>657</v>
       </c>
       <c r="B657" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -7829,7 +7835,7 @@
         <v>658</v>
       </c>
       <c r="B658" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -7837,7 +7843,7 @@
         <v>659</v>
       </c>
       <c r="B659" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -7845,7 +7851,7 @@
         <v>660</v>
       </c>
       <c r="B660" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -7853,7 +7859,7 @@
         <v>661</v>
       </c>
       <c r="B661" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -7861,7 +7867,7 @@
         <v>662</v>
       </c>
       <c r="B662" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -7869,7 +7875,7 @@
         <v>663</v>
       </c>
       <c r="B663" s="1">
-        <v>920</v>
+        <v>500</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -7877,7 +7883,7 @@
         <v>664</v>
       </c>
       <c r="B664" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -7885,7 +7891,7 @@
         <v>665</v>
       </c>
       <c r="B665" s="1">
-        <v>1040</v>
+        <v>920</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -7893,7 +7899,7 @@
         <v>666</v>
       </c>
       <c r="B666" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -7901,7 +7907,7 @@
         <v>667</v>
       </c>
       <c r="B667" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -7909,7 +7915,7 @@
         <v>668</v>
       </c>
       <c r="B668" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -7917,7 +7923,7 @@
         <v>669</v>
       </c>
       <c r="B669" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -7925,7 +7931,7 @@
         <v>670</v>
       </c>
       <c r="B670" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -7933,7 +7939,7 @@
         <v>671</v>
       </c>
       <c r="B671" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -7949,7 +7955,7 @@
         <v>673</v>
       </c>
       <c r="B673" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -7957,7 +7963,7 @@
         <v>674</v>
       </c>
       <c r="B674" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -7965,7 +7971,7 @@
         <v>675</v>
       </c>
       <c r="B675" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -7973,7 +7979,7 @@
         <v>676</v>
       </c>
       <c r="B676" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -7981,7 +7987,7 @@
         <v>677</v>
       </c>
       <c r="B677" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -7989,7 +7995,7 @@
         <v>678</v>
       </c>
       <c r="B678" s="1">
-        <v>400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -7997,7 +8003,7 @@
         <v>679</v>
       </c>
       <c r="B679" s="1">
-        <v>400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8005,7 +8011,7 @@
         <v>680</v>
       </c>
       <c r="B680" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8013,7 +8019,7 @@
         <v>681</v>
       </c>
       <c r="B681" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8029,7 +8035,7 @@
         <v>683</v>
       </c>
       <c r="B683" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8037,7 +8043,7 @@
         <v>684</v>
       </c>
       <c r="B684" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8045,7 +8051,7 @@
         <v>685</v>
       </c>
       <c r="B685" s="1">
-        <v>860</v>
+        <v>520</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8053,7 +8059,7 @@
         <v>686</v>
       </c>
       <c r="B686" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8061,7 +8067,7 @@
         <v>687</v>
       </c>
       <c r="B687" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8069,7 +8075,7 @@
         <v>688</v>
       </c>
       <c r="B688" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8077,7 +8083,7 @@
         <v>689</v>
       </c>
       <c r="B689" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8085,7 +8091,7 @@
         <v>690</v>
       </c>
       <c r="B690" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8093,7 +8099,7 @@
         <v>691</v>
       </c>
       <c r="B691" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8101,7 +8107,7 @@
         <v>692</v>
       </c>
       <c r="B692" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8109,7 +8115,7 @@
         <v>693</v>
       </c>
       <c r="B693" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8117,7 +8123,7 @@
         <v>694</v>
       </c>
       <c r="B694" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8125,7 +8131,7 @@
         <v>695</v>
       </c>
       <c r="B695" s="1">
-        <v>840</v>
+        <v>500</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8133,7 +8139,7 @@
         <v>696</v>
       </c>
       <c r="B696" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8141,7 +8147,7 @@
         <v>697</v>
       </c>
       <c r="B697" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8149,7 +8155,7 @@
         <v>698</v>
       </c>
       <c r="B698" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8157,7 +8163,7 @@
         <v>699</v>
       </c>
       <c r="B699" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8165,7 +8171,7 @@
         <v>700</v>
       </c>
       <c r="B700" s="1">
-        <v>1040</v>
+        <v>920</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8173,7 +8179,7 @@
         <v>701</v>
       </c>
       <c r="B701" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8181,7 +8187,7 @@
         <v>702</v>
       </c>
       <c r="B702" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8189,7 +8195,7 @@
         <v>703</v>
       </c>
       <c r="B703" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8197,7 +8203,7 @@
         <v>704</v>
       </c>
       <c r="B704" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8205,7 +8211,7 @@
         <v>705</v>
       </c>
       <c r="B705" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8213,7 +8219,7 @@
         <v>706</v>
       </c>
       <c r="B706" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8229,7 +8235,7 @@
         <v>708</v>
       </c>
       <c r="B708" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8237,7 +8243,7 @@
         <v>709</v>
       </c>
       <c r="B709" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8245,7 +8251,7 @@
         <v>710</v>
       </c>
       <c r="B710" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8253,7 +8259,7 @@
         <v>711</v>
       </c>
       <c r="B711" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8261,7 +8267,7 @@
         <v>712</v>
       </c>
       <c r="B712" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8277,7 +8283,7 @@
         <v>714</v>
       </c>
       <c r="B714" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8285,7 +8291,7 @@
         <v>715</v>
       </c>
       <c r="B715" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8301,7 +8307,7 @@
         <v>717</v>
       </c>
       <c r="B717" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8309,7 +8315,7 @@
         <v>718</v>
       </c>
       <c r="B718" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8317,7 +8323,7 @@
         <v>719</v>
       </c>
       <c r="B719" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8325,7 +8331,7 @@
         <v>720</v>
       </c>
       <c r="B720" s="1">
-        <v>420</v>
+        <v>520</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8333,7 +8339,7 @@
         <v>721</v>
       </c>
       <c r="B721" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8341,7 +8347,7 @@
         <v>722</v>
       </c>
       <c r="B722" s="1">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8349,7 +8355,7 @@
         <v>723</v>
       </c>
       <c r="B723" s="1">
-        <v>760</v>
+        <v>380</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8357,7 +8363,7 @@
         <v>724</v>
       </c>
       <c r="B724" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8365,7 +8371,7 @@
         <v>725</v>
       </c>
       <c r="B725" s="1">
-        <v>580</v>
+        <v>760</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8373,7 +8379,7 @@
         <v>726</v>
       </c>
       <c r="B726" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8389,7 +8395,7 @@
         <v>728</v>
       </c>
       <c r="B728" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8397,7 +8403,7 @@
         <v>729</v>
       </c>
       <c r="B729" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8405,6 +8411,22 @@
         <v>730</v>
       </c>
       <c r="B730" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2">
+      <c r="A731" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="B731" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2">
+      <c r="A732" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="B732" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="740">
   <si>
     <t>Наименование</t>
   </si>
@@ -464,6 +464,9 @@
     <t>Marstons Oyster stout, РОЗЛИВ, Англия</t>
   </si>
   <si>
+    <t>Midnight Project - Course Of The Queen (ESB), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Midnight Project - Cyberpunk Shotgun (DIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -2027,12 +2030,21 @@
     <t>вынос_Осьминогец - Конь Удачи (IPA),  Розлив, Россия</t>
   </si>
   <si>
+    <t>вынос_Осьминогец - Простота Без Пестроты (NEDIPA),  Розлив, Россия</t>
+  </si>
+  <si>
     <t>вынос_Осьминогец - Святой Михаил XIV (Quadruple),  Розлив, Россия</t>
   </si>
   <si>
+    <t>вынос_Осьминогец - Соковыжималка (Sour),  Розлив, Россия</t>
+  </si>
+  <si>
     <t>вынос_Петр Петрович - Exploring The Unknown (Pilsner), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Петр Петрович - Harbinger of Spring (American Lager), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Преснявары - Munich Helles , РОЗЛИВ</t>
   </si>
   <si>
@@ -2132,10 +2144,19 @@
     <t>Осьминогец - Конь Удачи (IPA),  Розлив, Россия</t>
   </si>
   <si>
+    <t>Осьминогец - Простота Без Пестроты (NEDIPA),  Розлив, Россия</t>
+  </si>
+  <si>
     <t>Осьминогец - Святой Михаил XIV (Quadruple),  Розлив, Россия</t>
   </si>
   <si>
+    <t>Осьминогец - Соковыжималка (Sour),  Розлив, Россия</t>
+  </si>
+  <si>
     <t>Петр Петрович - Exploring The Unknown (Pilsner), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>Петр Петрович - Harbinger of Spring (American Lager), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>Преснявары - Munich Helles , РОЗЛИВ</t>
@@ -2567,7 +2588,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B732"/>
+  <dimension ref="A1:B739"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -3763,7 +3784,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -3787,7 +3808,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3795,7 +3816,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3803,7 +3824,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -3811,7 +3832,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -3819,7 +3840,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -3827,7 +3848,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>460</v>
+        <v>700</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -3835,7 +3856,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -3843,7 +3864,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -3851,7 +3872,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -3859,7 +3880,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -3867,7 +3888,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -3883,7 +3904,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -3899,7 +3920,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -3907,7 +3928,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -3915,7 +3936,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -3923,7 +3944,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -3931,7 +3952,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -3939,7 +3960,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>740</v>
+        <v>400</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -3947,7 +3968,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -3955,7 +3976,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -3963,7 +3984,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -3971,7 +3992,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -3979,7 +4000,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -3987,7 +4008,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4003,7 +4024,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4011,7 +4032,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4019,7 +4040,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4035,7 +4056,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4043,7 +4064,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4051,7 +4072,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4059,7 +4080,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4067,7 +4088,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4075,7 +4096,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4083,7 +4104,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4091,7 +4112,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4099,7 +4120,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4107,7 +4128,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4115,7 +4136,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4123,7 +4144,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4131,7 +4152,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>480</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4139,7 +4160,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4147,7 +4168,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4155,7 +4176,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4163,7 +4184,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4171,7 +4192,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4179,7 +4200,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4187,7 +4208,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4195,7 +4216,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4203,7 +4224,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4211,7 +4232,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4219,7 +4240,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4227,7 +4248,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4243,7 +4264,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4259,7 +4280,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4267,7 +4288,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4275,7 +4296,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4283,7 +4304,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4291,7 +4312,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4299,7 +4320,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4307,7 +4328,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4331,7 +4352,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4339,7 +4360,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4347,7 +4368,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4363,7 +4384,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4371,7 +4392,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4379,7 +4400,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>758</v>
+        <v>500</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4387,7 +4408,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>2273</v>
+        <v>758</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4395,7 +4416,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>1515</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4403,7 +4424,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>520</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4411,7 +4432,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4419,7 +4440,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4427,7 +4448,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4435,7 +4456,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4451,7 +4472,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4459,7 +4480,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4467,7 +4488,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4475,7 +4496,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4483,7 +4504,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4491,7 +4512,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4499,7 +4520,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4507,7 +4528,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4515,7 +4536,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4523,7 +4544,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4531,7 +4552,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4539,7 +4560,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4547,7 +4568,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4555,7 +4576,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4563,7 +4584,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>460</v>
+        <v>580</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4571,7 +4592,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4579,7 +4600,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4587,7 +4608,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4595,7 +4616,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4619,7 +4640,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4635,7 +4656,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>1000</v>
+        <v>560</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4643,7 +4664,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4651,7 +4672,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4659,7 +4680,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4667,7 +4688,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4675,7 +4696,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4683,7 +4704,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4691,7 +4712,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4699,7 +4720,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4707,7 +4728,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4715,7 +4736,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4723,7 +4744,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4731,7 +4752,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4739,7 +4760,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4747,7 +4768,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4755,7 +4776,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4763,7 +4784,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4771,7 +4792,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4779,7 +4800,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4787,7 +4808,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4795,7 +4816,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4803,7 +4824,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4811,7 +4832,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>520</v>
+        <v>880</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4819,7 +4840,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4827,7 +4848,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4835,7 +4856,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4843,7 +4864,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4851,7 +4872,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4859,7 +4880,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4867,7 +4888,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>320</v>
+        <v>520</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4875,7 +4896,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>540</v>
+        <v>320</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4883,7 +4904,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4891,7 +4912,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -4907,7 +4928,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -4915,7 +4936,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -4923,7 +4944,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -4931,7 +4952,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>480</v>
+        <v>800</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -4939,7 +4960,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>780</v>
+        <v>480</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -4947,7 +4968,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -4955,7 +4976,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -4963,7 +4984,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -4971,7 +4992,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -4987,7 +5008,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -4995,7 +5016,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5003,7 +5024,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5011,7 +5032,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5019,7 +5040,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5027,7 +5048,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5035,7 +5056,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5043,7 +5064,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5051,7 +5072,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5059,7 +5080,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5075,7 +5096,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5083,7 +5104,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5091,7 +5112,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5099,7 +5120,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5107,7 +5128,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5115,7 +5136,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5131,7 +5152,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5139,7 +5160,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5147,7 +5168,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>640</v>
+        <v>480</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5155,7 +5176,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5163,7 +5184,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5171,7 +5192,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5179,7 +5200,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>520</v>
+        <v>860</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5187,7 +5208,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5195,7 +5216,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5211,7 +5232,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5219,7 +5240,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>700</v>
+        <v>420</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5227,7 +5248,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5235,7 +5256,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5243,7 +5264,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5251,7 +5272,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5259,7 +5280,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5267,7 +5288,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5275,7 +5296,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5283,7 +5304,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5291,7 +5312,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>440</v>
+        <v>620</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5299,7 +5320,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>320</v>
+        <v>440</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5315,7 +5336,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>820</v>
+        <v>320</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5323,7 +5344,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5331,7 +5352,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5347,7 +5368,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5355,7 +5376,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5371,7 +5392,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5379,7 +5400,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5387,7 +5408,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5395,7 +5416,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5403,7 +5424,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5411,7 +5432,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5419,7 +5440,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5435,7 +5456,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5443,7 +5464,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5451,7 +5472,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5459,7 +5480,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5467,7 +5488,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5475,7 +5496,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5483,7 +5504,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5491,7 +5512,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5499,7 +5520,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5507,7 +5528,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5515,7 +5536,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5523,7 +5544,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5531,7 +5552,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5539,7 +5560,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5547,7 +5568,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5555,7 +5576,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5563,7 +5584,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5571,7 +5592,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5587,7 +5608,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5595,7 +5616,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5603,7 +5624,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5611,7 +5632,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5619,7 +5640,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5635,7 +5656,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5643,7 +5664,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="1">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5651,7 +5672,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5659,7 +5680,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5667,7 +5688,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5675,7 +5696,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5683,7 +5704,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5699,7 +5720,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5707,7 +5728,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5715,7 +5736,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>640</v>
+        <v>920</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5723,7 +5744,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5731,7 +5752,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5739,7 +5760,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5747,7 +5768,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5755,7 +5776,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5763,7 +5784,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5771,7 +5792,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>860</v>
+        <v>640</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5779,7 +5800,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5787,7 +5808,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5795,7 +5816,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5803,7 +5824,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5811,7 +5832,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5819,7 +5840,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5827,7 +5848,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5835,7 +5856,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5843,7 +5864,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>620</v>
+        <v>480</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5851,7 +5872,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5859,7 +5880,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5867,7 +5888,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5875,7 +5896,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5883,7 +5904,7 @@
         <v>414</v>
       </c>
       <c r="B414" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5891,7 +5912,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5899,7 +5920,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5907,7 +5928,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5915,7 +5936,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>840</v>
+        <v>480</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5923,7 +5944,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5931,7 +5952,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5939,7 +5960,7 @@
         <v>421</v>
       </c>
       <c r="B421" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -5955,7 +5976,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -5963,7 +5984,7 @@
         <v>424</v>
       </c>
       <c r="B424" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -5979,7 +6000,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -5987,7 +6008,7 @@
         <v>427</v>
       </c>
       <c r="B427" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -5995,7 +6016,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6003,7 +6024,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>1100</v>
+        <v>660</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6011,7 +6032,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6019,7 +6040,7 @@
         <v>431</v>
       </c>
       <c r="B431" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6027,7 +6048,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6035,7 +6056,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>800</v>
+        <v>760</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6043,7 +6064,7 @@
         <v>434</v>
       </c>
       <c r="B434" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6059,7 +6080,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6067,7 +6088,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6075,7 +6096,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6083,7 +6104,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6091,7 +6112,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6099,7 +6120,7 @@
         <v>441</v>
       </c>
       <c r="B441" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6115,7 +6136,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6123,7 +6144,7 @@
         <v>444</v>
       </c>
       <c r="B444" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6131,7 +6152,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6139,7 +6160,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6147,7 +6168,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>880</v>
+        <v>620</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6155,7 +6176,7 @@
         <v>448</v>
       </c>
       <c r="B448" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6171,7 +6192,7 @@
         <v>450</v>
       </c>
       <c r="B450" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6179,7 +6200,7 @@
         <v>451</v>
       </c>
       <c r="B451" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6187,7 +6208,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6195,7 +6216,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>790</v>
+        <v>900</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6203,7 +6224,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>640</v>
+        <v>790</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6211,7 +6232,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6219,7 +6240,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6227,7 +6248,7 @@
         <v>457</v>
       </c>
       <c r="B457" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6243,7 +6264,7 @@
         <v>459</v>
       </c>
       <c r="B459" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6251,7 +6272,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6259,7 +6280,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6267,7 +6288,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6275,7 +6296,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6283,7 +6304,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6291,7 +6312,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6299,7 +6320,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6307,7 +6328,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6315,7 +6336,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6323,7 +6344,7 @@
         <v>469</v>
       </c>
       <c r="B469" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6339,7 +6360,7 @@
         <v>471</v>
       </c>
       <c r="B471" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6347,7 +6368,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6355,7 +6376,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6363,7 +6384,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>940</v>
+        <v>960</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6371,7 +6392,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6387,7 +6408,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>920</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6395,7 +6416,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6403,7 +6424,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6411,7 +6432,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6419,7 +6440,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6427,7 +6448,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6435,7 +6456,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6443,7 +6464,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6451,7 +6472,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6459,7 +6480,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6467,7 +6488,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6475,7 +6496,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6483,7 +6504,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>540</v>
+        <v>780</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6491,7 +6512,7 @@
         <v>490</v>
       </c>
       <c r="B490" s="1">
-        <v>1100</v>
+        <v>540</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6499,7 +6520,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6507,7 +6528,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6515,7 +6536,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6523,7 +6544,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6531,7 +6552,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6539,7 +6560,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>980</v>
+        <v>860</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6547,7 +6568,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>740</v>
+        <v>980</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6555,7 +6576,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6563,7 +6584,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6587,7 +6608,7 @@
         <v>502</v>
       </c>
       <c r="B502" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6603,7 +6624,7 @@
         <v>504</v>
       </c>
       <c r="B504" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6611,7 +6632,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6619,7 +6640,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6627,7 +6648,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6635,7 +6656,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6643,7 +6664,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6651,7 +6672,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6659,7 +6680,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6667,7 +6688,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6675,7 +6696,7 @@
         <v>513</v>
       </c>
       <c r="B513" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6683,7 +6704,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6691,7 +6712,7 @@
         <v>515</v>
       </c>
       <c r="B515" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6699,7 +6720,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6707,7 +6728,7 @@
         <v>517</v>
       </c>
       <c r="B517" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6715,7 +6736,7 @@
         <v>518</v>
       </c>
       <c r="B518" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6723,7 +6744,7 @@
         <v>519</v>
       </c>
       <c r="B519" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6731,7 +6752,7 @@
         <v>520</v>
       </c>
       <c r="B520" s="1">
-        <v>1400</v>
+        <v>720</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6739,7 +6760,7 @@
         <v>521</v>
       </c>
       <c r="B521" s="1">
-        <v>720</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6747,7 +6768,7 @@
         <v>522</v>
       </c>
       <c r="B522" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -6755,7 +6776,7 @@
         <v>523</v>
       </c>
       <c r="B523" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6763,7 +6784,7 @@
         <v>524</v>
       </c>
       <c r="B524" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6771,7 +6792,7 @@
         <v>525</v>
       </c>
       <c r="B525" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6779,7 +6800,7 @@
         <v>526</v>
       </c>
       <c r="B526" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6787,7 +6808,7 @@
         <v>527</v>
       </c>
       <c r="B527" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6795,7 +6816,7 @@
         <v>528</v>
       </c>
       <c r="B528" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6803,7 +6824,7 @@
         <v>529</v>
       </c>
       <c r="B529" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6811,7 +6832,7 @@
         <v>530</v>
       </c>
       <c r="B530" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6819,7 +6840,7 @@
         <v>531</v>
       </c>
       <c r="B531" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6827,7 +6848,7 @@
         <v>532</v>
       </c>
       <c r="B532" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6859,7 +6880,7 @@
         <v>536</v>
       </c>
       <c r="B536" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -6875,7 +6896,7 @@
         <v>538</v>
       </c>
       <c r="B538" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -6899,7 +6920,7 @@
         <v>541</v>
       </c>
       <c r="B541" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -6907,7 +6928,7 @@
         <v>542</v>
       </c>
       <c r="B542" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -6915,7 +6936,7 @@
         <v>543</v>
       </c>
       <c r="B543" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -6923,7 +6944,7 @@
         <v>544</v>
       </c>
       <c r="B544" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -6931,7 +6952,7 @@
         <v>545</v>
       </c>
       <c r="B545" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -6939,7 +6960,7 @@
         <v>546</v>
       </c>
       <c r="B546" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -6947,7 +6968,7 @@
         <v>547</v>
       </c>
       <c r="B547" s="1">
-        <v>660</v>
+        <v>540</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -6955,7 +6976,7 @@
         <v>548</v>
       </c>
       <c r="B548" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -6963,7 +6984,7 @@
         <v>549</v>
       </c>
       <c r="B549" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -6971,7 +6992,7 @@
         <v>550</v>
       </c>
       <c r="B550" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -6995,7 +7016,7 @@
         <v>553</v>
       </c>
       <c r="B553" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7003,7 +7024,7 @@
         <v>554</v>
       </c>
       <c r="B554" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7011,7 +7032,7 @@
         <v>555</v>
       </c>
       <c r="B555" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7019,7 +7040,7 @@
         <v>556</v>
       </c>
       <c r="B556" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7027,7 +7048,7 @@
         <v>557</v>
       </c>
       <c r="B557" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7043,7 +7064,7 @@
         <v>559</v>
       </c>
       <c r="B559" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7051,7 +7072,7 @@
         <v>560</v>
       </c>
       <c r="B560" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7059,7 +7080,7 @@
         <v>561</v>
       </c>
       <c r="B561" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7067,7 +7088,7 @@
         <v>562</v>
       </c>
       <c r="B562" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7075,7 +7096,7 @@
         <v>563</v>
       </c>
       <c r="B563" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7083,7 +7104,7 @@
         <v>564</v>
       </c>
       <c r="B564" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7091,7 +7112,7 @@
         <v>565</v>
       </c>
       <c r="B565" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7099,7 +7120,7 @@
         <v>566</v>
       </c>
       <c r="B566" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7107,7 +7128,7 @@
         <v>567</v>
       </c>
       <c r="B567" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7115,7 +7136,7 @@
         <v>568</v>
       </c>
       <c r="B568" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7123,7 +7144,7 @@
         <v>569</v>
       </c>
       <c r="B569" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7131,7 +7152,7 @@
         <v>570</v>
       </c>
       <c r="B570" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7139,7 +7160,7 @@
         <v>571</v>
       </c>
       <c r="B571" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7147,7 +7168,7 @@
         <v>572</v>
       </c>
       <c r="B572" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7155,7 +7176,7 @@
         <v>573</v>
       </c>
       <c r="B573" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7163,7 +7184,7 @@
         <v>574</v>
       </c>
       <c r="B574" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7171,7 +7192,7 @@
         <v>575</v>
       </c>
       <c r="B575" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7187,7 +7208,7 @@
         <v>577</v>
       </c>
       <c r="B577" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7195,7 +7216,7 @@
         <v>578</v>
       </c>
       <c r="B578" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7203,7 +7224,7 @@
         <v>579</v>
       </c>
       <c r="B579" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7211,7 +7232,7 @@
         <v>580</v>
       </c>
       <c r="B580" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7219,7 +7240,7 @@
         <v>581</v>
       </c>
       <c r="B581" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7227,7 +7248,7 @@
         <v>582</v>
       </c>
       <c r="B582" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7235,7 +7256,7 @@
         <v>583</v>
       </c>
       <c r="B583" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7243,7 +7264,7 @@
         <v>584</v>
       </c>
       <c r="B584" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7251,7 +7272,7 @@
         <v>585</v>
       </c>
       <c r="B585" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7259,7 +7280,7 @@
         <v>586</v>
       </c>
       <c r="B586" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7275,7 +7296,7 @@
         <v>588</v>
       </c>
       <c r="B588" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7283,7 +7304,7 @@
         <v>589</v>
       </c>
       <c r="B589" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7291,7 +7312,7 @@
         <v>590</v>
       </c>
       <c r="B590" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7299,7 +7320,7 @@
         <v>591</v>
       </c>
       <c r="B591" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7307,7 +7328,7 @@
         <v>592</v>
       </c>
       <c r="B592" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7315,7 +7336,7 @@
         <v>593</v>
       </c>
       <c r="B593" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7323,7 +7344,7 @@
         <v>594</v>
       </c>
       <c r="B594" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7331,7 +7352,7 @@
         <v>595</v>
       </c>
       <c r="B595" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7339,7 +7360,7 @@
         <v>596</v>
       </c>
       <c r="B596" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7347,7 +7368,7 @@
         <v>597</v>
       </c>
       <c r="B597" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7355,7 +7376,7 @@
         <v>598</v>
       </c>
       <c r="B598" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7363,7 +7384,7 @@
         <v>599</v>
       </c>
       <c r="B599" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7371,7 +7392,7 @@
         <v>600</v>
       </c>
       <c r="B600" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7379,7 +7400,7 @@
         <v>601</v>
       </c>
       <c r="B601" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7387,7 +7408,7 @@
         <v>602</v>
       </c>
       <c r="B602" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7395,7 +7416,7 @@
         <v>603</v>
       </c>
       <c r="B603" s="1">
-        <v>820</v>
+        <v>720</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7403,7 +7424,7 @@
         <v>604</v>
       </c>
       <c r="B604" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7411,7 +7432,7 @@
         <v>605</v>
       </c>
       <c r="B605" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7427,7 +7448,7 @@
         <v>607</v>
       </c>
       <c r="B607" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7435,7 +7456,7 @@
         <v>608</v>
       </c>
       <c r="B608" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7443,7 +7464,7 @@
         <v>609</v>
       </c>
       <c r="B609" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7451,7 +7472,7 @@
         <v>610</v>
       </c>
       <c r="B610" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7459,7 +7480,7 @@
         <v>611</v>
       </c>
       <c r="B611" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7475,7 +7496,7 @@
         <v>613</v>
       </c>
       <c r="B613" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7483,7 +7504,7 @@
         <v>614</v>
       </c>
       <c r="B614" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7491,7 +7512,7 @@
         <v>615</v>
       </c>
       <c r="B615" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7499,7 +7520,7 @@
         <v>616</v>
       </c>
       <c r="B616" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -7507,7 +7528,7 @@
         <v>617</v>
       </c>
       <c r="B617" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -7515,7 +7536,7 @@
         <v>618</v>
       </c>
       <c r="B618" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -7523,7 +7544,7 @@
         <v>619</v>
       </c>
       <c r="B619" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7531,7 +7552,7 @@
         <v>620</v>
       </c>
       <c r="B620" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7539,7 +7560,7 @@
         <v>621</v>
       </c>
       <c r="B621" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -7547,7 +7568,7 @@
         <v>622</v>
       </c>
       <c r="B622" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -7555,7 +7576,7 @@
         <v>623</v>
       </c>
       <c r="B623" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -7563,7 +7584,7 @@
         <v>624</v>
       </c>
       <c r="B624" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -7571,7 +7592,7 @@
         <v>625</v>
       </c>
       <c r="B625" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -7579,7 +7600,7 @@
         <v>626</v>
       </c>
       <c r="B626" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -7587,7 +7608,7 @@
         <v>627</v>
       </c>
       <c r="B627" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -7595,7 +7616,7 @@
         <v>628</v>
       </c>
       <c r="B628" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -7603,7 +7624,7 @@
         <v>629</v>
       </c>
       <c r="B629" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -7611,7 +7632,7 @@
         <v>630</v>
       </c>
       <c r="B630" s="1">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -7619,7 +7640,7 @@
         <v>631</v>
       </c>
       <c r="B631" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -7627,7 +7648,7 @@
         <v>632</v>
       </c>
       <c r="B632" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -7635,7 +7656,7 @@
         <v>633</v>
       </c>
       <c r="B633" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -7643,7 +7664,7 @@
         <v>634</v>
       </c>
       <c r="B634" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -7651,7 +7672,7 @@
         <v>635</v>
       </c>
       <c r="B635" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -7659,7 +7680,7 @@
         <v>636</v>
       </c>
       <c r="B636" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -7667,7 +7688,7 @@
         <v>637</v>
       </c>
       <c r="B637" s="1">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -7675,7 +7696,7 @@
         <v>638</v>
       </c>
       <c r="B638" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -7683,7 +7704,7 @@
         <v>639</v>
       </c>
       <c r="B639" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -7691,7 +7712,7 @@
         <v>640</v>
       </c>
       <c r="B640" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -7699,7 +7720,7 @@
         <v>641</v>
       </c>
       <c r="B641" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -7707,7 +7728,7 @@
         <v>642</v>
       </c>
       <c r="B642" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -7715,7 +7736,7 @@
         <v>643</v>
       </c>
       <c r="B643" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -7723,7 +7744,7 @@
         <v>644</v>
       </c>
       <c r="B644" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -7731,7 +7752,7 @@
         <v>645</v>
       </c>
       <c r="B645" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -7739,7 +7760,7 @@
         <v>646</v>
       </c>
       <c r="B646" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -7747,7 +7768,7 @@
         <v>647</v>
       </c>
       <c r="B647" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -7755,7 +7776,7 @@
         <v>648</v>
       </c>
       <c r="B648" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -7763,7 +7784,7 @@
         <v>649</v>
       </c>
       <c r="B649" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -7771,7 +7792,7 @@
         <v>650</v>
       </c>
       <c r="B650" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -7779,7 +7800,7 @@
         <v>651</v>
       </c>
       <c r="B651" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -7787,7 +7808,7 @@
         <v>652</v>
       </c>
       <c r="B652" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -7795,7 +7816,7 @@
         <v>653</v>
       </c>
       <c r="B653" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -7803,7 +7824,7 @@
         <v>654</v>
       </c>
       <c r="B654" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -7811,7 +7832,7 @@
         <v>655</v>
       </c>
       <c r="B655" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -7819,7 +7840,7 @@
         <v>656</v>
       </c>
       <c r="B656" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -7827,7 +7848,7 @@
         <v>657</v>
       </c>
       <c r="B657" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -7835,7 +7856,7 @@
         <v>658</v>
       </c>
       <c r="B658" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -7843,7 +7864,7 @@
         <v>659</v>
       </c>
       <c r="B659" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -7859,7 +7880,7 @@
         <v>661</v>
       </c>
       <c r="B661" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -7875,7 +7896,7 @@
         <v>663</v>
       </c>
       <c r="B663" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -7883,7 +7904,7 @@
         <v>664</v>
       </c>
       <c r="B664" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -7891,7 +7912,7 @@
         <v>665</v>
       </c>
       <c r="B665" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -7899,7 +7920,7 @@
         <v>666</v>
       </c>
       <c r="B666" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -7907,7 +7928,7 @@
         <v>667</v>
       </c>
       <c r="B667" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -7915,7 +7936,7 @@
         <v>668</v>
       </c>
       <c r="B668" s="1">
-        <v>940</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -7923,7 +7944,7 @@
         <v>669</v>
       </c>
       <c r="B669" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -7931,7 +7952,7 @@
         <v>670</v>
       </c>
       <c r="B670" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -7939,7 +7960,7 @@
         <v>671</v>
       </c>
       <c r="B671" s="1">
-        <v>740</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -7947,7 +7968,7 @@
         <v>672</v>
       </c>
       <c r="B672" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -7955,7 +7976,7 @@
         <v>673</v>
       </c>
       <c r="B673" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -7963,7 +7984,7 @@
         <v>674</v>
       </c>
       <c r="B674" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -7971,7 +7992,7 @@
         <v>675</v>
       </c>
       <c r="B675" s="1">
-        <v>560</v>
+        <v>820</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -7979,7 +8000,7 @@
         <v>676</v>
       </c>
       <c r="B676" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -7987,7 +8008,7 @@
         <v>677</v>
       </c>
       <c r="B677" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -7995,7 +8016,7 @@
         <v>678</v>
       </c>
       <c r="B678" s="1">
-        <v>760</v>
+        <v>440</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8003,7 +8024,7 @@
         <v>679</v>
       </c>
       <c r="B679" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8011,7 +8032,7 @@
         <v>680</v>
       </c>
       <c r="B680" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8019,7 +8040,7 @@
         <v>681</v>
       </c>
       <c r="B681" s="1">
-        <v>400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8027,7 +8048,7 @@
         <v>682</v>
       </c>
       <c r="B682" s="1">
-        <v>380</v>
+        <v>760</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8035,7 +8056,7 @@
         <v>683</v>
       </c>
       <c r="B683" s="1">
-        <v>380</v>
+        <v>760</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8043,7 +8064,7 @@
         <v>684</v>
       </c>
       <c r="B684" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8051,7 +8072,7 @@
         <v>685</v>
       </c>
       <c r="B685" s="1">
-        <v>520</v>
+        <v>400</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8059,7 +8080,7 @@
         <v>686</v>
       </c>
       <c r="B686" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8067,7 +8088,7 @@
         <v>687</v>
       </c>
       <c r="B687" s="1">
-        <v>860</v>
+        <v>380</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8075,7 +8096,7 @@
         <v>688</v>
       </c>
       <c r="B688" s="1">
-        <v>680</v>
+        <v>380</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8083,7 +8104,7 @@
         <v>689</v>
       </c>
       <c r="B689" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8091,7 +8112,7 @@
         <v>690</v>
       </c>
       <c r="B690" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8099,7 +8120,7 @@
         <v>691</v>
       </c>
       <c r="B691" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8107,7 +8128,7 @@
         <v>692</v>
       </c>
       <c r="B692" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8115,7 +8136,7 @@
         <v>693</v>
       </c>
       <c r="B693" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8123,7 +8144,7 @@
         <v>694</v>
       </c>
       <c r="B694" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8131,7 +8152,7 @@
         <v>695</v>
       </c>
       <c r="B695" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8139,7 +8160,7 @@
         <v>696</v>
       </c>
       <c r="B696" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8147,7 +8168,7 @@
         <v>697</v>
       </c>
       <c r="B697" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8155,7 +8176,7 @@
         <v>698</v>
       </c>
       <c r="B698" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8163,7 +8184,7 @@
         <v>699</v>
       </c>
       <c r="B699" s="1">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8171,7 +8192,7 @@
         <v>700</v>
       </c>
       <c r="B700" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8179,7 +8200,7 @@
         <v>701</v>
       </c>
       <c r="B701" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8187,7 +8208,7 @@
         <v>702</v>
       </c>
       <c r="B702" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8195,7 +8216,7 @@
         <v>703</v>
       </c>
       <c r="B703" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8203,7 +8224,7 @@
         <v>704</v>
       </c>
       <c r="B704" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8219,7 +8240,7 @@
         <v>706</v>
       </c>
       <c r="B706" s="1">
-        <v>740</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8227,7 +8248,7 @@
         <v>707</v>
       </c>
       <c r="B707" s="1">
-        <v>440</v>
+        <v>940</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8235,7 +8256,7 @@
         <v>708</v>
       </c>
       <c r="B708" s="1">
-        <v>500</v>
+        <v>900</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8243,7 +8264,7 @@
         <v>709</v>
       </c>
       <c r="B709" s="1">
-        <v>440</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8251,7 +8272,7 @@
         <v>710</v>
       </c>
       <c r="B710" s="1">
-        <v>560</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8259,7 +8280,7 @@
         <v>711</v>
       </c>
       <c r="B711" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8267,7 +8288,7 @@
         <v>712</v>
       </c>
       <c r="B712" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8275,7 +8296,7 @@
         <v>713</v>
       </c>
       <c r="B713" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8283,7 +8304,7 @@
         <v>714</v>
       </c>
       <c r="B714" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8291,7 +8312,7 @@
         <v>715</v>
       </c>
       <c r="B715" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8299,7 +8320,7 @@
         <v>716</v>
       </c>
       <c r="B716" s="1">
-        <v>480</v>
+        <v>440</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8307,7 +8328,7 @@
         <v>717</v>
       </c>
       <c r="B717" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8315,7 +8336,7 @@
         <v>718</v>
       </c>
       <c r="B718" s="1">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8323,7 +8344,7 @@
         <v>719</v>
       </c>
       <c r="B719" s="1">
-        <v>520</v>
+        <v>820</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8331,7 +8352,7 @@
         <v>720</v>
       </c>
       <c r="B720" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8339,7 +8360,7 @@
         <v>721</v>
       </c>
       <c r="B721" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8347,7 +8368,7 @@
         <v>722</v>
       </c>
       <c r="B722" s="1">
-        <v>420</v>
+        <v>380</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8355,7 +8376,7 @@
         <v>723</v>
       </c>
       <c r="B723" s="1">
-        <v>380</v>
+        <v>480</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8363,7 +8384,7 @@
         <v>724</v>
       </c>
       <c r="B724" s="1">
-        <v>600</v>
+        <v>480</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8371,7 +8392,7 @@
         <v>725</v>
       </c>
       <c r="B725" s="1">
-        <v>760</v>
+        <v>480</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8379,7 +8400,7 @@
         <v>726</v>
       </c>
       <c r="B726" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8387,7 +8408,7 @@
         <v>727</v>
       </c>
       <c r="B727" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8395,7 +8416,7 @@
         <v>728</v>
       </c>
       <c r="B728" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8403,7 +8424,7 @@
         <v>729</v>
       </c>
       <c r="B729" s="1">
-        <v>580</v>
+        <v>420</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8411,7 +8432,7 @@
         <v>730</v>
       </c>
       <c r="B730" s="1">
-        <v>620</v>
+        <v>380</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8419,7 +8440,7 @@
         <v>731</v>
       </c>
       <c r="B731" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8427,6 +8448,62 @@
         <v>732</v>
       </c>
       <c r="B732" s="1">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2">
+      <c r="A733" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B733" s="1">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2">
+      <c r="A734" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="B734" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2">
+      <c r="A735" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="B735" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2">
+      <c r="A736" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B736" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2">
+      <c r="A737" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="B737" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2">
+      <c r="A738" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="B738" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2">
+      <c r="A739" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B739" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="742">
   <si>
     <t>Наименование</t>
   </si>
@@ -653,6 +653,9 @@
     <t>Plan B  - Hops Signature Zamba (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Plan B  - Static Cloud (NEIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Plan B  - Отличный план (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1599,6 +1602,9 @@
   </si>
   <si>
     <t>вынос_Plague Brew - Saltlake (Gose), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Plan B  - Static Cloud (NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Plan B  - Отличный план (IPA), РОЗЛИВ, Россия</t>
@@ -2588,7 +2594,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B739"/>
+  <dimension ref="A1:B741"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -4288,7 +4294,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4296,7 +4302,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4304,7 +4310,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4312,7 +4318,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4320,7 +4326,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4328,7 +4334,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4336,7 +4342,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4360,7 +4366,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4368,7 +4374,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4376,7 +4382,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4392,7 +4398,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4400,7 +4406,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4408,7 +4414,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>758</v>
+        <v>500</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4416,7 +4422,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>2273</v>
+        <v>758</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4424,7 +4430,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>1515</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4432,7 +4438,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>520</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4440,7 +4446,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4448,7 +4454,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4456,7 +4462,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4464,7 +4470,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4480,7 +4486,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4488,7 +4494,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4496,7 +4502,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4504,7 +4510,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4512,7 +4518,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4520,7 +4526,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4528,7 +4534,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4536,7 +4542,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4544,7 +4550,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4552,7 +4558,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4560,7 +4566,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4568,7 +4574,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4576,7 +4582,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4584,7 +4590,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4592,7 +4598,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>460</v>
+        <v>580</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4600,7 +4606,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4608,7 +4614,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4616,7 +4622,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4624,7 +4630,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4648,7 +4654,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4664,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>1000</v>
+        <v>560</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4672,7 +4678,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4680,7 +4686,7 @@
         <v>261</v>
       </c>
       <c r="B261" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4688,7 +4694,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4696,7 +4702,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4704,7 +4710,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4712,7 +4718,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4720,7 +4726,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4728,7 +4734,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4736,7 +4742,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4744,7 +4750,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4752,7 +4758,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4760,7 +4766,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4768,7 +4774,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4776,7 +4782,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4784,7 +4790,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4792,7 +4798,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4800,7 +4806,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4808,7 +4814,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4816,7 +4822,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4824,7 +4830,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4832,7 +4838,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4840,7 +4846,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>520</v>
+        <v>880</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4848,7 +4854,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4856,7 +4862,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4864,7 +4870,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4872,7 +4878,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4880,7 +4886,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4888,7 +4894,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4896,7 +4902,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>320</v>
+        <v>520</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4904,7 +4910,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>540</v>
+        <v>320</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4912,7 +4918,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -4920,7 +4926,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -4936,7 +4942,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -4944,7 +4950,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -4952,7 +4958,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -4960,7 +4966,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>480</v>
+        <v>800</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -4968,7 +4974,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>780</v>
+        <v>480</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -4976,7 +4982,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -4984,7 +4990,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -4992,7 +4998,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5000,7 +5006,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5016,7 +5022,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5024,7 +5030,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5032,7 +5038,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5040,7 +5046,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5048,7 +5054,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5056,7 +5062,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5064,7 +5070,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5072,7 +5078,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5080,7 +5086,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5088,7 +5094,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5104,7 +5110,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5112,7 +5118,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5120,7 +5126,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5128,7 +5134,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5136,7 +5142,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5144,7 +5150,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5160,7 +5166,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5168,7 +5174,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5176,7 +5182,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>640</v>
+        <v>480</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5184,7 +5190,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5192,7 +5198,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5200,7 +5206,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5208,7 +5214,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>520</v>
+        <v>860</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5216,7 +5222,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5224,7 +5230,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5240,7 +5246,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5248,7 +5254,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>700</v>
+        <v>420</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5256,7 +5262,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5264,7 +5270,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5272,7 +5278,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5280,7 +5286,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5288,7 +5294,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5296,7 +5302,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5304,7 +5310,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5312,7 +5318,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5320,7 +5326,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>440</v>
+        <v>620</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5328,7 +5334,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>320</v>
+        <v>440</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5344,7 +5350,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>820</v>
+        <v>320</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5352,7 +5358,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5360,7 +5366,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5376,7 +5382,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5384,7 +5390,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5400,7 +5406,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5408,7 +5414,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5416,7 +5422,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5424,7 +5430,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5432,7 +5438,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5440,7 +5446,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5448,7 +5454,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5464,7 +5470,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5472,7 +5478,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5480,7 +5486,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5488,7 +5494,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5496,7 +5502,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5504,7 +5510,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5512,7 +5518,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5520,7 +5526,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5528,7 +5534,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5536,7 +5542,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5544,7 +5550,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5552,7 +5558,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5560,7 +5566,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5568,7 +5574,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5576,7 +5582,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5584,7 +5590,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5592,7 +5598,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5600,7 +5606,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5616,7 +5622,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5624,7 +5630,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5632,7 +5638,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5640,7 +5646,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5648,7 +5654,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5664,7 +5670,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5672,7 +5678,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5680,7 +5686,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5688,7 +5694,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5696,7 +5702,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5704,7 +5710,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5712,7 +5718,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5728,7 +5734,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5736,7 +5742,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5744,7 +5750,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>640</v>
+        <v>920</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5752,7 +5758,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5760,7 +5766,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5768,7 +5774,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5776,7 +5782,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5784,7 +5790,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5792,7 +5798,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5800,7 +5806,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>860</v>
+        <v>640</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5808,7 +5814,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5816,7 +5822,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5824,7 +5830,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5832,7 +5838,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5840,7 +5846,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5848,7 +5854,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5856,7 +5862,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5864,7 +5870,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5872,7 +5878,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>620</v>
+        <v>480</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5880,7 +5886,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5888,7 +5894,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5896,7 +5902,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5904,7 +5910,7 @@
         <v>414</v>
       </c>
       <c r="B414" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5912,7 +5918,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5920,7 +5926,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5928,7 +5934,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5936,7 +5942,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5944,7 +5950,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>840</v>
+        <v>480</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5952,7 +5958,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5960,7 +5966,7 @@
         <v>421</v>
       </c>
       <c r="B421" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -5968,7 +5974,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -5984,7 +5990,7 @@
         <v>424</v>
       </c>
       <c r="B424" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -5992,7 +5998,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6008,7 +6014,7 @@
         <v>427</v>
       </c>
       <c r="B427" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6016,7 +6022,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6024,7 +6030,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6032,7 +6038,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>1100</v>
+        <v>660</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6040,7 +6046,7 @@
         <v>431</v>
       </c>
       <c r="B431" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6048,7 +6054,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6056,7 +6062,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6064,7 +6070,7 @@
         <v>434</v>
       </c>
       <c r="B434" s="1">
-        <v>800</v>
+        <v>760</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6072,7 +6078,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6088,7 +6094,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6096,7 +6102,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6104,7 +6110,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6112,7 +6118,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6120,7 +6126,7 @@
         <v>441</v>
       </c>
       <c r="B441" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6128,7 +6134,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6144,7 +6150,7 @@
         <v>444</v>
       </c>
       <c r="B444" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6152,7 +6158,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6160,7 +6166,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6168,7 +6174,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6176,7 +6182,7 @@
         <v>448</v>
       </c>
       <c r="B448" s="1">
-        <v>880</v>
+        <v>620</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6184,7 +6190,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6200,7 +6206,7 @@
         <v>451</v>
       </c>
       <c r="B451" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6208,7 +6214,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6216,7 +6222,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6224,7 +6230,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>790</v>
+        <v>900</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6232,7 +6238,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>640</v>
+        <v>790</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6240,7 +6246,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6248,7 +6254,7 @@
         <v>457</v>
       </c>
       <c r="B457" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6256,7 +6262,7 @@
         <v>458</v>
       </c>
       <c r="B458" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6272,7 +6278,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6280,7 +6286,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6288,7 +6294,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6296,7 +6302,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6304,7 +6310,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6312,7 +6318,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6320,7 +6326,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6328,7 +6334,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6336,7 +6342,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6344,7 +6350,7 @@
         <v>469</v>
       </c>
       <c r="B469" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6352,7 +6358,7 @@
         <v>470</v>
       </c>
       <c r="B470" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6368,7 +6374,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6376,7 +6382,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6384,7 +6390,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6392,7 +6398,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>940</v>
+        <v>960</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6400,7 +6406,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6416,7 +6422,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>920</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6424,7 +6430,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6432,7 +6438,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6440,7 +6446,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6448,7 +6454,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6456,7 +6462,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6464,7 +6470,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6472,7 +6478,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6480,7 +6486,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6488,7 +6494,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6496,7 +6502,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6504,7 +6510,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6512,7 +6518,7 @@
         <v>490</v>
       </c>
       <c r="B490" s="1">
-        <v>540</v>
+        <v>780</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6520,7 +6526,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>1100</v>
+        <v>540</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6528,7 +6534,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6536,7 +6542,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6544,7 +6550,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6552,7 +6558,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6560,7 +6566,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6568,7 +6574,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>980</v>
+        <v>860</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6576,7 +6582,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>740</v>
+        <v>980</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6584,7 +6590,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6592,7 +6598,7 @@
         <v>500</v>
       </c>
       <c r="B500" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6616,7 +6622,7 @@
         <v>503</v>
       </c>
       <c r="B503" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6632,7 +6638,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6640,7 +6646,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6648,7 +6654,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6656,7 +6662,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6664,7 +6670,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6672,7 +6678,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6680,7 +6686,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6688,7 +6694,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6696,7 +6702,7 @@
         <v>513</v>
       </c>
       <c r="B513" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6704,7 +6710,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6712,7 +6718,7 @@
         <v>515</v>
       </c>
       <c r="B515" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6720,7 +6726,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6728,7 +6734,7 @@
         <v>517</v>
       </c>
       <c r="B517" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6736,7 +6742,7 @@
         <v>518</v>
       </c>
       <c r="B518" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6744,7 +6750,7 @@
         <v>519</v>
       </c>
       <c r="B519" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6752,7 +6758,7 @@
         <v>520</v>
       </c>
       <c r="B520" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6760,7 +6766,7 @@
         <v>521</v>
       </c>
       <c r="B521" s="1">
-        <v>1400</v>
+        <v>720</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6768,7 +6774,7 @@
         <v>522</v>
       </c>
       <c r="B522" s="1">
-        <v>720</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -6776,7 +6782,7 @@
         <v>523</v>
       </c>
       <c r="B523" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6784,7 +6790,7 @@
         <v>524</v>
       </c>
       <c r="B524" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6792,7 +6798,7 @@
         <v>525</v>
       </c>
       <c r="B525" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6800,7 +6806,7 @@
         <v>526</v>
       </c>
       <c r="B526" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6808,7 +6814,7 @@
         <v>527</v>
       </c>
       <c r="B527" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6816,7 +6822,7 @@
         <v>528</v>
       </c>
       <c r="B528" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6824,7 +6830,7 @@
         <v>529</v>
       </c>
       <c r="B529" s="1">
-        <v>760</v>
+        <v>900</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6832,7 +6838,7 @@
         <v>530</v>
       </c>
       <c r="B530" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6840,7 +6846,7 @@
         <v>531</v>
       </c>
       <c r="B531" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6848,7 +6854,7 @@
         <v>532</v>
       </c>
       <c r="B532" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6864,7 +6870,7 @@
         <v>534</v>
       </c>
       <c r="B534" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6888,7 +6894,7 @@
         <v>537</v>
       </c>
       <c r="B537" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -6896,7 +6902,7 @@
         <v>538</v>
       </c>
       <c r="B538" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -6904,7 +6910,7 @@
         <v>539</v>
       </c>
       <c r="B539" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -6912,7 +6918,7 @@
         <v>540</v>
       </c>
       <c r="B540" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -6928,7 +6934,7 @@
         <v>542</v>
       </c>
       <c r="B542" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -6936,7 +6942,7 @@
         <v>543</v>
       </c>
       <c r="B543" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -6944,7 +6950,7 @@
         <v>544</v>
       </c>
       <c r="B544" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -6952,7 +6958,7 @@
         <v>545</v>
       </c>
       <c r="B545" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -6960,7 +6966,7 @@
         <v>546</v>
       </c>
       <c r="B546" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -6968,7 +6974,7 @@
         <v>547</v>
       </c>
       <c r="B547" s="1">
-        <v>540</v>
+        <v>640</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -6984,7 +6990,7 @@
         <v>549</v>
       </c>
       <c r="B549" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -6992,7 +6998,7 @@
         <v>550</v>
       </c>
       <c r="B550" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7000,7 +7006,7 @@
         <v>551</v>
       </c>
       <c r="B551" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7008,7 +7014,7 @@
         <v>552</v>
       </c>
       <c r="B552" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7024,7 +7030,7 @@
         <v>554</v>
       </c>
       <c r="B554" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7040,7 +7046,7 @@
         <v>556</v>
       </c>
       <c r="B556" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7048,7 +7054,7 @@
         <v>557</v>
       </c>
       <c r="B557" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7056,7 +7062,7 @@
         <v>558</v>
       </c>
       <c r="B558" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7064,7 +7070,7 @@
         <v>559</v>
       </c>
       <c r="B559" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7072,7 +7078,7 @@
         <v>560</v>
       </c>
       <c r="B560" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7088,7 +7094,7 @@
         <v>562</v>
       </c>
       <c r="B562" s="1">
-        <v>800</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7096,7 +7102,7 @@
         <v>563</v>
       </c>
       <c r="B563" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7104,7 +7110,7 @@
         <v>564</v>
       </c>
       <c r="B564" s="1">
-        <v>640</v>
+        <v>800</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7112,7 +7118,7 @@
         <v>565</v>
       </c>
       <c r="B565" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7120,7 +7126,7 @@
         <v>566</v>
       </c>
       <c r="B566" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7128,7 +7134,7 @@
         <v>567</v>
       </c>
       <c r="B567" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7144,7 +7150,7 @@
         <v>569</v>
       </c>
       <c r="B569" s="1">
-        <v>880</v>
+        <v>640</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7152,7 +7158,7 @@
         <v>570</v>
       </c>
       <c r="B570" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7160,7 +7166,7 @@
         <v>571</v>
       </c>
       <c r="B571" s="1">
-        <v>600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7168,7 +7174,7 @@
         <v>572</v>
       </c>
       <c r="B572" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7184,7 +7190,7 @@
         <v>574</v>
       </c>
       <c r="B574" s="1">
-        <v>800</v>
+        <v>820</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7192,7 +7198,7 @@
         <v>575</v>
       </c>
       <c r="B575" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7200,7 +7206,7 @@
         <v>576</v>
       </c>
       <c r="B576" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7208,7 +7214,7 @@
         <v>577</v>
       </c>
       <c r="B577" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7216,7 +7222,7 @@
         <v>578</v>
       </c>
       <c r="B578" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7224,7 +7230,7 @@
         <v>579</v>
       </c>
       <c r="B579" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7232,7 +7238,7 @@
         <v>580</v>
       </c>
       <c r="B580" s="1">
-        <v>1020</v>
+        <v>720</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7240,7 +7246,7 @@
         <v>581</v>
       </c>
       <c r="B581" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7248,7 +7254,7 @@
         <v>582</v>
       </c>
       <c r="B582" s="1">
-        <v>700</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7256,7 +7262,7 @@
         <v>583</v>
       </c>
       <c r="B583" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7264,7 +7270,7 @@
         <v>584</v>
       </c>
       <c r="B584" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7272,7 +7278,7 @@
         <v>585</v>
       </c>
       <c r="B585" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7288,7 +7294,7 @@
         <v>587</v>
       </c>
       <c r="B587" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7296,7 +7302,7 @@
         <v>588</v>
       </c>
       <c r="B588" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7304,7 +7310,7 @@
         <v>589</v>
       </c>
       <c r="B589" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7312,7 +7318,7 @@
         <v>590</v>
       </c>
       <c r="B590" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7320,7 +7326,7 @@
         <v>591</v>
       </c>
       <c r="B591" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7328,7 +7334,7 @@
         <v>592</v>
       </c>
       <c r="B592" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7344,7 +7350,7 @@
         <v>594</v>
       </c>
       <c r="B594" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7360,7 +7366,7 @@
         <v>596</v>
       </c>
       <c r="B596" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7368,7 +7374,7 @@
         <v>597</v>
       </c>
       <c r="B597" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7376,7 +7382,7 @@
         <v>598</v>
       </c>
       <c r="B598" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7384,7 +7390,7 @@
         <v>599</v>
       </c>
       <c r="B599" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7392,7 +7398,7 @@
         <v>600</v>
       </c>
       <c r="B600" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7408,7 +7414,7 @@
         <v>602</v>
       </c>
       <c r="B602" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7416,7 +7422,7 @@
         <v>603</v>
       </c>
       <c r="B603" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7424,7 +7430,7 @@
         <v>604</v>
       </c>
       <c r="B604" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7432,7 +7438,7 @@
         <v>605</v>
       </c>
       <c r="B605" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7440,7 +7446,7 @@
         <v>606</v>
       </c>
       <c r="B606" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7448,7 +7454,7 @@
         <v>607</v>
       </c>
       <c r="B607" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7456,7 +7462,7 @@
         <v>608</v>
       </c>
       <c r="B608" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7464,7 +7470,7 @@
         <v>609</v>
       </c>
       <c r="B609" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7472,7 +7478,7 @@
         <v>610</v>
       </c>
       <c r="B610" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7480,7 +7486,7 @@
         <v>611</v>
       </c>
       <c r="B611" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7496,7 +7502,7 @@
         <v>613</v>
       </c>
       <c r="B613" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7504,7 +7510,7 @@
         <v>614</v>
       </c>
       <c r="B614" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7512,7 +7518,7 @@
         <v>615</v>
       </c>
       <c r="B615" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7520,7 +7526,7 @@
         <v>616</v>
       </c>
       <c r="B616" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -7528,7 +7534,7 @@
         <v>617</v>
       </c>
       <c r="B617" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -7536,7 +7542,7 @@
         <v>618</v>
       </c>
       <c r="B618" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -7544,7 +7550,7 @@
         <v>619</v>
       </c>
       <c r="B619" s="1">
-        <v>440</v>
+        <v>680</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7552,7 +7558,7 @@
         <v>620</v>
       </c>
       <c r="B620" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7560,7 +7566,7 @@
         <v>621</v>
       </c>
       <c r="B621" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -7568,7 +7574,7 @@
         <v>622</v>
       </c>
       <c r="B622" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -7576,7 +7582,7 @@
         <v>623</v>
       </c>
       <c r="B623" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -7584,7 +7590,7 @@
         <v>624</v>
       </c>
       <c r="B624" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -7592,7 +7598,7 @@
         <v>625</v>
       </c>
       <c r="B625" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -7600,7 +7606,7 @@
         <v>626</v>
       </c>
       <c r="B626" s="1">
-        <v>800</v>
+        <v>560</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -7608,7 +7614,7 @@
         <v>627</v>
       </c>
       <c r="B627" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -7616,7 +7622,7 @@
         <v>628</v>
       </c>
       <c r="B628" s="1">
-        <v>920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -7624,7 +7630,7 @@
         <v>629</v>
       </c>
       <c r="B629" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -7632,7 +7638,7 @@
         <v>630</v>
       </c>
       <c r="B630" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -7640,7 +7646,7 @@
         <v>631</v>
       </c>
       <c r="B631" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -7648,7 +7654,7 @@
         <v>632</v>
       </c>
       <c r="B632" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -7656,7 +7662,7 @@
         <v>633</v>
       </c>
       <c r="B633" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -7664,7 +7670,7 @@
         <v>634</v>
       </c>
       <c r="B634" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -7672,7 +7678,7 @@
         <v>635</v>
       </c>
       <c r="B635" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -7680,7 +7686,7 @@
         <v>636</v>
       </c>
       <c r="B636" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -7688,7 +7694,7 @@
         <v>637</v>
       </c>
       <c r="B637" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -7696,7 +7702,7 @@
         <v>638</v>
       </c>
       <c r="B638" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -7704,7 +7710,7 @@
         <v>639</v>
       </c>
       <c r="B639" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -7712,7 +7718,7 @@
         <v>640</v>
       </c>
       <c r="B640" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -7720,7 +7726,7 @@
         <v>641</v>
       </c>
       <c r="B641" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -7728,7 +7734,7 @@
         <v>642</v>
       </c>
       <c r="B642" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -7736,7 +7742,7 @@
         <v>643</v>
       </c>
       <c r="B643" s="1">
-        <v>660</v>
+        <v>860</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -7744,7 +7750,7 @@
         <v>644</v>
       </c>
       <c r="B644" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -7752,7 +7758,7 @@
         <v>645</v>
       </c>
       <c r="B645" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -7760,7 +7766,7 @@
         <v>646</v>
       </c>
       <c r="B646" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -7768,7 +7774,7 @@
         <v>647</v>
       </c>
       <c r="B647" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -7776,7 +7782,7 @@
         <v>648</v>
       </c>
       <c r="B648" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -7784,7 +7790,7 @@
         <v>649</v>
       </c>
       <c r="B649" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -7792,7 +7798,7 @@
         <v>650</v>
       </c>
       <c r="B650" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -7800,7 +7806,7 @@
         <v>651</v>
       </c>
       <c r="B651" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -7808,7 +7814,7 @@
         <v>652</v>
       </c>
       <c r="B652" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -7816,7 +7822,7 @@
         <v>653</v>
       </c>
       <c r="B653" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -7824,7 +7830,7 @@
         <v>654</v>
       </c>
       <c r="B654" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -7832,7 +7838,7 @@
         <v>655</v>
       </c>
       <c r="B655" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -7840,7 +7846,7 @@
         <v>656</v>
       </c>
       <c r="B656" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -7848,7 +7854,7 @@
         <v>657</v>
       </c>
       <c r="B657" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -7856,7 +7862,7 @@
         <v>658</v>
       </c>
       <c r="B658" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -7864,7 +7870,7 @@
         <v>659</v>
       </c>
       <c r="B659" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -7872,7 +7878,7 @@
         <v>660</v>
       </c>
       <c r="B660" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -7880,7 +7886,7 @@
         <v>661</v>
       </c>
       <c r="B661" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -7888,7 +7894,7 @@
         <v>662</v>
       </c>
       <c r="B662" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -7896,7 +7902,7 @@
         <v>663</v>
       </c>
       <c r="B663" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -7904,7 +7910,7 @@
         <v>664</v>
       </c>
       <c r="B664" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -7912,7 +7918,7 @@
         <v>665</v>
       </c>
       <c r="B665" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -7920,7 +7926,7 @@
         <v>666</v>
       </c>
       <c r="B666" s="1">
-        <v>920</v>
+        <v>500</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -7928,7 +7934,7 @@
         <v>667</v>
       </c>
       <c r="B667" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -7936,7 +7942,7 @@
         <v>668</v>
       </c>
       <c r="B668" s="1">
-        <v>1040</v>
+        <v>920</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -7944,7 +7950,7 @@
         <v>669</v>
       </c>
       <c r="B669" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -7952,7 +7958,7 @@
         <v>670</v>
       </c>
       <c r="B670" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -7960,7 +7966,7 @@
         <v>671</v>
       </c>
       <c r="B671" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -7968,7 +7974,7 @@
         <v>672</v>
       </c>
       <c r="B672" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -7976,7 +7982,7 @@
         <v>673</v>
       </c>
       <c r="B673" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -7984,7 +7990,7 @@
         <v>674</v>
       </c>
       <c r="B674" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -7992,7 +7998,7 @@
         <v>675</v>
       </c>
       <c r="B675" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8000,7 +8006,7 @@
         <v>676</v>
       </c>
       <c r="B676" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8008,7 +8014,7 @@
         <v>677</v>
       </c>
       <c r="B677" s="1">
-        <v>500</v>
+        <v>820</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8024,7 +8030,7 @@
         <v>679</v>
       </c>
       <c r="B679" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8032,7 +8038,7 @@
         <v>680</v>
       </c>
       <c r="B680" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8040,7 +8046,7 @@
         <v>681</v>
       </c>
       <c r="B681" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8048,7 +8054,7 @@
         <v>682</v>
       </c>
       <c r="B682" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8056,7 +8062,7 @@
         <v>683</v>
       </c>
       <c r="B683" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8064,7 +8070,7 @@
         <v>684</v>
       </c>
       <c r="B684" s="1">
-        <v>400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8072,7 +8078,7 @@
         <v>685</v>
       </c>
       <c r="B685" s="1">
-        <v>400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8080,7 +8086,7 @@
         <v>686</v>
       </c>
       <c r="B686" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8088,7 +8094,7 @@
         <v>687</v>
       </c>
       <c r="B687" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8104,7 +8110,7 @@
         <v>689</v>
       </c>
       <c r="B689" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8112,7 +8118,7 @@
         <v>690</v>
       </c>
       <c r="B690" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8120,7 +8126,7 @@
         <v>691</v>
       </c>
       <c r="B691" s="1">
-        <v>860</v>
+        <v>520</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8128,7 +8134,7 @@
         <v>692</v>
       </c>
       <c r="B692" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8136,7 +8142,7 @@
         <v>693</v>
       </c>
       <c r="B693" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8144,7 +8150,7 @@
         <v>694</v>
       </c>
       <c r="B694" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8152,7 +8158,7 @@
         <v>695</v>
       </c>
       <c r="B695" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8160,7 +8166,7 @@
         <v>696</v>
       </c>
       <c r="B696" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8168,7 +8174,7 @@
         <v>697</v>
       </c>
       <c r="B697" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8176,7 +8182,7 @@
         <v>698</v>
       </c>
       <c r="B698" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8184,7 +8190,7 @@
         <v>699</v>
       </c>
       <c r="B699" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8192,7 +8198,7 @@
         <v>700</v>
       </c>
       <c r="B700" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8200,7 +8206,7 @@
         <v>701</v>
       </c>
       <c r="B701" s="1">
-        <v>840</v>
+        <v>500</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8208,7 +8214,7 @@
         <v>702</v>
       </c>
       <c r="B702" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8216,7 +8222,7 @@
         <v>703</v>
       </c>
       <c r="B703" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8224,7 +8230,7 @@
         <v>704</v>
       </c>
       <c r="B704" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8232,7 +8238,7 @@
         <v>705</v>
       </c>
       <c r="B705" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8240,7 +8246,7 @@
         <v>706</v>
       </c>
       <c r="B706" s="1">
-        <v>1040</v>
+        <v>920</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8248,7 +8254,7 @@
         <v>707</v>
       </c>
       <c r="B707" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8256,7 +8262,7 @@
         <v>708</v>
       </c>
       <c r="B708" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8264,7 +8270,7 @@
         <v>709</v>
       </c>
       <c r="B709" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8272,7 +8278,7 @@
         <v>710</v>
       </c>
       <c r="B710" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8280,7 +8286,7 @@
         <v>711</v>
       </c>
       <c r="B711" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8288,7 +8294,7 @@
         <v>712</v>
       </c>
       <c r="B712" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8296,7 +8302,7 @@
         <v>713</v>
       </c>
       <c r="B713" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8304,7 +8310,7 @@
         <v>714</v>
       </c>
       <c r="B714" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8312,7 +8318,7 @@
         <v>715</v>
       </c>
       <c r="B715" s="1">
-        <v>500</v>
+        <v>820</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8328,7 +8334,7 @@
         <v>717</v>
       </c>
       <c r="B717" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8336,7 +8342,7 @@
         <v>718</v>
       </c>
       <c r="B718" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8344,7 +8350,7 @@
         <v>719</v>
       </c>
       <c r="B719" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8352,7 +8358,7 @@
         <v>720</v>
       </c>
       <c r="B720" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8360,7 +8366,7 @@
         <v>721</v>
       </c>
       <c r="B721" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8376,7 +8382,7 @@
         <v>723</v>
       </c>
       <c r="B723" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8384,7 +8390,7 @@
         <v>724</v>
       </c>
       <c r="B724" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8400,7 +8406,7 @@
         <v>726</v>
       </c>
       <c r="B726" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8408,7 +8414,7 @@
         <v>727</v>
       </c>
       <c r="B727" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8416,7 +8422,7 @@
         <v>728</v>
       </c>
       <c r="B728" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8424,7 +8430,7 @@
         <v>729</v>
       </c>
       <c r="B729" s="1">
-        <v>420</v>
+        <v>520</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8432,7 +8438,7 @@
         <v>730</v>
       </c>
       <c r="B730" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8440,7 +8446,7 @@
         <v>731</v>
       </c>
       <c r="B731" s="1">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8448,7 +8454,7 @@
         <v>732</v>
       </c>
       <c r="B732" s="1">
-        <v>760</v>
+        <v>380</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -8456,7 +8462,7 @@
         <v>733</v>
       </c>
       <c r="B733" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -8464,7 +8470,7 @@
         <v>734</v>
       </c>
       <c r="B734" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -8472,7 +8478,7 @@
         <v>735</v>
       </c>
       <c r="B735" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -8488,7 +8494,7 @@
         <v>737</v>
       </c>
       <c r="B737" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -8496,7 +8502,7 @@
         <v>738</v>
       </c>
       <c r="B738" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="739" spans="1:2">
@@ -8504,6 +8510,22 @@
         <v>739</v>
       </c>
       <c r="B739" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2">
+      <c r="A740" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="B740" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2">
+      <c r="A741" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="B741" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="744">
   <si>
     <t>Наименование</t>
   </si>
@@ -965,6 +965,9 @@
     <t>Stamm - Pinesleeper (Simcoe IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Stamm - Praha 10 (Czech Desitka), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Stamm - Red River (APA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1791,6 +1794,9 @@
   </si>
   <si>
     <t>вынос_Stamm - Pinesleeper (Simcoe IPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Stamm - Praha 10 (Czech Desitka), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Stamm - Red River (APA), РОЗЛИВ, Россия</t>
@@ -2594,7 +2600,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B741"/>
+  <dimension ref="A1:B743"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -5126,7 +5132,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5134,7 +5140,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5142,7 +5148,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5150,7 +5156,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5158,7 +5164,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5174,7 +5180,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5182,7 +5188,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5190,7 +5196,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>640</v>
+        <v>480</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5198,7 +5204,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5206,7 +5212,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5214,7 +5220,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5222,7 +5228,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>520</v>
+        <v>860</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5230,7 +5236,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5238,7 +5244,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5254,7 +5260,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5262,7 +5268,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>700</v>
+        <v>420</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5270,7 +5276,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5278,7 +5284,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5286,7 +5292,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5294,7 +5300,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5302,7 +5308,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5310,7 +5316,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5318,7 +5324,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5326,7 +5332,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5334,7 +5340,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>440</v>
+        <v>620</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5342,7 +5348,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>320</v>
+        <v>440</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5358,7 +5364,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>820</v>
+        <v>320</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5366,7 +5372,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5374,7 +5380,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5390,7 +5396,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5398,7 +5404,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5414,7 +5420,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5422,7 +5428,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5430,7 +5436,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5438,7 +5444,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5446,7 +5452,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5454,7 +5460,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5462,7 +5468,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5478,7 +5484,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5486,7 +5492,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5494,7 +5500,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5502,7 +5508,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5510,7 +5516,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5518,7 +5524,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5526,7 +5532,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5534,7 +5540,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5542,7 +5548,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5550,7 +5556,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5558,7 +5564,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5566,7 +5572,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5574,7 +5580,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5582,7 +5588,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5590,7 +5596,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5598,7 +5604,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5606,7 +5612,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5614,7 +5620,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5630,7 +5636,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5638,7 +5644,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5646,7 +5652,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5654,7 +5660,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5662,7 +5668,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5678,7 +5684,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5686,7 +5692,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5694,7 +5700,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5702,7 +5708,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5710,7 +5716,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5718,7 +5724,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5726,7 +5732,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5742,7 +5748,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5750,7 +5756,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5758,7 +5764,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>640</v>
+        <v>920</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5766,7 +5772,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5774,7 +5780,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5782,7 +5788,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5790,7 +5796,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5798,7 +5804,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5806,7 +5812,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5814,7 +5820,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>860</v>
+        <v>640</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5822,7 +5828,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5830,7 +5836,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5838,7 +5844,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5846,7 +5852,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5854,7 +5860,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5862,7 +5868,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5870,7 +5876,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5878,7 +5884,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5886,7 +5892,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>620</v>
+        <v>480</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5894,7 +5900,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5902,7 +5908,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5910,7 +5916,7 @@
         <v>414</v>
       </c>
       <c r="B414" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5918,7 +5924,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5926,7 +5932,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5934,7 +5940,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5942,7 +5948,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5950,7 +5956,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5958,7 +5964,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>840</v>
+        <v>480</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5966,7 +5972,7 @@
         <v>421</v>
       </c>
       <c r="B421" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -5974,7 +5980,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -5982,7 +5988,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -5998,7 +6004,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6006,7 +6012,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6022,7 +6028,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6030,7 +6036,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6038,7 +6044,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6046,7 +6052,7 @@
         <v>431</v>
       </c>
       <c r="B431" s="1">
-        <v>1100</v>
+        <v>660</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6054,7 +6060,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6062,7 +6068,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6070,7 +6076,7 @@
         <v>434</v>
       </c>
       <c r="B434" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6078,7 +6084,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>800</v>
+        <v>760</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6086,7 +6092,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6102,7 +6108,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6110,7 +6116,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6118,7 +6124,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6126,7 +6132,7 @@
         <v>441</v>
       </c>
       <c r="B441" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6134,7 +6140,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6142,7 +6148,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6158,7 +6164,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6166,7 +6172,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6174,7 +6180,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6182,7 +6188,7 @@
         <v>448</v>
       </c>
       <c r="B448" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6190,7 +6196,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>880</v>
+        <v>620</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6198,7 +6204,7 @@
         <v>450</v>
       </c>
       <c r="B450" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6214,7 +6220,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6222,7 +6228,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6230,7 +6236,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6238,7 +6244,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>790</v>
+        <v>900</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6246,7 +6252,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>640</v>
+        <v>790</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6254,7 +6260,7 @@
         <v>457</v>
       </c>
       <c r="B457" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6262,7 +6268,7 @@
         <v>458</v>
       </c>
       <c r="B458" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6270,7 +6276,7 @@
         <v>459</v>
       </c>
       <c r="B459" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6286,7 +6292,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6294,7 +6300,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6302,7 +6308,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6310,7 +6316,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6318,7 +6324,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6326,7 +6332,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6334,7 +6340,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6342,7 +6348,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6350,7 +6356,7 @@
         <v>469</v>
       </c>
       <c r="B469" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6358,7 +6364,7 @@
         <v>470</v>
       </c>
       <c r="B470" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6366,7 +6372,7 @@
         <v>471</v>
       </c>
       <c r="B471" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6382,7 +6388,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6390,7 +6396,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6398,7 +6404,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6406,7 +6412,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>940</v>
+        <v>960</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6414,7 +6420,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6430,7 +6436,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>920</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6438,7 +6444,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6446,7 +6452,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6454,7 +6460,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6462,7 +6468,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6470,7 +6476,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6478,7 +6484,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6486,7 +6492,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6494,7 +6500,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6502,7 +6508,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6510,7 +6516,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6518,7 +6524,7 @@
         <v>490</v>
       </c>
       <c r="B490" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6526,7 +6532,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>540</v>
+        <v>780</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6534,7 +6540,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>1100</v>
+        <v>540</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6542,7 +6548,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6550,7 +6556,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6558,7 +6564,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6566,7 +6572,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6574,7 +6580,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6582,7 +6588,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>980</v>
+        <v>860</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6590,7 +6596,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>740</v>
+        <v>980</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6598,7 +6604,7 @@
         <v>500</v>
       </c>
       <c r="B500" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6606,7 +6612,7 @@
         <v>501</v>
       </c>
       <c r="B501" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6630,7 +6636,7 @@
         <v>504</v>
       </c>
       <c r="B504" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6646,7 +6652,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6654,7 +6660,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6662,7 +6668,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6670,7 +6676,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6678,7 +6684,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6686,7 +6692,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6694,7 +6700,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6702,7 +6708,7 @@
         <v>513</v>
       </c>
       <c r="B513" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6710,7 +6716,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6718,7 +6724,7 @@
         <v>515</v>
       </c>
       <c r="B515" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6726,7 +6732,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6734,7 +6740,7 @@
         <v>517</v>
       </c>
       <c r="B517" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6742,7 +6748,7 @@
         <v>518</v>
       </c>
       <c r="B518" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6750,7 +6756,7 @@
         <v>519</v>
       </c>
       <c r="B519" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6758,7 +6764,7 @@
         <v>520</v>
       </c>
       <c r="B520" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6766,7 +6772,7 @@
         <v>521</v>
       </c>
       <c r="B521" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6774,7 +6780,7 @@
         <v>522</v>
       </c>
       <c r="B522" s="1">
-        <v>1400</v>
+        <v>720</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -6782,7 +6788,7 @@
         <v>523</v>
       </c>
       <c r="B523" s="1">
-        <v>720</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6790,7 +6796,7 @@
         <v>524</v>
       </c>
       <c r="B524" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6798,7 +6804,7 @@
         <v>525</v>
       </c>
       <c r="B525" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6806,7 +6812,7 @@
         <v>526</v>
       </c>
       <c r="B526" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6814,7 +6820,7 @@
         <v>527</v>
       </c>
       <c r="B527" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6822,7 +6828,7 @@
         <v>528</v>
       </c>
       <c r="B528" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6830,7 +6836,7 @@
         <v>529</v>
       </c>
       <c r="B529" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6838,7 +6844,7 @@
         <v>530</v>
       </c>
       <c r="B530" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6846,7 +6852,7 @@
         <v>531</v>
       </c>
       <c r="B531" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6854,7 +6860,7 @@
         <v>532</v>
       </c>
       <c r="B532" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6862,7 +6868,7 @@
         <v>533</v>
       </c>
       <c r="B533" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6870,7 +6876,7 @@
         <v>534</v>
       </c>
       <c r="B534" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6878,7 +6884,7 @@
         <v>535</v>
       </c>
       <c r="B535" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -6910,7 +6916,7 @@
         <v>539</v>
       </c>
       <c r="B539" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -6926,7 +6932,7 @@
         <v>541</v>
       </c>
       <c r="B541" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -6950,7 +6956,7 @@
         <v>544</v>
       </c>
       <c r="B544" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -6958,7 +6964,7 @@
         <v>545</v>
       </c>
       <c r="B545" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -6966,7 +6972,7 @@
         <v>546</v>
       </c>
       <c r="B546" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -6974,7 +6980,7 @@
         <v>547</v>
       </c>
       <c r="B547" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -6982,7 +6988,7 @@
         <v>548</v>
       </c>
       <c r="B548" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -6990,7 +6996,7 @@
         <v>549</v>
       </c>
       <c r="B549" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -6998,7 +7004,7 @@
         <v>550</v>
       </c>
       <c r="B550" s="1">
-        <v>660</v>
+        <v>540</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7006,7 +7012,7 @@
         <v>551</v>
       </c>
       <c r="B551" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7014,7 +7020,7 @@
         <v>552</v>
       </c>
       <c r="B552" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7022,7 +7028,7 @@
         <v>553</v>
       </c>
       <c r="B553" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7046,7 +7052,7 @@
         <v>556</v>
       </c>
       <c r="B556" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7054,7 +7060,7 @@
         <v>557</v>
       </c>
       <c r="B557" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7062,7 +7068,7 @@
         <v>558</v>
       </c>
       <c r="B558" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7070,7 +7076,7 @@
         <v>559</v>
       </c>
       <c r="B559" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7078,7 +7084,7 @@
         <v>560</v>
       </c>
       <c r="B560" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7094,7 +7100,7 @@
         <v>562</v>
       </c>
       <c r="B562" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7102,7 +7108,7 @@
         <v>563</v>
       </c>
       <c r="B563" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7110,7 +7116,7 @@
         <v>564</v>
       </c>
       <c r="B564" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7118,7 +7124,7 @@
         <v>565</v>
       </c>
       <c r="B565" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7126,7 +7132,7 @@
         <v>566</v>
       </c>
       <c r="B566" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7134,7 +7140,7 @@
         <v>567</v>
       </c>
       <c r="B567" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7142,7 +7148,7 @@
         <v>568</v>
       </c>
       <c r="B568" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7150,7 +7156,7 @@
         <v>569</v>
       </c>
       <c r="B569" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7158,7 +7164,7 @@
         <v>570</v>
       </c>
       <c r="B570" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7166,7 +7172,7 @@
         <v>571</v>
       </c>
       <c r="B571" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7174,7 +7180,7 @@
         <v>572</v>
       </c>
       <c r="B572" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7182,7 +7188,7 @@
         <v>573</v>
       </c>
       <c r="B573" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7190,7 +7196,7 @@
         <v>574</v>
       </c>
       <c r="B574" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7198,7 +7204,7 @@
         <v>575</v>
       </c>
       <c r="B575" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7206,7 +7212,7 @@
         <v>576</v>
       </c>
       <c r="B576" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7214,7 +7220,7 @@
         <v>577</v>
       </c>
       <c r="B577" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7222,7 +7228,7 @@
         <v>578</v>
       </c>
       <c r="B578" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7238,7 +7244,7 @@
         <v>580</v>
       </c>
       <c r="B580" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7246,7 +7252,7 @@
         <v>581</v>
       </c>
       <c r="B581" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7254,7 +7260,7 @@
         <v>582</v>
       </c>
       <c r="B582" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7262,7 +7268,7 @@
         <v>583</v>
       </c>
       <c r="B583" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7270,7 +7276,7 @@
         <v>584</v>
       </c>
       <c r="B584" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7278,7 +7284,7 @@
         <v>585</v>
       </c>
       <c r="B585" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7286,7 +7292,7 @@
         <v>586</v>
       </c>
       <c r="B586" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7294,7 +7300,7 @@
         <v>587</v>
       </c>
       <c r="B587" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7302,7 +7308,7 @@
         <v>588</v>
       </c>
       <c r="B588" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7310,7 +7316,7 @@
         <v>589</v>
       </c>
       <c r="B589" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7326,7 +7332,7 @@
         <v>591</v>
       </c>
       <c r="B591" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7334,7 +7340,7 @@
         <v>592</v>
       </c>
       <c r="B592" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7342,7 +7348,7 @@
         <v>593</v>
       </c>
       <c r="B593" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7350,7 +7356,7 @@
         <v>594</v>
       </c>
       <c r="B594" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7366,7 +7372,7 @@
         <v>596</v>
       </c>
       <c r="B596" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7382,7 +7388,7 @@
         <v>598</v>
       </c>
       <c r="B598" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7390,7 +7396,7 @@
         <v>599</v>
       </c>
       <c r="B599" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7398,7 +7404,7 @@
         <v>600</v>
       </c>
       <c r="B600" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7406,7 +7412,7 @@
         <v>601</v>
       </c>
       <c r="B601" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7414,7 +7420,7 @@
         <v>602</v>
       </c>
       <c r="B602" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7430,7 +7436,7 @@
         <v>604</v>
       </c>
       <c r="B604" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7438,7 +7444,7 @@
         <v>605</v>
       </c>
       <c r="B605" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7446,7 +7452,7 @@
         <v>606</v>
       </c>
       <c r="B606" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7454,7 +7460,7 @@
         <v>607</v>
       </c>
       <c r="B607" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7462,7 +7468,7 @@
         <v>608</v>
       </c>
       <c r="B608" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7470,7 +7476,7 @@
         <v>609</v>
       </c>
       <c r="B609" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7478,7 +7484,7 @@
         <v>610</v>
       </c>
       <c r="B610" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7486,7 +7492,7 @@
         <v>611</v>
       </c>
       <c r="B611" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7494,7 +7500,7 @@
         <v>612</v>
       </c>
       <c r="B612" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7502,7 +7508,7 @@
         <v>613</v>
       </c>
       <c r="B613" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7518,7 +7524,7 @@
         <v>615</v>
       </c>
       <c r="B615" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7526,7 +7532,7 @@
         <v>616</v>
       </c>
       <c r="B616" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -7534,7 +7540,7 @@
         <v>617</v>
       </c>
       <c r="B617" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -7542,7 +7548,7 @@
         <v>618</v>
       </c>
       <c r="B618" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -7550,7 +7556,7 @@
         <v>619</v>
       </c>
       <c r="B619" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7558,7 +7564,7 @@
         <v>620</v>
       </c>
       <c r="B620" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7566,7 +7572,7 @@
         <v>621</v>
       </c>
       <c r="B621" s="1">
-        <v>440</v>
+        <v>680</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -7574,7 +7580,7 @@
         <v>622</v>
       </c>
       <c r="B622" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -7582,7 +7588,7 @@
         <v>623</v>
       </c>
       <c r="B623" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -7590,7 +7596,7 @@
         <v>624</v>
       </c>
       <c r="B624" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -7598,7 +7604,7 @@
         <v>625</v>
       </c>
       <c r="B625" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -7606,7 +7612,7 @@
         <v>626</v>
       </c>
       <c r="B626" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -7614,7 +7620,7 @@
         <v>627</v>
       </c>
       <c r="B627" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -7622,7 +7628,7 @@
         <v>628</v>
       </c>
       <c r="B628" s="1">
-        <v>800</v>
+        <v>560</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -7630,7 +7636,7 @@
         <v>629</v>
       </c>
       <c r="B629" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -7638,7 +7644,7 @@
         <v>630</v>
       </c>
       <c r="B630" s="1">
-        <v>920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -7646,7 +7652,7 @@
         <v>631</v>
       </c>
       <c r="B631" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -7654,7 +7660,7 @@
         <v>632</v>
       </c>
       <c r="B632" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -7662,7 +7668,7 @@
         <v>633</v>
       </c>
       <c r="B633" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -7670,7 +7676,7 @@
         <v>634</v>
       </c>
       <c r="B634" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -7678,7 +7684,7 @@
         <v>635</v>
       </c>
       <c r="B635" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -7686,7 +7692,7 @@
         <v>636</v>
       </c>
       <c r="B636" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -7694,7 +7700,7 @@
         <v>637</v>
       </c>
       <c r="B637" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -7702,7 +7708,7 @@
         <v>638</v>
       </c>
       <c r="B638" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -7710,7 +7716,7 @@
         <v>639</v>
       </c>
       <c r="B639" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -7718,7 +7724,7 @@
         <v>640</v>
       </c>
       <c r="B640" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -7726,7 +7732,7 @@
         <v>641</v>
       </c>
       <c r="B641" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -7734,7 +7740,7 @@
         <v>642</v>
       </c>
       <c r="B642" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -7742,7 +7748,7 @@
         <v>643</v>
       </c>
       <c r="B643" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -7750,7 +7756,7 @@
         <v>644</v>
       </c>
       <c r="B644" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -7758,7 +7764,7 @@
         <v>645</v>
       </c>
       <c r="B645" s="1">
-        <v>660</v>
+        <v>860</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -7766,7 +7772,7 @@
         <v>646</v>
       </c>
       <c r="B646" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -7774,7 +7780,7 @@
         <v>647</v>
       </c>
       <c r="B647" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -7782,7 +7788,7 @@
         <v>648</v>
       </c>
       <c r="B648" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -7790,7 +7796,7 @@
         <v>649</v>
       </c>
       <c r="B649" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -7798,7 +7804,7 @@
         <v>650</v>
       </c>
       <c r="B650" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -7806,7 +7812,7 @@
         <v>651</v>
       </c>
       <c r="B651" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -7814,7 +7820,7 @@
         <v>652</v>
       </c>
       <c r="B652" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -7822,7 +7828,7 @@
         <v>653</v>
       </c>
       <c r="B653" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -7830,7 +7836,7 @@
         <v>654</v>
       </c>
       <c r="B654" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -7838,7 +7844,7 @@
         <v>655</v>
       </c>
       <c r="B655" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -7846,7 +7852,7 @@
         <v>656</v>
       </c>
       <c r="B656" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -7854,7 +7860,7 @@
         <v>657</v>
       </c>
       <c r="B657" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -7862,7 +7868,7 @@
         <v>658</v>
       </c>
       <c r="B658" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -7870,7 +7876,7 @@
         <v>659</v>
       </c>
       <c r="B659" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -7878,7 +7884,7 @@
         <v>660</v>
       </c>
       <c r="B660" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -7886,7 +7892,7 @@
         <v>661</v>
       </c>
       <c r="B661" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -7894,7 +7900,7 @@
         <v>662</v>
       </c>
       <c r="B662" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -7902,7 +7908,7 @@
         <v>663</v>
       </c>
       <c r="B663" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -7910,7 +7916,7 @@
         <v>664</v>
       </c>
       <c r="B664" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -7918,7 +7924,7 @@
         <v>665</v>
       </c>
       <c r="B665" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -7926,7 +7932,7 @@
         <v>666</v>
       </c>
       <c r="B666" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -7934,7 +7940,7 @@
         <v>667</v>
       </c>
       <c r="B667" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -7942,7 +7948,7 @@
         <v>668</v>
       </c>
       <c r="B668" s="1">
-        <v>920</v>
+        <v>500</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -7950,7 +7956,7 @@
         <v>669</v>
       </c>
       <c r="B669" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -7958,7 +7964,7 @@
         <v>670</v>
       </c>
       <c r="B670" s="1">
-        <v>1040</v>
+        <v>920</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -7966,7 +7972,7 @@
         <v>671</v>
       </c>
       <c r="B671" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -7974,7 +7980,7 @@
         <v>672</v>
       </c>
       <c r="B672" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -7982,7 +7988,7 @@
         <v>673</v>
       </c>
       <c r="B673" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -7990,7 +7996,7 @@
         <v>674</v>
       </c>
       <c r="B674" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -7998,7 +8004,7 @@
         <v>675</v>
       </c>
       <c r="B675" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8006,7 +8012,7 @@
         <v>676</v>
       </c>
       <c r="B676" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8014,7 +8020,7 @@
         <v>677</v>
       </c>
       <c r="B677" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8022,7 +8028,7 @@
         <v>678</v>
       </c>
       <c r="B678" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8030,7 +8036,7 @@
         <v>679</v>
       </c>
       <c r="B679" s="1">
-        <v>500</v>
+        <v>820</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8046,7 +8052,7 @@
         <v>681</v>
       </c>
       <c r="B681" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8054,7 +8060,7 @@
         <v>682</v>
       </c>
       <c r="B682" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8062,7 +8068,7 @@
         <v>683</v>
       </c>
       <c r="B683" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8070,7 +8076,7 @@
         <v>684</v>
       </c>
       <c r="B684" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8078,7 +8084,7 @@
         <v>685</v>
       </c>
       <c r="B685" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8086,7 +8092,7 @@
         <v>686</v>
       </c>
       <c r="B686" s="1">
-        <v>400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8094,7 +8100,7 @@
         <v>687</v>
       </c>
       <c r="B687" s="1">
-        <v>400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8102,7 +8108,7 @@
         <v>688</v>
       </c>
       <c r="B688" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8110,7 +8116,7 @@
         <v>689</v>
       </c>
       <c r="B689" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8126,7 +8132,7 @@
         <v>691</v>
       </c>
       <c r="B691" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8134,7 +8140,7 @@
         <v>692</v>
       </c>
       <c r="B692" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8142,7 +8148,7 @@
         <v>693</v>
       </c>
       <c r="B693" s="1">
-        <v>860</v>
+        <v>520</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8150,7 +8156,7 @@
         <v>694</v>
       </c>
       <c r="B694" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8158,7 +8164,7 @@
         <v>695</v>
       </c>
       <c r="B695" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8166,7 +8172,7 @@
         <v>696</v>
       </c>
       <c r="B696" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8174,7 +8180,7 @@
         <v>697</v>
       </c>
       <c r="B697" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8182,7 +8188,7 @@
         <v>698</v>
       </c>
       <c r="B698" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8190,7 +8196,7 @@
         <v>699</v>
       </c>
       <c r="B699" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8198,7 +8204,7 @@
         <v>700</v>
       </c>
       <c r="B700" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8206,7 +8212,7 @@
         <v>701</v>
       </c>
       <c r="B701" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8214,7 +8220,7 @@
         <v>702</v>
       </c>
       <c r="B702" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8222,7 +8228,7 @@
         <v>703</v>
       </c>
       <c r="B703" s="1">
-        <v>840</v>
+        <v>500</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8230,7 +8236,7 @@
         <v>704</v>
       </c>
       <c r="B704" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8238,7 +8244,7 @@
         <v>705</v>
       </c>
       <c r="B705" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8246,7 +8252,7 @@
         <v>706</v>
       </c>
       <c r="B706" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8254,7 +8260,7 @@
         <v>707</v>
       </c>
       <c r="B707" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8262,7 +8268,7 @@
         <v>708</v>
       </c>
       <c r="B708" s="1">
-        <v>1040</v>
+        <v>920</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8270,7 +8276,7 @@
         <v>709</v>
       </c>
       <c r="B709" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8278,7 +8284,7 @@
         <v>710</v>
       </c>
       <c r="B710" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8286,7 +8292,7 @@
         <v>711</v>
       </c>
       <c r="B711" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8294,7 +8300,7 @@
         <v>712</v>
       </c>
       <c r="B712" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8302,7 +8308,7 @@
         <v>713</v>
       </c>
       <c r="B713" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8310,7 +8316,7 @@
         <v>714</v>
       </c>
       <c r="B714" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8318,7 +8324,7 @@
         <v>715</v>
       </c>
       <c r="B715" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8326,7 +8332,7 @@
         <v>716</v>
       </c>
       <c r="B716" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8334,7 +8340,7 @@
         <v>717</v>
       </c>
       <c r="B717" s="1">
-        <v>500</v>
+        <v>820</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8350,7 +8356,7 @@
         <v>719</v>
       </c>
       <c r="B719" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8358,7 +8364,7 @@
         <v>720</v>
       </c>
       <c r="B720" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8366,7 +8372,7 @@
         <v>721</v>
       </c>
       <c r="B721" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8374,7 +8380,7 @@
         <v>722</v>
       </c>
       <c r="B722" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8382,7 +8388,7 @@
         <v>723</v>
       </c>
       <c r="B723" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8398,7 +8404,7 @@
         <v>725</v>
       </c>
       <c r="B725" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8406,7 +8412,7 @@
         <v>726</v>
       </c>
       <c r="B726" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8422,7 +8428,7 @@
         <v>728</v>
       </c>
       <c r="B728" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8430,7 +8436,7 @@
         <v>729</v>
       </c>
       <c r="B729" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8438,7 +8444,7 @@
         <v>730</v>
       </c>
       <c r="B730" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8446,7 +8452,7 @@
         <v>731</v>
       </c>
       <c r="B731" s="1">
-        <v>420</v>
+        <v>520</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8454,7 +8460,7 @@
         <v>732</v>
       </c>
       <c r="B732" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -8462,7 +8468,7 @@
         <v>733</v>
       </c>
       <c r="B733" s="1">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -8470,7 +8476,7 @@
         <v>734</v>
       </c>
       <c r="B734" s="1">
-        <v>820</v>
+        <v>380</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -8478,7 +8484,7 @@
         <v>735</v>
       </c>
       <c r="B735" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -8486,7 +8492,7 @@
         <v>736</v>
       </c>
       <c r="B736" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -8494,7 +8500,7 @@
         <v>737</v>
       </c>
       <c r="B737" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -8510,7 +8516,7 @@
         <v>739</v>
       </c>
       <c r="B739" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -8518,7 +8524,7 @@
         <v>740</v>
       </c>
       <c r="B740" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -8526,6 +8532,22 @@
         <v>741</v>
       </c>
       <c r="B741" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2">
+      <c r="A742" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B742" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2">
+      <c r="A743" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B743" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="752">
   <si>
     <t>Наименование</t>
   </si>
@@ -158,6 +158,9 @@
     <t>Big Village - Pacification (NE Pale Ale), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Big Village - Que Pasa (Mexican Lager), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Big Village - Roadside Story (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -173,6 +176,9 @@
     <t>Big Village - ПЕРИФЕРИЯ (NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Big Village - Пивной Шлем (NEDIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Big Village Imaginarium , РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -398,6 +404,12 @@
     <t>Jungle - Body Flow (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Jungle - Rising High (AIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>Jungle - Spin it Baby One More Time (Session NEIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Jungle - The Rush (AIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1373,6 +1385,9 @@
     <t>вынос_Big Village - Pacification (NE Pale Ale), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Big Village - Que Pasa (Mexican Lager), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Big Village - Roadside Story (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1385,6 +1400,9 @@
     <t>вынос_Big Village - ПЕРИФЕРИЯ (NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Big Village - Пивной Шлем (NEDIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Black Cat "70"  (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1497,6 +1515,12 @@
   </si>
   <si>
     <t>вынос_Jungle - Body Flow (IPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Jungle - Rising High (AIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Jungle - Spin it Baby One More Time (Session NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_KRIEKENBIER (Cherry Lager), Розлив, Бельгия</t>
@@ -2600,7 +2624,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B743"/>
+  <dimension ref="A1:B751"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -2980,7 +3004,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>860</v>
+        <v>800</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2988,7 +3012,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>480</v>
+        <v>860</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2996,7 +3020,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>760</v>
+        <v>480</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -3004,7 +3028,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3012,7 +3036,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -3020,7 +3044,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -3028,7 +3052,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3036,7 +3060,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -3044,7 +3068,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -3052,7 +3076,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -3060,7 +3084,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -3068,7 +3092,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3076,7 +3100,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -3084,7 +3108,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -3092,7 +3116,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -3108,7 +3132,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -3116,7 +3140,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -3124,7 +3148,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -3132,7 +3156,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -3156,7 +3180,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>920</v>
+        <v>820</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -3164,7 +3188,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -3172,7 +3196,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -3180,7 +3204,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>640</v>
+        <v>600</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -3188,7 +3212,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>700</v>
+        <v>880</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -3196,7 +3220,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -3212,7 +3236,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -3220,7 +3244,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -3228,7 +3252,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -3236,7 +3260,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>560</v>
+        <v>840</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -3244,7 +3268,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -3252,7 +3276,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -3284,7 +3308,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>540</v>
+        <v>480</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -3292,7 +3316,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -3300,7 +3324,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>720</v>
+        <v>540</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -3308,7 +3332,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>440</v>
+        <v>860</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3316,7 +3340,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3324,7 +3348,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>460</v>
+        <v>440</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3332,7 +3356,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>460</v>
+        <v>560</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3340,7 +3364,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>960</v>
+        <v>460</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3348,7 +3372,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>940</v>
+        <v>460</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3356,7 +3380,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3364,7 +3388,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3372,7 +3396,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>660</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3380,7 +3404,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>480</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3388,7 +3412,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>400</v>
+        <v>660</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3396,7 +3420,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3404,7 +3428,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>560</v>
+        <v>400</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3412,7 +3436,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3420,7 +3444,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3436,7 +3460,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3444,7 +3468,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>680</v>
+        <v>500</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3452,7 +3476,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>420</v>
+        <v>920</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3460,7 +3484,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>560</v>
+        <v>680</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -3468,7 +3492,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>580</v>
+        <v>420</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3476,7 +3500,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3484,7 +3508,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3492,7 +3516,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3500,7 +3524,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3508,7 +3532,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3516,7 +3540,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3524,7 +3548,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3532,7 +3556,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3540,7 +3564,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3548,7 +3572,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3556,7 +3580,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3564,7 +3588,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>720</v>
+        <v>960</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3572,7 +3596,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3580,7 +3604,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -3588,7 +3612,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>580</v>
+        <v>780</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -3596,7 +3620,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>540</v>
+        <v>500</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -3604,7 +3628,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -3612,7 +3636,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>1100</v>
+        <v>540</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -3620,7 +3644,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -3628,7 +3652,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>420</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -3636,7 +3660,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>520</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -3644,7 +3668,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -3652,7 +3676,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>460</v>
+        <v>560</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -3660,7 +3684,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -3668,7 +3692,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -3676,7 +3700,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -3684,7 +3708,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>620</v>
+        <v>460</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -3692,7 +3716,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -3700,7 +3724,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>980</v>
+        <v>580</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -3708,7 +3732,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>540</v>
+        <v>740</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -3716,7 +3740,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>580</v>
+        <v>620</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -3724,7 +3748,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -3732,7 +3756,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>760</v>
+        <v>980</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -3740,7 +3764,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -3748,7 +3772,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>1100</v>
+        <v>580</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -3756,7 +3780,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -3764,7 +3788,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -3780,7 +3804,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>640</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3788,7 +3812,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -3796,7 +3820,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="1">
-        <v>900</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -3804,7 +3828,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -3812,7 +3836,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>920</v>
+        <v>640</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3820,7 +3844,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3828,7 +3852,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3836,7 +3860,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -3844,7 +3868,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -3852,7 +3876,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -3860,7 +3884,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -3868,7 +3892,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>460</v>
+        <v>700</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -3876,7 +3900,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -3884,7 +3908,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -3892,7 +3916,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -3900,7 +3924,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>780</v>
+        <v>460</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -3908,7 +3932,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>260</v>
+        <v>580</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -3916,7 +3940,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>260</v>
+        <v>720</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -3924,7 +3948,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -3932,7 +3956,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>440</v>
+        <v>780</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -3940,7 +3964,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>800</v>
+        <v>260</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -3948,7 +3972,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>740</v>
+        <v>260</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -3956,7 +3980,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>720</v>
+        <v>440</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -3964,7 +3988,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -3972,7 +3996,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>400</v>
+        <v>800</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -3988,7 +4012,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -3996,7 +4020,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>780</v>
+        <v>500</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4004,7 +4028,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>620</v>
+        <v>400</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4012,7 +4036,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4028,7 +4052,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>580</v>
+        <v>780</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4036,7 +4060,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>580</v>
+        <v>620</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4044,7 +4068,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>620</v>
+        <v>640</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4052,7 +4076,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4084,7 +4108,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4092,7 +4116,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4100,7 +4124,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4108,7 +4132,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>580</v>
+        <v>620</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4124,7 +4148,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>700</v>
+        <v>560</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4132,7 +4156,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>820</v>
+        <v>520</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4140,7 +4164,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>760</v>
+        <v>580</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4148,7 +4172,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>720</v>
+        <v>540</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4156,7 +4180,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4164,7 +4188,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>1400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4172,7 +4196,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>480</v>
+        <v>760</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4188,7 +4212,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4196,7 +4220,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>600</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4204,7 +4228,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>700</v>
+        <v>480</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4212,7 +4236,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4220,7 +4244,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>720</v>
+        <v>660</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4228,7 +4252,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4236,7 +4260,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>520</v>
+        <v>700</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4244,7 +4268,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4252,7 +4276,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4260,7 +4284,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4268,7 +4292,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4276,7 +4300,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4284,7 +4308,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4292,7 +4316,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4300,7 +4324,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4308,7 +4332,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4316,7 +4340,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4324,7 +4348,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>760</v>
+        <v>640</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4332,7 +4356,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4340,7 +4364,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4348,7 +4372,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4356,7 +4380,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4364,7 +4388,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4380,7 +4404,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4396,7 +4420,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4404,7 +4428,7 @@
         <v>225</v>
       </c>
       <c r="B225" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4412,7 +4436,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>1000</v>
+        <v>560</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4420,7 +4444,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>500</v>
+        <v>780</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4428,7 +4452,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>758</v>
+        <v>640</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4436,7 +4460,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>2273</v>
+        <v>640</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4444,7 +4468,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>1515</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4452,7 +4476,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>520</v>
+        <v>500</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4460,7 +4484,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>720</v>
+        <v>758</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4468,7 +4492,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>560</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4476,7 +4500,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>480</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4484,7 +4508,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4500,7 +4524,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4508,7 +4532,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>700</v>
+        <v>480</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4516,7 +4540,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4524,7 +4548,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>520</v>
+        <v>720</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4532,7 +4556,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4540,7 +4564,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4556,7 +4580,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4564,7 +4588,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>380</v>
+        <v>680</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4572,7 +4596,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4580,7 +4604,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4588,7 +4612,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4596,7 +4620,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4604,7 +4628,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4612,7 +4636,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>460</v>
+        <v>540</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4628,7 +4652,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4636,7 +4660,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4644,7 +4668,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>900</v>
+        <v>460</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -4652,7 +4676,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>900</v>
+        <v>520</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4660,7 +4684,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4668,7 +4692,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4676,7 +4700,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4684,7 +4708,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4700,7 +4724,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>1040</v>
+        <v>560</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4708,7 +4732,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>680</v>
+        <v>560</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4724,7 +4748,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4732,7 +4756,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4740,7 +4764,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>1020</v>
+        <v>680</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4756,7 +4780,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>680</v>
+        <v>840</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4764,7 +4788,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>520</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4772,7 +4796,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>640</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4780,7 +4804,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4788,7 +4812,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4796,7 +4820,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>700</v>
+        <v>520</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4804,7 +4828,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4812,7 +4836,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>640</v>
+        <v>800</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4820,7 +4844,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4828,7 +4852,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4836,7 +4860,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4844,7 +4868,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4852,7 +4876,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4860,7 +4884,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>520</v>
+        <v>720</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4868,7 +4892,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4876,7 +4900,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4884,7 +4908,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4892,7 +4916,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4900,7 +4924,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>380</v>
+        <v>740</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4908,7 +4932,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>520</v>
+        <v>600</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4916,7 +4940,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>320</v>
+        <v>820</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4924,7 +4948,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>540</v>
+        <v>600</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -4932,7 +4956,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>560</v>
+        <v>380</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -4940,7 +4964,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -4948,7 +4972,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>480</v>
+        <v>320</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -4956,7 +4980,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -4964,7 +4988,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>500</v>
+        <v>560</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -4972,7 +4996,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -4988,7 +5012,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>780</v>
+        <v>520</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -4996,7 +5020,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>520</v>
+        <v>500</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5004,7 +5028,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>380</v>
+        <v>800</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5012,7 +5036,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>440</v>
+        <v>480</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5020,7 +5044,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5028,7 +5052,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>900</v>
+        <v>520</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5036,7 +5060,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>720</v>
+        <v>380</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5044,7 +5068,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>960</v>
+        <v>440</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5052,7 +5076,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5060,7 +5084,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5068,7 +5092,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5076,7 +5100,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>640</v>
+        <v>960</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5084,7 +5108,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5092,7 +5116,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5100,7 +5124,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5108,7 +5132,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5116,7 +5140,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5124,7 +5148,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5140,7 +5164,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5148,7 +5172,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5156,7 +5180,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5164,7 +5188,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5172,7 +5196,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5180,7 +5204,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5188,7 +5212,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5196,7 +5220,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5204,7 +5228,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5212,7 +5236,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5220,7 +5244,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5228,7 +5252,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>860</v>
+        <v>480</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5236,7 +5260,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>520</v>
+        <v>640</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5244,7 +5268,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>540</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5252,7 +5276,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5260,7 +5284,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>700</v>
+        <v>860</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5268,7 +5292,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>420</v>
+        <v>520</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5276,7 +5300,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5284,7 +5308,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5292,7 +5316,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5300,7 +5324,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>740</v>
+        <v>420</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5308,7 +5332,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5316,7 +5340,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>920</v>
+        <v>720</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5324,7 +5348,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>840</v>
+        <v>580</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5332,7 +5356,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5340,7 +5364,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>620</v>
+        <v>900</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5348,7 +5372,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>440</v>
+        <v>920</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5356,7 +5380,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>320</v>
+        <v>840</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5364,7 +5388,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>320</v>
+        <v>720</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5372,7 +5396,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>820</v>
+        <v>620</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5380,7 +5404,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>1000</v>
+        <v>440</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5388,7 +5412,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>580</v>
+        <v>320</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5396,7 +5420,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>580</v>
+        <v>320</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5404,7 +5428,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5412,7 +5436,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5428,7 +5452,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5444,7 +5468,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>920</v>
+        <v>580</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5452,7 +5476,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>1000</v>
+        <v>580</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5460,7 +5484,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5468,7 +5492,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5476,7 +5500,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5484,7 +5508,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5492,7 +5516,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5500,7 +5524,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>660</v>
+        <v>880</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5508,7 +5532,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5516,7 +5540,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5524,7 +5548,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5532,7 +5556,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5548,7 +5572,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>800</v>
+        <v>680</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5556,7 +5580,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5564,7 +5588,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>760</v>
+        <v>440</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5572,7 +5596,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5580,7 +5604,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5588,7 +5612,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>600</v>
+        <v>560</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5596,7 +5620,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>560</v>
+        <v>760</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5604,7 +5628,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5620,7 +5644,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>680</v>
+        <v>600</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5628,7 +5652,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5636,7 +5660,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>480</v>
+        <v>620</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5644,7 +5668,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5652,7 +5676,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>800</v>
+        <v>680</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5660,7 +5684,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="1">
-        <v>780</v>
+        <v>480</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5668,7 +5692,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="1">
-        <v>920</v>
+        <v>480</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5676,7 +5700,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5684,7 +5708,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5692,7 +5716,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>940</v>
+        <v>780</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5700,7 +5724,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>980</v>
+        <v>920</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5708,7 +5732,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5716,7 +5740,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5724,7 +5748,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>760</v>
+        <v>940</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5732,7 +5756,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5740,7 +5764,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>620</v>
+        <v>920</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5748,7 +5772,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5756,7 +5780,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5764,7 +5788,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5772,7 +5796,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5780,7 +5804,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>680</v>
+        <v>620</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5788,7 +5812,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>820</v>
+        <v>860</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5796,7 +5820,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>960</v>
+        <v>920</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5804,7 +5828,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5812,7 +5836,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5820,7 +5844,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>640</v>
+        <v>820</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5828,7 +5852,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>860</v>
+        <v>960</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5836,7 +5860,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>560</v>
+        <v>740</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5844,7 +5868,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5852,7 +5876,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5860,7 +5884,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>640</v>
+        <v>860</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5876,7 +5900,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5884,7 +5908,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>520</v>
+        <v>660</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5892,7 +5916,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>480</v>
+        <v>640</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5900,7 +5924,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5908,7 +5932,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5916,7 +5940,7 @@
         <v>414</v>
       </c>
       <c r="B414" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5924,7 +5948,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>820</v>
+        <v>480</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5932,7 +5956,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>760</v>
+        <v>620</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5940,7 +5964,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5948,7 +5972,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5956,7 +5980,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5964,7 +5988,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>480</v>
+        <v>760</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5972,7 +5996,7 @@
         <v>421</v>
       </c>
       <c r="B421" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -5980,7 +6004,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -5988,7 +6012,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -5996,7 +6020,7 @@
         <v>424</v>
       </c>
       <c r="B424" s="1">
-        <v>440</v>
+        <v>480</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6004,7 +6028,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>440</v>
+        <v>840</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6012,7 +6036,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6020,7 +6044,7 @@
         <v>427</v>
       </c>
       <c r="B427" s="1">
-        <v>880</v>
+        <v>700</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6028,7 +6052,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>880</v>
+        <v>440</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6036,7 +6060,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>760</v>
+        <v>440</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6044,7 +6068,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6052,7 +6076,7 @@
         <v>431</v>
       </c>
       <c r="B431" s="1">
-        <v>660</v>
+        <v>880</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6060,7 +6084,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>1100</v>
+        <v>880</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6068,7 +6092,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6076,7 +6100,7 @@
         <v>434</v>
       </c>
       <c r="B434" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6084,7 +6108,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6092,7 +6116,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>800</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6100,7 +6124,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6108,7 +6132,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6116,7 +6140,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6124,7 +6148,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6132,7 +6156,7 @@
         <v>441</v>
       </c>
       <c r="B441" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6140,7 +6164,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6148,7 +6172,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6156,7 +6180,7 @@
         <v>444</v>
       </c>
       <c r="B444" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6164,7 +6188,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6172,7 +6196,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6180,7 +6204,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>660</v>
+        <v>860</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6196,7 +6220,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6204,7 +6228,7 @@
         <v>450</v>
       </c>
       <c r="B450" s="1">
-        <v>880</v>
+        <v>800</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6212,7 +6236,7 @@
         <v>451</v>
       </c>
       <c r="B451" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6220,7 +6244,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>860</v>
+        <v>600</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6228,7 +6252,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>760</v>
+        <v>620</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6236,7 +6260,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>720</v>
+        <v>880</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6244,7 +6268,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6252,7 +6276,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>790</v>
+        <v>800</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6260,7 +6284,7 @@
         <v>457</v>
       </c>
       <c r="B457" s="1">
-        <v>640</v>
+        <v>860</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6268,7 +6292,7 @@
         <v>458</v>
       </c>
       <c r="B458" s="1">
-        <v>800</v>
+        <v>760</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6276,7 +6300,7 @@
         <v>459</v>
       </c>
       <c r="B459" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6284,7 +6308,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6292,7 +6316,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6300,7 +6324,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>820</v>
+        <v>790</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6308,7 +6332,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>760</v>
+        <v>640</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6316,7 +6340,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>820</v>
+        <v>800</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6324,7 +6348,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6332,7 +6356,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>920</v>
+        <v>700</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6340,7 +6364,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6348,7 +6372,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>880</v>
+        <v>820</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6356,7 +6380,7 @@
         <v>469</v>
       </c>
       <c r="B469" s="1">
-        <v>640</v>
+        <v>760</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6364,7 +6388,7 @@
         <v>470</v>
       </c>
       <c r="B470" s="1">
-        <v>700</v>
+        <v>820</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6372,7 +6396,7 @@
         <v>471</v>
       </c>
       <c r="B471" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6380,7 +6404,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>560</v>
+        <v>920</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6388,7 +6412,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6396,7 +6420,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6404,7 +6428,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6412,7 +6436,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6420,7 +6444,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>940</v>
+        <v>600</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6428,7 +6452,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>1040</v>
+        <v>560</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6436,7 +6460,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>1040</v>
+        <v>560</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6444,7 +6468,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6452,7 +6476,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6460,7 +6484,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>580</v>
+        <v>960</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6468,7 +6492,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>820</v>
+        <v>940</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6476,7 +6500,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>620</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6484,7 +6508,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6492,7 +6516,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6500,7 +6524,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6508,7 +6532,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>960</v>
+        <v>580</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6516,7 +6540,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6524,7 +6548,7 @@
         <v>490</v>
       </c>
       <c r="B490" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6532,7 +6556,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6540,7 +6564,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>540</v>
+        <v>780</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6548,7 +6572,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>1100</v>
+        <v>700</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6556,7 +6580,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>720</v>
+        <v>960</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6564,7 +6588,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6572,7 +6596,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6580,7 +6604,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6588,7 +6612,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>860</v>
+        <v>540</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6596,7 +6620,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>980</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6604,7 +6628,7 @@
         <v>500</v>
       </c>
       <c r="B500" s="1">
-        <v>740</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6612,7 +6636,7 @@
         <v>501</v>
       </c>
       <c r="B501" s="1">
-        <v>760</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6620,7 +6644,7 @@
         <v>502</v>
       </c>
       <c r="B502" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6628,7 +6652,7 @@
         <v>503</v>
       </c>
       <c r="B503" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6636,7 +6660,7 @@
         <v>504</v>
       </c>
       <c r="B504" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6644,7 +6668,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6652,7 +6676,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6660,7 +6684,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>720</v>
+        <v>980</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6668,7 +6692,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6676,7 +6700,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6684,7 +6708,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6692,7 +6716,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6700,7 +6724,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>800</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6708,7 +6732,7 @@
         <v>513</v>
       </c>
       <c r="B513" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6716,7 +6740,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6724,7 +6748,7 @@
         <v>515</v>
       </c>
       <c r="B515" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6732,7 +6756,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6740,7 +6764,7 @@
         <v>517</v>
       </c>
       <c r="B517" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6748,7 +6772,7 @@
         <v>518</v>
       </c>
       <c r="B518" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6756,7 +6780,7 @@
         <v>519</v>
       </c>
       <c r="B519" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6764,7 +6788,7 @@
         <v>520</v>
       </c>
       <c r="B520" s="1">
-        <v>820</v>
+        <v>800</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6772,7 +6796,7 @@
         <v>521</v>
       </c>
       <c r="B521" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6788,7 +6812,7 @@
         <v>523</v>
       </c>
       <c r="B523" s="1">
-        <v>1400</v>
+        <v>740</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6796,7 +6820,7 @@
         <v>524</v>
       </c>
       <c r="B524" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6804,7 +6828,7 @@
         <v>525</v>
       </c>
       <c r="B525" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6812,7 +6836,7 @@
         <v>526</v>
       </c>
       <c r="B526" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6820,7 +6844,7 @@
         <v>527</v>
       </c>
       <c r="B527" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6828,7 +6852,7 @@
         <v>528</v>
       </c>
       <c r="B528" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6836,7 +6860,7 @@
         <v>529</v>
       </c>
       <c r="B529" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6844,7 +6868,7 @@
         <v>530</v>
       </c>
       <c r="B530" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6852,7 +6876,7 @@
         <v>531</v>
       </c>
       <c r="B531" s="1">
-        <v>600</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6860,7 +6884,7 @@
         <v>532</v>
       </c>
       <c r="B532" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6868,7 +6892,7 @@
         <v>533</v>
       </c>
       <c r="B533" s="1">
-        <v>720</v>
+        <v>660</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6876,7 +6900,7 @@
         <v>534</v>
       </c>
       <c r="B534" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6884,7 +6908,7 @@
         <v>535</v>
       </c>
       <c r="B535" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -6892,7 +6916,7 @@
         <v>536</v>
       </c>
       <c r="B536" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -6908,7 +6932,7 @@
         <v>538</v>
       </c>
       <c r="B538" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -6916,7 +6940,7 @@
         <v>539</v>
       </c>
       <c r="B539" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -6924,7 +6948,7 @@
         <v>540</v>
       </c>
       <c r="B540" s="1">
-        <v>640</v>
+        <v>760</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -6932,7 +6956,7 @@
         <v>541</v>
       </c>
       <c r="B541" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -6940,7 +6964,7 @@
         <v>542</v>
       </c>
       <c r="B542" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -6948,7 +6972,7 @@
         <v>543</v>
       </c>
       <c r="B543" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -6956,7 +6980,7 @@
         <v>544</v>
       </c>
       <c r="B544" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -6964,7 +6988,7 @@
         <v>545</v>
       </c>
       <c r="B545" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -6972,7 +6996,7 @@
         <v>546</v>
       </c>
       <c r="B546" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -6980,7 +7004,7 @@
         <v>547</v>
       </c>
       <c r="B547" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -6996,7 +7020,7 @@
         <v>549</v>
       </c>
       <c r="B549" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7004,7 +7028,7 @@
         <v>550</v>
       </c>
       <c r="B550" s="1">
-        <v>540</v>
+        <v>720</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7012,7 +7036,7 @@
         <v>551</v>
       </c>
       <c r="B551" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7020,7 +7044,7 @@
         <v>552</v>
       </c>
       <c r="B552" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7028,7 +7052,7 @@
         <v>553</v>
       </c>
       <c r="B553" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7036,7 +7060,7 @@
         <v>554</v>
       </c>
       <c r="B554" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7044,7 +7068,7 @@
         <v>555</v>
       </c>
       <c r="B555" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7052,7 +7076,7 @@
         <v>556</v>
       </c>
       <c r="B556" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7060,7 +7084,7 @@
         <v>557</v>
       </c>
       <c r="B557" s="1">
-        <v>1000</v>
+        <v>660</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7068,7 +7092,7 @@
         <v>558</v>
       </c>
       <c r="B558" s="1">
-        <v>900</v>
+        <v>540</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7076,7 +7100,7 @@
         <v>559</v>
       </c>
       <c r="B559" s="1">
-        <v>1040</v>
+        <v>660</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7084,7 +7108,7 @@
         <v>560</v>
       </c>
       <c r="B560" s="1">
-        <v>680</v>
+        <v>580</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7092,7 +7116,7 @@
         <v>561</v>
       </c>
       <c r="B561" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7100,7 +7124,7 @@
         <v>562</v>
       </c>
       <c r="B562" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7108,7 +7132,7 @@
         <v>563</v>
       </c>
       <c r="B563" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7116,7 +7140,7 @@
         <v>564</v>
       </c>
       <c r="B564" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7124,7 +7148,7 @@
         <v>565</v>
       </c>
       <c r="B565" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7132,7 +7156,7 @@
         <v>566</v>
       </c>
       <c r="B566" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7140,7 +7164,7 @@
         <v>567</v>
       </c>
       <c r="B567" s="1">
-        <v>640</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7148,7 +7172,7 @@
         <v>568</v>
       </c>
       <c r="B568" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7156,7 +7180,7 @@
         <v>569</v>
       </c>
       <c r="B569" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7164,7 +7188,7 @@
         <v>570</v>
       </c>
       <c r="B570" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7172,7 +7196,7 @@
         <v>571</v>
       </c>
       <c r="B571" s="1">
-        <v>720</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7180,7 +7204,7 @@
         <v>572</v>
       </c>
       <c r="B572" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7188,7 +7212,7 @@
         <v>573</v>
       </c>
       <c r="B573" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7196,7 +7220,7 @@
         <v>574</v>
       </c>
       <c r="B574" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7204,7 +7228,7 @@
         <v>575</v>
       </c>
       <c r="B575" s="1">
-        <v>820</v>
+        <v>640</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7212,7 +7236,7 @@
         <v>576</v>
       </c>
       <c r="B576" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7220,7 +7244,7 @@
         <v>577</v>
       </c>
       <c r="B577" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7228,7 +7252,7 @@
         <v>578</v>
       </c>
       <c r="B578" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7236,7 +7260,7 @@
         <v>579</v>
       </c>
       <c r="B579" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7244,7 +7268,7 @@
         <v>580</v>
       </c>
       <c r="B580" s="1">
-        <v>900</v>
+        <v>880</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7252,7 +7276,7 @@
         <v>581</v>
       </c>
       <c r="B581" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7260,7 +7284,7 @@
         <v>582</v>
       </c>
       <c r="B582" s="1">
-        <v>960</v>
+        <v>600</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7268,7 +7292,7 @@
         <v>583</v>
       </c>
       <c r="B583" s="1">
-        <v>1020</v>
+        <v>820</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7276,7 +7300,7 @@
         <v>584</v>
       </c>
       <c r="B584" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7284,7 +7308,7 @@
         <v>585</v>
       </c>
       <c r="B585" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7292,7 +7316,7 @@
         <v>586</v>
       </c>
       <c r="B586" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7300,7 +7324,7 @@
         <v>587</v>
       </c>
       <c r="B587" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7308,7 +7332,7 @@
         <v>588</v>
       </c>
       <c r="B588" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7316,7 +7340,7 @@
         <v>589</v>
       </c>
       <c r="B589" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7324,7 +7348,7 @@
         <v>590</v>
       </c>
       <c r="B590" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7332,7 +7356,7 @@
         <v>591</v>
       </c>
       <c r="B591" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7348,7 +7372,7 @@
         <v>593</v>
       </c>
       <c r="B593" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7356,7 +7380,7 @@
         <v>594</v>
       </c>
       <c r="B594" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7364,7 +7388,7 @@
         <v>595</v>
       </c>
       <c r="B595" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7372,7 +7396,7 @@
         <v>596</v>
       </c>
       <c r="B596" s="1">
-        <v>760</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7380,7 +7404,7 @@
         <v>597</v>
       </c>
       <c r="B597" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7388,7 +7412,7 @@
         <v>598</v>
       </c>
       <c r="B598" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7396,7 +7420,7 @@
         <v>599</v>
       </c>
       <c r="B599" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7404,7 +7428,7 @@
         <v>600</v>
       </c>
       <c r="B600" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7412,7 +7436,7 @@
         <v>601</v>
       </c>
       <c r="B601" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7420,7 +7444,7 @@
         <v>602</v>
       </c>
       <c r="B602" s="1">
-        <v>860</v>
+        <v>720</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7428,7 +7452,7 @@
         <v>603</v>
       </c>
       <c r="B603" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7436,7 +7460,7 @@
         <v>604</v>
       </c>
       <c r="B604" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7444,7 +7468,7 @@
         <v>605</v>
       </c>
       <c r="B605" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7452,7 +7476,7 @@
         <v>606</v>
       </c>
       <c r="B606" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7460,7 +7484,7 @@
         <v>607</v>
       </c>
       <c r="B607" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7468,7 +7492,7 @@
         <v>608</v>
       </c>
       <c r="B608" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7476,7 +7500,7 @@
         <v>609</v>
       </c>
       <c r="B609" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7484,7 +7508,7 @@
         <v>610</v>
       </c>
       <c r="B610" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7492,7 +7516,7 @@
         <v>611</v>
       </c>
       <c r="B611" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7500,7 +7524,7 @@
         <v>612</v>
       </c>
       <c r="B612" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7508,7 +7532,7 @@
         <v>613</v>
       </c>
       <c r="B613" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7516,7 +7540,7 @@
         <v>614</v>
       </c>
       <c r="B614" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7524,7 +7548,7 @@
         <v>615</v>
       </c>
       <c r="B615" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7532,7 +7556,7 @@
         <v>616</v>
       </c>
       <c r="B616" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -7540,7 +7564,7 @@
         <v>617</v>
       </c>
       <c r="B617" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -7556,7 +7580,7 @@
         <v>619</v>
       </c>
       <c r="B619" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7564,7 +7588,7 @@
         <v>620</v>
       </c>
       <c r="B620" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7572,7 +7596,7 @@
         <v>621</v>
       </c>
       <c r="B621" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -7580,7 +7604,7 @@
         <v>622</v>
       </c>
       <c r="B622" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -7588,7 +7612,7 @@
         <v>623</v>
       </c>
       <c r="B623" s="1">
-        <v>440</v>
+        <v>880</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -7596,7 +7620,7 @@
         <v>624</v>
       </c>
       <c r="B624" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -7604,7 +7628,7 @@
         <v>625</v>
       </c>
       <c r="B625" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -7612,7 +7636,7 @@
         <v>626</v>
       </c>
       <c r="B626" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -7620,7 +7644,7 @@
         <v>627</v>
       </c>
       <c r="B627" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -7628,7 +7652,7 @@
         <v>628</v>
       </c>
       <c r="B628" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -7636,7 +7660,7 @@
         <v>629</v>
       </c>
       <c r="B629" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -7644,7 +7668,7 @@
         <v>630</v>
       </c>
       <c r="B630" s="1">
-        <v>800</v>
+        <v>660</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -7652,7 +7676,7 @@
         <v>631</v>
       </c>
       <c r="B631" s="1">
-        <v>780</v>
+        <v>440</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -7660,7 +7684,7 @@
         <v>632</v>
       </c>
       <c r="B632" s="1">
-        <v>920</v>
+        <v>700</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -7668,7 +7692,7 @@
         <v>633</v>
       </c>
       <c r="B633" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -7676,7 +7700,7 @@
         <v>634</v>
       </c>
       <c r="B634" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -7684,7 +7708,7 @@
         <v>635</v>
       </c>
       <c r="B635" s="1">
-        <v>980</v>
+        <v>600</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -7692,7 +7716,7 @@
         <v>636</v>
       </c>
       <c r="B636" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -7700,7 +7724,7 @@
         <v>637</v>
       </c>
       <c r="B637" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -7708,7 +7732,7 @@
         <v>638</v>
       </c>
       <c r="B638" s="1">
-        <v>860</v>
+        <v>800</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -7716,7 +7740,7 @@
         <v>639</v>
       </c>
       <c r="B639" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -7724,7 +7748,7 @@
         <v>640</v>
       </c>
       <c r="B640" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -7732,7 +7756,7 @@
         <v>641</v>
       </c>
       <c r="B641" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -7740,7 +7764,7 @@
         <v>642</v>
       </c>
       <c r="B642" s="1">
-        <v>960</v>
+        <v>940</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -7748,7 +7772,7 @@
         <v>643</v>
       </c>
       <c r="B643" s="1">
-        <v>740</v>
+        <v>980</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -7756,7 +7780,7 @@
         <v>644</v>
       </c>
       <c r="B644" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -7764,7 +7788,7 @@
         <v>645</v>
       </c>
       <c r="B645" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -7772,7 +7796,7 @@
         <v>646</v>
       </c>
       <c r="B646" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -7780,7 +7804,7 @@
         <v>647</v>
       </c>
       <c r="B647" s="1">
-        <v>660</v>
+        <v>920</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -7788,7 +7812,7 @@
         <v>648</v>
       </c>
       <c r="B648" s="1">
-        <v>840</v>
+        <v>680</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -7796,7 +7820,7 @@
         <v>649</v>
       </c>
       <c r="B649" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -7804,7 +7828,7 @@
         <v>650</v>
       </c>
       <c r="B650" s="1">
-        <v>820</v>
+        <v>960</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -7812,7 +7836,7 @@
         <v>651</v>
       </c>
       <c r="B651" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -7820,7 +7844,7 @@
         <v>652</v>
       </c>
       <c r="B652" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -7828,7 +7852,7 @@
         <v>653</v>
       </c>
       <c r="B653" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -7836,7 +7860,7 @@
         <v>654</v>
       </c>
       <c r="B654" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -7844,7 +7868,7 @@
         <v>655</v>
       </c>
       <c r="B655" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -7852,7 +7876,7 @@
         <v>656</v>
       </c>
       <c r="B656" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -7860,7 +7884,7 @@
         <v>657</v>
       </c>
       <c r="B657" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -7868,7 +7892,7 @@
         <v>658</v>
       </c>
       <c r="B658" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -7876,7 +7900,7 @@
         <v>659</v>
       </c>
       <c r="B659" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -7884,7 +7908,7 @@
         <v>660</v>
       </c>
       <c r="B660" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -7892,7 +7916,7 @@
         <v>661</v>
       </c>
       <c r="B661" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -7900,7 +7924,7 @@
         <v>662</v>
       </c>
       <c r="B662" s="1">
-        <v>740</v>
+        <v>600</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -7908,7 +7932,7 @@
         <v>663</v>
       </c>
       <c r="B663" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -7916,7 +7940,7 @@
         <v>664</v>
       </c>
       <c r="B664" s="1">
-        <v>720</v>
+        <v>660</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -7924,7 +7948,7 @@
         <v>665</v>
       </c>
       <c r="B665" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -7932,7 +7956,7 @@
         <v>666</v>
       </c>
       <c r="B666" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -7940,7 +7964,7 @@
         <v>667</v>
       </c>
       <c r="B667" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -7948,7 +7972,7 @@
         <v>668</v>
       </c>
       <c r="B668" s="1">
-        <v>500</v>
+        <v>860</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -7956,7 +7980,7 @@
         <v>669</v>
       </c>
       <c r="B669" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -7964,7 +7988,7 @@
         <v>670</v>
       </c>
       <c r="B670" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -7972,7 +7996,7 @@
         <v>671</v>
       </c>
       <c r="B671" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -7980,7 +8004,7 @@
         <v>672</v>
       </c>
       <c r="B672" s="1">
-        <v>1040</v>
+        <v>720</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -7988,7 +8012,7 @@
         <v>673</v>
       </c>
       <c r="B673" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -7996,7 +8020,7 @@
         <v>674</v>
       </c>
       <c r="B674" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -8004,7 +8028,7 @@
         <v>675</v>
       </c>
       <c r="B675" s="1">
-        <v>1100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8012,7 +8036,7 @@
         <v>676</v>
       </c>
       <c r="B676" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8020,7 +8044,7 @@
         <v>677</v>
       </c>
       <c r="B677" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8028,7 +8052,7 @@
         <v>678</v>
       </c>
       <c r="B678" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8036,7 +8060,7 @@
         <v>679</v>
       </c>
       <c r="B679" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8044,7 +8068,7 @@
         <v>680</v>
       </c>
       <c r="B680" s="1">
-        <v>440</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8052,7 +8076,7 @@
         <v>681</v>
       </c>
       <c r="B681" s="1">
-        <v>500</v>
+        <v>940</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8060,7 +8084,7 @@
         <v>682</v>
       </c>
       <c r="B682" s="1">
-        <v>440</v>
+        <v>900</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8068,7 +8092,7 @@
         <v>683</v>
       </c>
       <c r="B683" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8076,7 +8100,7 @@
         <v>684</v>
       </c>
       <c r="B684" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8084,7 +8108,7 @@
         <v>685</v>
       </c>
       <c r="B685" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8092,7 +8116,7 @@
         <v>686</v>
       </c>
       <c r="B686" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8100,7 +8124,7 @@
         <v>687</v>
       </c>
       <c r="B687" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8108,7 +8132,7 @@
         <v>688</v>
       </c>
       <c r="B688" s="1">
-        <v>400</v>
+        <v>440</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8116,7 +8140,7 @@
         <v>689</v>
       </c>
       <c r="B689" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8124,7 +8148,7 @@
         <v>690</v>
       </c>
       <c r="B690" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8132,7 +8156,7 @@
         <v>691</v>
       </c>
       <c r="B691" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8140,7 +8164,7 @@
         <v>692</v>
       </c>
       <c r="B692" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8148,7 +8172,7 @@
         <v>693</v>
       </c>
       <c r="B693" s="1">
-        <v>520</v>
+        <v>820</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8156,7 +8180,7 @@
         <v>694</v>
       </c>
       <c r="B694" s="1">
-        <v>700</v>
+        <v>820</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8164,7 +8188,7 @@
         <v>695</v>
       </c>
       <c r="B695" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8172,7 +8196,7 @@
         <v>696</v>
       </c>
       <c r="B696" s="1">
-        <v>680</v>
+        <v>400</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8180,7 +8204,7 @@
         <v>697</v>
       </c>
       <c r="B697" s="1">
-        <v>740</v>
+        <v>400</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8188,7 +8212,7 @@
         <v>698</v>
       </c>
       <c r="B698" s="1">
-        <v>780</v>
+        <v>380</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8196,7 +8220,7 @@
         <v>699</v>
       </c>
       <c r="B699" s="1">
-        <v>720</v>
+        <v>380</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8204,7 +8228,7 @@
         <v>700</v>
       </c>
       <c r="B700" s="1">
-        <v>720</v>
+        <v>380</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8212,7 +8236,7 @@
         <v>701</v>
       </c>
       <c r="B701" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8220,7 +8244,7 @@
         <v>702</v>
       </c>
       <c r="B702" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8228,7 +8252,7 @@
         <v>703</v>
       </c>
       <c r="B703" s="1">
-        <v>500</v>
+        <v>860</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8236,7 +8260,7 @@
         <v>704</v>
       </c>
       <c r="B704" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8244,7 +8268,7 @@
         <v>705</v>
       </c>
       <c r="B705" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8252,7 +8276,7 @@
         <v>706</v>
       </c>
       <c r="B706" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8260,7 +8284,7 @@
         <v>707</v>
       </c>
       <c r="B707" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8268,7 +8292,7 @@
         <v>708</v>
       </c>
       <c r="B708" s="1">
-        <v>920</v>
+        <v>720</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8276,7 +8300,7 @@
         <v>709</v>
       </c>
       <c r="B709" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8284,7 +8308,7 @@
         <v>710</v>
       </c>
       <c r="B710" s="1">
-        <v>1040</v>
+        <v>600</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8292,7 +8316,7 @@
         <v>711</v>
       </c>
       <c r="B711" s="1">
-        <v>940</v>
+        <v>500</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8300,7 +8324,7 @@
         <v>712</v>
       </c>
       <c r="B712" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8308,7 +8332,7 @@
         <v>713</v>
       </c>
       <c r="B713" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8316,7 +8340,7 @@
         <v>714</v>
       </c>
       <c r="B714" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8324,7 +8348,7 @@
         <v>715</v>
       </c>
       <c r="B715" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8332,7 +8356,7 @@
         <v>716</v>
       </c>
       <c r="B716" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8340,7 +8364,7 @@
         <v>717</v>
       </c>
       <c r="B717" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8348,7 +8372,7 @@
         <v>718</v>
       </c>
       <c r="B718" s="1">
-        <v>440</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8356,7 +8380,7 @@
         <v>719</v>
       </c>
       <c r="B719" s="1">
-        <v>500</v>
+        <v>940</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8364,7 +8388,7 @@
         <v>720</v>
       </c>
       <c r="B720" s="1">
-        <v>440</v>
+        <v>900</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8372,7 +8396,7 @@
         <v>721</v>
       </c>
       <c r="B721" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8380,7 +8404,7 @@
         <v>722</v>
       </c>
       <c r="B722" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8388,7 +8412,7 @@
         <v>723</v>
       </c>
       <c r="B723" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8396,7 +8420,7 @@
         <v>724</v>
       </c>
       <c r="B724" s="1">
-        <v>380</v>
+        <v>740</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8404,7 +8428,7 @@
         <v>725</v>
       </c>
       <c r="B725" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8412,7 +8436,7 @@
         <v>726</v>
       </c>
       <c r="B726" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8420,7 +8444,7 @@
         <v>727</v>
       </c>
       <c r="B727" s="1">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8428,7 +8452,7 @@
         <v>728</v>
       </c>
       <c r="B728" s="1">
-        <v>480</v>
+        <v>440</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8436,7 +8460,7 @@
         <v>729</v>
       </c>
       <c r="B729" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8444,7 +8468,7 @@
         <v>730</v>
       </c>
       <c r="B730" s="1">
-        <v>520</v>
+        <v>500</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8452,7 +8476,7 @@
         <v>731</v>
       </c>
       <c r="B731" s="1">
-        <v>520</v>
+        <v>820</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8460,7 +8484,7 @@
         <v>732</v>
       </c>
       <c r="B732" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -8468,7 +8492,7 @@
         <v>733</v>
       </c>
       <c r="B733" s="1">
-        <v>420</v>
+        <v>380</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -8484,7 +8508,7 @@
         <v>735</v>
       </c>
       <c r="B735" s="1">
-        <v>600</v>
+        <v>480</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -8492,7 +8516,7 @@
         <v>736</v>
       </c>
       <c r="B736" s="1">
-        <v>820</v>
+        <v>480</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -8500,7 +8524,7 @@
         <v>737</v>
       </c>
       <c r="B737" s="1">
-        <v>660</v>
+        <v>480</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -8508,7 +8532,7 @@
         <v>738</v>
       </c>
       <c r="B738" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="739" spans="1:2">
@@ -8516,7 +8540,7 @@
         <v>739</v>
       </c>
       <c r="B739" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -8524,7 +8548,7 @@
         <v>740</v>
       </c>
       <c r="B740" s="1">
-        <v>580</v>
+        <v>440</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -8532,7 +8556,7 @@
         <v>741</v>
       </c>
       <c r="B741" s="1">
-        <v>620</v>
+        <v>420</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -8540,7 +8564,7 @@
         <v>742</v>
       </c>
       <c r="B742" s="1">
-        <v>560</v>
+        <v>380</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -8548,6 +8572,70 @@
         <v>743</v>
       </c>
       <c r="B743" s="1">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2">
+      <c r="A744" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B744" s="1">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2">
+      <c r="A745" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B745" s="1">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2">
+      <c r="A746" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B746" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2">
+      <c r="A747" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="B747" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2">
+      <c r="A748" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="B748" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2">
+      <c r="A749" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B749" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2">
+      <c r="A750" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="B750" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2">
+      <c r="A751" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B751" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="756">
   <si>
     <t>Наименование</t>
   </si>
@@ -323,6 +323,9 @@
     <t>DUCHESSE DE BOURGOGNE (Sour red/brown), РОЗЛИВ</t>
   </si>
   <si>
+    <t>Dutch - IPA (IPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Einsiedler - Klausner Pils, РОЗЛИВ, Германия</t>
   </si>
   <si>
@@ -1172,6 +1175,9 @@
     <t>Zagovor  - And Washed Our Hops In The Sea (AIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Zagovor  - Brace Up (Dry Cider), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Zagovor  - ESB Nitro, РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1475,6 +1481,9 @@
     <t>вынос_Dieta  - Властелины Лапулина (DIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Dutch - IPA (IPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Ganza - Белое солнце (NEDIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1929,6 +1938,9 @@
   </si>
   <si>
     <t>вынос_Zagovor  - And Washed Our Hops In The Sea (AIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Zagovor  - Brace Up (Dry Cider), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Zagovor  - ESB Nitro, РОЗЛИВ, Россия</t>
@@ -2624,7 +2636,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B751"/>
+  <dimension ref="A1:B755"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -3444,7 +3456,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>560</v>
+        <v>840</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3452,7 +3464,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>500</v>
+        <v>560</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3460,7 +3472,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3468,7 +3480,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>500</v>
+        <v>760</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3476,7 +3488,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>920</v>
+        <v>500</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3484,7 +3496,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -3492,7 +3504,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>420</v>
+        <v>680</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3500,7 +3512,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3508,7 +3520,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3516,7 +3528,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3524,7 +3536,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3532,7 +3544,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3540,7 +3552,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>580</v>
+        <v>740</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3548,7 +3560,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3556,7 +3568,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3564,7 +3576,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3572,7 +3584,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3580,7 +3592,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3588,7 +3600,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3596,7 +3608,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3604,7 +3616,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -3612,7 +3624,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -3620,7 +3632,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>500</v>
+        <v>780</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -3628,7 +3640,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>580</v>
+        <v>500</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -3636,7 +3648,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -3644,7 +3656,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -3652,7 +3664,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>1100</v>
+        <v>520</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -3676,7 +3688,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -3684,7 +3696,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>420</v>
+        <v>560</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -3692,7 +3704,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>520</v>
+        <v>420</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -3700,7 +3712,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -3708,7 +3720,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>460</v>
+        <v>720</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -3716,7 +3728,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>560</v>
+        <v>460</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -3724,7 +3736,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -3732,7 +3744,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -3740,7 +3752,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -3748,7 +3760,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -3756,7 +3768,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>980</v>
+        <v>520</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -3764,7 +3776,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>540</v>
+        <v>980</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -3772,7 +3784,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -3780,7 +3792,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -3788,7 +3800,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -3796,7 +3808,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>560</v>
+        <v>760</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -3804,7 +3816,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3828,7 +3840,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -3836,7 +3848,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3844,7 +3856,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3852,7 +3864,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3860,7 +3872,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -3884,7 +3896,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -3892,7 +3904,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -3900,7 +3912,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -3908,7 +3920,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -3916,7 +3928,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -3924,7 +3936,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>460</v>
+        <v>700</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -3932,7 +3944,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -3940,7 +3952,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -3948,7 +3960,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -3956,7 +3968,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -3964,7 +3976,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -3980,7 +3992,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -3996,7 +4008,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4004,7 +4016,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4012,7 +4024,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4020,7 +4032,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4028,7 +4040,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4036,7 +4048,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>740</v>
+        <v>400</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4044,7 +4056,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4052,7 +4064,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4060,7 +4072,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4068,7 +4080,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4076,7 +4088,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4084,7 +4096,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4100,7 +4112,7 @@
         <v>184</v>
       </c>
       <c r="B184" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4108,7 +4120,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4116,7 +4128,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4132,7 +4144,7 @@
         <v>188</v>
       </c>
       <c r="B188" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4140,7 +4152,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4148,7 +4160,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4156,7 +4168,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4164,7 +4176,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4172,7 +4184,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4180,7 +4192,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4188,7 +4200,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4196,7 +4208,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4204,7 +4216,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4212,7 +4224,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4220,7 +4232,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4228,7 +4240,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>480</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4236,7 +4248,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4244,7 +4256,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4252,7 +4264,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4260,7 +4272,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4268,7 +4280,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4276,7 +4288,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4284,7 +4296,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4292,7 +4304,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4300,7 +4312,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4308,7 +4320,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4316,7 +4328,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4324,7 +4336,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4340,7 +4352,7 @@
         <v>214</v>
       </c>
       <c r="B214" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4356,7 +4368,7 @@
         <v>216</v>
       </c>
       <c r="B216" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4364,7 +4376,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4372,7 +4384,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4380,7 +4392,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4388,7 +4400,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4396,7 +4408,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4404,7 +4416,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4412,7 +4424,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4436,7 +4448,7 @@
         <v>226</v>
       </c>
       <c r="B226" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4444,7 +4456,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4452,7 +4464,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4468,7 +4480,7 @@
         <v>230</v>
       </c>
       <c r="B230" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4476,7 +4488,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4484,7 +4496,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>758</v>
+        <v>500</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4492,7 +4504,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>2273</v>
+        <v>758</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4500,7 +4512,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>1515</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4508,7 +4520,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>520</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4516,7 +4528,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4524,7 +4536,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4532,7 +4544,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4540,7 +4552,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4556,7 +4568,7 @@
         <v>241</v>
       </c>
       <c r="B241" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4564,7 +4576,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4572,7 +4584,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4580,7 +4592,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4588,7 +4600,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4596,7 +4608,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4604,7 +4616,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4612,7 +4624,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4620,7 +4632,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4628,7 +4640,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4636,7 +4648,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4644,7 +4656,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4652,7 +4664,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4660,7 +4672,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4668,7 +4680,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>460</v>
+        <v>580</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -4676,7 +4688,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4684,7 +4696,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4692,7 +4704,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4700,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4724,7 +4736,7 @@
         <v>262</v>
       </c>
       <c r="B262" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4740,7 +4752,7 @@
         <v>264</v>
       </c>
       <c r="B264" s="1">
-        <v>1000</v>
+        <v>560</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4748,7 +4760,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4756,7 +4768,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4764,7 +4776,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4772,7 +4784,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4780,7 +4792,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4788,7 +4800,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4796,7 +4808,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4804,7 +4816,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4812,7 +4824,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4820,7 +4832,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4828,7 +4840,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4836,7 +4848,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4844,7 +4856,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4852,7 +4864,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4860,7 +4872,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4868,7 +4880,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4876,7 +4888,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4884,7 +4896,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4892,7 +4904,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4900,7 +4912,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4908,7 +4920,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4916,7 +4928,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>520</v>
+        <v>880</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4924,7 +4936,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4932,7 +4944,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4940,7 +4952,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4948,7 +4960,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -4956,7 +4968,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -4964,7 +4976,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -4972,7 +4984,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>320</v>
+        <v>520</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -4980,7 +4992,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>540</v>
+        <v>320</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -4988,7 +5000,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -4996,7 +5008,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5012,7 +5024,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5020,7 +5032,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5028,7 +5040,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5036,7 +5048,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>480</v>
+        <v>800</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5044,7 +5056,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>780</v>
+        <v>480</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5052,7 +5064,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5060,7 +5072,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5068,7 +5080,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5076,7 +5088,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5092,7 +5104,7 @@
         <v>308</v>
       </c>
       <c r="B308" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5100,7 +5112,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5108,7 +5120,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5116,7 +5128,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5124,7 +5136,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5132,7 +5144,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5140,7 +5152,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5148,7 +5160,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5156,7 +5168,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5164,7 +5176,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5180,7 +5192,7 @@
         <v>319</v>
       </c>
       <c r="B319" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5196,7 +5208,7 @@
         <v>321</v>
       </c>
       <c r="B321" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5204,7 +5216,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5212,7 +5224,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5220,7 +5232,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5228,7 +5240,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5244,7 +5256,7 @@
         <v>327</v>
       </c>
       <c r="B327" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5252,7 +5264,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5260,7 +5272,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>640</v>
+        <v>480</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5268,7 +5280,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5276,7 +5288,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5284,7 +5296,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5292,7 +5304,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>520</v>
+        <v>860</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5300,7 +5312,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5308,7 +5320,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5324,7 +5336,7 @@
         <v>337</v>
       </c>
       <c r="B337" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5332,7 +5344,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>700</v>
+        <v>420</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5340,7 +5352,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5348,7 +5360,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5356,7 +5368,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5364,7 +5376,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5372,7 +5384,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5380,7 +5392,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5388,7 +5400,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5396,7 +5408,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5404,7 +5416,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>440</v>
+        <v>620</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5412,7 +5424,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>320</v>
+        <v>440</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5428,7 +5440,7 @@
         <v>350</v>
       </c>
       <c r="B350" s="1">
-        <v>820</v>
+        <v>320</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5436,7 +5448,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5444,7 +5456,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5460,7 +5472,7 @@
         <v>354</v>
       </c>
       <c r="B354" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5468,7 +5480,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5484,7 +5496,7 @@
         <v>357</v>
       </c>
       <c r="B357" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5492,7 +5504,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5500,7 +5512,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5508,7 +5520,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5516,7 +5528,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5524,7 +5536,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5532,7 +5544,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5548,7 +5560,7 @@
         <v>365</v>
       </c>
       <c r="B365" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5556,7 +5568,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5564,7 +5576,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5572,7 +5584,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5580,7 +5592,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5588,7 +5600,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5596,7 +5608,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5604,7 +5616,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5612,7 +5624,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5620,7 +5632,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5628,7 +5640,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5636,7 +5648,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5644,7 +5656,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5652,7 +5664,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5660,7 +5672,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5668,7 +5680,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5676,7 +5688,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5684,7 +5696,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5700,7 +5712,7 @@
         <v>384</v>
       </c>
       <c r="B384" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5708,7 +5720,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5716,7 +5728,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5724,7 +5736,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5732,7 +5744,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5740,7 +5752,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5748,7 +5760,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5756,7 +5768,7 @@
         <v>391</v>
       </c>
       <c r="B391" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5764,7 +5776,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5772,7 +5784,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>600</v>
+        <v>980</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5780,7 +5792,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>760</v>
+        <v>920</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5788,7 +5800,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5796,7 +5808,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>620</v>
+        <v>760</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5804,7 +5816,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5812,7 +5824,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5820,7 +5832,7 @@
         <v>399</v>
       </c>
       <c r="B399" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5828,7 +5840,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>640</v>
+        <v>860</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5836,7 +5848,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5844,7 +5856,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>820</v>
+        <v>640</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5852,7 +5864,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5860,7 +5872,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5868,7 +5880,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5876,7 +5888,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5884,7 +5896,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5892,7 +5904,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5900,7 +5912,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5908,7 +5920,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5916,7 +5928,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5924,7 +5936,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5932,7 +5944,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>840</v>
+        <v>640</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5940,7 +5952,7 @@
         <v>414</v>
       </c>
       <c r="B414" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5948,7 +5960,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>480</v>
+        <v>840</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5956,7 +5968,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5964,7 +5976,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>780</v>
+        <v>480</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5972,7 +5984,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5980,7 +5992,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -5988,7 +6000,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -5996,7 +6008,7 @@
         <v>421</v>
       </c>
       <c r="B421" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -6004,7 +6016,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -6012,7 +6024,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -6020,7 +6032,7 @@
         <v>424</v>
       </c>
       <c r="B424" s="1">
-        <v>480</v>
+        <v>780</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6028,7 +6040,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6036,7 +6048,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>660</v>
+        <v>480</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6044,7 +6056,7 @@
         <v>427</v>
       </c>
       <c r="B427" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6052,7 +6064,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6060,7 +6072,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6068,7 +6080,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6076,7 +6088,7 @@
         <v>431</v>
       </c>
       <c r="B431" s="1">
-        <v>880</v>
+        <v>440</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6084,7 +6096,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6092,7 +6104,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6100,7 +6112,7 @@
         <v>434</v>
       </c>
       <c r="B434" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6108,7 +6120,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6116,7 +6128,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6124,7 +6136,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6132,7 +6144,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6140,7 +6152,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6148,7 +6160,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6156,7 +6168,7 @@
         <v>441</v>
       </c>
       <c r="B441" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6164,7 +6176,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6172,7 +6184,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6180,7 +6192,7 @@
         <v>444</v>
       </c>
       <c r="B444" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6188,7 +6200,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6196,7 +6208,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6204,7 +6216,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6212,7 +6224,7 @@
         <v>448</v>
       </c>
       <c r="B448" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6220,7 +6232,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6228,7 +6240,7 @@
         <v>450</v>
       </c>
       <c r="B450" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6236,7 +6248,7 @@
         <v>451</v>
       </c>
       <c r="B451" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6244,7 +6256,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6252,7 +6264,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6260,7 +6272,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6268,7 +6280,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6276,7 +6288,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>800</v>
+        <v>880</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6292,7 +6304,7 @@
         <v>458</v>
       </c>
       <c r="B458" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6300,7 +6312,7 @@
         <v>459</v>
       </c>
       <c r="B459" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6308,7 +6320,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6316,7 +6328,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6324,7 +6336,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>790</v>
+        <v>900</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6332,7 +6344,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>640</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6340,7 +6352,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>800</v>
+        <v>790</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6348,7 +6360,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6356,7 +6368,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6364,7 +6376,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6372,7 +6384,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6380,7 +6392,7 @@
         <v>469</v>
       </c>
       <c r="B469" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6404,7 +6416,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>920</v>
+        <v>820</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6412,7 +6424,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6420,7 +6432,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6428,7 +6440,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>640</v>
+        <v>600</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6436,7 +6448,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>700</v>
+        <v>880</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6444,7 +6456,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6452,7 +6464,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6460,7 +6472,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6468,7 +6480,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6476,7 +6488,7 @@
         <v>481</v>
       </c>
       <c r="B481" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6484,7 +6496,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6492,7 +6504,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6500,7 +6512,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6508,7 +6520,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6516,7 +6528,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>920</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6524,7 +6536,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6532,7 +6544,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>580</v>
+        <v>840</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6540,7 +6552,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6548,7 +6560,7 @@
         <v>490</v>
       </c>
       <c r="B490" s="1">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6556,7 +6568,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6564,7 +6576,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6572,7 +6584,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>700</v>
+        <v>620</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6580,7 +6592,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6588,7 +6600,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6596,7 +6608,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6604,7 +6616,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6612,7 +6624,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>540</v>
+        <v>600</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6620,7 +6632,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6628,7 +6640,7 @@
         <v>500</v>
       </c>
       <c r="B500" s="1">
-        <v>1100</v>
+        <v>780</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6636,7 +6648,7 @@
         <v>501</v>
       </c>
       <c r="B501" s="1">
-        <v>1100</v>
+        <v>540</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6644,7 +6656,7 @@
         <v>502</v>
       </c>
       <c r="B502" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6652,7 +6664,7 @@
         <v>503</v>
       </c>
       <c r="B503" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6660,7 +6672,7 @@
         <v>504</v>
       </c>
       <c r="B504" s="1">
-        <v>740</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6668,7 +6680,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6676,7 +6688,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6684,7 +6696,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6692,7 +6704,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>740</v>
+        <v>620</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6700,7 +6712,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6708,7 +6720,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>1100</v>
+        <v>980</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6716,7 +6728,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6724,7 +6736,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6732,7 +6744,7 @@
         <v>513</v>
       </c>
       <c r="B513" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6740,7 +6752,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6748,7 +6760,7 @@
         <v>515</v>
       </c>
       <c r="B515" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6756,7 +6768,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6764,7 +6776,7 @@
         <v>517</v>
       </c>
       <c r="B517" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6772,7 +6784,7 @@
         <v>518</v>
       </c>
       <c r="B518" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6780,7 +6792,7 @@
         <v>519</v>
       </c>
       <c r="B519" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6788,7 +6800,7 @@
         <v>520</v>
       </c>
       <c r="B520" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6796,7 +6808,7 @@
         <v>521</v>
       </c>
       <c r="B521" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6812,7 +6824,7 @@
         <v>523</v>
       </c>
       <c r="B523" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6820,7 +6832,7 @@
         <v>524</v>
       </c>
       <c r="B524" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6828,7 +6840,7 @@
         <v>525</v>
       </c>
       <c r="B525" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6836,7 +6848,7 @@
         <v>526</v>
       </c>
       <c r="B526" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6844,7 +6856,7 @@
         <v>527</v>
       </c>
       <c r="B527" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6852,7 +6864,7 @@
         <v>528</v>
       </c>
       <c r="B528" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6860,7 +6872,7 @@
         <v>529</v>
       </c>
       <c r="B529" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6868,7 +6880,7 @@
         <v>530</v>
       </c>
       <c r="B530" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6876,7 +6888,7 @@
         <v>531</v>
       </c>
       <c r="B531" s="1">
-        <v>1400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6884,7 +6896,7 @@
         <v>532</v>
       </c>
       <c r="B532" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6892,7 +6904,7 @@
         <v>533</v>
       </c>
       <c r="B533" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6900,7 +6912,7 @@
         <v>534</v>
       </c>
       <c r="B534" s="1">
-        <v>700</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6908,7 +6920,7 @@
         <v>535</v>
       </c>
       <c r="B535" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -6916,7 +6928,7 @@
         <v>536</v>
       </c>
       <c r="B536" s="1">
-        <v>720</v>
+        <v>660</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -6924,7 +6936,7 @@
         <v>537</v>
       </c>
       <c r="B537" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -6932,7 +6944,7 @@
         <v>538</v>
       </c>
       <c r="B538" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -6940,7 +6952,7 @@
         <v>539</v>
       </c>
       <c r="B539" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -6948,7 +6960,7 @@
         <v>540</v>
       </c>
       <c r="B540" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -6956,7 +6968,7 @@
         <v>541</v>
       </c>
       <c r="B541" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -6964,7 +6976,7 @@
         <v>542</v>
       </c>
       <c r="B542" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -6972,7 +6984,7 @@
         <v>543</v>
       </c>
       <c r="B543" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -6980,7 +6992,7 @@
         <v>544</v>
       </c>
       <c r="B544" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -6996,7 +7008,7 @@
         <v>546</v>
       </c>
       <c r="B546" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -7012,7 +7024,7 @@
         <v>548</v>
       </c>
       <c r="B548" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -7020,7 +7032,7 @@
         <v>549</v>
       </c>
       <c r="B549" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7028,7 +7040,7 @@
         <v>550</v>
       </c>
       <c r="B550" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7036,7 +7048,7 @@
         <v>551</v>
       </c>
       <c r="B551" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7044,7 +7056,7 @@
         <v>552</v>
       </c>
       <c r="B552" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7052,7 +7064,7 @@
         <v>553</v>
       </c>
       <c r="B553" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7060,7 +7072,7 @@
         <v>554</v>
       </c>
       <c r="B554" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7068,7 +7080,7 @@
         <v>555</v>
       </c>
       <c r="B555" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7076,7 +7088,7 @@
         <v>556</v>
       </c>
       <c r="B556" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7084,7 +7096,7 @@
         <v>557</v>
       </c>
       <c r="B557" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7092,7 +7104,7 @@
         <v>558</v>
       </c>
       <c r="B558" s="1">
-        <v>540</v>
+        <v>680</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7100,7 +7112,7 @@
         <v>559</v>
       </c>
       <c r="B559" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7108,7 +7120,7 @@
         <v>560</v>
       </c>
       <c r="B560" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7116,7 +7128,7 @@
         <v>561</v>
       </c>
       <c r="B561" s="1">
-        <v>860</v>
+        <v>540</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7124,7 +7136,7 @@
         <v>562</v>
       </c>
       <c r="B562" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7132,7 +7144,7 @@
         <v>563</v>
       </c>
       <c r="B563" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7140,7 +7152,7 @@
         <v>564</v>
       </c>
       <c r="B564" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7148,7 +7160,7 @@
         <v>565</v>
       </c>
       <c r="B565" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7164,7 +7176,7 @@
         <v>567</v>
       </c>
       <c r="B567" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7172,7 +7184,7 @@
         <v>568</v>
       </c>
       <c r="B568" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7180,7 +7192,7 @@
         <v>569</v>
       </c>
       <c r="B569" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7188,7 +7200,7 @@
         <v>570</v>
       </c>
       <c r="B570" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7196,7 +7208,7 @@
         <v>571</v>
       </c>
       <c r="B571" s="1">
-        <v>1020</v>
+        <v>680</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7212,7 +7224,7 @@
         <v>573</v>
       </c>
       <c r="B573" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7220,7 +7232,7 @@
         <v>574</v>
       </c>
       <c r="B574" s="1">
-        <v>700</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7228,7 +7240,7 @@
         <v>575</v>
       </c>
       <c r="B575" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7236,7 +7248,7 @@
         <v>576</v>
       </c>
       <c r="B576" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7244,7 +7256,7 @@
         <v>577</v>
       </c>
       <c r="B577" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7260,7 +7272,7 @@
         <v>579</v>
       </c>
       <c r="B579" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7268,7 +7280,7 @@
         <v>580</v>
       </c>
       <c r="B580" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7276,7 +7288,7 @@
         <v>581</v>
       </c>
       <c r="B581" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7284,7 +7296,7 @@
         <v>582</v>
       </c>
       <c r="B582" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7292,7 +7304,7 @@
         <v>583</v>
       </c>
       <c r="B583" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7300,7 +7312,7 @@
         <v>584</v>
       </c>
       <c r="B584" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7308,7 +7320,7 @@
         <v>585</v>
       </c>
       <c r="B585" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7316,7 +7328,7 @@
         <v>586</v>
       </c>
       <c r="B586" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7324,7 +7336,7 @@
         <v>587</v>
       </c>
       <c r="B587" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7332,7 +7344,7 @@
         <v>588</v>
       </c>
       <c r="B588" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7340,7 +7352,7 @@
         <v>589</v>
       </c>
       <c r="B589" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7348,7 +7360,7 @@
         <v>590</v>
       </c>
       <c r="B590" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7356,7 +7368,7 @@
         <v>591</v>
       </c>
       <c r="B591" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7364,7 +7376,7 @@
         <v>592</v>
       </c>
       <c r="B592" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7372,7 +7384,7 @@
         <v>593</v>
       </c>
       <c r="B593" s="1">
-        <v>700</v>
+        <v>960</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7380,7 +7392,7 @@
         <v>594</v>
       </c>
       <c r="B594" s="1">
-        <v>640</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7396,7 +7408,7 @@
         <v>596</v>
       </c>
       <c r="B596" s="1">
-        <v>1020</v>
+        <v>700</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7404,7 +7416,7 @@
         <v>597</v>
       </c>
       <c r="B597" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7412,7 +7424,7 @@
         <v>598</v>
       </c>
       <c r="B598" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7420,7 +7432,7 @@
         <v>599</v>
       </c>
       <c r="B599" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7436,7 +7448,7 @@
         <v>601</v>
       </c>
       <c r="B601" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7444,7 +7456,7 @@
         <v>602</v>
       </c>
       <c r="B602" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7452,7 +7464,7 @@
         <v>603</v>
       </c>
       <c r="B603" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7460,7 +7472,7 @@
         <v>604</v>
       </c>
       <c r="B604" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7468,7 +7480,7 @@
         <v>605</v>
       </c>
       <c r="B605" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7476,7 +7488,7 @@
         <v>606</v>
       </c>
       <c r="B606" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7484,7 +7496,7 @@
         <v>607</v>
       </c>
       <c r="B607" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7492,7 +7504,7 @@
         <v>608</v>
       </c>
       <c r="B608" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7500,7 +7512,7 @@
         <v>609</v>
       </c>
       <c r="B609" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7508,7 +7520,7 @@
         <v>610</v>
       </c>
       <c r="B610" s="1">
-        <v>860</v>
+        <v>680</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7516,7 +7528,7 @@
         <v>611</v>
       </c>
       <c r="B611" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7524,7 +7536,7 @@
         <v>612</v>
       </c>
       <c r="B612" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7532,7 +7544,7 @@
         <v>613</v>
       </c>
       <c r="B613" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7540,7 +7552,7 @@
         <v>614</v>
       </c>
       <c r="B614" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7548,7 +7560,7 @@
         <v>615</v>
       </c>
       <c r="B615" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7556,7 +7568,7 @@
         <v>616</v>
       </c>
       <c r="B616" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -7564,7 +7576,7 @@
         <v>617</v>
       </c>
       <c r="B617" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -7572,7 +7584,7 @@
         <v>618</v>
       </c>
       <c r="B618" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -7580,7 +7592,7 @@
         <v>619</v>
       </c>
       <c r="B619" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7588,7 +7600,7 @@
         <v>620</v>
       </c>
       <c r="B620" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7596,7 +7608,7 @@
         <v>621</v>
       </c>
       <c r="B621" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -7604,7 +7616,7 @@
         <v>622</v>
       </c>
       <c r="B622" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -7612,7 +7624,7 @@
         <v>623</v>
       </c>
       <c r="B623" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -7620,7 +7632,7 @@
         <v>624</v>
       </c>
       <c r="B624" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -7636,7 +7648,7 @@
         <v>626</v>
       </c>
       <c r="B626" s="1">
-        <v>900</v>
+        <v>880</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -7644,7 +7656,7 @@
         <v>627</v>
       </c>
       <c r="B627" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -7652,7 +7664,7 @@
         <v>628</v>
       </c>
       <c r="B628" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -7660,7 +7672,7 @@
         <v>629</v>
       </c>
       <c r="B629" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -7676,7 +7688,7 @@
         <v>631</v>
       </c>
       <c r="B631" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -7684,7 +7696,7 @@
         <v>632</v>
       </c>
       <c r="B632" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -7692,7 +7704,7 @@
         <v>633</v>
       </c>
       <c r="B633" s="1">
-        <v>800</v>
+        <v>660</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -7700,7 +7712,7 @@
         <v>634</v>
       </c>
       <c r="B634" s="1">
-        <v>720</v>
+        <v>440</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -7708,7 +7720,7 @@
         <v>635</v>
       </c>
       <c r="B635" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -7716,7 +7728,7 @@
         <v>636</v>
       </c>
       <c r="B636" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -7724,7 +7736,7 @@
         <v>637</v>
       </c>
       <c r="B637" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -7732,7 +7744,7 @@
         <v>638</v>
       </c>
       <c r="B638" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -7740,7 +7752,7 @@
         <v>639</v>
       </c>
       <c r="B639" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -7748,7 +7760,7 @@
         <v>640</v>
       </c>
       <c r="B640" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -7756,7 +7768,7 @@
         <v>641</v>
       </c>
       <c r="B641" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -7764,7 +7776,7 @@
         <v>642</v>
       </c>
       <c r="B642" s="1">
-        <v>940</v>
+        <v>800</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -7772,7 +7784,7 @@
         <v>643</v>
       </c>
       <c r="B643" s="1">
-        <v>980</v>
+        <v>780</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -7788,7 +7800,7 @@
         <v>645</v>
       </c>
       <c r="B645" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -7796,7 +7808,7 @@
         <v>646</v>
       </c>
       <c r="B646" s="1">
-        <v>860</v>
+        <v>940</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -7804,7 +7816,7 @@
         <v>647</v>
       </c>
       <c r="B647" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -7812,7 +7824,7 @@
         <v>648</v>
       </c>
       <c r="B648" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -7820,7 +7832,7 @@
         <v>649</v>
       </c>
       <c r="B649" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -7828,7 +7840,7 @@
         <v>650</v>
       </c>
       <c r="B650" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -7836,7 +7848,7 @@
         <v>651</v>
       </c>
       <c r="B651" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -7844,7 +7856,7 @@
         <v>652</v>
       </c>
       <c r="B652" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -7852,7 +7864,7 @@
         <v>653</v>
       </c>
       <c r="B653" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -7860,7 +7872,7 @@
         <v>654</v>
       </c>
       <c r="B654" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -7868,7 +7880,7 @@
         <v>655</v>
       </c>
       <c r="B655" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -7876,7 +7888,7 @@
         <v>656</v>
       </c>
       <c r="B656" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -7884,7 +7896,7 @@
         <v>657</v>
       </c>
       <c r="B657" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -7892,7 +7904,7 @@
         <v>658</v>
       </c>
       <c r="B658" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -7900,7 +7912,7 @@
         <v>659</v>
       </c>
       <c r="B659" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -7908,7 +7920,7 @@
         <v>660</v>
       </c>
       <c r="B660" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -7924,7 +7936,7 @@
         <v>662</v>
       </c>
       <c r="B662" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -7932,7 +7944,7 @@
         <v>663</v>
       </c>
       <c r="B663" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -7940,7 +7952,7 @@
         <v>664</v>
       </c>
       <c r="B664" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -7948,7 +7960,7 @@
         <v>665</v>
       </c>
       <c r="B665" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -7956,7 +7968,7 @@
         <v>666</v>
       </c>
       <c r="B666" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -7964,7 +7976,7 @@
         <v>667</v>
       </c>
       <c r="B667" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -7972,7 +7984,7 @@
         <v>668</v>
       </c>
       <c r="B668" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -7980,7 +7992,7 @@
         <v>669</v>
       </c>
       <c r="B669" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -7988,7 +8000,7 @@
         <v>670</v>
       </c>
       <c r="B670" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -7996,7 +8008,7 @@
         <v>671</v>
       </c>
       <c r="B671" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -8004,7 +8016,7 @@
         <v>672</v>
       </c>
       <c r="B672" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -8012,7 +8024,7 @@
         <v>673</v>
       </c>
       <c r="B673" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8020,7 +8032,7 @@
         <v>674</v>
       </c>
       <c r="B674" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -8028,7 +8040,7 @@
         <v>675</v>
       </c>
       <c r="B675" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8036,7 +8048,7 @@
         <v>676</v>
       </c>
       <c r="B676" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8044,7 +8056,7 @@
         <v>677</v>
       </c>
       <c r="B677" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8052,7 +8064,7 @@
         <v>678</v>
       </c>
       <c r="B678" s="1">
-        <v>920</v>
+        <v>600</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8060,7 +8072,7 @@
         <v>679</v>
       </c>
       <c r="B679" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8068,7 +8080,7 @@
         <v>680</v>
       </c>
       <c r="B680" s="1">
-        <v>1040</v>
+        <v>500</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8076,7 +8088,7 @@
         <v>681</v>
       </c>
       <c r="B681" s="1">
-        <v>940</v>
+        <v>760</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8084,7 +8096,7 @@
         <v>682</v>
       </c>
       <c r="B682" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8092,7 +8104,7 @@
         <v>683</v>
       </c>
       <c r="B683" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8100,7 +8112,7 @@
         <v>684</v>
       </c>
       <c r="B684" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8108,7 +8120,7 @@
         <v>685</v>
       </c>
       <c r="B685" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8116,7 +8128,7 @@
         <v>686</v>
       </c>
       <c r="B686" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8124,7 +8136,7 @@
         <v>687</v>
       </c>
       <c r="B687" s="1">
-        <v>820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8132,7 +8144,7 @@
         <v>688</v>
       </c>
       <c r="B688" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8140,7 +8152,7 @@
         <v>689</v>
       </c>
       <c r="B689" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8148,7 +8160,7 @@
         <v>690</v>
       </c>
       <c r="B690" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8156,7 +8168,7 @@
         <v>691</v>
       </c>
       <c r="B691" s="1">
-        <v>560</v>
+        <v>820</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8164,7 +8176,7 @@
         <v>692</v>
       </c>
       <c r="B692" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8172,7 +8184,7 @@
         <v>693</v>
       </c>
       <c r="B693" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8180,7 +8192,7 @@
         <v>694</v>
       </c>
       <c r="B694" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8188,7 +8200,7 @@
         <v>695</v>
       </c>
       <c r="B695" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8196,7 +8208,7 @@
         <v>696</v>
       </c>
       <c r="B696" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8204,7 +8216,7 @@
         <v>697</v>
       </c>
       <c r="B697" s="1">
-        <v>400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8212,7 +8224,7 @@
         <v>698</v>
       </c>
       <c r="B698" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8220,7 +8232,7 @@
         <v>699</v>
       </c>
       <c r="B699" s="1">
-        <v>380</v>
+        <v>760</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8228,7 +8240,7 @@
         <v>700</v>
       </c>
       <c r="B700" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8236,7 +8248,7 @@
         <v>701</v>
       </c>
       <c r="B701" s="1">
-        <v>520</v>
+        <v>400</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8244,7 +8256,7 @@
         <v>702</v>
       </c>
       <c r="B702" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8252,7 +8264,7 @@
         <v>703</v>
       </c>
       <c r="B703" s="1">
-        <v>860</v>
+        <v>380</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8260,7 +8272,7 @@
         <v>704</v>
       </c>
       <c r="B704" s="1">
-        <v>680</v>
+        <v>380</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8268,7 +8280,7 @@
         <v>705</v>
       </c>
       <c r="B705" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8276,7 +8288,7 @@
         <v>706</v>
       </c>
       <c r="B706" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8284,7 +8296,7 @@
         <v>707</v>
       </c>
       <c r="B707" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8292,7 +8304,7 @@
         <v>708</v>
       </c>
       <c r="B708" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8300,7 +8312,7 @@
         <v>709</v>
       </c>
       <c r="B709" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8308,7 +8320,7 @@
         <v>710</v>
       </c>
       <c r="B710" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8316,7 +8328,7 @@
         <v>711</v>
       </c>
       <c r="B711" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8324,7 +8336,7 @@
         <v>712</v>
       </c>
       <c r="B712" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8332,7 +8344,7 @@
         <v>713</v>
       </c>
       <c r="B713" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8340,7 +8352,7 @@
         <v>714</v>
       </c>
       <c r="B714" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8348,7 +8360,7 @@
         <v>715</v>
       </c>
       <c r="B715" s="1">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8356,7 +8368,7 @@
         <v>716</v>
       </c>
       <c r="B716" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8364,7 +8376,7 @@
         <v>717</v>
       </c>
       <c r="B717" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8372,7 +8384,7 @@
         <v>718</v>
       </c>
       <c r="B718" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8380,7 +8392,7 @@
         <v>719</v>
       </c>
       <c r="B719" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8388,7 +8400,7 @@
         <v>720</v>
       </c>
       <c r="B720" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8396,7 +8408,7 @@
         <v>721</v>
       </c>
       <c r="B721" s="1">
-        <v>1100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8404,7 +8416,7 @@
         <v>722</v>
       </c>
       <c r="B722" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8412,7 +8424,7 @@
         <v>723</v>
       </c>
       <c r="B723" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8420,7 +8432,7 @@
         <v>724</v>
       </c>
       <c r="B724" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8428,7 +8440,7 @@
         <v>725</v>
       </c>
       <c r="B725" s="1">
-        <v>820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8436,7 +8448,7 @@
         <v>726</v>
       </c>
       <c r="B726" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8444,7 +8456,7 @@
         <v>727</v>
       </c>
       <c r="B727" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8452,7 +8464,7 @@
         <v>728</v>
       </c>
       <c r="B728" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8460,7 +8472,7 @@
         <v>729</v>
       </c>
       <c r="B729" s="1">
-        <v>560</v>
+        <v>820</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8468,7 +8480,7 @@
         <v>730</v>
       </c>
       <c r="B730" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8476,7 +8488,7 @@
         <v>731</v>
       </c>
       <c r="B731" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8484,7 +8496,7 @@
         <v>732</v>
       </c>
       <c r="B732" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -8492,7 +8504,7 @@
         <v>733</v>
       </c>
       <c r="B733" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -8500,7 +8512,7 @@
         <v>734</v>
       </c>
       <c r="B734" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -8508,7 +8520,7 @@
         <v>735</v>
       </c>
       <c r="B735" s="1">
-        <v>480</v>
+        <v>820</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -8516,7 +8528,7 @@
         <v>736</v>
       </c>
       <c r="B736" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -8524,7 +8536,7 @@
         <v>737</v>
       </c>
       <c r="B737" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -8532,7 +8544,7 @@
         <v>738</v>
       </c>
       <c r="B738" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="739" spans="1:2">
@@ -8540,7 +8552,7 @@
         <v>739</v>
       </c>
       <c r="B739" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -8548,7 +8560,7 @@
         <v>740</v>
       </c>
       <c r="B740" s="1">
-        <v>440</v>
+        <v>480</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -8556,7 +8568,7 @@
         <v>741</v>
       </c>
       <c r="B741" s="1">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -8564,7 +8576,7 @@
         <v>742</v>
       </c>
       <c r="B742" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -8572,7 +8584,7 @@
         <v>743</v>
       </c>
       <c r="B743" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="744" spans="1:2">
@@ -8580,7 +8592,7 @@
         <v>744</v>
       </c>
       <c r="B744" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -8588,7 +8600,7 @@
         <v>745</v>
       </c>
       <c r="B745" s="1">
-        <v>660</v>
+        <v>420</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -8596,7 +8608,7 @@
         <v>746</v>
       </c>
       <c r="B746" s="1">
-        <v>580</v>
+        <v>380</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -8604,7 +8616,7 @@
         <v>747</v>
       </c>
       <c r="B747" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -8612,7 +8624,7 @@
         <v>748</v>
       </c>
       <c r="B748" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -8620,7 +8632,7 @@
         <v>749</v>
       </c>
       <c r="B749" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -8628,7 +8640,7 @@
         <v>750</v>
       </c>
       <c r="B750" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="751" spans="1:2">
@@ -8636,6 +8648,38 @@
         <v>751</v>
       </c>
       <c r="B751" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2">
+      <c r="A752" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="B752" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2">
+      <c r="A753" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B753" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2">
+      <c r="A754" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="B754" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2">
+      <c r="A755" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="B755" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -323,7 +323,7 @@
     <t>DUCHESSE DE BOURGOGNE (Sour red/brown), РОЗЛИВ</t>
   </si>
   <si>
-    <t>Dutch - IPA (IPA), РОЗЛИВ, Россия</t>
+    <t>dutch. ipa (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>Einsiedler - Klausner Pils, РОЗЛИВ, Германия</t>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="758">
   <si>
     <t>Наименование</t>
   </si>
@@ -284,6 +284,9 @@
     <t>CHIBIS  - Честные 0.45 (AIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Chmeleon - Baklazka (IPL), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coma - Искра, Розлив, Россия </t>
   </si>
   <si>
@@ -1464,6 +1467,9 @@
   </si>
   <si>
     <t>вынос_CHIBIS  - Честные 0.45 (AIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Chmeleon - Baklazka (IPL), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t xml:space="preserve">вынос_Coma - Искра, Розлив, Россия </t>
@@ -2636,7 +2642,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B755"/>
+  <dimension ref="A1:B757"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -3352,7 +3358,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3360,7 +3366,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>440</v>
+        <v>720</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3368,7 +3374,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3376,7 +3382,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>460</v>
+        <v>560</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3392,7 +3398,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>960</v>
+        <v>460</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3400,7 +3406,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>940</v>
+        <v>960</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3408,7 +3414,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3424,7 +3430,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>660</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3432,7 +3438,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>480</v>
+        <v>660</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3440,7 +3446,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>400</v>
+        <v>480</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3448,7 +3454,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>720</v>
+        <v>400</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3456,7 +3462,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3464,7 +3470,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>560</v>
+        <v>840</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3472,7 +3478,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>500</v>
+        <v>560</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3480,7 +3486,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3488,7 +3494,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>500</v>
+        <v>760</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3496,7 +3502,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>920</v>
+        <v>500</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -3504,7 +3510,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3512,7 +3518,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>420</v>
+        <v>680</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3520,7 +3526,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3528,7 +3534,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3536,7 +3542,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3544,7 +3550,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3552,7 +3558,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3560,7 +3566,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>580</v>
+        <v>740</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3568,7 +3574,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3576,7 +3582,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3584,7 +3590,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3592,7 +3598,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3600,7 +3606,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3608,7 +3614,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3616,7 +3622,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -3624,7 +3630,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -3632,7 +3638,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -3640,7 +3646,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>500</v>
+        <v>780</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -3648,7 +3654,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>580</v>
+        <v>500</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -3656,7 +3662,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -3664,7 +3670,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -3672,7 +3678,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>1100</v>
+        <v>520</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -3696,7 +3702,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -3704,7 +3710,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>420</v>
+        <v>560</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -3712,7 +3718,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>520</v>
+        <v>420</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -3720,7 +3726,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -3728,7 +3734,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>460</v>
+        <v>720</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -3736,7 +3742,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>560</v>
+        <v>460</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -3744,7 +3750,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -3752,7 +3758,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -3760,7 +3766,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -3768,7 +3774,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -3776,7 +3782,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>980</v>
+        <v>520</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -3784,7 +3790,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>540</v>
+        <v>980</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -3792,7 +3798,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -3800,7 +3806,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -3808,7 +3814,7 @@
         <v>146</v>
       </c>
       <c r="B146" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -3816,7 +3822,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="1">
-        <v>560</v>
+        <v>760</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3824,7 +3830,7 @@
         <v>148</v>
       </c>
       <c r="B148" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -3848,7 +3854,7 @@
         <v>151</v>
       </c>
       <c r="B151" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3856,7 +3862,7 @@
         <v>152</v>
       </c>
       <c r="B152" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3864,7 +3870,7 @@
         <v>153</v>
       </c>
       <c r="B153" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3872,7 +3878,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -3880,7 +3886,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -3904,7 +3910,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -3912,7 +3918,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -3920,7 +3926,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -3928,7 +3934,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -3936,7 +3942,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -3944,7 +3950,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="1">
-        <v>460</v>
+        <v>700</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -3952,7 +3958,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -3960,7 +3966,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -3968,7 +3974,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -3976,7 +3982,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -3984,7 +3990,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4000,7 +4006,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -4016,7 +4022,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4024,7 +4030,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4032,7 +4038,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4040,7 +4046,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4048,7 +4054,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4056,7 +4062,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="1">
-        <v>740</v>
+        <v>400</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4064,7 +4070,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4072,7 +4078,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4080,7 +4086,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4088,7 +4094,7 @@
         <v>181</v>
       </c>
       <c r="B181" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4096,7 +4102,7 @@
         <v>182</v>
       </c>
       <c r="B182" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4104,7 +4110,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4120,7 +4126,7 @@
         <v>185</v>
       </c>
       <c r="B185" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4128,7 +4134,7 @@
         <v>186</v>
       </c>
       <c r="B186" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4136,7 +4142,7 @@
         <v>187</v>
       </c>
       <c r="B187" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4152,7 +4158,7 @@
         <v>189</v>
       </c>
       <c r="B189" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4160,7 +4166,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4168,7 +4174,7 @@
         <v>191</v>
       </c>
       <c r="B191" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4176,7 +4182,7 @@
         <v>192</v>
       </c>
       <c r="B192" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4184,7 +4190,7 @@
         <v>193</v>
       </c>
       <c r="B193" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4192,7 +4198,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4200,7 +4206,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4208,7 +4214,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4216,7 +4222,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4224,7 +4230,7 @@
         <v>198</v>
       </c>
       <c r="B198" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4232,7 +4238,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4240,7 +4246,7 @@
         <v>200</v>
       </c>
       <c r="B200" s="1">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4248,7 +4254,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="1">
-        <v>480</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4256,7 +4262,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4264,7 +4270,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4272,7 +4278,7 @@
         <v>204</v>
       </c>
       <c r="B204" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4280,7 +4286,7 @@
         <v>205</v>
       </c>
       <c r="B205" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4288,7 +4294,7 @@
         <v>206</v>
       </c>
       <c r="B206" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4296,7 +4302,7 @@
         <v>207</v>
       </c>
       <c r="B207" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4304,7 +4310,7 @@
         <v>208</v>
       </c>
       <c r="B208" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4312,7 +4318,7 @@
         <v>209</v>
       </c>
       <c r="B209" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4320,7 +4326,7 @@
         <v>210</v>
       </c>
       <c r="B210" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4328,7 +4334,7 @@
         <v>211</v>
       </c>
       <c r="B211" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4336,7 +4342,7 @@
         <v>212</v>
       </c>
       <c r="B212" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4344,7 +4350,7 @@
         <v>213</v>
       </c>
       <c r="B213" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4360,7 +4366,7 @@
         <v>215</v>
       </c>
       <c r="B215" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4376,7 +4382,7 @@
         <v>217</v>
       </c>
       <c r="B217" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4384,7 +4390,7 @@
         <v>218</v>
       </c>
       <c r="B218" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4392,7 +4398,7 @@
         <v>219</v>
       </c>
       <c r="B219" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4400,7 +4406,7 @@
         <v>220</v>
       </c>
       <c r="B220" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4408,7 +4414,7 @@
         <v>221</v>
       </c>
       <c r="B221" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4416,7 +4422,7 @@
         <v>222</v>
       </c>
       <c r="B222" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4424,7 +4430,7 @@
         <v>223</v>
       </c>
       <c r="B223" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4432,7 +4438,7 @@
         <v>224</v>
       </c>
       <c r="B224" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4456,7 +4462,7 @@
         <v>227</v>
       </c>
       <c r="B227" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4464,7 +4470,7 @@
         <v>228</v>
       </c>
       <c r="B228" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4472,7 +4478,7 @@
         <v>229</v>
       </c>
       <c r="B229" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4488,7 +4494,7 @@
         <v>231</v>
       </c>
       <c r="B231" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4496,7 +4502,7 @@
         <v>232</v>
       </c>
       <c r="B232" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4504,7 +4510,7 @@
         <v>233</v>
       </c>
       <c r="B233" s="1">
-        <v>758</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4512,7 +4518,7 @@
         <v>234</v>
       </c>
       <c r="B234" s="1">
-        <v>2273</v>
+        <v>758</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4520,7 +4526,7 @@
         <v>235</v>
       </c>
       <c r="B235" s="1">
-        <v>1515</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4528,7 +4534,7 @@
         <v>236</v>
       </c>
       <c r="B236" s="1">
-        <v>520</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4536,7 +4542,7 @@
         <v>237</v>
       </c>
       <c r="B237" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4544,7 +4550,7 @@
         <v>238</v>
       </c>
       <c r="B238" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4552,7 +4558,7 @@
         <v>239</v>
       </c>
       <c r="B239" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4560,7 +4566,7 @@
         <v>240</v>
       </c>
       <c r="B240" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4576,7 +4582,7 @@
         <v>242</v>
       </c>
       <c r="B242" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4584,7 +4590,7 @@
         <v>243</v>
       </c>
       <c r="B243" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4592,7 +4598,7 @@
         <v>244</v>
       </c>
       <c r="B244" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4600,7 +4606,7 @@
         <v>245</v>
       </c>
       <c r="B245" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4608,7 +4614,7 @@
         <v>246</v>
       </c>
       <c r="B246" s="1">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4616,7 +4622,7 @@
         <v>247</v>
       </c>
       <c r="B247" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4624,7 +4630,7 @@
         <v>248</v>
       </c>
       <c r="B248" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4632,7 +4638,7 @@
         <v>249</v>
       </c>
       <c r="B249" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4640,7 +4646,7 @@
         <v>250</v>
       </c>
       <c r="B250" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4648,7 +4654,7 @@
         <v>251</v>
       </c>
       <c r="B251" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4656,7 +4662,7 @@
         <v>252</v>
       </c>
       <c r="B252" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4664,7 +4670,7 @@
         <v>253</v>
       </c>
       <c r="B253" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4672,7 +4678,7 @@
         <v>254</v>
       </c>
       <c r="B254" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4680,7 +4686,7 @@
         <v>255</v>
       </c>
       <c r="B255" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -4688,7 +4694,7 @@
         <v>256</v>
       </c>
       <c r="B256" s="1">
-        <v>460</v>
+        <v>580</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4696,7 +4702,7 @@
         <v>257</v>
       </c>
       <c r="B257" s="1">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4704,7 +4710,7 @@
         <v>258</v>
       </c>
       <c r="B258" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4712,7 +4718,7 @@
         <v>259</v>
       </c>
       <c r="B259" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4720,7 +4726,7 @@
         <v>260</v>
       </c>
       <c r="B260" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4744,7 +4750,7 @@
         <v>263</v>
       </c>
       <c r="B263" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4760,7 +4766,7 @@
         <v>265</v>
       </c>
       <c r="B265" s="1">
-        <v>1000</v>
+        <v>560</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4768,7 +4774,7 @@
         <v>266</v>
       </c>
       <c r="B266" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4776,7 +4782,7 @@
         <v>267</v>
       </c>
       <c r="B267" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4784,7 +4790,7 @@
         <v>268</v>
       </c>
       <c r="B268" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4792,7 +4798,7 @@
         <v>269</v>
       </c>
       <c r="B269" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4800,7 +4806,7 @@
         <v>270</v>
       </c>
       <c r="B270" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4808,7 +4814,7 @@
         <v>271</v>
       </c>
       <c r="B271" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4816,7 +4822,7 @@
         <v>272</v>
       </c>
       <c r="B272" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4824,7 +4830,7 @@
         <v>273</v>
       </c>
       <c r="B273" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4832,7 +4838,7 @@
         <v>274</v>
       </c>
       <c r="B274" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4840,7 +4846,7 @@
         <v>275</v>
       </c>
       <c r="B275" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4848,7 +4854,7 @@
         <v>276</v>
       </c>
       <c r="B276" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4856,7 +4862,7 @@
         <v>277</v>
       </c>
       <c r="B277" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4864,7 +4870,7 @@
         <v>278</v>
       </c>
       <c r="B278" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4872,7 +4878,7 @@
         <v>279</v>
       </c>
       <c r="B279" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4880,7 +4886,7 @@
         <v>280</v>
       </c>
       <c r="B280" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4888,7 +4894,7 @@
         <v>281</v>
       </c>
       <c r="B281" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4896,7 +4902,7 @@
         <v>282</v>
       </c>
       <c r="B282" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4904,7 +4910,7 @@
         <v>283</v>
       </c>
       <c r="B283" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4912,7 +4918,7 @@
         <v>284</v>
       </c>
       <c r="B284" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4920,7 +4926,7 @@
         <v>285</v>
       </c>
       <c r="B285" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4928,7 +4934,7 @@
         <v>286</v>
       </c>
       <c r="B286" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4936,7 +4942,7 @@
         <v>287</v>
       </c>
       <c r="B287" s="1">
-        <v>520</v>
+        <v>880</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4944,7 +4950,7 @@
         <v>288</v>
       </c>
       <c r="B288" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4952,7 +4958,7 @@
         <v>289</v>
       </c>
       <c r="B289" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4960,7 +4966,7 @@
         <v>290</v>
       </c>
       <c r="B290" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -4968,7 +4974,7 @@
         <v>291</v>
       </c>
       <c r="B291" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -4976,7 +4982,7 @@
         <v>292</v>
       </c>
       <c r="B292" s="1">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -4984,7 +4990,7 @@
         <v>293</v>
       </c>
       <c r="B293" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -4992,7 +4998,7 @@
         <v>294</v>
       </c>
       <c r="B294" s="1">
-        <v>320</v>
+        <v>520</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5000,7 +5006,7 @@
         <v>295</v>
       </c>
       <c r="B295" s="1">
-        <v>540</v>
+        <v>320</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5008,7 +5014,7 @@
         <v>296</v>
       </c>
       <c r="B296" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5016,7 +5022,7 @@
         <v>297</v>
       </c>
       <c r="B297" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5032,7 +5038,7 @@
         <v>299</v>
       </c>
       <c r="B299" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5040,7 +5046,7 @@
         <v>300</v>
       </c>
       <c r="B300" s="1">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5048,7 +5054,7 @@
         <v>301</v>
       </c>
       <c r="B301" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5056,7 +5062,7 @@
         <v>302</v>
       </c>
       <c r="B302" s="1">
-        <v>480</v>
+        <v>800</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5064,7 +5070,7 @@
         <v>303</v>
       </c>
       <c r="B303" s="1">
-        <v>780</v>
+        <v>480</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5072,7 +5078,7 @@
         <v>304</v>
       </c>
       <c r="B304" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5080,7 +5086,7 @@
         <v>305</v>
       </c>
       <c r="B305" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5088,7 +5094,7 @@
         <v>306</v>
       </c>
       <c r="B306" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5096,7 +5102,7 @@
         <v>307</v>
       </c>
       <c r="B307" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5112,7 +5118,7 @@
         <v>309</v>
       </c>
       <c r="B309" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5120,7 +5126,7 @@
         <v>310</v>
       </c>
       <c r="B310" s="1">
-        <v>960</v>
+        <v>720</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5128,7 +5134,7 @@
         <v>311</v>
       </c>
       <c r="B311" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5136,7 +5142,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5144,7 +5150,7 @@
         <v>313</v>
       </c>
       <c r="B313" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5152,7 +5158,7 @@
         <v>314</v>
       </c>
       <c r="B314" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5160,7 +5166,7 @@
         <v>315</v>
       </c>
       <c r="B315" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5168,7 +5174,7 @@
         <v>316</v>
       </c>
       <c r="B316" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5176,7 +5182,7 @@
         <v>317</v>
       </c>
       <c r="B317" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5184,7 +5190,7 @@
         <v>318</v>
       </c>
       <c r="B318" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5200,7 +5206,7 @@
         <v>320</v>
       </c>
       <c r="B320" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5216,7 +5222,7 @@
         <v>322</v>
       </c>
       <c r="B322" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5224,7 +5230,7 @@
         <v>323</v>
       </c>
       <c r="B323" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5232,7 +5238,7 @@
         <v>324</v>
       </c>
       <c r="B324" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5240,7 +5246,7 @@
         <v>325</v>
       </c>
       <c r="B325" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5248,7 +5254,7 @@
         <v>326</v>
       </c>
       <c r="B326" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5264,7 +5270,7 @@
         <v>328</v>
       </c>
       <c r="B328" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5272,7 +5278,7 @@
         <v>329</v>
       </c>
       <c r="B329" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5280,7 +5286,7 @@
         <v>330</v>
       </c>
       <c r="B330" s="1">
-        <v>640</v>
+        <v>480</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5288,7 +5294,7 @@
         <v>331</v>
       </c>
       <c r="B331" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5296,7 +5302,7 @@
         <v>332</v>
       </c>
       <c r="B332" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5304,7 +5310,7 @@
         <v>333</v>
       </c>
       <c r="B333" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5312,7 +5318,7 @@
         <v>334</v>
       </c>
       <c r="B334" s="1">
-        <v>520</v>
+        <v>860</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5320,7 +5326,7 @@
         <v>335</v>
       </c>
       <c r="B335" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5328,7 +5334,7 @@
         <v>336</v>
       </c>
       <c r="B336" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5344,7 +5350,7 @@
         <v>338</v>
       </c>
       <c r="B338" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5352,7 +5358,7 @@
         <v>339</v>
       </c>
       <c r="B339" s="1">
-        <v>700</v>
+        <v>420</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5360,7 +5366,7 @@
         <v>340</v>
       </c>
       <c r="B340" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5368,7 +5374,7 @@
         <v>341</v>
       </c>
       <c r="B341" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5376,7 +5382,7 @@
         <v>342</v>
       </c>
       <c r="B342" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5384,7 +5390,7 @@
         <v>343</v>
       </c>
       <c r="B343" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5392,7 +5398,7 @@
         <v>344</v>
       </c>
       <c r="B344" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5400,7 +5406,7 @@
         <v>345</v>
       </c>
       <c r="B345" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5408,7 +5414,7 @@
         <v>346</v>
       </c>
       <c r="B346" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5416,7 +5422,7 @@
         <v>347</v>
       </c>
       <c r="B347" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5424,7 +5430,7 @@
         <v>348</v>
       </c>
       <c r="B348" s="1">
-        <v>440</v>
+        <v>620</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5432,7 +5438,7 @@
         <v>349</v>
       </c>
       <c r="B349" s="1">
-        <v>320</v>
+        <v>440</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5448,7 +5454,7 @@
         <v>351</v>
       </c>
       <c r="B351" s="1">
-        <v>820</v>
+        <v>320</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5456,7 +5462,7 @@
         <v>352</v>
       </c>
       <c r="B352" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5464,7 +5470,7 @@
         <v>353</v>
       </c>
       <c r="B353" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5480,7 +5486,7 @@
         <v>355</v>
       </c>
       <c r="B355" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5488,7 +5494,7 @@
         <v>356</v>
       </c>
       <c r="B356" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5504,7 +5510,7 @@
         <v>358</v>
       </c>
       <c r="B358" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5512,7 +5518,7 @@
         <v>359</v>
       </c>
       <c r="B359" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5520,7 +5526,7 @@
         <v>360</v>
       </c>
       <c r="B360" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5528,7 +5534,7 @@
         <v>361</v>
       </c>
       <c r="B361" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5536,7 +5542,7 @@
         <v>362</v>
       </c>
       <c r="B362" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5544,7 +5550,7 @@
         <v>363</v>
       </c>
       <c r="B363" s="1">
-        <v>880</v>
+        <v>780</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5552,7 +5558,7 @@
         <v>364</v>
       </c>
       <c r="B364" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5568,7 +5574,7 @@
         <v>366</v>
       </c>
       <c r="B366" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5576,7 +5582,7 @@
         <v>367</v>
       </c>
       <c r="B367" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5584,7 +5590,7 @@
         <v>368</v>
       </c>
       <c r="B368" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5592,7 +5598,7 @@
         <v>369</v>
       </c>
       <c r="B369" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5600,7 +5606,7 @@
         <v>370</v>
       </c>
       <c r="B370" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5608,7 +5614,7 @@
         <v>371</v>
       </c>
       <c r="B371" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5616,7 +5622,7 @@
         <v>372</v>
       </c>
       <c r="B372" s="1">
-        <v>700</v>
+        <v>440</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5624,7 +5630,7 @@
         <v>373</v>
       </c>
       <c r="B373" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5632,7 +5638,7 @@
         <v>374</v>
       </c>
       <c r="B374" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5640,7 +5646,7 @@
         <v>375</v>
       </c>
       <c r="B375" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5648,7 +5654,7 @@
         <v>376</v>
       </c>
       <c r="B376" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5656,7 +5662,7 @@
         <v>377</v>
       </c>
       <c r="B377" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5664,7 +5670,7 @@
         <v>378</v>
       </c>
       <c r="B378" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5672,7 +5678,7 @@
         <v>379</v>
       </c>
       <c r="B379" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5680,7 +5686,7 @@
         <v>380</v>
       </c>
       <c r="B380" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5688,7 +5694,7 @@
         <v>381</v>
       </c>
       <c r="B381" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5696,7 +5702,7 @@
         <v>382</v>
       </c>
       <c r="B382" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5704,7 +5710,7 @@
         <v>383</v>
       </c>
       <c r="B383" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5720,7 +5726,7 @@
         <v>385</v>
       </c>
       <c r="B385" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5728,7 +5734,7 @@
         <v>386</v>
       </c>
       <c r="B386" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5736,7 +5742,7 @@
         <v>387</v>
       </c>
       <c r="B387" s="1">
-        <v>800</v>
+        <v>880</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5744,7 +5750,7 @@
         <v>388</v>
       </c>
       <c r="B388" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5752,7 +5758,7 @@
         <v>389</v>
       </c>
       <c r="B389" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5760,7 +5766,7 @@
         <v>390</v>
       </c>
       <c r="B390" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5776,7 +5782,7 @@
         <v>392</v>
       </c>
       <c r="B392" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5784,7 +5790,7 @@
         <v>393</v>
       </c>
       <c r="B393" s="1">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5792,7 +5798,7 @@
         <v>394</v>
       </c>
       <c r="B394" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5800,7 +5806,7 @@
         <v>395</v>
       </c>
       <c r="B395" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5808,7 +5814,7 @@
         <v>396</v>
       </c>
       <c r="B396" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5816,7 +5822,7 @@
         <v>397</v>
       </c>
       <c r="B397" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5824,7 +5830,7 @@
         <v>398</v>
       </c>
       <c r="B398" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5840,7 +5846,7 @@
         <v>400</v>
       </c>
       <c r="B400" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5848,7 +5854,7 @@
         <v>401</v>
       </c>
       <c r="B401" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5856,7 +5862,7 @@
         <v>402</v>
       </c>
       <c r="B402" s="1">
-        <v>640</v>
+        <v>920</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5864,7 +5870,7 @@
         <v>403</v>
       </c>
       <c r="B403" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5872,7 +5878,7 @@
         <v>404</v>
       </c>
       <c r="B404" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5880,7 +5886,7 @@
         <v>405</v>
       </c>
       <c r="B405" s="1">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5888,7 +5894,7 @@
         <v>406</v>
       </c>
       <c r="B406" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5896,7 +5902,7 @@
         <v>407</v>
       </c>
       <c r="B407" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5904,7 +5910,7 @@
         <v>408</v>
       </c>
       <c r="B408" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5912,7 +5918,7 @@
         <v>409</v>
       </c>
       <c r="B409" s="1">
-        <v>860</v>
+        <v>640</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5920,7 +5926,7 @@
         <v>410</v>
       </c>
       <c r="B410" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5928,7 +5934,7 @@
         <v>411</v>
       </c>
       <c r="B411" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5936,7 +5942,7 @@
         <v>412</v>
       </c>
       <c r="B412" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5944,7 +5950,7 @@
         <v>413</v>
       </c>
       <c r="B413" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5952,7 +5958,7 @@
         <v>414</v>
       </c>
       <c r="B414" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5960,7 +5966,7 @@
         <v>415</v>
       </c>
       <c r="B415" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -5968,7 +5974,7 @@
         <v>416</v>
       </c>
       <c r="B416" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -5976,7 +5982,7 @@
         <v>417</v>
       </c>
       <c r="B417" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -5984,7 +5990,7 @@
         <v>418</v>
       </c>
       <c r="B418" s="1">
-        <v>620</v>
+        <v>480</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -5992,7 +5998,7 @@
         <v>419</v>
       </c>
       <c r="B419" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -6000,7 +6006,7 @@
         <v>420</v>
       </c>
       <c r="B420" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -6008,7 +6014,7 @@
         <v>421</v>
       </c>
       <c r="B421" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -6016,7 +6022,7 @@
         <v>422</v>
       </c>
       <c r="B422" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -6024,7 +6030,7 @@
         <v>423</v>
       </c>
       <c r="B423" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -6032,7 +6038,7 @@
         <v>424</v>
       </c>
       <c r="B424" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6040,7 +6046,7 @@
         <v>425</v>
       </c>
       <c r="B425" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6048,7 +6054,7 @@
         <v>426</v>
       </c>
       <c r="B426" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6056,7 +6062,7 @@
         <v>427</v>
       </c>
       <c r="B427" s="1">
-        <v>840</v>
+        <v>480</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6064,7 +6070,7 @@
         <v>428</v>
       </c>
       <c r="B428" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6072,7 +6078,7 @@
         <v>429</v>
       </c>
       <c r="B429" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6080,7 +6086,7 @@
         <v>430</v>
       </c>
       <c r="B430" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6096,7 +6102,7 @@
         <v>432</v>
       </c>
       <c r="B432" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6104,7 +6110,7 @@
         <v>433</v>
       </c>
       <c r="B433" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6120,7 +6126,7 @@
         <v>435</v>
       </c>
       <c r="B435" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6128,7 +6134,7 @@
         <v>436</v>
       </c>
       <c r="B436" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6136,7 +6142,7 @@
         <v>437</v>
       </c>
       <c r="B437" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6144,7 +6150,7 @@
         <v>438</v>
       </c>
       <c r="B438" s="1">
-        <v>1100</v>
+        <v>660</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6152,7 +6158,7 @@
         <v>439</v>
       </c>
       <c r="B439" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6160,7 +6166,7 @@
         <v>440</v>
       </c>
       <c r="B440" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6168,7 +6174,7 @@
         <v>441</v>
       </c>
       <c r="B441" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6176,7 +6182,7 @@
         <v>442</v>
       </c>
       <c r="B442" s="1">
-        <v>800</v>
+        <v>760</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6184,7 +6190,7 @@
         <v>443</v>
       </c>
       <c r="B443" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6200,7 +6206,7 @@
         <v>445</v>
       </c>
       <c r="B445" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6208,7 +6214,7 @@
         <v>446</v>
       </c>
       <c r="B446" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6216,7 +6222,7 @@
         <v>447</v>
       </c>
       <c r="B447" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6224,7 +6230,7 @@
         <v>448</v>
       </c>
       <c r="B448" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6232,7 +6238,7 @@
         <v>449</v>
       </c>
       <c r="B449" s="1">
-        <v>860</v>
+        <v>700</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6240,7 +6246,7 @@
         <v>450</v>
       </c>
       <c r="B450" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6256,7 +6262,7 @@
         <v>452</v>
       </c>
       <c r="B452" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6264,7 +6270,7 @@
         <v>453</v>
       </c>
       <c r="B453" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6272,7 +6278,7 @@
         <v>454</v>
       </c>
       <c r="B454" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6280,7 +6286,7 @@
         <v>455</v>
       </c>
       <c r="B455" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6288,7 +6294,7 @@
         <v>456</v>
       </c>
       <c r="B456" s="1">
-        <v>880</v>
+        <v>620</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6296,7 +6302,7 @@
         <v>457</v>
       </c>
       <c r="B457" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6304,7 +6310,7 @@
         <v>458</v>
       </c>
       <c r="B458" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6312,7 +6318,7 @@
         <v>459</v>
       </c>
       <c r="B459" s="1">
-        <v>860</v>
+        <v>800</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6320,7 +6326,7 @@
         <v>460</v>
       </c>
       <c r="B460" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6328,7 +6334,7 @@
         <v>461</v>
       </c>
       <c r="B461" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6336,7 +6342,7 @@
         <v>462</v>
       </c>
       <c r="B462" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6344,7 +6350,7 @@
         <v>463</v>
       </c>
       <c r="B463" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6352,7 +6358,7 @@
         <v>464</v>
       </c>
       <c r="B464" s="1">
-        <v>790</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6360,7 +6366,7 @@
         <v>465</v>
       </c>
       <c r="B465" s="1">
-        <v>640</v>
+        <v>790</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6368,7 +6374,7 @@
         <v>466</v>
       </c>
       <c r="B466" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6376,7 +6382,7 @@
         <v>467</v>
       </c>
       <c r="B467" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6384,7 +6390,7 @@
         <v>468</v>
       </c>
       <c r="B468" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6400,7 +6406,7 @@
         <v>470</v>
       </c>
       <c r="B470" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6408,7 +6414,7 @@
         <v>471</v>
       </c>
       <c r="B471" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6416,7 +6422,7 @@
         <v>472</v>
       </c>
       <c r="B472" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6424,7 +6430,7 @@
         <v>473</v>
       </c>
       <c r="B473" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6432,7 +6438,7 @@
         <v>474</v>
       </c>
       <c r="B474" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6440,7 +6446,7 @@
         <v>475</v>
       </c>
       <c r="B475" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6448,7 +6454,7 @@
         <v>476</v>
       </c>
       <c r="B476" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6456,7 +6462,7 @@
         <v>477</v>
       </c>
       <c r="B477" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6464,7 +6470,7 @@
         <v>478</v>
       </c>
       <c r="B478" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6472,7 +6478,7 @@
         <v>479</v>
       </c>
       <c r="B479" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6480,7 +6486,7 @@
         <v>480</v>
       </c>
       <c r="B480" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6496,7 +6502,7 @@
         <v>482</v>
       </c>
       <c r="B482" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6504,7 +6510,7 @@
         <v>483</v>
       </c>
       <c r="B483" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6512,7 +6518,7 @@
         <v>484</v>
       </c>
       <c r="B484" s="1">
-        <v>960</v>
+        <v>840</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6520,7 +6526,7 @@
         <v>485</v>
       </c>
       <c r="B485" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6528,7 +6534,7 @@
         <v>486</v>
       </c>
       <c r="B486" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6536,7 +6542,7 @@
         <v>487</v>
       </c>
       <c r="B487" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6544,7 +6550,7 @@
         <v>488</v>
       </c>
       <c r="B488" s="1">
-        <v>840</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6552,7 +6558,7 @@
         <v>489</v>
       </c>
       <c r="B489" s="1">
-        <v>920</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6560,7 +6566,7 @@
         <v>490</v>
       </c>
       <c r="B490" s="1">
-        <v>680</v>
+        <v>840</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6568,7 +6574,7 @@
         <v>491</v>
       </c>
       <c r="B491" s="1">
-        <v>580</v>
+        <v>920</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6576,7 +6582,7 @@
         <v>492</v>
       </c>
       <c r="B492" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6584,7 +6590,7 @@
         <v>493</v>
       </c>
       <c r="B493" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6592,7 +6598,7 @@
         <v>494</v>
       </c>
       <c r="B494" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6600,7 +6606,7 @@
         <v>495</v>
       </c>
       <c r="B495" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6608,7 +6614,7 @@
         <v>496</v>
       </c>
       <c r="B496" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6616,7 +6622,7 @@
         <v>497</v>
       </c>
       <c r="B497" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6624,7 +6630,7 @@
         <v>498</v>
       </c>
       <c r="B498" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6632,7 +6638,7 @@
         <v>499</v>
       </c>
       <c r="B499" s="1">
-        <v>720</v>
+        <v>960</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6640,7 +6646,7 @@
         <v>500</v>
       </c>
       <c r="B500" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6648,7 +6654,7 @@
         <v>501</v>
       </c>
       <c r="B501" s="1">
-        <v>540</v>
+        <v>720</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6656,7 +6662,7 @@
         <v>502</v>
       </c>
       <c r="B502" s="1">
-        <v>1100</v>
+        <v>780</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6664,7 +6670,7 @@
         <v>503</v>
       </c>
       <c r="B503" s="1">
-        <v>1100</v>
+        <v>540</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6680,7 +6686,7 @@
         <v>505</v>
       </c>
       <c r="B505" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6688,7 +6694,7 @@
         <v>506</v>
       </c>
       <c r="B506" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6696,7 +6702,7 @@
         <v>507</v>
       </c>
       <c r="B507" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6704,7 +6710,7 @@
         <v>508</v>
       </c>
       <c r="B508" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6712,7 +6718,7 @@
         <v>509</v>
       </c>
       <c r="B509" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6720,7 +6726,7 @@
         <v>510</v>
       </c>
       <c r="B510" s="1">
-        <v>980</v>
+        <v>620</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6728,7 +6734,7 @@
         <v>511</v>
       </c>
       <c r="B511" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6736,7 +6742,7 @@
         <v>512</v>
       </c>
       <c r="B512" s="1">
-        <v>760</v>
+        <v>980</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6744,7 +6750,7 @@
         <v>513</v>
       </c>
       <c r="B513" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6752,7 +6758,7 @@
         <v>514</v>
       </c>
       <c r="B514" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6768,7 +6774,7 @@
         <v>516</v>
       </c>
       <c r="B516" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6776,7 +6782,7 @@
         <v>517</v>
       </c>
       <c r="B517" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6784,7 +6790,7 @@
         <v>518</v>
       </c>
       <c r="B518" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6792,7 +6798,7 @@
         <v>519</v>
       </c>
       <c r="B519" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6800,7 +6806,7 @@
         <v>520</v>
       </c>
       <c r="B520" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6816,7 +6822,7 @@
         <v>522</v>
       </c>
       <c r="B522" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -6824,7 +6830,7 @@
         <v>523</v>
       </c>
       <c r="B523" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6832,7 +6838,7 @@
         <v>524</v>
       </c>
       <c r="B524" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6840,7 +6846,7 @@
         <v>525</v>
       </c>
       <c r="B525" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6856,7 +6862,7 @@
         <v>527</v>
       </c>
       <c r="B527" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6864,7 +6870,7 @@
         <v>528</v>
       </c>
       <c r="B528" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6880,7 +6886,7 @@
         <v>530</v>
       </c>
       <c r="B530" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6888,7 +6894,7 @@
         <v>531</v>
       </c>
       <c r="B531" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6896,7 +6902,7 @@
         <v>532</v>
       </c>
       <c r="B532" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6904,7 +6910,7 @@
         <v>533</v>
       </c>
       <c r="B533" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6912,7 +6918,7 @@
         <v>534</v>
       </c>
       <c r="B534" s="1">
-        <v>1400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6928,7 +6934,7 @@
         <v>536</v>
       </c>
       <c r="B536" s="1">
-        <v>660</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -6936,7 +6942,7 @@
         <v>537</v>
       </c>
       <c r="B537" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -6944,7 +6950,7 @@
         <v>538</v>
       </c>
       <c r="B538" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -6952,7 +6958,7 @@
         <v>539</v>
       </c>
       <c r="B539" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -6960,7 +6966,7 @@
         <v>540</v>
       </c>
       <c r="B540" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -6968,7 +6974,7 @@
         <v>541</v>
       </c>
       <c r="B541" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -6976,7 +6982,7 @@
         <v>542</v>
       </c>
       <c r="B542" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -6984,7 +6990,7 @@
         <v>543</v>
       </c>
       <c r="B543" s="1">
-        <v>760</v>
+        <v>900</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -6992,7 +6998,7 @@
         <v>544</v>
       </c>
       <c r="B544" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -7000,7 +7006,7 @@
         <v>545</v>
       </c>
       <c r="B545" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -7008,7 +7014,7 @@
         <v>546</v>
       </c>
       <c r="B546" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -7024,7 +7030,7 @@
         <v>548</v>
       </c>
       <c r="B548" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -7048,7 +7054,7 @@
         <v>551</v>
       </c>
       <c r="B551" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7056,7 +7062,7 @@
         <v>552</v>
       </c>
       <c r="B552" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7064,7 +7070,7 @@
         <v>553</v>
       </c>
       <c r="B553" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7072,7 +7078,7 @@
         <v>554</v>
       </c>
       <c r="B554" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7088,7 +7094,7 @@
         <v>556</v>
       </c>
       <c r="B556" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7096,7 +7102,7 @@
         <v>557</v>
       </c>
       <c r="B557" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7104,7 +7110,7 @@
         <v>558</v>
       </c>
       <c r="B558" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7112,7 +7118,7 @@
         <v>559</v>
       </c>
       <c r="B559" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7120,7 +7126,7 @@
         <v>560</v>
       </c>
       <c r="B560" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7128,7 +7134,7 @@
         <v>561</v>
       </c>
       <c r="B561" s="1">
-        <v>540</v>
+        <v>640</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7144,7 +7150,7 @@
         <v>563</v>
       </c>
       <c r="B563" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7152,7 +7158,7 @@
         <v>564</v>
       </c>
       <c r="B564" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7160,7 +7166,7 @@
         <v>565</v>
       </c>
       <c r="B565" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7168,7 +7174,7 @@
         <v>566</v>
       </c>
       <c r="B566" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7184,7 +7190,7 @@
         <v>568</v>
       </c>
       <c r="B568" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7200,7 +7206,7 @@
         <v>570</v>
       </c>
       <c r="B570" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7208,7 +7214,7 @@
         <v>571</v>
       </c>
       <c r="B571" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7216,7 +7222,7 @@
         <v>572</v>
       </c>
       <c r="B572" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7224,7 +7230,7 @@
         <v>573</v>
       </c>
       <c r="B573" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7232,7 +7238,7 @@
         <v>574</v>
       </c>
       <c r="B574" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7248,7 +7254,7 @@
         <v>576</v>
       </c>
       <c r="B576" s="1">
-        <v>800</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7256,7 +7262,7 @@
         <v>577</v>
       </c>
       <c r="B577" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7264,7 +7270,7 @@
         <v>578</v>
       </c>
       <c r="B578" s="1">
-        <v>640</v>
+        <v>800</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7272,7 +7278,7 @@
         <v>579</v>
       </c>
       <c r="B579" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7280,7 +7286,7 @@
         <v>580</v>
       </c>
       <c r="B580" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7288,7 +7294,7 @@
         <v>581</v>
       </c>
       <c r="B581" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7304,7 +7310,7 @@
         <v>583</v>
       </c>
       <c r="B583" s="1">
-        <v>880</v>
+        <v>640</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7312,7 +7318,7 @@
         <v>584</v>
       </c>
       <c r="B584" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7320,7 +7326,7 @@
         <v>585</v>
       </c>
       <c r="B585" s="1">
-        <v>600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7328,7 +7334,7 @@
         <v>586</v>
       </c>
       <c r="B586" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7344,7 +7350,7 @@
         <v>588</v>
       </c>
       <c r="B588" s="1">
-        <v>800</v>
+        <v>820</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7352,7 +7358,7 @@
         <v>589</v>
       </c>
       <c r="B589" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7360,7 +7366,7 @@
         <v>590</v>
       </c>
       <c r="B590" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7368,7 +7374,7 @@
         <v>591</v>
       </c>
       <c r="B591" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7376,7 +7382,7 @@
         <v>592</v>
       </c>
       <c r="B592" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7384,7 +7390,7 @@
         <v>593</v>
       </c>
       <c r="B593" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7392,7 +7398,7 @@
         <v>594</v>
       </c>
       <c r="B594" s="1">
-        <v>1020</v>
+        <v>720</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7400,7 +7406,7 @@
         <v>595</v>
       </c>
       <c r="B595" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7408,7 +7414,7 @@
         <v>596</v>
       </c>
       <c r="B596" s="1">
-        <v>700</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7416,7 +7422,7 @@
         <v>597</v>
       </c>
       <c r="B597" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7424,7 +7430,7 @@
         <v>598</v>
       </c>
       <c r="B598" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7432,7 +7438,7 @@
         <v>599</v>
       </c>
       <c r="B599" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7448,7 +7454,7 @@
         <v>601</v>
       </c>
       <c r="B601" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7456,7 +7462,7 @@
         <v>602</v>
       </c>
       <c r="B602" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7464,7 +7470,7 @@
         <v>603</v>
       </c>
       <c r="B603" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7472,7 +7478,7 @@
         <v>604</v>
       </c>
       <c r="B604" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7480,7 +7486,7 @@
         <v>605</v>
       </c>
       <c r="B605" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7488,7 +7494,7 @@
         <v>606</v>
       </c>
       <c r="B606" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7496,7 +7502,7 @@
         <v>607</v>
       </c>
       <c r="B607" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7512,7 +7518,7 @@
         <v>609</v>
       </c>
       <c r="B609" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7528,7 +7534,7 @@
         <v>611</v>
       </c>
       <c r="B611" s="1">
-        <v>1000</v>
+        <v>740</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7536,7 +7542,7 @@
         <v>612</v>
       </c>
       <c r="B612" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7544,7 +7550,7 @@
         <v>613</v>
       </c>
       <c r="B613" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7552,7 +7558,7 @@
         <v>614</v>
       </c>
       <c r="B614" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7560,7 +7566,7 @@
         <v>615</v>
       </c>
       <c r="B615" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7576,7 +7582,7 @@
         <v>617</v>
       </c>
       <c r="B617" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -7584,7 +7590,7 @@
         <v>618</v>
       </c>
       <c r="B618" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -7592,7 +7598,7 @@
         <v>619</v>
       </c>
       <c r="B619" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7600,7 +7606,7 @@
         <v>620</v>
       </c>
       <c r="B620" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7608,7 +7614,7 @@
         <v>621</v>
       </c>
       <c r="B621" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -7616,7 +7622,7 @@
         <v>622</v>
       </c>
       <c r="B622" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -7624,7 +7630,7 @@
         <v>623</v>
       </c>
       <c r="B623" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -7632,7 +7638,7 @@
         <v>624</v>
       </c>
       <c r="B624" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -7640,7 +7646,7 @@
         <v>625</v>
       </c>
       <c r="B625" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -7648,7 +7654,7 @@
         <v>626</v>
       </c>
       <c r="B626" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -7664,7 +7670,7 @@
         <v>628</v>
       </c>
       <c r="B628" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -7672,7 +7678,7 @@
         <v>629</v>
       </c>
       <c r="B629" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -7680,7 +7686,7 @@
         <v>630</v>
       </c>
       <c r="B630" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -7688,7 +7694,7 @@
         <v>631</v>
       </c>
       <c r="B631" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -7696,7 +7702,7 @@
         <v>632</v>
       </c>
       <c r="B632" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -7704,7 +7710,7 @@
         <v>633</v>
       </c>
       <c r="B633" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -7712,7 +7718,7 @@
         <v>634</v>
       </c>
       <c r="B634" s="1">
-        <v>440</v>
+        <v>680</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -7720,7 +7726,7 @@
         <v>635</v>
       </c>
       <c r="B635" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -7728,7 +7734,7 @@
         <v>636</v>
       </c>
       <c r="B636" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -7736,7 +7742,7 @@
         <v>637</v>
       </c>
       <c r="B637" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -7744,7 +7750,7 @@
         <v>638</v>
       </c>
       <c r="B638" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -7752,7 +7758,7 @@
         <v>639</v>
       </c>
       <c r="B639" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -7760,7 +7766,7 @@
         <v>640</v>
       </c>
       <c r="B640" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -7768,7 +7774,7 @@
         <v>641</v>
       </c>
       <c r="B641" s="1">
-        <v>880</v>
+        <v>560</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -7776,7 +7782,7 @@
         <v>642</v>
       </c>
       <c r="B642" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -7784,7 +7790,7 @@
         <v>643</v>
       </c>
       <c r="B643" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -7792,7 +7798,7 @@
         <v>644</v>
       </c>
       <c r="B644" s="1">
-        <v>920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -7800,7 +7806,7 @@
         <v>645</v>
       </c>
       <c r="B645" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -7808,7 +7814,7 @@
         <v>646</v>
       </c>
       <c r="B646" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -7816,7 +7822,7 @@
         <v>647</v>
       </c>
       <c r="B647" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -7824,7 +7830,7 @@
         <v>648</v>
       </c>
       <c r="B648" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -7832,7 +7838,7 @@
         <v>649</v>
       </c>
       <c r="B649" s="1">
-        <v>780</v>
+        <v>980</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -7840,7 +7846,7 @@
         <v>650</v>
       </c>
       <c r="B650" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -7848,7 +7854,7 @@
         <v>651</v>
       </c>
       <c r="B651" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -7856,7 +7862,7 @@
         <v>652</v>
       </c>
       <c r="B652" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -7864,7 +7870,7 @@
         <v>653</v>
       </c>
       <c r="B653" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -7872,7 +7878,7 @@
         <v>654</v>
       </c>
       <c r="B654" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -7880,7 +7886,7 @@
         <v>655</v>
       </c>
       <c r="B655" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -7888,7 +7894,7 @@
         <v>656</v>
       </c>
       <c r="B656" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -7896,7 +7902,7 @@
         <v>657</v>
       </c>
       <c r="B657" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -7904,7 +7910,7 @@
         <v>658</v>
       </c>
       <c r="B658" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -7912,7 +7918,7 @@
         <v>659</v>
       </c>
       <c r="B659" s="1">
-        <v>660</v>
+        <v>860</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -7920,7 +7926,7 @@
         <v>660</v>
       </c>
       <c r="B660" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -7928,7 +7934,7 @@
         <v>661</v>
       </c>
       <c r="B661" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -7936,7 +7942,7 @@
         <v>662</v>
       </c>
       <c r="B662" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -7944,7 +7950,7 @@
         <v>663</v>
       </c>
       <c r="B663" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -7952,7 +7958,7 @@
         <v>664</v>
       </c>
       <c r="B664" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -7960,7 +7966,7 @@
         <v>665</v>
       </c>
       <c r="B665" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -7968,7 +7974,7 @@
         <v>666</v>
       </c>
       <c r="B666" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -7976,7 +7982,7 @@
         <v>667</v>
       </c>
       <c r="B667" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -7984,7 +7990,7 @@
         <v>668</v>
       </c>
       <c r="B668" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -7992,7 +7998,7 @@
         <v>669</v>
       </c>
       <c r="B669" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -8000,7 +8006,7 @@
         <v>670</v>
       </c>
       <c r="B670" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8008,7 +8014,7 @@
         <v>671</v>
       </c>
       <c r="B671" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -8016,7 +8022,7 @@
         <v>672</v>
       </c>
       <c r="B672" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -8024,7 +8030,7 @@
         <v>673</v>
       </c>
       <c r="B673" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8032,7 +8038,7 @@
         <v>674</v>
       </c>
       <c r="B674" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -8040,7 +8046,7 @@
         <v>675</v>
       </c>
       <c r="B675" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8048,7 +8054,7 @@
         <v>676</v>
       </c>
       <c r="B676" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8056,7 +8062,7 @@
         <v>677</v>
       </c>
       <c r="B677" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8064,7 +8070,7 @@
         <v>678</v>
       </c>
       <c r="B678" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8072,7 +8078,7 @@
         <v>679</v>
       </c>
       <c r="B679" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8080,7 +8086,7 @@
         <v>680</v>
       </c>
       <c r="B680" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8088,7 +8094,7 @@
         <v>681</v>
       </c>
       <c r="B681" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8096,7 +8102,7 @@
         <v>682</v>
       </c>
       <c r="B682" s="1">
-        <v>920</v>
+        <v>500</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8104,7 +8110,7 @@
         <v>683</v>
       </c>
       <c r="B683" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8112,7 +8118,7 @@
         <v>684</v>
       </c>
       <c r="B684" s="1">
-        <v>1040</v>
+        <v>920</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8120,7 +8126,7 @@
         <v>685</v>
       </c>
       <c r="B685" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8128,7 +8134,7 @@
         <v>686</v>
       </c>
       <c r="B686" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8136,7 +8142,7 @@
         <v>687</v>
       </c>
       <c r="B687" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8144,7 +8150,7 @@
         <v>688</v>
       </c>
       <c r="B688" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8152,7 +8158,7 @@
         <v>689</v>
       </c>
       <c r="B689" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8160,7 +8166,7 @@
         <v>690</v>
       </c>
       <c r="B690" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8168,7 +8174,7 @@
         <v>691</v>
       </c>
       <c r="B691" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8176,7 +8182,7 @@
         <v>692</v>
       </c>
       <c r="B692" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8184,7 +8190,7 @@
         <v>693</v>
       </c>
       <c r="B693" s="1">
-        <v>500</v>
+        <v>820</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8200,7 +8206,7 @@
         <v>695</v>
       </c>
       <c r="B695" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8208,7 +8214,7 @@
         <v>696</v>
       </c>
       <c r="B696" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8216,7 +8222,7 @@
         <v>697</v>
       </c>
       <c r="B697" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8224,7 +8230,7 @@
         <v>698</v>
       </c>
       <c r="B698" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8232,7 +8238,7 @@
         <v>699</v>
       </c>
       <c r="B699" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8240,7 +8246,7 @@
         <v>700</v>
       </c>
       <c r="B700" s="1">
-        <v>400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8248,7 +8254,7 @@
         <v>701</v>
       </c>
       <c r="B701" s="1">
-        <v>400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8256,7 +8262,7 @@
         <v>702</v>
       </c>
       <c r="B702" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8264,7 +8270,7 @@
         <v>703</v>
       </c>
       <c r="B703" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8280,7 +8286,7 @@
         <v>705</v>
       </c>
       <c r="B705" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8288,7 +8294,7 @@
         <v>706</v>
       </c>
       <c r="B706" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8296,7 +8302,7 @@
         <v>707</v>
       </c>
       <c r="B707" s="1">
-        <v>860</v>
+        <v>520</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8304,7 +8310,7 @@
         <v>708</v>
       </c>
       <c r="B708" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8312,7 +8318,7 @@
         <v>709</v>
       </c>
       <c r="B709" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8320,7 +8326,7 @@
         <v>710</v>
       </c>
       <c r="B710" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8328,7 +8334,7 @@
         <v>711</v>
       </c>
       <c r="B711" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8336,7 +8342,7 @@
         <v>712</v>
       </c>
       <c r="B712" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8344,7 +8350,7 @@
         <v>713</v>
       </c>
       <c r="B713" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8352,7 +8358,7 @@
         <v>714</v>
       </c>
       <c r="B714" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8360,7 +8366,7 @@
         <v>715</v>
       </c>
       <c r="B715" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8368,7 +8374,7 @@
         <v>716</v>
       </c>
       <c r="B716" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8376,7 +8382,7 @@
         <v>717</v>
       </c>
       <c r="B717" s="1">
-        <v>840</v>
+        <v>500</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8384,7 +8390,7 @@
         <v>718</v>
       </c>
       <c r="B718" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8392,7 +8398,7 @@
         <v>719</v>
       </c>
       <c r="B719" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8400,7 +8406,7 @@
         <v>720</v>
       </c>
       <c r="B720" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8408,7 +8414,7 @@
         <v>721</v>
       </c>
       <c r="B721" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8416,7 +8422,7 @@
         <v>722</v>
       </c>
       <c r="B722" s="1">
-        <v>1040</v>
+        <v>920</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8424,7 +8430,7 @@
         <v>723</v>
       </c>
       <c r="B723" s="1">
-        <v>940</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8432,7 +8438,7 @@
         <v>724</v>
       </c>
       <c r="B724" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8440,7 +8446,7 @@
         <v>725</v>
       </c>
       <c r="B725" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8448,7 +8454,7 @@
         <v>726</v>
       </c>
       <c r="B726" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8456,7 +8462,7 @@
         <v>727</v>
       </c>
       <c r="B727" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8464,7 +8470,7 @@
         <v>728</v>
       </c>
       <c r="B728" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8472,7 +8478,7 @@
         <v>729</v>
       </c>
       <c r="B729" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8480,7 +8486,7 @@
         <v>730</v>
       </c>
       <c r="B730" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8488,7 +8494,7 @@
         <v>731</v>
       </c>
       <c r="B731" s="1">
-        <v>500</v>
+        <v>820</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8504,7 +8510,7 @@
         <v>733</v>
       </c>
       <c r="B733" s="1">
-        <v>560</v>
+        <v>500</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -8512,7 +8518,7 @@
         <v>734</v>
       </c>
       <c r="B734" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -8520,7 +8526,7 @@
         <v>735</v>
       </c>
       <c r="B735" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -8528,7 +8534,7 @@
         <v>736</v>
       </c>
       <c r="B736" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -8536,7 +8542,7 @@
         <v>737</v>
       </c>
       <c r="B737" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -8552,7 +8558,7 @@
         <v>739</v>
       </c>
       <c r="B739" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -8560,7 +8566,7 @@
         <v>740</v>
       </c>
       <c r="B740" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -8576,7 +8582,7 @@
         <v>742</v>
       </c>
       <c r="B742" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -8584,7 +8590,7 @@
         <v>743</v>
       </c>
       <c r="B743" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="744" spans="1:2">
@@ -8592,7 +8598,7 @@
         <v>744</v>
       </c>
       <c r="B744" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -8600,7 +8606,7 @@
         <v>745</v>
       </c>
       <c r="B745" s="1">
-        <v>420</v>
+        <v>520</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -8608,7 +8614,7 @@
         <v>746</v>
       </c>
       <c r="B746" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -8616,7 +8622,7 @@
         <v>747</v>
       </c>
       <c r="B747" s="1">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -8624,7 +8630,7 @@
         <v>748</v>
       </c>
       <c r="B748" s="1">
-        <v>820</v>
+        <v>380</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -8632,7 +8638,7 @@
         <v>749</v>
       </c>
       <c r="B749" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -8640,7 +8646,7 @@
         <v>750</v>
       </c>
       <c r="B750" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="751" spans="1:2">
@@ -8648,7 +8654,7 @@
         <v>751</v>
       </c>
       <c r="B751" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -8664,7 +8670,7 @@
         <v>753</v>
       </c>
       <c r="B753" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="754" spans="1:2">
@@ -8672,7 +8678,7 @@
         <v>754</v>
       </c>
       <c r="B754" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -8680,6 +8686,22 @@
         <v>755</v>
       </c>
       <c r="B755" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2">
+      <c r="A756" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="B756" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2">
+      <c r="A757" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B757" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Saturnych\ohmybeer.ru\src\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37469B8C-8ED2-4E10-B63E-3577678F0511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Лист 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="758">
   <si>
     <t>Наименование</t>
   </si>
@@ -326,9 +331,6 @@
     <t>DUCHESSE DE BOURGOGNE (Sour red/brown), РОЗЛИВ</t>
   </si>
   <si>
-    <t>dutch. ipa (IPA), РОЗЛИВ, Россия</t>
-  </si>
-  <si>
     <t>Einsiedler - Klausner Pils, РОЗЛИВ, Германия</t>
   </si>
   <si>
@@ -2289,28 +2291,23 @@
   </si>
   <si>
     <t>Чаща – Doppelganger½ Citra (IPA) РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>Khoffner - dutch. ipa (IPA), РОЗЛИВ, Россия</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -2321,34 +2318,43 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -2638,18 +2644,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B757"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="25.85083" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="122.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2657,7 +2660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2665,7 +2668,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -2673,7 +2676,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -2681,7 +2684,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -2689,7 +2692,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -2697,7 +2700,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -2705,7 +2708,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -2713,7 +2716,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -2721,7 +2724,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -2729,7 +2732,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
@@ -2737,7 +2740,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
@@ -2745,7 +2748,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -2753,7 +2756,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
@@ -2761,7 +2764,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
@@ -2769,7 +2772,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
@@ -2777,7 +2780,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
@@ -2785,7 +2788,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
@@ -2793,7 +2796,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -2801,7 +2804,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
@@ -2809,7 +2812,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>21</v>
       </c>
@@ -2817,7 +2820,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>22</v>
       </c>
@@ -2825,7 +2828,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
@@ -2833,7 +2836,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -2841,7 +2844,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>25</v>
       </c>
@@ -2849,7 +2852,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
@@ -2857,7 +2860,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>27</v>
       </c>
@@ -2865,7 +2868,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>28</v>
       </c>
@@ -2873,7 +2876,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>29</v>
       </c>
@@ -2881,7 +2884,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>30</v>
       </c>
@@ -2889,7 +2892,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>31</v>
       </c>
@@ -2897,7 +2900,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>32</v>
       </c>
@@ -2905,7 +2908,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>33</v>
       </c>
@@ -2913,7 +2916,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>34</v>
       </c>
@@ -2921,7 +2924,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>35</v>
       </c>
@@ -2929,7 +2932,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>36</v>
       </c>
@@ -2937,7 +2940,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>37</v>
       </c>
@@ -2945,7 +2948,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>38</v>
       </c>
@@ -2953,7 +2956,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>39</v>
       </c>
@@ -2961,7 +2964,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>40</v>
       </c>
@@ -2969,7 +2972,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>41</v>
       </c>
@@ -2977,7 +2980,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>42</v>
       </c>
@@ -2985,7 +2988,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>43</v>
       </c>
@@ -2993,7 +2996,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>44</v>
       </c>
@@ -3001,7 +3004,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>45</v>
       </c>
@@ -3009,7 +3012,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>46</v>
       </c>
@@ -3017,7 +3020,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>47</v>
       </c>
@@ -3025,7 +3028,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>48</v>
       </c>
@@ -3033,7 +3036,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>49</v>
       </c>
@@ -3041,7 +3044,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>50</v>
       </c>
@@ -3049,7 +3052,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>51</v>
       </c>
@@ -3057,7 +3060,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>52</v>
       </c>
@@ -3065,7 +3068,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>53</v>
       </c>
@@ -3073,7 +3076,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>54</v>
       </c>
@@ -3081,7 +3084,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>55</v>
       </c>
@@ -3089,7 +3092,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>56</v>
       </c>
@@ -3097,7 +3100,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>57</v>
       </c>
@@ -3105,7 +3108,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>58</v>
       </c>
@@ -3113,7 +3116,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>59</v>
       </c>
@@ -3121,7 +3124,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>60</v>
       </c>
@@ -3129,7 +3132,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>61</v>
       </c>
@@ -3137,7 +3140,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>62</v>
       </c>
@@ -3145,7 +3148,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>63</v>
       </c>
@@ -3153,7 +3156,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>64</v>
       </c>
@@ -3161,7 +3164,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>65</v>
       </c>
@@ -3169,7 +3172,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>66</v>
       </c>
@@ -3177,7 +3180,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>67</v>
       </c>
@@ -3185,7 +3188,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>68</v>
       </c>
@@ -3193,7 +3196,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>69</v>
       </c>
@@ -3201,7 +3204,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>70</v>
       </c>
@@ -3209,7 +3212,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>71</v>
       </c>
@@ -3217,7 +3220,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>72</v>
       </c>
@@ -3225,7 +3228,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>73</v>
       </c>
@@ -3233,7 +3236,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>74</v>
       </c>
@@ -3241,7 +3244,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>75</v>
       </c>
@@ -3249,7 +3252,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>76</v>
       </c>
@@ -3257,7 +3260,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>77</v>
       </c>
@@ -3265,7 +3268,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>78</v>
       </c>
@@ -3273,7 +3276,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>79</v>
       </c>
@@ -3281,7 +3284,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>80</v>
       </c>
@@ -3289,7 +3292,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>81</v>
       </c>
@@ -3297,7 +3300,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>82</v>
       </c>
@@ -3305,7 +3308,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>83</v>
       </c>
@@ -3313,7 +3316,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>84</v>
       </c>
@@ -3321,7 +3324,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>85</v>
       </c>
@@ -3329,7 +3332,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>86</v>
       </c>
@@ -3337,7 +3340,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>87</v>
       </c>
@@ -3345,7 +3348,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>88</v>
       </c>
@@ -3353,7 +3356,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>89</v>
       </c>
@@ -3361,7 +3364,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>90</v>
       </c>
@@ -3369,7 +3372,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>91</v>
       </c>
@@ -3377,7 +3380,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>92</v>
       </c>
@@ -3385,7 +3388,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>93</v>
       </c>
@@ -3393,7 +3396,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>94</v>
       </c>
@@ -3401,7 +3404,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>95</v>
       </c>
@@ -3409,7 +3412,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>96</v>
       </c>
@@ -3417,7 +3420,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>97</v>
       </c>
@@ -3425,7 +3428,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>98</v>
       </c>
@@ -3433,7 +3436,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>99</v>
       </c>
@@ -3441,7 +3444,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>100</v>
       </c>
@@ -3449,7 +3452,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>101</v>
       </c>
@@ -3457,7 +3460,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>102</v>
       </c>
@@ -3465,5258 +3468,5248 @@
         <v>720</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>103</v>
+        <v>757</v>
       </c>
       <c r="B103" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B104" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B105" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B106" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B107" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B108" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B109" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B110" s="1">
         <v>420</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B111" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B112" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B113" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B114" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B115" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B116" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B117" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B118" s="1">
         <v>620</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B119" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B120" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B121" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B122" s="1">
         <v>960</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B123" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B124" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B125" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B126" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B127" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B128" s="1">
         <v>540</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B129" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B130" s="1">
         <v>1100</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B131" s="1">
         <v>1100</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B132" s="1">
         <v>1100</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B133" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B134" s="1">
         <v>420</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B135" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B136" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B137" s="1">
         <v>460</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B138" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B139" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B140" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B141" s="1">
         <v>620</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B142" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B143" s="1">
         <v>980</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B144" s="1">
         <v>540</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B145" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B146" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B147" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B148" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B149" s="1">
         <v>1100</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B150" s="1">
         <v>1100</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B151" s="1">
         <v>1100</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B152" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B153" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B154" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B155" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B156" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B157" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B158" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B159" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B160" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B161" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B162" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B163" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B164" s="1">
         <v>460</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B165" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B166" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B167" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="168" spans="1:2">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B168" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B169" s="1">
         <v>260</v>
       </c>
     </row>
-    <row r="170" spans="1:2">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B170" s="1">
         <v>260</v>
       </c>
     </row>
-    <row r="171" spans="1:2">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B171" s="1">
         <v>440</v>
       </c>
     </row>
-    <row r="172" spans="1:2">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B172" s="1">
         <v>440</v>
       </c>
     </row>
-    <row r="173" spans="1:2">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B173" s="1">
         <v>800</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B174" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="175" spans="1:2">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B175" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="176" spans="1:2">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B176" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B177" s="1">
         <v>400</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B178" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B179" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="180" spans="1:2">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B180" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="181" spans="1:2">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B181" s="1">
         <v>620</v>
       </c>
     </row>
-    <row r="182" spans="1:2">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B182" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="183" spans="1:2">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B183" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="184" spans="1:2">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B184" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="185" spans="1:2">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B185" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="186" spans="1:2">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B186" s="1">
         <v>620</v>
       </c>
     </row>
-    <row r="187" spans="1:2">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B187" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="188" spans="1:2">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B188" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="189" spans="1:2">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B189" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B190" s="1">
         <v>620</v>
       </c>
     </row>
-    <row r="191" spans="1:2">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B191" s="1">
         <v>540</v>
       </c>
     </row>
-    <row r="192" spans="1:2">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B192" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="193" spans="1:2">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B193" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="194" spans="1:2">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B194" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="195" spans="1:2">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B195" s="1">
         <v>540</v>
       </c>
     </row>
-    <row r="196" spans="1:2">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B196" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="197" spans="1:2">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B197" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="198" spans="1:2">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B198" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="199" spans="1:2">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B199" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="200" spans="1:2">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B200" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="201" spans="1:2">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B201" s="1">
         <v>1400</v>
       </c>
     </row>
-    <row r="202" spans="1:2">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B202" s="1">
         <v>480</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B203" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="204" spans="1:2">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B204" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="205" spans="1:2">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B205" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="206" spans="1:2">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B206" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="207" spans="1:2">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B207" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="208" spans="1:2">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B208" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="209" spans="1:2">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B209" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="210" spans="1:2">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B210" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="211" spans="1:2">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B211" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="212" spans="1:2">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B212" s="1">
         <v>620</v>
       </c>
     </row>
-    <row r="213" spans="1:2">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B213" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="214" spans="1:2">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B214" s="1">
         <v>620</v>
       </c>
     </row>
-    <row r="215" spans="1:2">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B215" s="1">
         <v>620</v>
       </c>
     </row>
-    <row r="216" spans="1:2">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B216" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="217" spans="1:2">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B217" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="218" spans="1:2">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B218" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="219" spans="1:2">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B219" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="220" spans="1:2">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B220" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="221" spans="1:2">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B221" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="222" spans="1:2">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B222" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="223" spans="1:2">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B223" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="224" spans="1:2">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B224" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="225" spans="1:2">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B225" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="226" spans="1:2">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B226" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="227" spans="1:2">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B227" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="228" spans="1:2">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B228" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="229" spans="1:2">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B229" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="230" spans="1:2">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B230" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="231" spans="1:2">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B231" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="232" spans="1:2">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B232" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="233" spans="1:2">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B233" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="234" spans="1:2">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B234" s="1">
         <v>758</v>
       </c>
     </row>
-    <row r="235" spans="1:2">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B235" s="1">
         <v>2273</v>
       </c>
     </row>
-    <row r="236" spans="1:2">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B236" s="1">
         <v>1515</v>
       </c>
     </row>
-    <row r="237" spans="1:2">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B237" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="238" spans="1:2">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B238" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="239" spans="1:2">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B239" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="240" spans="1:2">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B240" s="1">
         <v>480</v>
       </c>
     </row>
-    <row r="241" spans="1:2">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B241" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="242" spans="1:2">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B242" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="243" spans="1:2">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B243" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="244" spans="1:2">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B244" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="245" spans="1:2">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B245" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="246" spans="1:2">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B246" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="247" spans="1:2">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B247" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="248" spans="1:2">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B248" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="249" spans="1:2">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B249" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="250" spans="1:2">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B250" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="251" spans="1:2">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B251" s="1">
         <v>380</v>
       </c>
     </row>
-    <row r="252" spans="1:2">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B252" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="253" spans="1:2">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B253" s="1">
         <v>540</v>
       </c>
     </row>
-    <row r="254" spans="1:2">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B254" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="255" spans="1:2">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B255" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="256" spans="1:2">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B256" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="257" spans="1:2">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B257" s="1">
         <v>460</v>
       </c>
     </row>
-    <row r="258" spans="1:2">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B258" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="259" spans="1:2">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B259" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="260" spans="1:2">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B260" s="1">
         <v>860</v>
       </c>
     </row>
-    <row r="261" spans="1:2">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B261" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="262" spans="1:2">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B262" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="263" spans="1:2">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B263" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="264" spans="1:2">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B264" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="265" spans="1:2">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B265" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="266" spans="1:2">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B266" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="267" spans="1:2">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B267" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="268" spans="1:2">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B268" s="1">
         <v>1040</v>
       </c>
     </row>
-    <row r="269" spans="1:2">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B269" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="270" spans="1:2">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B270" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="271" spans="1:2">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B271" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="272" spans="1:2">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B272" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="273" spans="1:2">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B273" s="1">
         <v>1020</v>
       </c>
     </row>
-    <row r="274" spans="1:2">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B274" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="275" spans="1:2">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B275" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="276" spans="1:2">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B276" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="277" spans="1:2">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B277" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="278" spans="1:2">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B278" s="1">
         <v>800</v>
       </c>
     </row>
-    <row r="279" spans="1:2">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B279" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="280" spans="1:2">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B280" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="281" spans="1:2">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B281" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="282" spans="1:2">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B282" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="283" spans="1:2">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B283" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="284" spans="1:2">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B284" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="285" spans="1:2">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B285" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="286" spans="1:2">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B286" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="287" spans="1:2">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B287" s="1">
         <v>880</v>
       </c>
     </row>
-    <row r="288" spans="1:2">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B288" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="289" spans="1:2">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B289" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="290" spans="1:2">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B290" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="291" spans="1:2">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B291" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="292" spans="1:2">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B292" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="293" spans="1:2">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B293" s="1">
         <v>380</v>
       </c>
     </row>
-    <row r="294" spans="1:2">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B294" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="295" spans="1:2">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B295" s="1">
         <v>320</v>
       </c>
     </row>
-    <row r="296" spans="1:2">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B296" s="1">
         <v>540</v>
       </c>
     </row>
-    <row r="297" spans="1:2">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B297" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="298" spans="1:2">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B298" s="1">
         <v>480</v>
       </c>
     </row>
-    <row r="299" spans="1:2">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B299" s="1">
         <v>480</v>
       </c>
     </row>
-    <row r="300" spans="1:2">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B300" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="301" spans="1:2">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B301" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="302" spans="1:2">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B302" s="1">
         <v>800</v>
       </c>
     </row>
-    <row r="303" spans="1:2">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B303" s="1">
         <v>480</v>
       </c>
     </row>
-    <row r="304" spans="1:2">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B304" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="305" spans="1:2">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B305" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="306" spans="1:2">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B306" s="1">
         <v>380</v>
       </c>
     </row>
-    <row r="307" spans="1:2">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B307" s="1">
         <v>440</v>
       </c>
     </row>
-    <row r="308" spans="1:2">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B308" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="309" spans="1:2">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B309" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="310" spans="1:2">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B310" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="311" spans="1:2">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B311" s="1">
         <v>960</v>
       </c>
     </row>
-    <row r="312" spans="1:2">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B312" s="1">
         <v>1020</v>
       </c>
     </row>
-    <row r="313" spans="1:2">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B313" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="314" spans="1:2">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B314" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="315" spans="1:2">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B315" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="316" spans="1:2">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B316" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="317" spans="1:2">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B317" s="1">
         <v>1020</v>
       </c>
     </row>
-    <row r="318" spans="1:2">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B318" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="319" spans="1:2">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B319" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="320" spans="1:2">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B320" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="321" spans="1:2">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B321" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="322" spans="1:2">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B322" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="323" spans="1:2">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B323" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="324" spans="1:2">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B324" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="325" spans="1:2">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B325" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="326" spans="1:2">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B326" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="327" spans="1:2">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B327" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="328" spans="1:2">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B328" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="329" spans="1:2">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B329" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="330" spans="1:2">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B330" s="1">
         <v>480</v>
       </c>
     </row>
-    <row r="331" spans="1:2">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B331" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="332" spans="1:2">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B332" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="333" spans="1:2">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B333" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="334" spans="1:2">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B334" s="1">
         <v>860</v>
       </c>
     </row>
-    <row r="335" spans="1:2">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B335" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="336" spans="1:2">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B336" s="1">
         <v>540</v>
       </c>
     </row>
-    <row r="337" spans="1:2">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B337" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="338" spans="1:2">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B338" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="339" spans="1:2">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B339" s="1">
         <v>420</v>
       </c>
     </row>
-    <row r="340" spans="1:2">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B340" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="341" spans="1:2">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B341" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="342" spans="1:2">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B342" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="343" spans="1:2">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B343" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="344" spans="1:2">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B344" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="345" spans="1:2">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B345" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="346" spans="1:2">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B346" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="347" spans="1:2">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B347" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="348" spans="1:2">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B348" s="1">
         <v>620</v>
       </c>
     </row>
-    <row r="349" spans="1:2">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B349" s="1">
         <v>440</v>
       </c>
     </row>
-    <row r="350" spans="1:2">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B350" s="1">
         <v>320</v>
       </c>
     </row>
-    <row r="351" spans="1:2">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B351" s="1">
         <v>320</v>
       </c>
     </row>
-    <row r="352" spans="1:2">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B352" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="353" spans="1:2">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B353" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="354" spans="1:2">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B354" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="355" spans="1:2">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B355" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="356" spans="1:2">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B356" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="357" spans="1:2">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B357" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="358" spans="1:2">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B358" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="359" spans="1:2">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B359" s="1">
         <v>620</v>
       </c>
     </row>
-    <row r="360" spans="1:2">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B360" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="361" spans="1:2">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B361" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="362" spans="1:2">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B362" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="363" spans="1:2">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B363" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="364" spans="1:2">
+    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B364" s="1">
         <v>880</v>
       </c>
     </row>
-    <row r="365" spans="1:2">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B365" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="366" spans="1:2">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B366" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="367" spans="1:2">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B367" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="368" spans="1:2">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B368" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="369" spans="1:2">
+    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B369" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="370" spans="1:2">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B370" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="371" spans="1:2">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B371" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="372" spans="1:2">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B372" s="1">
         <v>440</v>
       </c>
     </row>
-    <row r="373" spans="1:2">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B373" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="374" spans="1:2">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B374" s="1">
         <v>800</v>
       </c>
     </row>
-    <row r="375" spans="1:2">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B375" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="376" spans="1:2">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B376" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="377" spans="1:2">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B377" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="378" spans="1:2">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B378" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="379" spans="1:2">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B379" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="380" spans="1:2">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B380" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="381" spans="1:2">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B381" s="1">
         <v>620</v>
       </c>
     </row>
-    <row r="382" spans="1:2">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B382" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="383" spans="1:2">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B383" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="384" spans="1:2">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B384" s="1">
         <v>480</v>
       </c>
     </row>
-    <row r="385" spans="1:2">
+    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B385" s="1">
         <v>480</v>
       </c>
     </row>
-    <row r="386" spans="1:2">
+    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B386" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="387" spans="1:2">
+    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B387" s="1">
         <v>880</v>
       </c>
     </row>
-    <row r="388" spans="1:2">
+    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B388" s="1">
         <v>800</v>
       </c>
     </row>
-    <row r="389" spans="1:2">
+    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B389" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="390" spans="1:2">
+    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B390" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="391" spans="1:2">
+    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B391" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="392" spans="1:2">
+    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B392" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="393" spans="1:2">
+    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B393" s="1">
         <v>940</v>
       </c>
     </row>
-    <row r="394" spans="1:2">
+    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B394" s="1">
         <v>980</v>
       </c>
     </row>
-    <row r="395" spans="1:2">
+    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B395" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="396" spans="1:2">
+    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B396" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="397" spans="1:2">
+    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B397" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="398" spans="1:2">
+    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B398" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="399" spans="1:2">
+    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B399" s="1">
         <v>620</v>
       </c>
     </row>
-    <row r="400" spans="1:2">
+    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B400" s="1">
         <v>620</v>
       </c>
     </row>
-    <row r="401" spans="1:2">
+    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B401" s="1">
         <v>860</v>
       </c>
     </row>
-    <row r="402" spans="1:2">
+    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B402" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="403" spans="1:2">
+    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B403" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="404" spans="1:2">
+    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B404" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="405" spans="1:2">
+    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B405" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="406" spans="1:2">
+    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B406" s="1">
         <v>960</v>
       </c>
     </row>
-    <row r="407" spans="1:2">
+    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B407" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="408" spans="1:2">
+    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B408" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="409" spans="1:2">
+    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B409" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="410" spans="1:2">
+    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B410" s="1">
         <v>860</v>
       </c>
     </row>
-    <row r="411" spans="1:2">
+    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B411" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="412" spans="1:2">
+    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B412" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="413" spans="1:2">
+    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B413" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="414" spans="1:2">
+    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B414" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="415" spans="1:2">
+    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B415" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="416" spans="1:2">
+    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B416" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="417" spans="1:2">
+    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B417" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="418" spans="1:2">
+    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B418" s="1">
         <v>480</v>
       </c>
     </row>
-    <row r="419" spans="1:2">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B419" s="1">
         <v>620</v>
       </c>
     </row>
-    <row r="420" spans="1:2">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B420" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="421" spans="1:2">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B421" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="422" spans="1:2">
+    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B422" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="423" spans="1:2">
+    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B423" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="424" spans="1:2">
+    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B424" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="425" spans="1:2">
+    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B425" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="426" spans="1:2">
+    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B426" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="427" spans="1:2">
+    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B427" s="1">
         <v>480</v>
       </c>
     </row>
-    <row r="428" spans="1:2">
+    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B428" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="429" spans="1:2">
+    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B429" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="430" spans="1:2">
+    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B430" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="431" spans="1:2">
+    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B431" s="1">
         <v>440</v>
       </c>
     </row>
-    <row r="432" spans="1:2">
+    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B432" s="1">
         <v>440</v>
       </c>
     </row>
-    <row r="433" spans="1:2">
+    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B433" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="434" spans="1:2">
+    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B434" s="1">
         <v>880</v>
       </c>
     </row>
-    <row r="435" spans="1:2">
+    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B435" s="1">
         <v>880</v>
       </c>
     </row>
-    <row r="436" spans="1:2">
+    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B436" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="437" spans="1:2">
+    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B437" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="438" spans="1:2">
+    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B438" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="439" spans="1:2">
+    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B439" s="1">
         <v>1100</v>
       </c>
     </row>
-    <row r="440" spans="1:2">
+    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B440" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="441" spans="1:2">
+    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B441" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="442" spans="1:2">
+    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B442" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="443" spans="1:2">
+    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B443" s="1">
         <v>800</v>
       </c>
     </row>
-    <row r="444" spans="1:2">
+    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B444" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="445" spans="1:2">
+    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B445" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="446" spans="1:2">
+    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B446" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="447" spans="1:2">
+    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B447" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="448" spans="1:2">
+    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B448" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="449" spans="1:2">
+    <row r="449" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B449" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="450" spans="1:2">
+    <row r="450" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B450" s="1">
         <v>860</v>
       </c>
     </row>
-    <row r="451" spans="1:2">
+    <row r="451" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B451" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="452" spans="1:2">
+    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B452" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="453" spans="1:2">
+    <row r="453" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B453" s="1">
         <v>800</v>
       </c>
     </row>
-    <row r="454" spans="1:2">
+    <row r="454" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B454" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="455" spans="1:2">
+    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B455" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="456" spans="1:2">
+    <row r="456" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B456" s="1">
         <v>620</v>
       </c>
     </row>
-    <row r="457" spans="1:2">
+    <row r="457" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B457" s="1">
         <v>880</v>
       </c>
     </row>
-    <row r="458" spans="1:2">
+    <row r="458" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B458" s="1">
         <v>860</v>
       </c>
     </row>
-    <row r="459" spans="1:2">
+    <row r="459" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B459" s="1">
         <v>800</v>
       </c>
     </row>
-    <row r="460" spans="1:2">
+    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B460" s="1">
         <v>860</v>
       </c>
     </row>
-    <row r="461" spans="1:2">
+    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B461" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="462" spans="1:2">
+    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B462" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="463" spans="1:2">
+    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B463" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="464" spans="1:2">
+    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B464" s="1">
         <v>1100</v>
       </c>
     </row>
-    <row r="465" spans="1:2">
+    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B465" s="1">
         <v>790</v>
       </c>
     </row>
-    <row r="466" spans="1:2">
+    <row r="466" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B466" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="467" spans="1:2">
+    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B467" s="1">
         <v>800</v>
       </c>
     </row>
-    <row r="468" spans="1:2">
+    <row r="468" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B468" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="469" spans="1:2">
+    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B469" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="470" spans="1:2">
+    <row r="470" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B470" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="471" spans="1:2">
+    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B471" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="472" spans="1:2">
+    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B472" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="473" spans="1:2">
+    <row r="473" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B473" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="474" spans="1:2">
+    <row r="474" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B474" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="475" spans="1:2">
+    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B475" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="476" spans="1:2">
+    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B476" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="477" spans="1:2">
+    <row r="477" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B477" s="1">
         <v>880</v>
       </c>
     </row>
-    <row r="478" spans="1:2">
+    <row r="478" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B478" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="479" spans="1:2">
+    <row r="479" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B479" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="480" spans="1:2">
+    <row r="480" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B480" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="481" spans="1:2">
+    <row r="481" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B481" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="482" spans="1:2">
+    <row r="482" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B482" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="483" spans="1:2">
+    <row r="483" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B483" s="1">
         <v>860</v>
       </c>
     </row>
-    <row r="484" spans="1:2">
+    <row r="484" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B484" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="485" spans="1:2">
+    <row r="485" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B485" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="486" spans="1:2">
+    <row r="486" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B486" s="1">
         <v>960</v>
       </c>
     </row>
-    <row r="487" spans="1:2">
+    <row r="487" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B487" s="1">
         <v>940</v>
       </c>
     </row>
-    <row r="488" spans="1:2">
+    <row r="488" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B488" s="1">
         <v>1040</v>
       </c>
     </row>
-    <row r="489" spans="1:2">
+    <row r="489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B489" s="1">
         <v>1040</v>
       </c>
     </row>
-    <row r="490" spans="1:2">
+    <row r="490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B490" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="491" spans="1:2">
+    <row r="491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B491" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="492" spans="1:2">
+    <row r="492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B492" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="493" spans="1:2">
+    <row r="493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B493" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="494" spans="1:2">
+    <row r="494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B494" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="495" spans="1:2">
+    <row r="495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B495" s="1">
         <v>620</v>
       </c>
     </row>
-    <row r="496" spans="1:2">
+    <row r="496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B496" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="497" spans="1:2">
+    <row r="497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B497" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="498" spans="1:2">
+    <row r="498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B498" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="499" spans="1:2">
+    <row r="499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B499" s="1">
         <v>960</v>
       </c>
     </row>
-    <row r="500" spans="1:2">
+    <row r="500" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B500" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="501" spans="1:2">
+    <row r="501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B501" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="502" spans="1:2">
+    <row r="502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B502" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="503" spans="1:2">
+    <row r="503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B503" s="1">
         <v>540</v>
       </c>
     </row>
-    <row r="504" spans="1:2">
+    <row r="504" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B504" s="1">
         <v>1100</v>
       </c>
     </row>
-    <row r="505" spans="1:2">
+    <row r="505" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B505" s="1">
         <v>1100</v>
       </c>
     </row>
-    <row r="506" spans="1:2">
+    <row r="506" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B506" s="1">
         <v>1100</v>
       </c>
     </row>
-    <row r="507" spans="1:2">
+    <row r="507" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B507" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="508" spans="1:2">
+    <row r="508" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B508" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="509" spans="1:2">
+    <row r="509" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B509" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="510" spans="1:2">
+    <row r="510" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B510" s="1">
         <v>620</v>
       </c>
     </row>
-    <row r="511" spans="1:2">
+    <row r="511" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B511" s="1">
         <v>860</v>
       </c>
     </row>
-    <row r="512" spans="1:2">
+    <row r="512" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B512" s="1">
         <v>980</v>
       </c>
     </row>
-    <row r="513" spans="1:2">
+    <row r="513" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B513" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="514" spans="1:2">
+    <row r="514" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B514" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="515" spans="1:2">
+    <row r="515" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B515" s="1">
         <v>1100</v>
       </c>
     </row>
-    <row r="516" spans="1:2">
+    <row r="516" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B516" s="1">
         <v>1100</v>
       </c>
     </row>
-    <row r="517" spans="1:2">
+    <row r="517" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B517" s="1">
         <v>1100</v>
       </c>
     </row>
-    <row r="518" spans="1:2">
+    <row r="518" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B518" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="519" spans="1:2">
+    <row r="519" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B519" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="520" spans="1:2">
+    <row r="520" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B520" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="521" spans="1:2">
+    <row r="521" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B521" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="522" spans="1:2">
+    <row r="522" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B522" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="523" spans="1:2">
+    <row r="523" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B523" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="524" spans="1:2">
+    <row r="524" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B524" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="525" spans="1:2">
+    <row r="525" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B525" s="1">
         <v>800</v>
       </c>
     </row>
-    <row r="526" spans="1:2">
+    <row r="526" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B526" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="527" spans="1:2">
+    <row r="527" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B527" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="528" spans="1:2">
+    <row r="528" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B528" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="529" spans="1:2">
+    <row r="529" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B529" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="530" spans="1:2">
+    <row r="530" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B530" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="531" spans="1:2">
+    <row r="531" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B531" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="532" spans="1:2">
+    <row r="532" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B532" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="533" spans="1:2">
+    <row r="533" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B533" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="534" spans="1:2">
+    <row r="534" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B534" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="535" spans="1:2">
+    <row r="535" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B535" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="536" spans="1:2">
+    <row r="536" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B536" s="1">
         <v>1400</v>
       </c>
     </row>
-    <row r="537" spans="1:2">
+    <row r="537" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B537" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="538" spans="1:2">
+    <row r="538" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B538" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="539" spans="1:2">
+    <row r="539" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B539" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="540" spans="1:2">
+    <row r="540" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B540" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="541" spans="1:2">
+    <row r="541" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B541" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="542" spans="1:2">
+    <row r="542" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B542" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="543" spans="1:2">
+    <row r="543" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B543" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="544" spans="1:2">
+    <row r="544" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B544" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="545" spans="1:2">
+    <row r="545" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B545" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="546" spans="1:2">
+    <row r="546" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B546" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="547" spans="1:2">
+    <row r="547" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B547" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="548" spans="1:2">
+    <row r="548" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B548" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="549" spans="1:2">
+    <row r="549" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B549" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="550" spans="1:2">
+    <row r="550" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B550" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="551" spans="1:2">
+    <row r="551" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B551" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="552" spans="1:2">
+    <row r="552" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B552" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="553" spans="1:2">
+    <row r="553" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B553" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="554" spans="1:2">
+    <row r="554" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B554" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="555" spans="1:2">
+    <row r="555" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B555" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="556" spans="1:2">
+    <row r="556" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B556" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="557" spans="1:2">
+    <row r="557" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B557" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="558" spans="1:2">
+    <row r="558" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B558" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="559" spans="1:2">
+    <row r="559" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B559" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="560" spans="1:2">
+    <row r="560" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B560" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="561" spans="1:2">
+    <row r="561" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B561" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="562" spans="1:2">
+    <row r="562" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B562" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="563" spans="1:2">
+    <row r="563" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B563" s="1">
         <v>540</v>
       </c>
     </row>
-    <row r="564" spans="1:2">
+    <row r="564" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B564" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="565" spans="1:2">
+    <row r="565" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B565" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="566" spans="1:2">
+    <row r="566" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B566" s="1">
         <v>860</v>
       </c>
     </row>
-    <row r="567" spans="1:2">
+    <row r="567" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B567" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="568" spans="1:2">
+    <row r="568" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B568" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="569" spans="1:2">
+    <row r="569" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B569" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="570" spans="1:2">
+    <row r="570" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B570" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="571" spans="1:2">
+    <row r="571" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B571" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="572" spans="1:2">
+    <row r="572" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B572" s="1">
         <v>1040</v>
       </c>
     </row>
-    <row r="573" spans="1:2">
+    <row r="573" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B573" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="574" spans="1:2">
+    <row r="574" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B574" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="575" spans="1:2">
+    <row r="575" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B575" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="576" spans="1:2">
+    <row r="576" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B576" s="1">
         <v>1020</v>
       </c>
     </row>
-    <row r="577" spans="1:2">
+    <row r="577" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B577" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="578" spans="1:2">
+    <row r="578" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B578" s="1">
         <v>800</v>
       </c>
     </row>
-    <row r="579" spans="1:2">
+    <row r="579" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B579" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="580" spans="1:2">
+    <row r="580" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B580" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="581" spans="1:2">
+    <row r="581" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B581" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="582" spans="1:2">
+    <row r="582" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B582" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="583" spans="1:2">
+    <row r="583" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B583" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="584" spans="1:2">
+    <row r="584" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B584" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="585" spans="1:2">
+    <row r="585" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B585" s="1">
         <v>880</v>
       </c>
     </row>
-    <row r="586" spans="1:2">
+    <row r="586" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B586" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="587" spans="1:2">
+    <row r="587" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B587" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="588" spans="1:2">
+    <row r="588" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B588" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="589" spans="1:2">
+    <row r="589" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B589" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="590" spans="1:2">
+    <row r="590" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B590" s="1">
         <v>800</v>
       </c>
     </row>
-    <row r="591" spans="1:2">
+    <row r="591" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B591" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="592" spans="1:2">
+    <row r="592" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B592" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="593" spans="1:2">
+    <row r="593" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B593" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="594" spans="1:2">
+    <row r="594" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B594" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="595" spans="1:2">
+    <row r="595" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B595" s="1">
         <v>960</v>
       </c>
     </row>
-    <row r="596" spans="1:2">
+    <row r="596" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B596" s="1">
         <v>1020</v>
       </c>
     </row>
-    <row r="597" spans="1:2">
+    <row r="597" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B597" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="598" spans="1:2">
+    <row r="598" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B598" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="599" spans="1:2">
+    <row r="599" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B599" s="1">
         <v>640</v>
       </c>
     </row>
-    <row r="600" spans="1:2">
+    <row r="600" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B600" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="601" spans="1:2">
+    <row r="601" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B601" s="1">
         <v>1020</v>
       </c>
     </row>
-    <row r="602" spans="1:2">
+    <row r="602" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B602" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="603" spans="1:2">
+    <row r="603" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B603" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="604" spans="1:2">
+    <row r="604" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B604" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="605" spans="1:2">
+    <row r="605" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B605" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="606" spans="1:2">
+    <row r="606" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B606" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="607" spans="1:2">
+    <row r="607" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B607" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="608" spans="1:2">
+    <row r="608" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B608" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="609" spans="1:2">
+    <row r="609" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B609" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="610" spans="1:2">
+    <row r="610" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B610" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="611" spans="1:2">
+    <row r="611" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B611" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="612" spans="1:2">
+    <row r="612" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B612" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="613" spans="1:2">
+    <row r="613" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B613" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="614" spans="1:2">
+    <row r="614" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B614" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="615" spans="1:2">
+    <row r="615" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B615" s="1">
         <v>860</v>
       </c>
     </row>
-    <row r="616" spans="1:2">
+    <row r="616" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B616" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="617" spans="1:2">
+    <row r="617" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B617" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="618" spans="1:2">
+    <row r="618" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B618" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="619" spans="1:2">
+    <row r="619" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B619" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="620" spans="1:2">
+    <row r="620" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B620" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="621" spans="1:2">
+    <row r="621" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B621" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="622" spans="1:2">
+    <row r="622" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B622" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="623" spans="1:2">
+    <row r="623" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B623" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="624" spans="1:2">
+    <row r="624" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B624" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="625" spans="1:2">
+    <row r="625" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B625" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="626" spans="1:2">
+    <row r="626" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B626" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="627" spans="1:2">
+    <row r="627" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B627" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="628" spans="1:2">
+    <row r="628" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B628" s="1">
         <v>880</v>
       </c>
     </row>
-    <row r="629" spans="1:2">
+    <row r="629" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B629" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="630" spans="1:2">
+    <row r="630" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B630" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="631" spans="1:2">
+    <row r="631" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B631" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="632" spans="1:2">
+    <row r="632" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B632" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="633" spans="1:2">
+    <row r="633" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B633" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="634" spans="1:2">
+    <row r="634" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B634" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="635" spans="1:2">
+    <row r="635" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B635" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="636" spans="1:2">
+    <row r="636" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B636" s="1">
         <v>440</v>
       </c>
     </row>
-    <row r="637" spans="1:2">
+    <row r="637" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B637" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="638" spans="1:2">
+    <row r="638" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B638" s="1">
         <v>800</v>
       </c>
     </row>
-    <row r="639" spans="1:2">
+    <row r="639" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B639" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="640" spans="1:2">
+    <row r="640" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B640" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="641" spans="1:2">
+    <row r="641" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B641" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="642" spans="1:2">
+    <row r="642" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B642" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="643" spans="1:2">
+    <row r="643" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B643" s="1">
         <v>880</v>
       </c>
     </row>
-    <row r="644" spans="1:2">
+    <row r="644" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B644" s="1">
         <v>800</v>
       </c>
     </row>
-    <row r="645" spans="1:2">
+    <row r="645" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B645" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="646" spans="1:2">
+    <row r="646" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B646" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="647" spans="1:2">
+    <row r="647" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B647" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="648" spans="1:2">
+    <row r="648" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B648" s="1">
         <v>940</v>
       </c>
     </row>
-    <row r="649" spans="1:2">
+    <row r="649" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B649" s="1">
         <v>980</v>
       </c>
     </row>
-    <row r="650" spans="1:2">
+    <row r="650" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B650" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="651" spans="1:2">
+    <row r="651" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B651" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="652" spans="1:2">
+    <row r="652" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B652" s="1">
         <v>860</v>
       </c>
     </row>
-    <row r="653" spans="1:2">
+    <row r="653" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B653" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="654" spans="1:2">
+    <row r="654" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B654" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="655" spans="1:2">
+    <row r="655" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B655" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="656" spans="1:2">
+    <row r="656" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B656" s="1">
         <v>960</v>
       </c>
     </row>
-    <row r="657" spans="1:2">
+    <row r="657" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B657" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="658" spans="1:2">
+    <row r="658" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B658" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="659" spans="1:2">
+    <row r="659" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B659" s="1">
         <v>860</v>
       </c>
     </row>
-    <row r="660" spans="1:2">
+    <row r="660" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B660" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="661" spans="1:2">
+    <row r="661" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B661" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="662" spans="1:2">
+    <row r="662" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B662" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="663" spans="1:2">
+    <row r="663" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B663" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="664" spans="1:2">
+    <row r="664" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B664" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="665" spans="1:2">
+    <row r="665" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B665" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="666" spans="1:2">
+    <row r="666" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B666" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="667" spans="1:2">
+    <row r="667" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B667" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="668" spans="1:2">
+    <row r="668" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B668" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="669" spans="1:2">
+    <row r="669" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B669" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="670" spans="1:2">
+    <row r="670" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B670" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="671" spans="1:2">
+    <row r="671" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B671" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="672" spans="1:2">
+    <row r="672" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B672" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="673" spans="1:2">
+    <row r="673" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B673" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="674" spans="1:2">
+    <row r="674" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B674" s="1">
         <v>860</v>
       </c>
     </row>
-    <row r="675" spans="1:2">
+    <row r="675" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B675" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="676" spans="1:2">
+    <row r="676" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B676" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="677" spans="1:2">
+    <row r="677" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B677" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="678" spans="1:2">
+    <row r="678" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B678" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="679" spans="1:2">
+    <row r="679" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B679" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="680" spans="1:2">
+    <row r="680" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B680" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="681" spans="1:2">
+    <row r="681" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B681" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="682" spans="1:2">
+    <row r="682" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B682" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="683" spans="1:2">
+    <row r="683" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B683" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="684" spans="1:2">
+    <row r="684" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B684" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="685" spans="1:2">
+    <row r="685" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B685" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="686" spans="1:2">
+    <row r="686" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B686" s="1">
         <v>1040</v>
       </c>
     </row>
-    <row r="687" spans="1:2">
+    <row r="687" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B687" s="1">
         <v>940</v>
       </c>
     </row>
-    <row r="688" spans="1:2">
+    <row r="688" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B688" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="689" spans="1:2">
+    <row r="689" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B689" s="1">
         <v>1100</v>
       </c>
     </row>
-    <row r="690" spans="1:2">
+    <row r="690" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B690" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="691" spans="1:2">
+    <row r="691" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B691" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="692" spans="1:2">
+    <row r="692" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B692" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="693" spans="1:2">
+    <row r="693" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B693" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="694" spans="1:2">
+    <row r="694" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B694" s="1">
         <v>440</v>
       </c>
     </row>
-    <row r="695" spans="1:2">
+    <row r="695" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B695" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="696" spans="1:2">
+    <row r="696" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B696" s="1">
         <v>440</v>
       </c>
     </row>
-    <row r="697" spans="1:2">
+    <row r="697" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B697" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="698" spans="1:2">
+    <row r="698" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B698" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="699" spans="1:2">
+    <row r="699" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B699" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="700" spans="1:2">
+    <row r="700" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B700" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="701" spans="1:2">
+    <row r="701" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B701" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="702" spans="1:2">
+    <row r="702" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B702" s="1">
         <v>400</v>
       </c>
     </row>
-    <row r="703" spans="1:2">
+    <row r="703" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A703" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B703" s="1">
         <v>400</v>
       </c>
     </row>
-    <row r="704" spans="1:2">
+    <row r="704" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A704" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B704" s="1">
         <v>380</v>
       </c>
     </row>
-    <row r="705" spans="1:2">
+    <row r="705" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B705" s="1">
         <v>380</v>
       </c>
     </row>
-    <row r="706" spans="1:2">
+    <row r="706" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B706" s="1">
         <v>380</v>
       </c>
     </row>
-    <row r="707" spans="1:2">
+    <row r="707" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B707" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="708" spans="1:2">
+    <row r="708" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B708" s="1">
         <v>700</v>
       </c>
     </row>
-    <row r="709" spans="1:2">
+    <row r="709" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B709" s="1">
         <v>860</v>
       </c>
     </row>
-    <row r="710" spans="1:2">
+    <row r="710" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B710" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="711" spans="1:2">
+    <row r="711" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A711" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B711" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="712" spans="1:2">
+    <row r="712" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A712" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B712" s="1">
         <v>780</v>
       </c>
     </row>
-    <row r="713" spans="1:2">
+    <row r="713" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A713" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B713" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="714" spans="1:2">
+    <row r="714" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A714" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B714" s="1">
         <v>720</v>
       </c>
     </row>
-    <row r="715" spans="1:2">
+    <row r="715" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B715" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="716" spans="1:2">
+    <row r="716" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A716" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B716" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="717" spans="1:2">
+    <row r="717" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A717" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B717" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="718" spans="1:2">
+    <row r="718" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A718" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B718" s="1">
         <v>760</v>
       </c>
     </row>
-    <row r="719" spans="1:2">
+    <row r="719" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A719" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B719" s="1">
         <v>840</v>
       </c>
     </row>
-    <row r="720" spans="1:2">
+    <row r="720" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A720" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B720" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="721" spans="1:2">
+    <row r="721" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B721" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="722" spans="1:2">
+    <row r="722" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A722" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B722" s="1">
         <v>920</v>
       </c>
     </row>
-    <row r="723" spans="1:2">
+    <row r="723" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A723" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B723" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="724" spans="1:2">
+    <row r="724" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A724" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B724" s="1">
         <v>1040</v>
       </c>
     </row>
-    <row r="725" spans="1:2">
+    <row r="725" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A725" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B725" s="1">
         <v>940</v>
       </c>
     </row>
-    <row r="726" spans="1:2">
+    <row r="726" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A726" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B726" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="727" spans="1:2">
+    <row r="727" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A727" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B727" s="1">
         <v>1100</v>
       </c>
     </row>
-    <row r="728" spans="1:2">
+    <row r="728" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A728" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B728" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="729" spans="1:2">
+    <row r="729" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A729" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B729" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="730" spans="1:2">
+    <row r="730" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A730" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B730" s="1">
         <v>740</v>
       </c>
     </row>
-    <row r="731" spans="1:2">
+    <row r="731" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A731" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B731" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="732" spans="1:2">
+    <row r="732" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A732" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B732" s="1">
         <v>440</v>
       </c>
     </row>
-    <row r="733" spans="1:2">
+    <row r="733" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A733" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B733" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="734" spans="1:2">
+    <row r="734" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A734" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B734" s="1">
         <v>440</v>
       </c>
     </row>
-    <row r="735" spans="1:2">
+    <row r="735" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A735" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B735" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="736" spans="1:2">
+    <row r="736" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A736" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B736" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="737" spans="1:2">
+    <row r="737" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A737" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B737" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="738" spans="1:2">
+    <row r="738" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A738" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B738" s="1">
         <v>380</v>
       </c>
     </row>
-    <row r="739" spans="1:2">
+    <row r="739" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A739" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B739" s="1">
         <v>380</v>
       </c>
     </row>
-    <row r="740" spans="1:2">
+    <row r="740" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A740" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B740" s="1">
         <v>380</v>
       </c>
     </row>
-    <row r="741" spans="1:2">
+    <row r="741" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A741" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B741" s="1">
         <v>480</v>
       </c>
     </row>
-    <row r="742" spans="1:2">
+    <row r="742" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A742" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B742" s="1">
         <v>480</v>
       </c>
     </row>
-    <row r="743" spans="1:2">
+    <row r="743" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A743" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B743" s="1">
         <v>480</v>
       </c>
     </row>
-    <row r="744" spans="1:2">
+    <row r="744" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A744" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B744" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="745" spans="1:2">
+    <row r="745" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A745" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B745" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="746" spans="1:2">
+    <row r="746" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A746" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B746" s="1">
         <v>440</v>
       </c>
     </row>
-    <row r="747" spans="1:2">
+    <row r="747" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A747" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B747" s="1">
         <v>420</v>
       </c>
     </row>
-    <row r="748" spans="1:2">
+    <row r="748" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A748" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B748" s="1">
         <v>380</v>
       </c>
     </row>
-    <row r="749" spans="1:2">
+    <row r="749" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A749" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B749" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="750" spans="1:2">
+    <row r="750" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A750" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B750" s="1">
         <v>820</v>
       </c>
     </row>
-    <row r="751" spans="1:2">
+    <row r="751" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A751" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B751" s="1">
         <v>660</v>
       </c>
     </row>
-    <row r="752" spans="1:2">
+    <row r="752" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A752" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B752" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="753" spans="1:2">
+    <row r="753" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A753" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B753" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="754" spans="1:2">
+    <row r="754" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A754" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B754" s="1">
         <v>580</v>
       </c>
     </row>
-    <row r="755" spans="1:2">
+    <row r="755" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A755" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B755" s="1">
         <v>620</v>
       </c>
     </row>
-    <row r="756" spans="1:2">
+    <row r="756" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A756" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B756" s="1">
         <v>560</v>
       </c>
     </row>
-    <row r="757" spans="1:2">
+    <row r="757" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A757" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B757" s="1">
         <v>560</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="773">
   <si>
     <t>Наименование</t>
   </si>
@@ -413,6 +413,9 @@
     <t>Jungle - Body Flow (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Jungle - Hired Gun (APA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Jungle - Rising High (AIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -953,6 +956,9 @@
     <t>Stamm - Alpha Hops: Mosaic (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Stamm - Bremen (German Pils), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Stamm - Brezn (Festival Lager), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1073,6 +1079,9 @@
     <t>Travel Bus -  Funky Road (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Valaduta Brovar - TripWave (NEDIIPA), РОЗИВ</t>
+  </si>
+  <si>
     <t>Velka Morava  "Золотой ярлык"  (Lager), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1541,6 +1550,9 @@
     <t>вынос_Jungle - Body Flow (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Jungle - Hired Gun (APA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Jungle - Rising High (AIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1811,6 +1823,9 @@
     <t>вынос_Stamm - Alpha Hops: Mosaic (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Stamm - Bremen (German Pils), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Stamm - Brezn (Festival Lager), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1890,6 +1905,9 @@
   </si>
   <si>
     <t>вынос_Switch Brewery - Крафтпит (lezak), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Valaduta Brovar - TripWave (NEDIIPA), РОЗИВ</t>
   </si>
   <si>
     <t>вынос_Velka Morava - Take Five (APA), РОЗЛИВ, Россия</t>
@@ -2669,7 +2687,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B767"/>
+  <dimension ref="A1:B773"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -3729,7 +3747,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>1100</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -3745,7 +3763,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -3753,12 +3771,12 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B136" s="1">
         <v>840</v>
@@ -3769,7 +3787,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="1">
-        <v>420</v>
+        <v>840</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -3777,7 +3795,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="1">
-        <v>520</v>
+        <v>420</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -3785,7 +3803,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -3793,7 +3811,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="1">
-        <v>460</v>
+        <v>720</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -3801,7 +3819,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="1">
-        <v>560</v>
+        <v>460</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -3809,7 +3827,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -3817,7 +3835,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -3825,7 +3843,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -3833,7 +3851,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -3841,7 +3859,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="1">
-        <v>980</v>
+        <v>520</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -3849,7 +3867,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="1">
-        <v>540</v>
+        <v>980</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3857,7 +3875,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -3865,7 +3883,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -3873,7 +3891,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -3881,7 +3899,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="1">
-        <v>560</v>
+        <v>760</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3889,7 +3907,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3913,7 +3931,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -3921,7 +3939,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -3929,7 +3947,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -3937,7 +3955,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -3945,7 +3963,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -3969,7 +3987,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -3977,7 +3995,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -3985,7 +4003,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -3993,7 +4011,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4001,7 +4019,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4009,7 +4027,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="1">
-        <v>460</v>
+        <v>700</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -4017,7 +4035,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4025,7 +4043,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4033,7 +4051,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -4041,7 +4059,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4049,7 +4067,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4065,7 +4083,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4081,7 +4099,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4089,7 +4107,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4097,7 +4115,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4105,7 +4123,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4113,7 +4131,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4121,7 +4139,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="1">
-        <v>740</v>
+        <v>400</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4129,7 +4147,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4137,7 +4155,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4145,7 +4163,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4153,7 +4171,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4161,7 +4179,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4169,7 +4187,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4185,7 +4203,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4193,7 +4211,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4201,7 +4219,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4217,7 +4235,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4225,7 +4243,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4233,7 +4251,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4241,7 +4259,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4249,7 +4267,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4257,7 +4275,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4265,7 +4283,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4273,7 +4291,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4281,7 +4299,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4289,7 +4307,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4297,7 +4315,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4305,7 +4323,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="1">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4313,7 +4331,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="1">
-        <v>480</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4321,7 +4339,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4329,7 +4347,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4337,7 +4355,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4345,7 +4363,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4353,7 +4371,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4361,7 +4379,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4369,7 +4387,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4377,7 +4395,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4385,7 +4403,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4393,7 +4411,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4401,7 +4419,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4409,7 +4427,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4425,7 +4443,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4441,7 +4459,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4449,7 +4467,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4457,7 +4475,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4465,7 +4483,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4473,7 +4491,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4481,7 +4499,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4489,7 +4507,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4497,7 +4515,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4521,7 +4539,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4529,7 +4547,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4537,7 +4555,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4553,7 +4571,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4561,7 +4579,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4569,7 +4587,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="1">
-        <v>758</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4577,7 +4595,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="1">
-        <v>2273</v>
+        <v>758</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4585,7 +4603,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="1">
-        <v>1515</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4593,7 +4611,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="1">
-        <v>520</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4601,7 +4619,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4609,7 +4627,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4617,7 +4635,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4625,7 +4643,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4641,7 +4659,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4649,7 +4667,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4657,7 +4675,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4665,7 +4683,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4673,7 +4691,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="1">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4681,7 +4699,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4689,7 +4707,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4697,7 +4715,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4705,7 +4723,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4713,7 +4731,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -4721,7 +4739,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4729,7 +4747,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4737,7 +4755,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4745,7 +4763,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4753,7 +4771,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="1">
-        <v>460</v>
+        <v>580</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4761,7 +4779,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="1">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4769,7 +4787,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4777,7 +4795,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4785,7 +4803,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4809,7 +4827,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4825,7 +4843,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="1">
-        <v>1000</v>
+        <v>560</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4833,7 +4851,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4841,7 +4859,7 @@
         <v>270</v>
       </c>
       <c r="B271" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4849,7 +4867,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4857,7 +4875,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4865,7 +4883,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4873,7 +4891,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4881,7 +4899,7 @@
         <v>275</v>
       </c>
       <c r="B276" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4889,7 +4907,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4897,7 +4915,7 @@
         <v>277</v>
       </c>
       <c r="B278" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4905,7 +4923,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4913,7 +4931,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4921,7 +4939,7 @@
         <v>280</v>
       </c>
       <c r="B281" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4929,7 +4947,7 @@
         <v>281</v>
       </c>
       <c r="B282" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4937,7 +4955,7 @@
         <v>282</v>
       </c>
       <c r="B283" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4945,7 +4963,7 @@
         <v>283</v>
       </c>
       <c r="B284" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4953,7 +4971,7 @@
         <v>284</v>
       </c>
       <c r="B285" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4961,7 +4979,7 @@
         <v>285</v>
       </c>
       <c r="B286" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4969,7 +4987,7 @@
         <v>286</v>
       </c>
       <c r="B287" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4977,7 +4995,7 @@
         <v>287</v>
       </c>
       <c r="B288" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -4985,7 +5003,7 @@
         <v>288</v>
       </c>
       <c r="B289" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -4993,7 +5011,7 @@
         <v>289</v>
       </c>
       <c r="B290" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5001,7 +5019,7 @@
         <v>290</v>
       </c>
       <c r="B291" s="1">
-        <v>520</v>
+        <v>880</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5009,7 +5027,7 @@
         <v>291</v>
       </c>
       <c r="B292" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5017,7 +5035,7 @@
         <v>292</v>
       </c>
       <c r="B293" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5025,7 +5043,7 @@
         <v>293</v>
       </c>
       <c r="B294" s="1">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5033,7 +5051,7 @@
         <v>294</v>
       </c>
       <c r="B295" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5041,7 +5059,7 @@
         <v>295</v>
       </c>
       <c r="B296" s="1">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5049,7 +5067,7 @@
         <v>296</v>
       </c>
       <c r="B297" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5057,7 +5075,7 @@
         <v>297</v>
       </c>
       <c r="B298" s="1">
-        <v>320</v>
+        <v>520</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5065,7 +5083,7 @@
         <v>298</v>
       </c>
       <c r="B299" s="1">
-        <v>540</v>
+        <v>320</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5073,7 +5091,7 @@
         <v>299</v>
       </c>
       <c r="B300" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5081,7 +5099,7 @@
         <v>300</v>
       </c>
       <c r="B301" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5097,7 +5115,7 @@
         <v>302</v>
       </c>
       <c r="B303" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5105,7 +5123,7 @@
         <v>303</v>
       </c>
       <c r="B304" s="1">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5113,7 +5131,7 @@
         <v>304</v>
       </c>
       <c r="B305" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5121,7 +5139,7 @@
         <v>305</v>
       </c>
       <c r="B306" s="1">
-        <v>480</v>
+        <v>800</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5129,7 +5147,7 @@
         <v>306</v>
       </c>
       <c r="B307" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5137,7 +5155,7 @@
         <v>307</v>
       </c>
       <c r="B308" s="1">
-        <v>520</v>
+        <v>800</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5145,7 +5163,7 @@
         <v>308</v>
       </c>
       <c r="B309" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5153,7 +5171,7 @@
         <v>309</v>
       </c>
       <c r="B310" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5161,7 +5179,7 @@
         <v>310</v>
       </c>
       <c r="B311" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5177,7 +5195,7 @@
         <v>312</v>
       </c>
       <c r="B313" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5185,7 +5203,7 @@
         <v>313</v>
       </c>
       <c r="B314" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5193,7 +5211,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="1">
-        <v>1020</v>
+        <v>720</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5201,7 +5219,7 @@
         <v>315</v>
       </c>
       <c r="B316" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5209,7 +5227,7 @@
         <v>316</v>
       </c>
       <c r="B317" s="1">
-        <v>700</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5217,7 +5235,7 @@
         <v>317</v>
       </c>
       <c r="B318" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5225,7 +5243,7 @@
         <v>318</v>
       </c>
       <c r="B319" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5233,7 +5251,7 @@
         <v>319</v>
       </c>
       <c r="B320" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5249,7 +5267,7 @@
         <v>321</v>
       </c>
       <c r="B322" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5257,7 +5275,7 @@
         <v>322</v>
       </c>
       <c r="B323" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5265,7 +5283,7 @@
         <v>323</v>
       </c>
       <c r="B324" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5273,7 +5291,7 @@
         <v>324</v>
       </c>
       <c r="B325" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5281,7 +5299,7 @@
         <v>325</v>
       </c>
       <c r="B326" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5289,7 +5307,7 @@
         <v>326</v>
       </c>
       <c r="B327" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5297,7 +5315,7 @@
         <v>327</v>
       </c>
       <c r="B328" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5313,7 +5331,7 @@
         <v>329</v>
       </c>
       <c r="B330" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5321,7 +5339,7 @@
         <v>330</v>
       </c>
       <c r="B331" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5329,7 +5347,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5337,7 +5355,7 @@
         <v>332</v>
       </c>
       <c r="B333" s="1">
-        <v>480</v>
+        <v>740</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5345,7 +5363,7 @@
         <v>333</v>
       </c>
       <c r="B334" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5353,7 +5371,7 @@
         <v>334</v>
       </c>
       <c r="B335" s="1">
-        <v>1000</v>
+        <v>480</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5361,7 +5379,7 @@
         <v>335</v>
       </c>
       <c r="B336" s="1">
-        <v>920</v>
+        <v>640</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5369,7 +5387,7 @@
         <v>336</v>
       </c>
       <c r="B337" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5377,7 +5395,7 @@
         <v>337</v>
       </c>
       <c r="B338" s="1">
-        <v>520</v>
+        <v>920</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5385,7 +5403,7 @@
         <v>338</v>
       </c>
       <c r="B339" s="1">
-        <v>540</v>
+        <v>860</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5393,7 +5411,7 @@
         <v>339</v>
       </c>
       <c r="B340" s="1">
-        <v>700</v>
+        <v>520</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5401,7 +5419,7 @@
         <v>340</v>
       </c>
       <c r="B341" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5409,7 +5427,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5425,7 +5443,7 @@
         <v>343</v>
       </c>
       <c r="B344" s="1">
-        <v>720</v>
+        <v>420</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5433,7 +5451,7 @@
         <v>344</v>
       </c>
       <c r="B345" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5441,7 +5459,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5449,7 +5467,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5457,7 +5475,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5465,7 +5483,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5473,7 +5491,7 @@
         <v>349</v>
       </c>
       <c r="B350" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5481,7 +5499,7 @@
         <v>350</v>
       </c>
       <c r="B351" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5489,7 +5507,7 @@
         <v>351</v>
       </c>
       <c r="B352" s="1">
-        <v>440</v>
+        <v>720</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5497,7 +5515,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="1">
-        <v>320</v>
+        <v>620</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5505,7 +5523,7 @@
         <v>353</v>
       </c>
       <c r="B354" s="1">
-        <v>320</v>
+        <v>440</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5513,7 +5531,7 @@
         <v>354</v>
       </c>
       <c r="B355" s="1">
-        <v>820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5521,7 +5539,7 @@
         <v>355</v>
       </c>
       <c r="B356" s="1">
-        <v>1000</v>
+        <v>320</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5529,7 +5547,7 @@
         <v>356</v>
       </c>
       <c r="B357" s="1">
-        <v>580</v>
+        <v>320</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5537,7 +5555,7 @@
         <v>357</v>
       </c>
       <c r="B358" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5545,7 +5563,7 @@
         <v>358</v>
       </c>
       <c r="B359" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5569,7 +5587,7 @@
         <v>361</v>
       </c>
       <c r="B362" s="1">
-        <v>620</v>
+        <v>900</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5577,7 +5595,7 @@
         <v>362</v>
       </c>
       <c r="B363" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5585,7 +5603,7 @@
         <v>363</v>
       </c>
       <c r="B364" s="1">
-        <v>920</v>
+        <v>580</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5593,7 +5611,7 @@
         <v>364</v>
       </c>
       <c r="B365" s="1">
-        <v>1000</v>
+        <v>620</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5601,7 +5619,7 @@
         <v>365</v>
       </c>
       <c r="B366" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5609,7 +5627,7 @@
         <v>366</v>
       </c>
       <c r="B367" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5617,7 +5635,7 @@
         <v>367</v>
       </c>
       <c r="B368" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5633,7 +5651,7 @@
         <v>369</v>
       </c>
       <c r="B370" s="1">
-        <v>900</v>
+        <v>880</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5641,7 +5659,7 @@
         <v>370</v>
       </c>
       <c r="B371" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5649,7 +5667,7 @@
         <v>371</v>
       </c>
       <c r="B372" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5657,7 +5675,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5673,7 +5691,7 @@
         <v>374</v>
       </c>
       <c r="B375" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5681,7 +5699,7 @@
         <v>375</v>
       </c>
       <c r="B376" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5689,7 +5707,7 @@
         <v>376</v>
       </c>
       <c r="B377" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5697,7 +5715,7 @@
         <v>377</v>
       </c>
       <c r="B378" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5705,7 +5723,7 @@
         <v>378</v>
       </c>
       <c r="B379" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5713,7 +5731,7 @@
         <v>379</v>
       </c>
       <c r="B380" s="1">
-        <v>760</v>
+        <v>900</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5721,7 +5739,7 @@
         <v>380</v>
       </c>
       <c r="B381" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5729,7 +5747,7 @@
         <v>381</v>
       </c>
       <c r="B382" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5737,7 +5755,7 @@
         <v>382</v>
       </c>
       <c r="B383" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5745,7 +5763,7 @@
         <v>383</v>
       </c>
       <c r="B384" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5753,7 +5771,7 @@
         <v>384</v>
       </c>
       <c r="B385" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5761,7 +5779,7 @@
         <v>385</v>
       </c>
       <c r="B386" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5769,7 +5787,7 @@
         <v>386</v>
       </c>
       <c r="B387" s="1">
-        <v>680</v>
+        <v>560</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5777,7 +5795,7 @@
         <v>387</v>
       </c>
       <c r="B388" s="1">
-        <v>480</v>
+        <v>620</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5785,7 +5803,7 @@
         <v>388</v>
       </c>
       <c r="B389" s="1">
-        <v>480</v>
+        <v>720</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5793,7 +5811,7 @@
         <v>389</v>
       </c>
       <c r="B390" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5801,7 +5819,7 @@
         <v>390</v>
       </c>
       <c r="B391" s="1">
-        <v>880</v>
+        <v>480</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5809,7 +5827,7 @@
         <v>391</v>
       </c>
       <c r="B392" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5817,7 +5835,7 @@
         <v>392</v>
       </c>
       <c r="B393" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5825,7 +5843,7 @@
         <v>393</v>
       </c>
       <c r="B394" s="1">
-        <v>920</v>
+        <v>880</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5833,7 +5851,7 @@
         <v>394</v>
       </c>
       <c r="B395" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5841,7 +5859,7 @@
         <v>395</v>
       </c>
       <c r="B396" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5849,7 +5867,7 @@
         <v>396</v>
       </c>
       <c r="B397" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5857,7 +5875,7 @@
         <v>397</v>
       </c>
       <c r="B398" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5865,7 +5883,7 @@
         <v>398</v>
       </c>
       <c r="B399" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5873,7 +5891,7 @@
         <v>399</v>
       </c>
       <c r="B400" s="1">
-        <v>600</v>
+        <v>940</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5881,7 +5899,7 @@
         <v>400</v>
       </c>
       <c r="B401" s="1">
-        <v>760</v>
+        <v>980</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5889,7 +5907,7 @@
         <v>401</v>
       </c>
       <c r="B402" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5897,7 +5915,7 @@
         <v>402</v>
       </c>
       <c r="B403" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5905,7 +5923,7 @@
         <v>403</v>
       </c>
       <c r="B404" s="1">
-        <v>620</v>
+        <v>760</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5913,7 +5931,7 @@
         <v>404</v>
       </c>
       <c r="B405" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5921,7 +5939,7 @@
         <v>405</v>
       </c>
       <c r="B406" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5929,7 +5947,7 @@
         <v>406</v>
       </c>
       <c r="B407" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5937,7 +5955,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5945,7 +5963,7 @@
         <v>408</v>
       </c>
       <c r="B409" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5953,7 +5971,7 @@
         <v>409</v>
       </c>
       <c r="B410" s="1">
-        <v>960</v>
+        <v>640</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5961,7 +5979,7 @@
         <v>410</v>
       </c>
       <c r="B411" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5969,7 +5987,7 @@
         <v>411</v>
       </c>
       <c r="B412" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5977,7 +5995,7 @@
         <v>412</v>
       </c>
       <c r="B413" s="1">
-        <v>640</v>
+        <v>960</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -5985,7 +6003,7 @@
         <v>413</v>
       </c>
       <c r="B414" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -5993,7 +6011,7 @@
         <v>414</v>
       </c>
       <c r="B415" s="1">
-        <v>560</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -6001,7 +6019,7 @@
         <v>415</v>
       </c>
       <c r="B416" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -6009,7 +6027,7 @@
         <v>416</v>
       </c>
       <c r="B417" s="1">
-        <v>660</v>
+        <v>860</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -6017,7 +6035,7 @@
         <v>417</v>
       </c>
       <c r="B418" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -6025,7 +6043,7 @@
         <v>418</v>
       </c>
       <c r="B419" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -6033,7 +6051,7 @@
         <v>419</v>
       </c>
       <c r="B420" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -6041,7 +6059,7 @@
         <v>420</v>
       </c>
       <c r="B421" s="1">
-        <v>520</v>
+        <v>640</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -6049,7 +6067,7 @@
         <v>421</v>
       </c>
       <c r="B422" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -6057,7 +6075,7 @@
         <v>422</v>
       </c>
       <c r="B423" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -6065,7 +6083,7 @@
         <v>423</v>
       </c>
       <c r="B424" s="1">
-        <v>780</v>
+        <v>520</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6073,7 +6091,7 @@
         <v>424</v>
       </c>
       <c r="B425" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6081,7 +6099,7 @@
         <v>425</v>
       </c>
       <c r="B426" s="1">
-        <v>820</v>
+        <v>620</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6089,7 +6107,7 @@
         <v>426</v>
       </c>
       <c r="B427" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6097,7 +6115,7 @@
         <v>427</v>
       </c>
       <c r="B428" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6105,7 +6123,7 @@
         <v>428</v>
       </c>
       <c r="B429" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6113,7 +6131,7 @@
         <v>429</v>
       </c>
       <c r="B430" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6121,7 +6139,7 @@
         <v>430</v>
       </c>
       <c r="B431" s="1">
-        <v>480</v>
+        <v>740</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6129,7 +6147,7 @@
         <v>431</v>
       </c>
       <c r="B432" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6137,7 +6155,7 @@
         <v>432</v>
       </c>
       <c r="B433" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6145,7 +6163,7 @@
         <v>433</v>
       </c>
       <c r="B434" s="1">
-        <v>700</v>
+        <v>480</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6153,7 +6171,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="1">
-        <v>440</v>
+        <v>840</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6161,7 +6179,7 @@
         <v>435</v>
       </c>
       <c r="B436" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6169,7 +6187,7 @@
         <v>436</v>
       </c>
       <c r="B437" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6177,7 +6195,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="1">
-        <v>880</v>
+        <v>440</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6185,7 +6203,7 @@
         <v>438</v>
       </c>
       <c r="B439" s="1">
-        <v>880</v>
+        <v>440</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6193,7 +6211,7 @@
         <v>439</v>
       </c>
       <c r="B440" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6201,7 +6219,7 @@
         <v>440</v>
       </c>
       <c r="B441" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6209,7 +6227,7 @@
         <v>441</v>
       </c>
       <c r="B442" s="1">
-        <v>660</v>
+        <v>880</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6217,7 +6235,7 @@
         <v>442</v>
       </c>
       <c r="B443" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6233,7 +6251,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6241,7 +6259,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="1">
-        <v>760</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6249,7 +6267,7 @@
         <v>446</v>
       </c>
       <c r="B447" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6257,7 +6275,7 @@
         <v>447</v>
       </c>
       <c r="B448" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6265,7 +6283,7 @@
         <v>448</v>
       </c>
       <c r="B449" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6273,7 +6291,7 @@
         <v>449</v>
       </c>
       <c r="B450" s="1">
-        <v>840</v>
+        <v>800</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6281,7 +6299,7 @@
         <v>450</v>
       </c>
       <c r="B451" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6289,7 +6307,7 @@
         <v>451</v>
       </c>
       <c r="B452" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6297,7 +6315,7 @@
         <v>452</v>
       </c>
       <c r="B453" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6305,7 +6323,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6313,7 +6331,7 @@
         <v>454</v>
       </c>
       <c r="B455" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6321,7 +6339,7 @@
         <v>455</v>
       </c>
       <c r="B456" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6329,7 +6347,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6337,7 +6355,7 @@
         <v>457</v>
       </c>
       <c r="B458" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6353,7 +6371,7 @@
         <v>459</v>
       </c>
       <c r="B460" s="1">
-        <v>620</v>
+        <v>800</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6361,7 +6379,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="1">
-        <v>880</v>
+        <v>660</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6369,7 +6387,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="1">
-        <v>860</v>
+        <v>600</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6377,7 +6395,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="1">
-        <v>800</v>
+        <v>620</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6385,7 +6403,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="1">
-        <v>860</v>
+        <v>880</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6393,7 +6411,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6401,7 +6419,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6409,7 +6427,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6417,7 +6435,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6425,7 +6443,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="1">
-        <v>790</v>
+        <v>720</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6433,7 +6451,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="1">
-        <v>640</v>
+        <v>900</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6441,7 +6459,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="1">
-        <v>800</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6449,7 +6467,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="1">
-        <v>660</v>
+        <v>790</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6457,7 +6475,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6465,7 +6483,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6473,7 +6491,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="1">
-        <v>820</v>
+        <v>660</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6481,7 +6499,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6489,7 +6507,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6497,7 +6515,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6505,7 +6523,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6513,7 +6531,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6521,7 +6539,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="1">
-        <v>880</v>
+        <v>760</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6529,7 +6547,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="1">
-        <v>640</v>
+        <v>920</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6537,7 +6555,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6545,7 +6563,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="1">
-        <v>600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6553,7 +6571,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6561,7 +6579,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6569,7 +6587,7 @@
         <v>486</v>
       </c>
       <c r="B487" s="1">
-        <v>860</v>
+        <v>600</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6577,7 +6595,7 @@
         <v>487</v>
       </c>
       <c r="B488" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6585,7 +6603,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6593,7 +6611,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6601,7 +6619,7 @@
         <v>490</v>
       </c>
       <c r="B491" s="1">
-        <v>940</v>
+        <v>840</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6609,7 +6627,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="1">
-        <v>1040</v>
+        <v>720</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6617,7 +6635,7 @@
         <v>492</v>
       </c>
       <c r="B493" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6625,7 +6643,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6633,7 +6651,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="1">
-        <v>920</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6641,7 +6659,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6649,7 +6667,7 @@
         <v>496</v>
       </c>
       <c r="B497" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6657,7 +6675,7 @@
         <v>497</v>
       </c>
       <c r="B498" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6665,7 +6683,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="1">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6673,7 +6691,7 @@
         <v>499</v>
       </c>
       <c r="B500" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6681,7 +6699,7 @@
         <v>500</v>
       </c>
       <c r="B501" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6689,7 +6707,7 @@
         <v>501</v>
       </c>
       <c r="B502" s="1">
-        <v>700</v>
+        <v>620</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6697,7 +6715,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6705,7 +6723,7 @@
         <v>503</v>
       </c>
       <c r="B504" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6713,7 +6731,7 @@
         <v>504</v>
       </c>
       <c r="B505" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6721,7 +6739,7 @@
         <v>505</v>
       </c>
       <c r="B506" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6729,7 +6747,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="1">
-        <v>540</v>
+        <v>600</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6737,7 +6755,7 @@
         <v>507</v>
       </c>
       <c r="B508" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6745,7 +6763,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="1">
-        <v>1100</v>
+        <v>780</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6753,7 +6771,7 @@
         <v>509</v>
       </c>
       <c r="B510" s="1">
-        <v>1100</v>
+        <v>540</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6761,7 +6779,7 @@
         <v>510</v>
       </c>
       <c r="B511" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6769,7 +6787,7 @@
         <v>511</v>
       </c>
       <c r="B512" s="1">
-        <v>720</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6777,7 +6795,7 @@
         <v>512</v>
       </c>
       <c r="B513" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6785,7 +6803,7 @@
         <v>513</v>
       </c>
       <c r="B514" s="1">
-        <v>740</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6793,7 +6811,7 @@
         <v>514</v>
       </c>
       <c r="B515" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6801,7 +6819,7 @@
         <v>515</v>
       </c>
       <c r="B516" s="1">
-        <v>860</v>
+        <v>720</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6809,7 +6827,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="1">
-        <v>980</v>
+        <v>560</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6825,7 +6843,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="1">
-        <v>760</v>
+        <v>620</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6833,7 +6851,7 @@
         <v>519</v>
       </c>
       <c r="B520" s="1">
-        <v>1100</v>
+        <v>860</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6841,7 +6859,7 @@
         <v>520</v>
       </c>
       <c r="B521" s="1">
-        <v>1100</v>
+        <v>980</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6849,7 +6867,7 @@
         <v>521</v>
       </c>
       <c r="B522" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -6857,7 +6875,7 @@
         <v>522</v>
       </c>
       <c r="B523" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6865,7 +6883,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6873,7 +6891,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6881,7 +6899,7 @@
         <v>525</v>
       </c>
       <c r="B526" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6889,7 +6907,7 @@
         <v>526</v>
       </c>
       <c r="B527" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6897,7 +6915,7 @@
         <v>527</v>
       </c>
       <c r="B528" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6913,7 +6931,7 @@
         <v>529</v>
       </c>
       <c r="B530" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6921,7 +6939,7 @@
         <v>530</v>
       </c>
       <c r="B531" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6929,7 +6947,7 @@
         <v>531</v>
       </c>
       <c r="B532" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6937,7 +6955,7 @@
         <v>532</v>
       </c>
       <c r="B533" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6945,7 +6963,7 @@
         <v>533</v>
       </c>
       <c r="B534" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6953,7 +6971,7 @@
         <v>534</v>
       </c>
       <c r="B535" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -6961,7 +6979,7 @@
         <v>535</v>
       </c>
       <c r="B536" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -6969,7 +6987,7 @@
         <v>536</v>
       </c>
       <c r="B537" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -6977,7 +6995,7 @@
         <v>537</v>
       </c>
       <c r="B538" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -6985,7 +7003,7 @@
         <v>538</v>
       </c>
       <c r="B539" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -6993,7 +7011,7 @@
         <v>539</v>
       </c>
       <c r="B540" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -7001,7 +7019,7 @@
         <v>540</v>
       </c>
       <c r="B541" s="1">
-        <v>1400</v>
+        <v>700</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -7009,7 +7027,7 @@
         <v>541</v>
       </c>
       <c r="B542" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -7017,7 +7035,7 @@
         <v>542</v>
       </c>
       <c r="B543" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -7025,7 +7043,7 @@
         <v>543</v>
       </c>
       <c r="B544" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -7033,7 +7051,7 @@
         <v>544</v>
       </c>
       <c r="B545" s="1">
-        <v>740</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -7049,7 +7067,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -7057,7 +7075,7 @@
         <v>547</v>
       </c>
       <c r="B548" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -7065,7 +7083,7 @@
         <v>548</v>
       </c>
       <c r="B549" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7073,7 +7091,7 @@
         <v>549</v>
       </c>
       <c r="B550" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7081,7 +7099,7 @@
         <v>550</v>
       </c>
       <c r="B551" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7089,7 +7107,7 @@
         <v>551</v>
       </c>
       <c r="B552" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7097,7 +7115,7 @@
         <v>552</v>
       </c>
       <c r="B553" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7105,7 +7123,7 @@
         <v>553</v>
       </c>
       <c r="B554" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7113,7 +7131,7 @@
         <v>554</v>
       </c>
       <c r="B555" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7129,7 +7147,7 @@
         <v>556</v>
       </c>
       <c r="B557" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7137,7 +7155,7 @@
         <v>557</v>
       </c>
       <c r="B558" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7145,7 +7163,7 @@
         <v>558</v>
       </c>
       <c r="B559" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7153,7 +7171,7 @@
         <v>559</v>
       </c>
       <c r="B560" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7161,7 +7179,7 @@
         <v>560</v>
       </c>
       <c r="B561" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7169,7 +7187,7 @@
         <v>561</v>
       </c>
       <c r="B562" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7177,7 +7195,7 @@
         <v>562</v>
       </c>
       <c r="B563" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7185,7 +7203,7 @@
         <v>563</v>
       </c>
       <c r="B564" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7193,7 +7211,7 @@
         <v>564</v>
       </c>
       <c r="B565" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7201,7 +7219,7 @@
         <v>565</v>
       </c>
       <c r="B566" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7217,7 +7235,7 @@
         <v>567</v>
       </c>
       <c r="B568" s="1">
-        <v>540</v>
+        <v>700</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7225,7 +7243,7 @@
         <v>568</v>
       </c>
       <c r="B569" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7233,7 +7251,7 @@
         <v>569</v>
       </c>
       <c r="B570" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7241,7 +7259,7 @@
         <v>570</v>
       </c>
       <c r="B571" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7249,7 +7267,7 @@
         <v>571</v>
       </c>
       <c r="B572" s="1">
-        <v>900</v>
+        <v>540</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7257,7 +7275,7 @@
         <v>572</v>
       </c>
       <c r="B573" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7265,7 +7283,7 @@
         <v>573</v>
       </c>
       <c r="B574" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7273,7 +7291,7 @@
         <v>574</v>
       </c>
       <c r="B575" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7289,7 +7307,7 @@
         <v>576</v>
       </c>
       <c r="B577" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7297,7 +7315,7 @@
         <v>577</v>
       </c>
       <c r="B578" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7313,7 +7331,7 @@
         <v>579</v>
       </c>
       <c r="B580" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7321,7 +7339,7 @@
         <v>580</v>
       </c>
       <c r="B581" s="1">
-        <v>1020</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7329,7 +7347,7 @@
         <v>581</v>
       </c>
       <c r="B582" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7337,7 +7355,7 @@
         <v>582</v>
       </c>
       <c r="B583" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7345,7 +7363,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7353,7 +7371,7 @@
         <v>584</v>
       </c>
       <c r="B585" s="1">
-        <v>640</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7361,7 +7379,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7369,7 +7387,7 @@
         <v>586</v>
       </c>
       <c r="B587" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7377,7 +7395,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7385,7 +7403,7 @@
         <v>588</v>
       </c>
       <c r="B589" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7393,7 +7411,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7401,7 +7419,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7409,7 +7427,7 @@
         <v>591</v>
       </c>
       <c r="B592" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7417,7 +7435,7 @@
         <v>592</v>
       </c>
       <c r="B593" s="1">
-        <v>820</v>
+        <v>720</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7425,7 +7443,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="1">
-        <v>600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7433,7 +7451,7 @@
         <v>594</v>
       </c>
       <c r="B595" s="1">
-        <v>800</v>
+        <v>740</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7441,7 +7459,7 @@
         <v>595</v>
       </c>
       <c r="B596" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7449,7 +7467,7 @@
         <v>596</v>
       </c>
       <c r="B597" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7457,7 +7475,7 @@
         <v>597</v>
       </c>
       <c r="B598" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7465,7 +7483,7 @@
         <v>598</v>
       </c>
       <c r="B599" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7473,7 +7491,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7481,7 +7499,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7489,7 +7507,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7497,7 +7515,7 @@
         <v>602</v>
       </c>
       <c r="B603" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7505,7 +7523,7 @@
         <v>603</v>
       </c>
       <c r="B604" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7513,7 +7531,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7537,7 +7555,7 @@
         <v>607</v>
       </c>
       <c r="B608" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7545,7 +7563,7 @@
         <v>608</v>
       </c>
       <c r="B609" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7561,7 +7579,7 @@
         <v>610</v>
       </c>
       <c r="B611" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7569,7 +7587,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7577,7 +7595,7 @@
         <v>612</v>
       </c>
       <c r="B613" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7585,7 +7603,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="1">
-        <v>760</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7593,7 +7611,7 @@
         <v>614</v>
       </c>
       <c r="B615" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7601,7 +7619,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -7609,7 +7627,7 @@
         <v>616</v>
       </c>
       <c r="B617" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -7617,7 +7635,7 @@
         <v>617</v>
       </c>
       <c r="B618" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -7625,7 +7643,7 @@
         <v>618</v>
       </c>
       <c r="B619" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7633,7 +7651,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="1">
-        <v>860</v>
+        <v>680</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7649,7 +7667,7 @@
         <v>621</v>
       </c>
       <c r="B622" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -7657,7 +7675,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -7665,7 +7683,7 @@
         <v>623</v>
       </c>
       <c r="B624" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -7673,7 +7691,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -7681,7 +7699,7 @@
         <v>625</v>
       </c>
       <c r="B626" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -7689,7 +7707,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -7697,7 +7715,7 @@
         <v>627</v>
       </c>
       <c r="B628" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -7705,7 +7723,7 @@
         <v>628</v>
       </c>
       <c r="B629" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -7713,7 +7731,7 @@
         <v>629</v>
       </c>
       <c r="B630" s="1">
-        <v>920</v>
+        <v>720</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -7721,7 +7739,7 @@
         <v>630</v>
       </c>
       <c r="B631" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -7729,7 +7747,7 @@
         <v>631</v>
       </c>
       <c r="B632" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -7737,7 +7755,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -7745,7 +7763,7 @@
         <v>633</v>
       </c>
       <c r="B634" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -7753,7 +7771,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -7761,7 +7779,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -7769,7 +7787,7 @@
         <v>636</v>
       </c>
       <c r="B637" s="1">
-        <v>660</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -7777,7 +7795,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -7785,7 +7803,7 @@
         <v>638</v>
       </c>
       <c r="B639" s="1">
-        <v>680</v>
+        <v>880</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -7793,7 +7811,7 @@
         <v>639</v>
       </c>
       <c r="B640" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -7801,7 +7819,7 @@
         <v>640</v>
       </c>
       <c r="B641" s="1">
-        <v>440</v>
+        <v>780</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -7809,7 +7827,7 @@
         <v>641</v>
       </c>
       <c r="B642" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -7817,7 +7835,7 @@
         <v>642</v>
       </c>
       <c r="B643" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -7825,7 +7843,7 @@
         <v>643</v>
       </c>
       <c r="B644" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -7833,7 +7851,7 @@
         <v>644</v>
       </c>
       <c r="B645" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -7841,7 +7859,7 @@
         <v>645</v>
       </c>
       <c r="B646" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -7849,7 +7867,7 @@
         <v>646</v>
       </c>
       <c r="B647" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -7857,7 +7875,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -7865,7 +7883,7 @@
         <v>648</v>
       </c>
       <c r="B649" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -7881,7 +7899,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -7889,7 +7907,7 @@
         <v>651</v>
       </c>
       <c r="B652" s="1">
-        <v>920</v>
+        <v>600</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -7897,7 +7915,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -7905,7 +7923,7 @@
         <v>653</v>
       </c>
       <c r="B654" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -7913,7 +7931,7 @@
         <v>654</v>
       </c>
       <c r="B655" s="1">
-        <v>980</v>
+        <v>880</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -7921,7 +7939,7 @@
         <v>655</v>
       </c>
       <c r="B656" s="1">
-        <v>920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -7937,7 +7955,7 @@
         <v>657</v>
       </c>
       <c r="B658" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -7945,7 +7963,7 @@
         <v>658</v>
       </c>
       <c r="B659" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -7953,7 +7971,7 @@
         <v>659</v>
       </c>
       <c r="B660" s="1">
-        <v>680</v>
+        <v>940</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -7961,7 +7979,7 @@
         <v>660</v>
       </c>
       <c r="B661" s="1">
-        <v>820</v>
+        <v>980</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -7969,7 +7987,7 @@
         <v>661</v>
       </c>
       <c r="B662" s="1">
-        <v>960</v>
+        <v>920</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -7977,7 +7995,7 @@
         <v>662</v>
       </c>
       <c r="B663" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -7985,7 +8003,7 @@
         <v>663</v>
       </c>
       <c r="B664" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -7993,7 +8011,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -8001,7 +8019,7 @@
         <v>665</v>
       </c>
       <c r="B666" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -8009,7 +8027,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="1">
-        <v>660</v>
+        <v>820</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -8017,7 +8035,7 @@
         <v>667</v>
       </c>
       <c r="B668" s="1">
-        <v>840</v>
+        <v>960</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -8025,7 +8043,7 @@
         <v>668</v>
       </c>
       <c r="B669" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -8033,7 +8051,7 @@
         <v>669</v>
       </c>
       <c r="B670" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8041,7 +8059,7 @@
         <v>670</v>
       </c>
       <c r="B671" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -8049,7 +8067,7 @@
         <v>671</v>
       </c>
       <c r="B672" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -8057,7 +8075,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8065,7 +8083,7 @@
         <v>673</v>
       </c>
       <c r="B674" s="1">
-        <v>600</v>
+        <v>840</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -8073,7 +8091,7 @@
         <v>674</v>
       </c>
       <c r="B675" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8081,7 +8099,7 @@
         <v>675</v>
       </c>
       <c r="B676" s="1">
-        <v>660</v>
+        <v>820</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8089,7 +8107,7 @@
         <v>676</v>
       </c>
       <c r="B677" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8097,7 +8115,7 @@
         <v>677</v>
       </c>
       <c r="B678" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8105,7 +8123,7 @@
         <v>678</v>
       </c>
       <c r="B679" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8113,7 +8131,7 @@
         <v>679</v>
       </c>
       <c r="B680" s="1">
-        <v>860</v>
+        <v>600</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8121,7 +8139,7 @@
         <v>680</v>
       </c>
       <c r="B681" s="1">
-        <v>680</v>
+        <v>840</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8129,7 +8147,7 @@
         <v>681</v>
       </c>
       <c r="B682" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8137,7 +8155,7 @@
         <v>682</v>
       </c>
       <c r="B683" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8145,7 +8163,7 @@
         <v>683</v>
       </c>
       <c r="B684" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8153,7 +8171,7 @@
         <v>684</v>
       </c>
       <c r="B685" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8161,7 +8179,7 @@
         <v>685</v>
       </c>
       <c r="B686" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8169,7 +8187,7 @@
         <v>686</v>
       </c>
       <c r="B687" s="1">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8177,7 +8195,7 @@
         <v>687</v>
       </c>
       <c r="B688" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8185,7 +8203,7 @@
         <v>688</v>
       </c>
       <c r="B689" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8193,7 +8211,7 @@
         <v>689</v>
       </c>
       <c r="B690" s="1">
-        <v>920</v>
+        <v>720</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8201,7 +8219,7 @@
         <v>690</v>
       </c>
       <c r="B691" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8209,7 +8227,7 @@
         <v>691</v>
       </c>
       <c r="B692" s="1">
-        <v>1040</v>
+        <v>600</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8217,7 +8235,7 @@
         <v>692</v>
       </c>
       <c r="B693" s="1">
-        <v>940</v>
+        <v>600</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8225,7 +8243,7 @@
         <v>693</v>
       </c>
       <c r="B694" s="1">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8233,7 +8251,7 @@
         <v>694</v>
       </c>
       <c r="B695" s="1">
-        <v>1040</v>
+        <v>760</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8241,7 +8259,7 @@
         <v>695</v>
       </c>
       <c r="B696" s="1">
-        <v>1100</v>
+        <v>920</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8257,7 +8275,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8265,7 +8283,7 @@
         <v>698</v>
       </c>
       <c r="B699" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8273,7 +8291,7 @@
         <v>699</v>
       </c>
       <c r="B700" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8281,7 +8299,7 @@
         <v>700</v>
       </c>
       <c r="B701" s="1">
-        <v>820</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8289,7 +8307,7 @@
         <v>701</v>
       </c>
       <c r="B702" s="1">
-        <v>440</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8297,7 +8315,7 @@
         <v>702</v>
       </c>
       <c r="B703" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8305,7 +8323,7 @@
         <v>703</v>
       </c>
       <c r="B704" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8313,7 +8331,7 @@
         <v>704</v>
       </c>
       <c r="B705" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8321,7 +8339,7 @@
         <v>705</v>
       </c>
       <c r="B706" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8337,7 +8355,7 @@
         <v>707</v>
       </c>
       <c r="B708" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8345,7 +8363,7 @@
         <v>708</v>
       </c>
       <c r="B709" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8353,7 +8371,7 @@
         <v>709</v>
       </c>
       <c r="B710" s="1">
-        <v>400</v>
+        <v>440</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8361,7 +8379,7 @@
         <v>710</v>
       </c>
       <c r="B711" s="1">
-        <v>400</v>
+        <v>560</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8369,7 +8387,7 @@
         <v>711</v>
       </c>
       <c r="B712" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8377,7 +8395,7 @@
         <v>712</v>
       </c>
       <c r="B713" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8385,7 +8403,7 @@
         <v>713</v>
       </c>
       <c r="B714" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8393,7 +8411,7 @@
         <v>714</v>
       </c>
       <c r="B715" s="1">
-        <v>520</v>
+        <v>760</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8401,7 +8419,7 @@
         <v>715</v>
       </c>
       <c r="B716" s="1">
-        <v>700</v>
+        <v>400</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8409,7 +8427,7 @@
         <v>716</v>
       </c>
       <c r="B717" s="1">
-        <v>860</v>
+        <v>400</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8417,7 +8435,7 @@
         <v>717</v>
       </c>
       <c r="B718" s="1">
-        <v>680</v>
+        <v>380</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8425,7 +8443,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="1">
-        <v>740</v>
+        <v>380</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8433,7 +8451,7 @@
         <v>719</v>
       </c>
       <c r="B720" s="1">
-        <v>780</v>
+        <v>380</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8441,7 +8459,7 @@
         <v>720</v>
       </c>
       <c r="B721" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8449,7 +8467,7 @@
         <v>721</v>
       </c>
       <c r="B722" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8457,7 +8475,7 @@
         <v>722</v>
       </c>
       <c r="B723" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8465,7 +8483,7 @@
         <v>723</v>
       </c>
       <c r="B724" s="1">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8473,7 +8491,7 @@
         <v>724</v>
       </c>
       <c r="B725" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8481,7 +8499,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8489,7 +8507,7 @@
         <v>726</v>
       </c>
       <c r="B727" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8497,7 +8515,7 @@
         <v>727</v>
       </c>
       <c r="B728" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8505,7 +8523,7 @@
         <v>728</v>
       </c>
       <c r="B729" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8513,7 +8531,7 @@
         <v>729</v>
       </c>
       <c r="B730" s="1">
-        <v>920</v>
+        <v>600</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8521,7 +8539,7 @@
         <v>730</v>
       </c>
       <c r="B731" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8529,7 +8547,7 @@
         <v>731</v>
       </c>
       <c r="B732" s="1">
-        <v>1040</v>
+        <v>760</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -8537,7 +8555,7 @@
         <v>732</v>
       </c>
       <c r="B733" s="1">
-        <v>940</v>
+        <v>840</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -8553,7 +8571,7 @@
         <v>734</v>
       </c>
       <c r="B735" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -8561,7 +8579,7 @@
         <v>735</v>
       </c>
       <c r="B736" s="1">
-        <v>1100</v>
+        <v>920</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -8577,7 +8595,7 @@
         <v>737</v>
       </c>
       <c r="B738" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="739" spans="1:2">
@@ -8585,7 +8603,7 @@
         <v>738</v>
       </c>
       <c r="B739" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -8593,7 +8611,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -8601,7 +8619,7 @@
         <v>740</v>
       </c>
       <c r="B741" s="1">
-        <v>820</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -8609,7 +8627,7 @@
         <v>741</v>
       </c>
       <c r="B742" s="1">
-        <v>440</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -8617,7 +8635,7 @@
         <v>742</v>
       </c>
       <c r="B743" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="744" spans="1:2">
@@ -8625,7 +8643,7 @@
         <v>743</v>
       </c>
       <c r="B744" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -8633,7 +8651,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -8641,7 +8659,7 @@
         <v>745</v>
       </c>
       <c r="B746" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -8657,7 +8675,7 @@
         <v>747</v>
       </c>
       <c r="B748" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -8665,7 +8683,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -8673,7 +8691,7 @@
         <v>749</v>
       </c>
       <c r="B750" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="751" spans="1:2">
@@ -8681,7 +8699,7 @@
         <v>750</v>
       </c>
       <c r="B751" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -8689,7 +8707,7 @@
         <v>751</v>
       </c>
       <c r="B752" s="1">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -8697,7 +8715,7 @@
         <v>752</v>
       </c>
       <c r="B753" s="1">
-        <v>480</v>
+        <v>820</v>
       </c>
     </row>
     <row r="754" spans="1:2">
@@ -8705,7 +8723,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -8713,7 +8731,7 @@
         <v>754</v>
       </c>
       <c r="B755" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="756" spans="1:2">
@@ -8721,7 +8739,7 @@
         <v>755</v>
       </c>
       <c r="B756" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -8729,7 +8747,7 @@
         <v>756</v>
       </c>
       <c r="B757" s="1">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row r="758" spans="1:2">
@@ -8737,7 +8755,7 @@
         <v>757</v>
       </c>
       <c r="B758" s="1">
-        <v>380</v>
+        <v>480</v>
       </c>
     </row>
     <row r="759" spans="1:2">
@@ -8745,7 +8763,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="1">
-        <v>600</v>
+        <v>480</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -8753,7 +8771,7 @@
         <v>759</v>
       </c>
       <c r="B760" s="1">
-        <v>820</v>
+        <v>520</v>
       </c>
     </row>
     <row r="761" spans="1:2">
@@ -8761,7 +8779,7 @@
         <v>760</v>
       </c>
       <c r="B761" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="762" spans="1:2">
@@ -8769,7 +8787,7 @@
         <v>761</v>
       </c>
       <c r="B762" s="1">
-        <v>580</v>
+        <v>440</v>
       </c>
     </row>
     <row r="763" spans="1:2">
@@ -8777,7 +8795,7 @@
         <v>762</v>
       </c>
       <c r="B763" s="1">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -8785,7 +8803,7 @@
         <v>763</v>
       </c>
       <c r="B764" s="1">
-        <v>580</v>
+        <v>380</v>
       </c>
     </row>
     <row r="765" spans="1:2">
@@ -8793,7 +8811,7 @@
         <v>764</v>
       </c>
       <c r="B765" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -8801,7 +8819,7 @@
         <v>765</v>
       </c>
       <c r="B766" s="1">
-        <v>560</v>
+        <v>820</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -8809,6 +8827,54 @@
         <v>766</v>
       </c>
       <c r="B767" s="1">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2">
+      <c r="A768" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B768" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2">
+      <c r="A769" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="B769" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2">
+      <c r="A770" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B770" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2">
+      <c r="A771" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="B771" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2">
+      <c r="A772" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="B772" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2">
+      <c r="A773" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B773" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="779">
   <si>
     <t>Наименование</t>
   </si>
@@ -149,6 +149,9 @@
     <t>Big Village - ICEBREAKER (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Big Village - London (ESB), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Big Village - LUMINBLOOM (NEPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -179,6 +182,9 @@
     <t>Big Village - Пивной Шлем (NEDIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Big Village - Шапито (AIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Big Village Imaginarium , РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -389,6 +395,9 @@
     <t>Horror Brewing - Nonstop Feeling (DIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Horror Brewing - Obscur (RIS),  РОЗЛИВ ,Россия</t>
+  </si>
+  <si>
     <t>Horror Brewing - Same Shit Different Day (Pils), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1406,6 +1415,9 @@
     <t>вынос_Big Village - ICEBREAKER (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Big Village - London (ESB), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Big Village - LUMINBLOOM (NEPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1430,6 +1442,9 @@
     <t>вынос_Big Village - Пивной Шлем (NEDIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Big Village - Шапито (AIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Black Cat "70"  (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1533,6 +1548,9 @@
   </si>
   <si>
     <t>вынос_Horror Brewing - Nonstop Feeling (DIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Horror Brewing - Obscur (RIS),  РОЗЛИВ ,Россия</t>
   </si>
   <si>
     <t>вынос_Horror Brewing - Same Shit Different Day (Pils), РОЗЛИВ, Россия</t>
@@ -2687,7 +2705,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B773"/>
+  <dimension ref="A1:B779"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -3043,7 +3061,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3051,7 +3069,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>720</v>
+        <v>880</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3059,7 +3077,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>860</v>
+        <v>720</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3067,7 +3085,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3075,7 +3093,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>860</v>
+        <v>800</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -3083,7 +3101,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>480</v>
+        <v>860</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -3091,7 +3109,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>760</v>
+        <v>480</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3099,7 +3117,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -3107,7 +3125,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -3115,7 +3133,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3123,7 +3141,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>580</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -3131,7 +3149,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>560</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -3139,7 +3157,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -3147,7 +3165,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -3155,7 +3173,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3163,7 +3181,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -3171,7 +3189,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -3179,7 +3197,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -3187,7 +3205,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -3195,7 +3213,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -3203,7 +3221,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -3211,7 +3229,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -3219,7 +3237,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -3227,7 +3245,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -3235,7 +3253,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -3243,7 +3261,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -3267,7 +3285,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>920</v>
+        <v>820</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -3275,7 +3293,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -3283,7 +3301,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -3291,7 +3309,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>640</v>
+        <v>600</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3299,7 +3317,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>700</v>
+        <v>880</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -3307,7 +3325,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -3323,7 +3341,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -3331,7 +3349,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -3339,7 +3357,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -3347,7 +3365,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>560</v>
+        <v>840</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -3355,7 +3373,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -3363,7 +3381,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -3395,7 +3413,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>540</v>
+        <v>480</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3403,7 +3421,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3411,7 +3429,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>840</v>
+        <v>540</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3419,7 +3437,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3427,7 +3445,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>440</v>
+        <v>840</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3435,7 +3453,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3443,7 +3461,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>460</v>
+        <v>440</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3451,7 +3469,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>460</v>
+        <v>560</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3459,7 +3477,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>960</v>
+        <v>460</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3467,7 +3485,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>940</v>
+        <v>460</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3475,7 +3493,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3483,7 +3501,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3491,7 +3509,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>660</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3499,7 +3517,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>480</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3507,7 +3525,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>400</v>
+        <v>660</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3515,7 +3533,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3523,7 +3541,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>560</v>
+        <v>400</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3531,7 +3549,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3539,7 +3557,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3555,7 +3573,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3563,7 +3581,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>920</v>
+        <v>500</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3571,7 +3589,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3579,7 +3597,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>420</v>
+        <v>920</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3587,7 +3605,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>560</v>
+        <v>680</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3595,7 +3613,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>580</v>
+        <v>420</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3603,7 +3621,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3611,7 +3629,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3619,7 +3637,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3627,7 +3645,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3635,7 +3653,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3643,7 +3661,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3651,7 +3669,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3659,7 +3677,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3667,7 +3685,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -3675,7 +3693,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -3683,7 +3701,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -3691,7 +3709,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>720</v>
+        <v>960</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -3699,7 +3717,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -3707,7 +3725,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -3715,7 +3733,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -3723,7 +3741,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>540</v>
+        <v>780</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -3731,7 +3749,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>520</v>
+        <v>500</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -3739,7 +3757,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>1100</v>
+        <v>580</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -3747,7 +3765,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>1060</v>
+        <v>540</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -3755,7 +3773,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>1100</v>
+        <v>520</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -3771,7 +3789,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>560</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -3779,31 +3797,31 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>420</v>
+        <v>560</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -3811,7 +3829,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -3819,7 +3837,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="1">
-        <v>460</v>
+        <v>420</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -3827,7 +3845,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -3835,7 +3853,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -3843,7 +3861,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="1">
-        <v>740</v>
+        <v>460</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -3851,7 +3869,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -3859,7 +3877,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -3867,7 +3885,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3875,7 +3893,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -3883,7 +3901,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -3891,7 +3909,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="1">
-        <v>740</v>
+        <v>980</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -3899,7 +3917,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="1">
-        <v>760</v>
+        <v>540</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3907,7 +3925,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3915,7 +3933,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3923,7 +3941,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -3931,7 +3949,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -3939,7 +3957,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -3947,7 +3965,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="1">
-        <v>640</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -3955,7 +3973,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -3963,7 +3981,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -3971,7 +3989,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="1">
-        <v>920</v>
+        <v>640</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -3979,7 +3997,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -3987,7 +4005,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -3995,7 +4013,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -4003,7 +4021,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -4011,7 +4029,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4019,7 +4037,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4035,7 +4053,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="1">
-        <v>460</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4043,7 +4061,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="1">
-        <v>580</v>
+        <v>840</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4051,7 +4069,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -4059,7 +4077,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="1">
-        <v>660</v>
+        <v>460</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4067,7 +4085,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="1">
-        <v>780</v>
+        <v>580</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4075,7 +4093,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="1">
-        <v>260</v>
+        <v>720</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4083,7 +4101,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="1">
-        <v>260</v>
+        <v>660</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4091,7 +4109,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="1">
-        <v>440</v>
+        <v>780</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4099,7 +4117,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4107,7 +4125,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="1">
-        <v>800</v>
+        <v>260</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4115,7 +4133,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4123,7 +4141,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="1">
-        <v>720</v>
+        <v>440</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4131,7 +4149,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="1">
-        <v>500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4139,7 +4157,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="1">
-        <v>400</v>
+        <v>740</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4147,7 +4165,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4155,7 +4173,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="1">
-        <v>680</v>
+        <v>500</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4163,7 +4181,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="1">
-        <v>780</v>
+        <v>400</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4171,7 +4189,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4179,7 +4197,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4187,7 +4205,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4195,7 +4213,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="1">
-        <v>580</v>
+        <v>620</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4203,7 +4221,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4211,7 +4229,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="1">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4219,7 +4237,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4235,7 +4253,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="1">
-        <v>580</v>
+        <v>620</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4243,7 +4261,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="1">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4251,7 +4269,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4259,7 +4277,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4267,7 +4285,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4275,7 +4293,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4283,7 +4301,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="1">
-        <v>540</v>
+        <v>560</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4291,7 +4309,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="1">
-        <v>700</v>
+        <v>520</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4299,7 +4317,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4307,7 +4325,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="1">
-        <v>760</v>
+        <v>540</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4315,7 +4333,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4323,7 +4341,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4331,7 +4349,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="1">
-        <v>1400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4339,7 +4357,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="1">
-        <v>480</v>
+        <v>720</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4347,7 +4365,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4355,7 +4373,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="1">
-        <v>660</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4363,7 +4381,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="1">
-        <v>600</v>
+        <v>480</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4371,7 +4389,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4379,7 +4397,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4387,7 +4405,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4395,7 +4413,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4403,7 +4421,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="1">
-        <v>520</v>
+        <v>740</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4411,7 +4429,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4419,7 +4437,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4427,7 +4445,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4435,7 +4453,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4451,7 +4469,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4459,7 +4477,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4467,7 +4485,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4475,7 +4493,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4483,7 +4501,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4491,7 +4509,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="1">
-        <v>760</v>
+        <v>900</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4499,7 +4517,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4507,7 +4525,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4515,7 +4533,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4523,7 +4541,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4539,7 +4557,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4547,7 +4565,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4563,7 +4581,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4571,7 +4589,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4579,7 +4597,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4587,7 +4605,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="1">
-        <v>500</v>
+        <v>640</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4595,7 +4613,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="1">
-        <v>758</v>
+        <v>640</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4603,7 +4621,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="1">
-        <v>2273</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4611,7 +4629,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="1">
-        <v>1515</v>
+        <v>500</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4619,7 +4637,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="1">
-        <v>520</v>
+        <v>758</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4627,7 +4645,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="1">
-        <v>720</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4635,7 +4653,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="1">
-        <v>560</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4643,7 +4661,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4659,7 +4677,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4667,7 +4685,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="1">
-        <v>660</v>
+        <v>480</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4675,7 +4693,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4683,7 +4701,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4691,7 +4709,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="1">
-        <v>520</v>
+        <v>660</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4699,7 +4717,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4707,7 +4725,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4715,7 +4733,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4723,7 +4741,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="1">
-        <v>560</v>
+        <v>680</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4731,7 +4749,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="1">
-        <v>380</v>
+        <v>640</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -4739,7 +4757,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="1">
-        <v>660</v>
+        <v>580</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4747,7 +4765,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="1">
-        <v>540</v>
+        <v>560</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4755,7 +4773,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4771,7 +4789,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4779,7 +4797,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="1">
-        <v>460</v>
+        <v>520</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4787,7 +4805,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="1">
-        <v>520</v>
+        <v>660</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4803,7 +4821,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="1">
-        <v>860</v>
+        <v>460</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4811,7 +4829,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="1">
-        <v>900</v>
+        <v>520</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4819,7 +4837,7 @@
         <v>265</v>
       </c>
       <c r="B266" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4827,7 +4845,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4835,7 +4853,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4843,7 +4861,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4851,7 +4869,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4859,7 +4877,7 @@
         <v>270</v>
       </c>
       <c r="B271" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4867,7 +4885,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="1">
-        <v>1040</v>
+        <v>560</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4875,7 +4893,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4883,7 +4901,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4891,7 +4909,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="1">
-        <v>840</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4899,7 +4917,7 @@
         <v>275</v>
       </c>
       <c r="B276" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4907,7 +4925,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4915,7 +4933,7 @@
         <v>277</v>
       </c>
       <c r="B278" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4923,7 +4941,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4931,7 +4949,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="1">
-        <v>520</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4939,7 +4957,7 @@
         <v>280</v>
       </c>
       <c r="B281" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4947,7 +4965,7 @@
         <v>281</v>
       </c>
       <c r="B282" s="1">
-        <v>800</v>
+        <v>680</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4955,7 +4973,7 @@
         <v>282</v>
       </c>
       <c r="B283" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4963,7 +4981,7 @@
         <v>283</v>
       </c>
       <c r="B284" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4971,7 +4989,7 @@
         <v>284</v>
       </c>
       <c r="B285" s="1">
-        <v>580</v>
+        <v>800</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4979,7 +4997,7 @@
         <v>285</v>
       </c>
       <c r="B286" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -4987,7 +5005,7 @@
         <v>286</v>
       </c>
       <c r="B287" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -4995,7 +5013,7 @@
         <v>287</v>
       </c>
       <c r="B288" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5011,7 +5029,7 @@
         <v>289</v>
       </c>
       <c r="B290" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5019,7 +5037,7 @@
         <v>290</v>
       </c>
       <c r="B291" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5027,7 +5045,7 @@
         <v>291</v>
       </c>
       <c r="B292" s="1">
-        <v>520</v>
+        <v>640</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5035,7 +5053,7 @@
         <v>292</v>
       </c>
       <c r="B293" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5043,7 +5061,7 @@
         <v>293</v>
       </c>
       <c r="B294" s="1">
-        <v>600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5051,7 +5069,7 @@
         <v>294</v>
       </c>
       <c r="B295" s="1">
-        <v>820</v>
+        <v>520</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5059,7 +5077,7 @@
         <v>295</v>
       </c>
       <c r="B296" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5067,7 +5085,7 @@
         <v>296</v>
       </c>
       <c r="B297" s="1">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5075,7 +5093,7 @@
         <v>297</v>
       </c>
       <c r="B298" s="1">
-        <v>520</v>
+        <v>820</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5083,7 +5101,7 @@
         <v>298</v>
       </c>
       <c r="B299" s="1">
-        <v>320</v>
+        <v>600</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5091,7 +5109,7 @@
         <v>299</v>
       </c>
       <c r="B300" s="1">
-        <v>540</v>
+        <v>380</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5099,7 +5117,7 @@
         <v>300</v>
       </c>
       <c r="B301" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5107,7 +5125,7 @@
         <v>301</v>
       </c>
       <c r="B302" s="1">
-        <v>480</v>
+        <v>320</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5115,7 +5133,7 @@
         <v>302</v>
       </c>
       <c r="B303" s="1">
-        <v>480</v>
+        <v>540</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5123,7 +5141,7 @@
         <v>303</v>
       </c>
       <c r="B304" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5131,7 +5149,7 @@
         <v>304</v>
       </c>
       <c r="B305" s="1">
-        <v>500</v>
+        <v>480</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5139,7 +5157,7 @@
         <v>305</v>
       </c>
       <c r="B306" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5147,7 +5165,7 @@
         <v>306</v>
       </c>
       <c r="B307" s="1">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5155,7 +5173,7 @@
         <v>307</v>
       </c>
       <c r="B308" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5163,7 +5181,7 @@
         <v>308</v>
       </c>
       <c r="B309" s="1">
-        <v>520</v>
+        <v>800</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5171,7 +5189,7 @@
         <v>309</v>
       </c>
       <c r="B310" s="1">
-        <v>380</v>
+        <v>480</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5179,7 +5197,7 @@
         <v>310</v>
       </c>
       <c r="B311" s="1">
-        <v>440</v>
+        <v>800</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5187,7 +5205,7 @@
         <v>311</v>
       </c>
       <c r="B312" s="1">
-        <v>900</v>
+        <v>520</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5195,7 +5213,7 @@
         <v>312</v>
       </c>
       <c r="B313" s="1">
-        <v>900</v>
+        <v>380</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5203,7 +5221,7 @@
         <v>313</v>
       </c>
       <c r="B314" s="1">
-        <v>780</v>
+        <v>440</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5211,7 +5229,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5219,7 +5237,7 @@
         <v>315</v>
       </c>
       <c r="B316" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5227,7 +5245,7 @@
         <v>316</v>
       </c>
       <c r="B317" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5235,7 +5253,7 @@
         <v>317</v>
       </c>
       <c r="B318" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5243,7 +5261,7 @@
         <v>318</v>
       </c>
       <c r="B319" s="1">
-        <v>700</v>
+        <v>960</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5251,7 +5269,7 @@
         <v>319</v>
       </c>
       <c r="B320" s="1">
-        <v>640</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5267,7 +5285,7 @@
         <v>321</v>
       </c>
       <c r="B322" s="1">
-        <v>1020</v>
+        <v>700</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5275,7 +5293,7 @@
         <v>322</v>
       </c>
       <c r="B323" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5283,7 +5301,7 @@
         <v>323</v>
       </c>
       <c r="B324" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5291,7 +5309,7 @@
         <v>324</v>
       </c>
       <c r="B325" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5307,7 +5325,7 @@
         <v>326</v>
       </c>
       <c r="B327" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5315,7 +5333,7 @@
         <v>327</v>
       </c>
       <c r="B328" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5323,7 +5341,7 @@
         <v>328</v>
       </c>
       <c r="B329" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5331,7 +5349,7 @@
         <v>329</v>
       </c>
       <c r="B330" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5339,7 +5357,7 @@
         <v>330</v>
       </c>
       <c r="B331" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5347,7 +5365,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5355,7 +5373,7 @@
         <v>332</v>
       </c>
       <c r="B333" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5371,7 +5389,7 @@
         <v>334</v>
       </c>
       <c r="B335" s="1">
-        <v>480</v>
+        <v>740</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5379,7 +5397,7 @@
         <v>335</v>
       </c>
       <c r="B336" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5387,7 +5405,7 @@
         <v>336</v>
       </c>
       <c r="B337" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5395,7 +5413,7 @@
         <v>337</v>
       </c>
       <c r="B338" s="1">
-        <v>920</v>
+        <v>480</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5403,7 +5421,7 @@
         <v>338</v>
       </c>
       <c r="B339" s="1">
-        <v>860</v>
+        <v>640</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5411,7 +5429,7 @@
         <v>339</v>
       </c>
       <c r="B340" s="1">
-        <v>520</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5419,7 +5437,7 @@
         <v>340</v>
       </c>
       <c r="B341" s="1">
-        <v>540</v>
+        <v>920</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5427,7 +5445,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="1">
-        <v>700</v>
+        <v>860</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5435,7 +5453,7 @@
         <v>342</v>
       </c>
       <c r="B343" s="1">
-        <v>700</v>
+        <v>520</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5443,7 +5461,7 @@
         <v>343</v>
       </c>
       <c r="B344" s="1">
-        <v>420</v>
+        <v>540</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5459,7 +5477,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5467,7 +5485,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="1">
-        <v>580</v>
+        <v>420</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5475,7 +5493,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5483,7 +5501,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5491,7 +5509,7 @@
         <v>349</v>
       </c>
       <c r="B350" s="1">
-        <v>920</v>
+        <v>580</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5499,7 +5517,7 @@
         <v>350</v>
       </c>
       <c r="B351" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5507,7 +5525,7 @@
         <v>351</v>
       </c>
       <c r="B352" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5515,7 +5533,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="1">
-        <v>620</v>
+        <v>920</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5523,7 +5541,7 @@
         <v>353</v>
       </c>
       <c r="B354" s="1">
-        <v>440</v>
+        <v>840</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5531,7 +5549,7 @@
         <v>354</v>
       </c>
       <c r="B355" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5539,7 +5557,7 @@
         <v>355</v>
       </c>
       <c r="B356" s="1">
-        <v>320</v>
+        <v>620</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5547,7 +5565,7 @@
         <v>356</v>
       </c>
       <c r="B357" s="1">
-        <v>320</v>
+        <v>440</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5555,7 +5573,7 @@
         <v>357</v>
       </c>
       <c r="B358" s="1">
-        <v>820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5563,7 +5581,7 @@
         <v>358</v>
       </c>
       <c r="B359" s="1">
-        <v>1000</v>
+        <v>320</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5571,7 +5589,7 @@
         <v>359</v>
       </c>
       <c r="B360" s="1">
-        <v>580</v>
+        <v>320</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5579,7 +5597,7 @@
         <v>360</v>
       </c>
       <c r="B361" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5587,7 +5605,7 @@
         <v>361</v>
       </c>
       <c r="B362" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5611,7 +5629,7 @@
         <v>364</v>
       </c>
       <c r="B365" s="1">
-        <v>620</v>
+        <v>900</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5619,7 +5637,7 @@
         <v>365</v>
       </c>
       <c r="B366" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5627,7 +5645,7 @@
         <v>366</v>
       </c>
       <c r="B367" s="1">
-        <v>920</v>
+        <v>580</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5635,7 +5653,7 @@
         <v>367</v>
       </c>
       <c r="B368" s="1">
-        <v>1000</v>
+        <v>620</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5643,7 +5661,7 @@
         <v>368</v>
       </c>
       <c r="B369" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5651,7 +5669,7 @@
         <v>369</v>
       </c>
       <c r="B370" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5659,7 +5677,7 @@
         <v>370</v>
       </c>
       <c r="B371" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5675,7 +5693,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="1">
-        <v>900</v>
+        <v>880</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5683,7 +5701,7 @@
         <v>373</v>
       </c>
       <c r="B374" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5691,7 +5709,7 @@
         <v>374</v>
       </c>
       <c r="B375" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5699,7 +5717,7 @@
         <v>375</v>
       </c>
       <c r="B376" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5715,7 +5733,7 @@
         <v>377</v>
       </c>
       <c r="B378" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5723,7 +5741,7 @@
         <v>378</v>
       </c>
       <c r="B379" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5731,7 +5749,7 @@
         <v>379</v>
       </c>
       <c r="B380" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5739,7 +5757,7 @@
         <v>380</v>
       </c>
       <c r="B381" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5747,7 +5765,7 @@
         <v>381</v>
       </c>
       <c r="B382" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5755,7 +5773,7 @@
         <v>382</v>
       </c>
       <c r="B383" s="1">
-        <v>760</v>
+        <v>900</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5763,7 +5781,7 @@
         <v>383</v>
       </c>
       <c r="B384" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5771,7 +5789,7 @@
         <v>384</v>
       </c>
       <c r="B385" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5779,7 +5797,7 @@
         <v>385</v>
       </c>
       <c r="B386" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5787,7 +5805,7 @@
         <v>386</v>
       </c>
       <c r="B387" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5795,7 +5813,7 @@
         <v>387</v>
       </c>
       <c r="B388" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5803,7 +5821,7 @@
         <v>388</v>
       </c>
       <c r="B389" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5811,7 +5829,7 @@
         <v>389</v>
       </c>
       <c r="B390" s="1">
-        <v>680</v>
+        <v>560</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5819,7 +5837,7 @@
         <v>390</v>
       </c>
       <c r="B391" s="1">
-        <v>480</v>
+        <v>620</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5827,7 +5845,7 @@
         <v>391</v>
       </c>
       <c r="B392" s="1">
-        <v>480</v>
+        <v>720</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5835,7 +5853,7 @@
         <v>392</v>
       </c>
       <c r="B393" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5843,7 +5861,7 @@
         <v>393</v>
       </c>
       <c r="B394" s="1">
-        <v>880</v>
+        <v>480</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5851,7 +5869,7 @@
         <v>394</v>
       </c>
       <c r="B395" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5859,7 +5877,7 @@
         <v>395</v>
       </c>
       <c r="B396" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5867,7 +5885,7 @@
         <v>396</v>
       </c>
       <c r="B397" s="1">
-        <v>920</v>
+        <v>880</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5875,7 +5893,7 @@
         <v>397</v>
       </c>
       <c r="B398" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5883,7 +5901,7 @@
         <v>398</v>
       </c>
       <c r="B399" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5891,7 +5909,7 @@
         <v>399</v>
       </c>
       <c r="B400" s="1">
-        <v>940</v>
+        <v>920</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5899,7 +5917,7 @@
         <v>400</v>
       </c>
       <c r="B401" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5907,7 +5925,7 @@
         <v>401</v>
       </c>
       <c r="B402" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5915,7 +5933,7 @@
         <v>402</v>
       </c>
       <c r="B403" s="1">
-        <v>600</v>
+        <v>940</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5923,7 +5941,7 @@
         <v>403</v>
       </c>
       <c r="B404" s="1">
-        <v>760</v>
+        <v>980</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5931,7 +5949,7 @@
         <v>404</v>
       </c>
       <c r="B405" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5939,7 +5957,7 @@
         <v>405</v>
       </c>
       <c r="B406" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5947,7 +5965,7 @@
         <v>406</v>
       </c>
       <c r="B407" s="1">
-        <v>620</v>
+        <v>760</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5955,7 +5973,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5963,7 +5981,7 @@
         <v>408</v>
       </c>
       <c r="B409" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5971,7 +5989,7 @@
         <v>409</v>
       </c>
       <c r="B410" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5979,7 +5997,7 @@
         <v>410</v>
       </c>
       <c r="B411" s="1">
-        <v>680</v>
+        <v>860</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -5987,7 +6005,7 @@
         <v>411</v>
       </c>
       <c r="B412" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -5995,7 +6013,7 @@
         <v>412</v>
       </c>
       <c r="B413" s="1">
-        <v>960</v>
+        <v>640</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -6003,7 +6021,7 @@
         <v>413</v>
       </c>
       <c r="B414" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -6011,7 +6029,7 @@
         <v>414</v>
       </c>
       <c r="B415" s="1">
-        <v>1000</v>
+        <v>820</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -6019,7 +6037,7 @@
         <v>415</v>
       </c>
       <c r="B416" s="1">
-        <v>640</v>
+        <v>960</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -6027,7 +6045,7 @@
         <v>416</v>
       </c>
       <c r="B417" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -6035,7 +6053,7 @@
         <v>417</v>
       </c>
       <c r="B418" s="1">
-        <v>560</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -6043,7 +6061,7 @@
         <v>418</v>
       </c>
       <c r="B419" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -6051,7 +6069,7 @@
         <v>419</v>
       </c>
       <c r="B420" s="1">
-        <v>660</v>
+        <v>860</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -6059,7 +6077,7 @@
         <v>420</v>
       </c>
       <c r="B421" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -6067,7 +6085,7 @@
         <v>421</v>
       </c>
       <c r="B422" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -6075,7 +6093,7 @@
         <v>422</v>
       </c>
       <c r="B423" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -6083,7 +6101,7 @@
         <v>423</v>
       </c>
       <c r="B424" s="1">
-        <v>520</v>
+        <v>640</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6091,7 +6109,7 @@
         <v>424</v>
       </c>
       <c r="B425" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6099,7 +6117,7 @@
         <v>425</v>
       </c>
       <c r="B426" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6107,7 +6125,7 @@
         <v>426</v>
       </c>
       <c r="B427" s="1">
-        <v>780</v>
+        <v>520</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6115,7 +6133,7 @@
         <v>427</v>
       </c>
       <c r="B428" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6123,7 +6141,7 @@
         <v>428</v>
       </c>
       <c r="B429" s="1">
-        <v>820</v>
+        <v>620</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6131,7 +6149,7 @@
         <v>429</v>
       </c>
       <c r="B430" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6139,7 +6157,7 @@
         <v>430</v>
       </c>
       <c r="B431" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6147,7 +6165,7 @@
         <v>431</v>
       </c>
       <c r="B432" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6155,7 +6173,7 @@
         <v>432</v>
       </c>
       <c r="B433" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6163,7 +6181,7 @@
         <v>433</v>
       </c>
       <c r="B434" s="1">
-        <v>480</v>
+        <v>740</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6171,7 +6189,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6179,7 +6197,7 @@
         <v>435</v>
       </c>
       <c r="B436" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6187,7 +6205,7 @@
         <v>436</v>
       </c>
       <c r="B437" s="1">
-        <v>700</v>
+        <v>480</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6195,7 +6213,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="1">
-        <v>440</v>
+        <v>840</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6203,7 +6221,7 @@
         <v>438</v>
       </c>
       <c r="B439" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6211,7 +6229,7 @@
         <v>439</v>
       </c>
       <c r="B440" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6219,7 +6237,7 @@
         <v>440</v>
       </c>
       <c r="B441" s="1">
-        <v>880</v>
+        <v>440</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6227,7 +6245,7 @@
         <v>441</v>
       </c>
       <c r="B442" s="1">
-        <v>880</v>
+        <v>440</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6235,7 +6253,7 @@
         <v>442</v>
       </c>
       <c r="B443" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6243,7 +6261,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6251,7 +6269,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="1">
-        <v>660</v>
+        <v>880</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6259,7 +6277,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6275,7 +6293,7 @@
         <v>447</v>
       </c>
       <c r="B448" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6283,7 +6301,7 @@
         <v>448</v>
       </c>
       <c r="B449" s="1">
-        <v>760</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6291,7 +6309,7 @@
         <v>449</v>
       </c>
       <c r="B450" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6299,7 +6317,7 @@
         <v>450</v>
       </c>
       <c r="B451" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6307,7 +6325,7 @@
         <v>451</v>
       </c>
       <c r="B452" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6315,7 +6333,7 @@
         <v>452</v>
       </c>
       <c r="B453" s="1">
-        <v>840</v>
+        <v>800</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6323,7 +6341,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6331,7 +6349,7 @@
         <v>454</v>
       </c>
       <c r="B455" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6339,7 +6357,7 @@
         <v>455</v>
       </c>
       <c r="B456" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6347,7 +6365,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6355,7 +6373,7 @@
         <v>457</v>
       </c>
       <c r="B458" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6363,7 +6381,7 @@
         <v>458</v>
       </c>
       <c r="B459" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6371,7 +6389,7 @@
         <v>459</v>
       </c>
       <c r="B460" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6379,7 +6397,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6395,7 +6413,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="1">
-        <v>620</v>
+        <v>800</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6403,7 +6421,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="1">
-        <v>880</v>
+        <v>660</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6411,7 +6429,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="1">
-        <v>860</v>
+        <v>600</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6419,7 +6437,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="1">
-        <v>800</v>
+        <v>620</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6427,7 +6445,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6435,7 +6453,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6443,7 +6461,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6451,7 +6469,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6459,7 +6477,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="1">
-        <v>1100</v>
+        <v>860</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6467,7 +6485,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="1">
-        <v>790</v>
+        <v>760</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6475,7 +6493,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6483,7 +6501,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6491,7 +6509,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="1">
-        <v>660</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6499,7 +6517,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6507,7 +6525,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="1">
-        <v>700</v>
+        <v>790</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6515,7 +6533,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="1">
-        <v>820</v>
+        <v>640</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6523,7 +6541,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6531,7 +6549,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="1">
-        <v>820</v>
+        <v>660</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6539,7 +6557,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6547,7 +6565,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="1">
-        <v>920</v>
+        <v>700</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6555,7 +6573,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6563,7 +6581,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="1">
-        <v>880</v>
+        <v>760</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6571,7 +6589,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="1">
-        <v>640</v>
+        <v>820</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6579,7 +6597,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6587,7 +6605,7 @@
         <v>486</v>
       </c>
       <c r="B487" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6595,7 +6613,7 @@
         <v>487</v>
       </c>
       <c r="B488" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6603,7 +6621,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="1">
-        <v>560</v>
+        <v>880</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6611,7 +6629,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="1">
-        <v>860</v>
+        <v>640</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6619,7 +6637,7 @@
         <v>490</v>
       </c>
       <c r="B491" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6627,7 +6645,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6635,7 +6653,7 @@
         <v>492</v>
       </c>
       <c r="B493" s="1">
-        <v>960</v>
+        <v>560</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6643,7 +6661,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="1">
-        <v>940</v>
+        <v>560</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6651,7 +6669,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="1">
-        <v>1040</v>
+        <v>860</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6659,7 +6677,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="1">
-        <v>1040</v>
+        <v>840</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6667,7 +6685,7 @@
         <v>496</v>
       </c>
       <c r="B497" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6675,7 +6693,7 @@
         <v>497</v>
       </c>
       <c r="B498" s="1">
-        <v>920</v>
+        <v>960</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6683,7 +6701,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="1">
-        <v>680</v>
+        <v>940</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6691,7 +6709,7 @@
         <v>499</v>
       </c>
       <c r="B500" s="1">
-        <v>580</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6699,7 +6717,7 @@
         <v>500</v>
       </c>
       <c r="B501" s="1">
-        <v>820</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6707,7 +6725,7 @@
         <v>501</v>
       </c>
       <c r="B502" s="1">
-        <v>620</v>
+        <v>900</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6715,7 +6733,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6723,7 +6741,7 @@
         <v>503</v>
       </c>
       <c r="B504" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6731,7 +6749,7 @@
         <v>504</v>
       </c>
       <c r="B505" s="1">
-        <v>700</v>
+        <v>580</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6739,7 +6757,7 @@
         <v>505</v>
       </c>
       <c r="B506" s="1">
-        <v>960</v>
+        <v>820</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6747,7 +6765,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="1">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6755,7 +6773,7 @@
         <v>507</v>
       </c>
       <c r="B508" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6771,7 +6789,7 @@
         <v>509</v>
       </c>
       <c r="B510" s="1">
-        <v>540</v>
+        <v>700</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6779,7 +6797,7 @@
         <v>510</v>
       </c>
       <c r="B511" s="1">
-        <v>1100</v>
+        <v>960</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6787,7 +6805,7 @@
         <v>511</v>
       </c>
       <c r="B512" s="1">
-        <v>1060</v>
+        <v>900</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6795,7 +6813,7 @@
         <v>512</v>
       </c>
       <c r="B513" s="1">
-        <v>1100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6803,7 +6821,7 @@
         <v>513</v>
       </c>
       <c r="B514" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6811,7 +6829,7 @@
         <v>514</v>
       </c>
       <c r="B515" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6819,7 +6837,7 @@
         <v>515</v>
       </c>
       <c r="B516" s="1">
-        <v>720</v>
+        <v>540</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6827,7 +6845,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6835,7 +6853,7 @@
         <v>517</v>
       </c>
       <c r="B518" s="1">
-        <v>740</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6843,7 +6861,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="1">
-        <v>620</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6851,7 +6869,7 @@
         <v>519</v>
       </c>
       <c r="B520" s="1">
-        <v>860</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6859,7 +6877,7 @@
         <v>520</v>
       </c>
       <c r="B521" s="1">
-        <v>980</v>
+        <v>840</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6867,7 +6885,7 @@
         <v>521</v>
       </c>
       <c r="B522" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -6875,7 +6893,7 @@
         <v>522</v>
       </c>
       <c r="B523" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6883,7 +6901,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6891,7 +6909,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1">
-        <v>1100</v>
+        <v>620</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6899,7 +6917,7 @@
         <v>525</v>
       </c>
       <c r="B526" s="1">
-        <v>1100</v>
+        <v>860</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6907,7 +6925,7 @@
         <v>526</v>
       </c>
       <c r="B527" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6915,7 +6933,7 @@
         <v>527</v>
       </c>
       <c r="B528" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6923,7 +6941,7 @@
         <v>528</v>
       </c>
       <c r="B529" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6931,7 +6949,7 @@
         <v>529</v>
       </c>
       <c r="B530" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6939,7 +6957,7 @@
         <v>530</v>
       </c>
       <c r="B531" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6947,7 +6965,7 @@
         <v>531</v>
       </c>
       <c r="B532" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6955,7 +6973,7 @@
         <v>532</v>
       </c>
       <c r="B533" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6963,7 +6981,7 @@
         <v>533</v>
       </c>
       <c r="B534" s="1">
-        <v>800</v>
+        <v>920</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6971,7 +6989,7 @@
         <v>534</v>
       </c>
       <c r="B535" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -6979,7 +6997,7 @@
         <v>535</v>
       </c>
       <c r="B536" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -6987,7 +7005,7 @@
         <v>536</v>
       </c>
       <c r="B537" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -6995,7 +7013,7 @@
         <v>537</v>
       </c>
       <c r="B538" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -7003,7 +7021,7 @@
         <v>538</v>
       </c>
       <c r="B539" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -7011,7 +7029,7 @@
         <v>539</v>
       </c>
       <c r="B540" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -7019,7 +7037,7 @@
         <v>540</v>
       </c>
       <c r="B541" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -7027,7 +7045,7 @@
         <v>541</v>
       </c>
       <c r="B542" s="1">
-        <v>820</v>
+        <v>720</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -7035,7 +7053,7 @@
         <v>542</v>
       </c>
       <c r="B543" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -7043,7 +7061,7 @@
         <v>543</v>
       </c>
       <c r="B544" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -7051,7 +7069,7 @@
         <v>544</v>
       </c>
       <c r="B545" s="1">
-        <v>1400</v>
+        <v>780</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -7059,7 +7077,7 @@
         <v>545</v>
       </c>
       <c r="B546" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -7067,7 +7085,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -7075,7 +7093,7 @@
         <v>547</v>
       </c>
       <c r="B548" s="1">
-        <v>700</v>
+        <v>820</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -7083,7 +7101,7 @@
         <v>548</v>
       </c>
       <c r="B549" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7099,7 +7117,7 @@
         <v>550</v>
       </c>
       <c r="B551" s="1">
-        <v>780</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7107,7 +7125,7 @@
         <v>551</v>
       </c>
       <c r="B552" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7115,7 +7133,7 @@
         <v>552</v>
       </c>
       <c r="B553" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7123,7 +7141,7 @@
         <v>553</v>
       </c>
       <c r="B554" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7131,7 +7149,7 @@
         <v>554</v>
       </c>
       <c r="B555" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7139,7 +7157,7 @@
         <v>555</v>
       </c>
       <c r="B556" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7147,7 +7165,7 @@
         <v>556</v>
       </c>
       <c r="B557" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7155,7 +7173,7 @@
         <v>557</v>
       </c>
       <c r="B558" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7163,7 +7181,7 @@
         <v>558</v>
       </c>
       <c r="B559" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7171,7 +7189,7 @@
         <v>559</v>
       </c>
       <c r="B560" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7179,7 +7197,7 @@
         <v>560</v>
       </c>
       <c r="B561" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7187,7 +7205,7 @@
         <v>561</v>
       </c>
       <c r="B562" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7195,7 +7213,7 @@
         <v>562</v>
       </c>
       <c r="B563" s="1">
-        <v>640</v>
+        <v>900</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7203,7 +7221,7 @@
         <v>563</v>
       </c>
       <c r="B564" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7211,7 +7229,7 @@
         <v>564</v>
       </c>
       <c r="B565" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7219,7 +7237,7 @@
         <v>565</v>
       </c>
       <c r="B566" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7227,7 +7245,7 @@
         <v>566</v>
       </c>
       <c r="B567" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7235,7 +7253,7 @@
         <v>567</v>
       </c>
       <c r="B568" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7243,7 +7261,7 @@
         <v>568</v>
       </c>
       <c r="B569" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7251,7 +7269,7 @@
         <v>569</v>
       </c>
       <c r="B570" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7259,7 +7277,7 @@
         <v>570</v>
       </c>
       <c r="B571" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7267,7 +7285,7 @@
         <v>571</v>
       </c>
       <c r="B572" s="1">
-        <v>540</v>
+        <v>720</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7283,7 +7301,7 @@
         <v>573</v>
       </c>
       <c r="B574" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7291,7 +7309,7 @@
         <v>574</v>
       </c>
       <c r="B575" s="1">
-        <v>860</v>
+        <v>680</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7299,7 +7317,7 @@
         <v>575</v>
       </c>
       <c r="B576" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7307,7 +7325,7 @@
         <v>576</v>
       </c>
       <c r="B577" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7315,7 +7333,7 @@
         <v>577</v>
       </c>
       <c r="B578" s="1">
-        <v>900</v>
+        <v>540</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7323,7 +7341,7 @@
         <v>578</v>
       </c>
       <c r="B579" s="1">
-        <v>1000</v>
+        <v>660</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7331,7 +7349,7 @@
         <v>579</v>
       </c>
       <c r="B580" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7339,7 +7357,7 @@
         <v>580</v>
       </c>
       <c r="B581" s="1">
-        <v>1040</v>
+        <v>860</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7347,7 +7365,7 @@
         <v>581</v>
       </c>
       <c r="B582" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7355,7 +7373,7 @@
         <v>582</v>
       </c>
       <c r="B583" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7363,7 +7381,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7371,7 +7389,7 @@
         <v>584</v>
       </c>
       <c r="B585" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7379,7 +7397,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7387,7 +7405,7 @@
         <v>586</v>
       </c>
       <c r="B587" s="1">
-        <v>800</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7395,7 +7413,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7403,7 +7421,7 @@
         <v>588</v>
       </c>
       <c r="B589" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7411,7 +7429,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7419,7 +7437,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="1">
-        <v>720</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7427,7 +7445,7 @@
         <v>591</v>
       </c>
       <c r="B592" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7435,7 +7453,7 @@
         <v>592</v>
       </c>
       <c r="B593" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7443,7 +7461,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="1">
-        <v>880</v>
+        <v>700</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7451,7 +7469,7 @@
         <v>594</v>
       </c>
       <c r="B595" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7459,7 +7477,7 @@
         <v>595</v>
       </c>
       <c r="B596" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7467,7 +7485,7 @@
         <v>596</v>
       </c>
       <c r="B597" s="1">
-        <v>820</v>
+        <v>720</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7475,7 +7493,7 @@
         <v>597</v>
       </c>
       <c r="B598" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7483,7 +7501,7 @@
         <v>598</v>
       </c>
       <c r="B599" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7491,7 +7509,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7499,7 +7517,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7507,7 +7525,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7515,7 +7533,7 @@
         <v>602</v>
       </c>
       <c r="B603" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7523,7 +7541,7 @@
         <v>603</v>
       </c>
       <c r="B604" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7531,7 +7549,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="1">
-        <v>960</v>
+        <v>800</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7539,7 +7557,7 @@
         <v>605</v>
       </c>
       <c r="B606" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7547,7 +7565,7 @@
         <v>606</v>
       </c>
       <c r="B607" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7555,7 +7573,7 @@
         <v>607</v>
       </c>
       <c r="B608" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7563,7 +7581,7 @@
         <v>608</v>
       </c>
       <c r="B609" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7571,7 +7589,7 @@
         <v>609</v>
       </c>
       <c r="B610" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7579,7 +7597,7 @@
         <v>610</v>
       </c>
       <c r="B611" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7587,7 +7605,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7595,7 +7613,7 @@
         <v>612</v>
       </c>
       <c r="B613" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7603,7 +7621,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7611,7 +7629,7 @@
         <v>614</v>
       </c>
       <c r="B615" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7627,7 +7645,7 @@
         <v>616</v>
       </c>
       <c r="B617" s="1">
-        <v>720</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -7635,7 +7653,7 @@
         <v>617</v>
       </c>
       <c r="B618" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -7643,7 +7661,7 @@
         <v>618</v>
       </c>
       <c r="B619" s="1">
-        <v>760</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7651,7 +7669,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7659,7 +7677,7 @@
         <v>620</v>
       </c>
       <c r="B621" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -7667,7 +7685,7 @@
         <v>621</v>
       </c>
       <c r="B622" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -7675,7 +7693,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -7683,7 +7701,7 @@
         <v>623</v>
       </c>
       <c r="B624" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -7691,7 +7709,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -7699,7 +7717,7 @@
         <v>625</v>
       </c>
       <c r="B626" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -7707,7 +7725,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -7715,7 +7733,7 @@
         <v>627</v>
       </c>
       <c r="B628" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -7723,7 +7741,7 @@
         <v>628</v>
       </c>
       <c r="B629" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -7731,7 +7749,7 @@
         <v>629</v>
       </c>
       <c r="B630" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -7739,7 +7757,7 @@
         <v>630</v>
       </c>
       <c r="B631" s="1">
-        <v>1100</v>
+        <v>860</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -7747,7 +7765,7 @@
         <v>631</v>
       </c>
       <c r="B632" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -7755,7 +7773,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -7763,7 +7781,7 @@
         <v>633</v>
       </c>
       <c r="B634" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -7771,7 +7789,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -7779,7 +7797,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="1">
-        <v>920</v>
+        <v>720</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -7787,7 +7805,7 @@
         <v>636</v>
       </c>
       <c r="B637" s="1">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -7795,7 +7813,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -7803,7 +7821,7 @@
         <v>638</v>
       </c>
       <c r="B639" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -7811,7 +7829,7 @@
         <v>639</v>
       </c>
       <c r="B640" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -7819,7 +7837,7 @@
         <v>640</v>
       </c>
       <c r="B641" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -7827,7 +7845,7 @@
         <v>641</v>
       </c>
       <c r="B642" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -7835,7 +7853,7 @@
         <v>642</v>
       </c>
       <c r="B643" s="1">
-        <v>660</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -7843,7 +7861,7 @@
         <v>643</v>
       </c>
       <c r="B644" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -7851,7 +7869,7 @@
         <v>644</v>
       </c>
       <c r="B645" s="1">
-        <v>680</v>
+        <v>880</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -7859,7 +7877,7 @@
         <v>645</v>
       </c>
       <c r="B646" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -7867,7 +7885,7 @@
         <v>646</v>
       </c>
       <c r="B647" s="1">
-        <v>440</v>
+        <v>780</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -7875,7 +7893,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -7883,7 +7901,7 @@
         <v>648</v>
       </c>
       <c r="B649" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -7891,7 +7909,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -7899,7 +7917,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -7907,7 +7925,7 @@
         <v>651</v>
       </c>
       <c r="B652" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -7915,7 +7933,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -7923,7 +7941,7 @@
         <v>653</v>
       </c>
       <c r="B654" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -7931,7 +7949,7 @@
         <v>654</v>
       </c>
       <c r="B655" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -7947,7 +7965,7 @@
         <v>656</v>
       </c>
       <c r="B657" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -7955,7 +7973,7 @@
         <v>657</v>
       </c>
       <c r="B658" s="1">
-        <v>920</v>
+        <v>600</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -7963,7 +7981,7 @@
         <v>658</v>
       </c>
       <c r="B659" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -7971,7 +7989,7 @@
         <v>659</v>
       </c>
       <c r="B660" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -7979,7 +7997,7 @@
         <v>660</v>
       </c>
       <c r="B661" s="1">
-        <v>980</v>
+        <v>880</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -7987,7 +8005,7 @@
         <v>661</v>
       </c>
       <c r="B662" s="1">
-        <v>920</v>
+        <v>800</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -8003,7 +8021,7 @@
         <v>663</v>
       </c>
       <c r="B664" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -8011,7 +8029,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -8019,7 +8037,7 @@
         <v>665</v>
       </c>
       <c r="B666" s="1">
-        <v>680</v>
+        <v>940</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -8027,7 +8045,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="1">
-        <v>820</v>
+        <v>980</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -8035,7 +8053,7 @@
         <v>667</v>
       </c>
       <c r="B668" s="1">
-        <v>960</v>
+        <v>920</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -8043,7 +8061,7 @@
         <v>668</v>
       </c>
       <c r="B669" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -8051,7 +8069,7 @@
         <v>669</v>
       </c>
       <c r="B670" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8059,7 +8077,7 @@
         <v>670</v>
       </c>
       <c r="B671" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -8067,7 +8085,7 @@
         <v>671</v>
       </c>
       <c r="B672" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -8075,7 +8093,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="1">
-        <v>660</v>
+        <v>820</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8083,7 +8101,7 @@
         <v>673</v>
       </c>
       <c r="B674" s="1">
-        <v>840</v>
+        <v>960</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -8091,7 +8109,7 @@
         <v>674</v>
       </c>
       <c r="B675" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8099,7 +8117,7 @@
         <v>675</v>
       </c>
       <c r="B676" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8107,7 +8125,7 @@
         <v>676</v>
       </c>
       <c r="B677" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8115,7 +8133,7 @@
         <v>677</v>
       </c>
       <c r="B678" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8123,7 +8141,7 @@
         <v>678</v>
       </c>
       <c r="B679" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8131,7 +8149,7 @@
         <v>679</v>
       </c>
       <c r="B680" s="1">
-        <v>600</v>
+        <v>840</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8139,7 +8157,7 @@
         <v>680</v>
       </c>
       <c r="B681" s="1">
-        <v>840</v>
+        <v>780</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8147,7 +8165,7 @@
         <v>681</v>
       </c>
       <c r="B682" s="1">
-        <v>660</v>
+        <v>820</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8155,7 +8173,7 @@
         <v>682</v>
       </c>
       <c r="B683" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8163,7 +8181,7 @@
         <v>683</v>
       </c>
       <c r="B684" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8171,7 +8189,7 @@
         <v>684</v>
       </c>
       <c r="B685" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8179,7 +8197,7 @@
         <v>685</v>
       </c>
       <c r="B686" s="1">
-        <v>860</v>
+        <v>600</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8187,7 +8205,7 @@
         <v>686</v>
       </c>
       <c r="B687" s="1">
-        <v>680</v>
+        <v>840</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8195,7 +8213,7 @@
         <v>687</v>
       </c>
       <c r="B688" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8203,7 +8221,7 @@
         <v>688</v>
       </c>
       <c r="B689" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8211,7 +8229,7 @@
         <v>689</v>
       </c>
       <c r="B690" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8219,7 +8237,7 @@
         <v>690</v>
       </c>
       <c r="B691" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8227,7 +8245,7 @@
         <v>691</v>
       </c>
       <c r="B692" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8235,7 +8253,7 @@
         <v>692</v>
       </c>
       <c r="B693" s="1">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8243,7 +8261,7 @@
         <v>693</v>
       </c>
       <c r="B694" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8251,7 +8269,7 @@
         <v>694</v>
       </c>
       <c r="B695" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8259,7 +8277,7 @@
         <v>695</v>
       </c>
       <c r="B696" s="1">
-        <v>920</v>
+        <v>720</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8267,7 +8285,7 @@
         <v>696</v>
       </c>
       <c r="B697" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8275,7 +8293,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="1">
-        <v>1040</v>
+        <v>600</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8283,7 +8301,7 @@
         <v>698</v>
       </c>
       <c r="B699" s="1">
-        <v>940</v>
+        <v>600</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8291,7 +8309,7 @@
         <v>699</v>
       </c>
       <c r="B700" s="1">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8299,7 +8317,7 @@
         <v>700</v>
       </c>
       <c r="B701" s="1">
-        <v>1040</v>
+        <v>760</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8307,7 +8325,7 @@
         <v>701</v>
       </c>
       <c r="B702" s="1">
-        <v>1100</v>
+        <v>920</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8323,7 +8341,7 @@
         <v>703</v>
       </c>
       <c r="B704" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8331,7 +8349,7 @@
         <v>704</v>
       </c>
       <c r="B705" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8339,7 +8357,7 @@
         <v>705</v>
       </c>
       <c r="B706" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8347,7 +8365,7 @@
         <v>706</v>
       </c>
       <c r="B707" s="1">
-        <v>820</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8355,7 +8373,7 @@
         <v>707</v>
       </c>
       <c r="B708" s="1">
-        <v>440</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8363,7 +8381,7 @@
         <v>708</v>
       </c>
       <c r="B709" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8371,7 +8389,7 @@
         <v>709</v>
       </c>
       <c r="B710" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8379,7 +8397,7 @@
         <v>710</v>
       </c>
       <c r="B711" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8387,7 +8405,7 @@
         <v>711</v>
       </c>
       <c r="B712" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8403,7 +8421,7 @@
         <v>713</v>
       </c>
       <c r="B714" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8411,7 +8429,7 @@
         <v>714</v>
       </c>
       <c r="B715" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8419,7 +8437,7 @@
         <v>715</v>
       </c>
       <c r="B716" s="1">
-        <v>400</v>
+        <v>440</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8427,7 +8445,7 @@
         <v>716</v>
       </c>
       <c r="B717" s="1">
-        <v>400</v>
+        <v>560</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8435,7 +8453,7 @@
         <v>717</v>
       </c>
       <c r="B718" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8443,7 +8461,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8451,7 +8469,7 @@
         <v>719</v>
       </c>
       <c r="B720" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8459,7 +8477,7 @@
         <v>720</v>
       </c>
       <c r="B721" s="1">
-        <v>520</v>
+        <v>760</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8467,7 +8485,7 @@
         <v>721</v>
       </c>
       <c r="B722" s="1">
-        <v>700</v>
+        <v>400</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8475,7 +8493,7 @@
         <v>722</v>
       </c>
       <c r="B723" s="1">
-        <v>860</v>
+        <v>400</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8483,7 +8501,7 @@
         <v>723</v>
       </c>
       <c r="B724" s="1">
-        <v>680</v>
+        <v>380</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8491,7 +8509,7 @@
         <v>724</v>
       </c>
       <c r="B725" s="1">
-        <v>740</v>
+        <v>380</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8499,7 +8517,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="1">
-        <v>780</v>
+        <v>380</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8507,7 +8525,7 @@
         <v>726</v>
       </c>
       <c r="B727" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8515,7 +8533,7 @@
         <v>727</v>
       </c>
       <c r="B728" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8523,7 +8541,7 @@
         <v>728</v>
       </c>
       <c r="B729" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8531,7 +8549,7 @@
         <v>729</v>
       </c>
       <c r="B730" s="1">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8539,7 +8557,7 @@
         <v>730</v>
       </c>
       <c r="B731" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8547,7 +8565,7 @@
         <v>731</v>
       </c>
       <c r="B732" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -8555,7 +8573,7 @@
         <v>732</v>
       </c>
       <c r="B733" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -8563,7 +8581,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -8571,7 +8589,7 @@
         <v>734</v>
       </c>
       <c r="B735" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -8579,7 +8597,7 @@
         <v>735</v>
       </c>
       <c r="B736" s="1">
-        <v>920</v>
+        <v>600</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -8587,7 +8605,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -8595,7 +8613,7 @@
         <v>737</v>
       </c>
       <c r="B738" s="1">
-        <v>1040</v>
+        <v>760</v>
       </c>
     </row>
     <row r="739" spans="1:2">
@@ -8603,7 +8621,7 @@
         <v>738</v>
       </c>
       <c r="B739" s="1">
-        <v>940</v>
+        <v>840</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -8619,7 +8637,7 @@
         <v>740</v>
       </c>
       <c r="B741" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -8627,7 +8645,7 @@
         <v>741</v>
       </c>
       <c r="B742" s="1">
-        <v>1100</v>
+        <v>920</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -8643,7 +8661,7 @@
         <v>743</v>
       </c>
       <c r="B744" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -8651,7 +8669,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="1">
-        <v>1100</v>
+        <v>940</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -8659,7 +8677,7 @@
         <v>745</v>
       </c>
       <c r="B746" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -8667,7 +8685,7 @@
         <v>746</v>
       </c>
       <c r="B747" s="1">
-        <v>820</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -8675,7 +8693,7 @@
         <v>747</v>
       </c>
       <c r="B748" s="1">
-        <v>440</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -8683,7 +8701,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -8691,7 +8709,7 @@
         <v>749</v>
       </c>
       <c r="B750" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="751" spans="1:2">
@@ -8699,7 +8717,7 @@
         <v>750</v>
       </c>
       <c r="B751" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -8707,7 +8725,7 @@
         <v>751</v>
       </c>
       <c r="B752" s="1">
-        <v>500</v>
+        <v>740</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -8723,7 +8741,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -8731,7 +8749,7 @@
         <v>754</v>
       </c>
       <c r="B755" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="756" spans="1:2">
@@ -8739,7 +8757,7 @@
         <v>755</v>
       </c>
       <c r="B756" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -8747,7 +8765,7 @@
         <v>756</v>
       </c>
       <c r="B757" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="758" spans="1:2">
@@ -8755,7 +8773,7 @@
         <v>757</v>
       </c>
       <c r="B758" s="1">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row r="759" spans="1:2">
@@ -8763,7 +8781,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="1">
-        <v>480</v>
+        <v>820</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -8771,7 +8789,7 @@
         <v>759</v>
       </c>
       <c r="B760" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="761" spans="1:2">
@@ -8779,7 +8797,7 @@
         <v>760</v>
       </c>
       <c r="B761" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="762" spans="1:2">
@@ -8787,7 +8805,7 @@
         <v>761</v>
       </c>
       <c r="B762" s="1">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="763" spans="1:2">
@@ -8795,7 +8813,7 @@
         <v>762</v>
       </c>
       <c r="B763" s="1">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -8803,7 +8821,7 @@
         <v>763</v>
       </c>
       <c r="B764" s="1">
-        <v>380</v>
+        <v>480</v>
       </c>
     </row>
     <row r="765" spans="1:2">
@@ -8811,7 +8829,7 @@
         <v>764</v>
       </c>
       <c r="B765" s="1">
-        <v>600</v>
+        <v>480</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -8819,7 +8837,7 @@
         <v>765</v>
       </c>
       <c r="B766" s="1">
-        <v>820</v>
+        <v>520</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -8827,7 +8845,7 @@
         <v>766</v>
       </c>
       <c r="B767" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="768" spans="1:2">
@@ -8835,7 +8853,7 @@
         <v>767</v>
       </c>
       <c r="B768" s="1">
-        <v>580</v>
+        <v>440</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -8843,7 +8861,7 @@
         <v>768</v>
       </c>
       <c r="B769" s="1">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -8851,7 +8869,7 @@
         <v>769</v>
       </c>
       <c r="B770" s="1">
-        <v>580</v>
+        <v>380</v>
       </c>
     </row>
     <row r="771" spans="1:2">
@@ -8859,7 +8877,7 @@
         <v>770</v>
       </c>
       <c r="B771" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="772" spans="1:2">
@@ -8867,7 +8885,7 @@
         <v>771</v>
       </c>
       <c r="B772" s="1">
-        <v>560</v>
+        <v>820</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -8875,6 +8893,54 @@
         <v>772</v>
       </c>
       <c r="B773" s="1">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2">
+      <c r="A774" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="B774" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2">
+      <c r="A775" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="B775" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2">
+      <c r="A776" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="B776" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2">
+      <c r="A777" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="B777" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2">
+      <c r="A778" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="B778" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2">
+      <c r="A779" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="B779" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="783">
   <si>
     <t>Наименование</t>
   </si>
@@ -752,6 +752,9 @@
     <t>Red Button -MOST WONDERFUL TIME 4 A BEER (Stout), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Red Button X Ability Brewing Project - BUT70N 0F 481L17Y (Freeze-Distilled Beer), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Red Rocket - Basement Vibes (Imperial Stout), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -899,6 +902,9 @@
     <t>Selfmade - Suncity Blues (NEPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Selfmade - Suncity Groove (APA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Selfmade - Sweet Deal (Stout), РОЗЛИВ</t>
   </si>
   <si>
@@ -1727,6 +1733,9 @@
     <t>вынос_Red Button -MOST WONDERFUL TIME 4 A BEER (Stout), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Red Button X Ability Brewing Project - BUT70N 0F 481L17Y (Freeze-Distilled Beer), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Red Rocket - Connection (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1815,6 +1824,9 @@
   </si>
   <si>
     <t>вынос_Selfmade - Suncity Blues (NEPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Selfmade - Suncity Groove (APA), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_SINDROM Brewery - DEEP PACIFICATION (DIPA), РОЗЛИВ, Россия</t>
@@ -2705,7 +2717,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B779"/>
+  <dimension ref="A1:B783"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -4533,7 +4545,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4669,7 +4681,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4677,7 +4689,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="1">
-        <v>560</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4685,7 +4697,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4693,7 +4705,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4709,7 +4721,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4717,7 +4729,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4725,7 +4737,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4733,7 +4745,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4741,7 +4753,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="1">
-        <v>680</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4749,7 +4761,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -4757,7 +4769,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4765,7 +4777,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4773,7 +4785,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4781,7 +4793,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4789,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="1">
-        <v>540</v>
+        <v>660</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4797,7 +4809,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4805,7 +4817,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4813,7 +4825,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4821,7 +4833,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="1">
-        <v>460</v>
+        <v>580</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4829,7 +4841,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="1">
-        <v>520</v>
+        <v>460</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4837,7 +4849,7 @@
         <v>265</v>
       </c>
       <c r="B266" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4845,7 +4857,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="1">
-        <v>860</v>
+        <v>580</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4853,7 +4865,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4877,7 +4889,7 @@
         <v>270</v>
       </c>
       <c r="B271" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4893,7 +4905,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="1">
-        <v>1000</v>
+        <v>560</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4901,7 +4913,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4909,7 +4921,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4917,7 +4929,7 @@
         <v>275</v>
       </c>
       <c r="B276" s="1">
-        <v>680</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4925,7 +4937,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4933,7 +4945,7 @@
         <v>277</v>
       </c>
       <c r="B278" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4941,7 +4953,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4949,7 +4961,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="1">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4957,7 +4969,7 @@
         <v>280</v>
       </c>
       <c r="B281" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4965,7 +4977,7 @@
         <v>281</v>
       </c>
       <c r="B282" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4973,7 +4985,7 @@
         <v>282</v>
       </c>
       <c r="B283" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4981,7 +4993,7 @@
         <v>283</v>
       </c>
       <c r="B284" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -4989,7 +5001,7 @@
         <v>284</v>
       </c>
       <c r="B285" s="1">
-        <v>800</v>
+        <v>640</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -4997,7 +5009,7 @@
         <v>285</v>
       </c>
       <c r="B286" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5005,7 +5017,7 @@
         <v>286</v>
       </c>
       <c r="B287" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5013,7 +5025,7 @@
         <v>287</v>
       </c>
       <c r="B288" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5021,7 +5033,7 @@
         <v>288</v>
       </c>
       <c r="B289" s="1">
-        <v>640</v>
+        <v>580</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5029,7 +5041,7 @@
         <v>289</v>
       </c>
       <c r="B290" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5037,7 +5049,7 @@
         <v>290</v>
       </c>
       <c r="B291" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5045,7 +5057,7 @@
         <v>291</v>
       </c>
       <c r="B292" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5053,7 +5065,7 @@
         <v>292</v>
       </c>
       <c r="B293" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5061,7 +5073,7 @@
         <v>293</v>
       </c>
       <c r="B294" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5069,7 +5081,7 @@
         <v>294</v>
       </c>
       <c r="B295" s="1">
-        <v>520</v>
+        <v>880</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5077,7 +5089,7 @@
         <v>295</v>
       </c>
       <c r="B296" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5085,7 +5097,7 @@
         <v>296</v>
       </c>
       <c r="B297" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5093,7 +5105,7 @@
         <v>297</v>
       </c>
       <c r="B298" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5109,7 +5121,7 @@
         <v>299</v>
       </c>
       <c r="B300" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5117,7 +5129,7 @@
         <v>300</v>
       </c>
       <c r="B301" s="1">
-        <v>520</v>
+        <v>600</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5125,7 +5137,7 @@
         <v>301</v>
       </c>
       <c r="B302" s="1">
-        <v>320</v>
+        <v>380</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5133,7 +5145,7 @@
         <v>302</v>
       </c>
       <c r="B303" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5141,7 +5153,7 @@
         <v>303</v>
       </c>
       <c r="B304" s="1">
-        <v>560</v>
+        <v>320</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5149,7 +5161,7 @@
         <v>304</v>
       </c>
       <c r="B305" s="1">
-        <v>480</v>
+        <v>540</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5157,7 +5169,7 @@
         <v>305</v>
       </c>
       <c r="B306" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5165,7 +5177,7 @@
         <v>306</v>
       </c>
       <c r="B307" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5173,7 +5185,7 @@
         <v>307</v>
       </c>
       <c r="B308" s="1">
-        <v>500</v>
+        <v>480</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5181,7 +5193,7 @@
         <v>308</v>
       </c>
       <c r="B309" s="1">
-        <v>800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5189,7 +5201,7 @@
         <v>309</v>
       </c>
       <c r="B310" s="1">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5205,7 +5217,7 @@
         <v>311</v>
       </c>
       <c r="B312" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5213,7 +5225,7 @@
         <v>312</v>
       </c>
       <c r="B313" s="1">
-        <v>380</v>
+        <v>800</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5221,7 +5233,7 @@
         <v>313</v>
       </c>
       <c r="B314" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5229,7 +5241,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="1">
-        <v>900</v>
+        <v>380</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5237,7 +5249,7 @@
         <v>315</v>
       </c>
       <c r="B316" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5245,7 +5257,7 @@
         <v>316</v>
       </c>
       <c r="B317" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5253,7 +5265,7 @@
         <v>317</v>
       </c>
       <c r="B318" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5261,7 +5273,7 @@
         <v>318</v>
       </c>
       <c r="B319" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5269,7 +5281,7 @@
         <v>319</v>
       </c>
       <c r="B320" s="1">
-        <v>1020</v>
+        <v>720</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5277,7 +5289,7 @@
         <v>320</v>
       </c>
       <c r="B321" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5285,7 +5297,7 @@
         <v>321</v>
       </c>
       <c r="B322" s="1">
-        <v>700</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5293,7 +5305,7 @@
         <v>322</v>
       </c>
       <c r="B323" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5301,7 +5313,7 @@
         <v>323</v>
       </c>
       <c r="B324" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5309,7 +5321,7 @@
         <v>324</v>
       </c>
       <c r="B325" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5325,7 +5337,7 @@
         <v>326</v>
       </c>
       <c r="B327" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5333,7 +5345,7 @@
         <v>327</v>
       </c>
       <c r="B328" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5341,7 +5353,7 @@
         <v>328</v>
       </c>
       <c r="B329" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5349,7 +5361,7 @@
         <v>329</v>
       </c>
       <c r="B330" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5357,7 +5369,7 @@
         <v>330</v>
       </c>
       <c r="B331" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5365,7 +5377,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5373,7 +5385,7 @@
         <v>332</v>
       </c>
       <c r="B333" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5389,7 +5401,7 @@
         <v>334</v>
       </c>
       <c r="B335" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5397,7 +5409,7 @@
         <v>335</v>
       </c>
       <c r="B336" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5405,7 +5417,7 @@
         <v>336</v>
       </c>
       <c r="B337" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5413,7 +5425,7 @@
         <v>337</v>
       </c>
       <c r="B338" s="1">
-        <v>480</v>
+        <v>740</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5421,7 +5433,7 @@
         <v>338</v>
       </c>
       <c r="B339" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5429,7 +5441,7 @@
         <v>339</v>
       </c>
       <c r="B340" s="1">
-        <v>1000</v>
+        <v>480</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5437,7 +5449,7 @@
         <v>340</v>
       </c>
       <c r="B341" s="1">
-        <v>920</v>
+        <v>640</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5445,7 +5457,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5453,7 +5465,7 @@
         <v>342</v>
       </c>
       <c r="B343" s="1">
-        <v>520</v>
+        <v>920</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5461,7 +5473,7 @@
         <v>343</v>
       </c>
       <c r="B344" s="1">
-        <v>540</v>
+        <v>860</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5469,7 +5481,7 @@
         <v>344</v>
       </c>
       <c r="B345" s="1">
-        <v>700</v>
+        <v>520</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5477,7 +5489,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5485,7 +5497,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5501,7 +5513,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="1">
-        <v>720</v>
+        <v>420</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5509,7 +5521,7 @@
         <v>349</v>
       </c>
       <c r="B350" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5517,7 +5529,7 @@
         <v>350</v>
       </c>
       <c r="B351" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5525,7 +5537,7 @@
         <v>351</v>
       </c>
       <c r="B352" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5533,7 +5545,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5541,7 +5553,7 @@
         <v>353</v>
       </c>
       <c r="B354" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5549,7 +5561,7 @@
         <v>354</v>
       </c>
       <c r="B355" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5557,7 +5569,7 @@
         <v>355</v>
       </c>
       <c r="B356" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5565,7 +5577,7 @@
         <v>356</v>
       </c>
       <c r="B357" s="1">
-        <v>440</v>
+        <v>720</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5573,7 +5585,7 @@
         <v>357</v>
       </c>
       <c r="B358" s="1">
-        <v>1100</v>
+        <v>620</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5581,7 +5593,7 @@
         <v>358</v>
       </c>
       <c r="B359" s="1">
-        <v>320</v>
+        <v>440</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5589,7 +5601,7 @@
         <v>359</v>
       </c>
       <c r="B360" s="1">
-        <v>320</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5597,7 +5609,7 @@
         <v>360</v>
       </c>
       <c r="B361" s="1">
-        <v>820</v>
+        <v>320</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5605,7 +5617,7 @@
         <v>361</v>
       </c>
       <c r="B362" s="1">
-        <v>1000</v>
+        <v>320</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5613,7 +5625,7 @@
         <v>362</v>
       </c>
       <c r="B363" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5621,7 +5633,7 @@
         <v>363</v>
       </c>
       <c r="B364" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5629,7 +5641,7 @@
         <v>364</v>
       </c>
       <c r="B365" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5645,7 +5657,7 @@
         <v>366</v>
       </c>
       <c r="B367" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5653,7 +5665,7 @@
         <v>367</v>
       </c>
       <c r="B368" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5661,7 +5673,7 @@
         <v>368</v>
       </c>
       <c r="B369" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5669,7 +5681,7 @@
         <v>369</v>
       </c>
       <c r="B370" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5677,7 +5689,7 @@
         <v>370</v>
       </c>
       <c r="B371" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5685,7 +5697,7 @@
         <v>371</v>
       </c>
       <c r="B372" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5693,7 +5705,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5709,7 +5721,7 @@
         <v>374</v>
       </c>
       <c r="B375" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5717,7 +5729,7 @@
         <v>375</v>
       </c>
       <c r="B376" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5725,7 +5737,7 @@
         <v>376</v>
       </c>
       <c r="B377" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5733,7 +5745,7 @@
         <v>377</v>
       </c>
       <c r="B378" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5741,7 +5753,7 @@
         <v>378</v>
       </c>
       <c r="B379" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5749,7 +5761,7 @@
         <v>379</v>
       </c>
       <c r="B380" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5757,7 +5769,7 @@
         <v>380</v>
       </c>
       <c r="B381" s="1">
-        <v>440</v>
+        <v>680</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5765,7 +5777,7 @@
         <v>381</v>
       </c>
       <c r="B382" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5773,7 +5785,7 @@
         <v>382</v>
       </c>
       <c r="B383" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5781,7 +5793,7 @@
         <v>383</v>
       </c>
       <c r="B384" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5789,7 +5801,7 @@
         <v>384</v>
       </c>
       <c r="B385" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5797,7 +5809,7 @@
         <v>385</v>
       </c>
       <c r="B386" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5805,7 +5817,7 @@
         <v>386</v>
       </c>
       <c r="B387" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5813,7 +5825,7 @@
         <v>387</v>
       </c>
       <c r="B388" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5821,7 +5833,7 @@
         <v>388</v>
       </c>
       <c r="B389" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5829,7 +5841,7 @@
         <v>389</v>
       </c>
       <c r="B390" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5837,7 +5849,7 @@
         <v>390</v>
       </c>
       <c r="B391" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5845,7 +5857,7 @@
         <v>391</v>
       </c>
       <c r="B392" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5853,7 +5865,7 @@
         <v>392</v>
       </c>
       <c r="B393" s="1">
-        <v>680</v>
+        <v>620</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5861,7 +5873,7 @@
         <v>393</v>
       </c>
       <c r="B394" s="1">
-        <v>480</v>
+        <v>720</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5869,7 +5881,7 @@
         <v>394</v>
       </c>
       <c r="B395" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5877,7 +5889,7 @@
         <v>395</v>
       </c>
       <c r="B396" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5885,7 +5897,7 @@
         <v>396</v>
       </c>
       <c r="B397" s="1">
-        <v>880</v>
+        <v>480</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5901,7 +5913,7 @@
         <v>398</v>
       </c>
       <c r="B399" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5909,7 +5921,7 @@
         <v>399</v>
       </c>
       <c r="B400" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5917,7 +5929,7 @@
         <v>400</v>
       </c>
       <c r="B401" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5925,7 +5937,7 @@
         <v>401</v>
       </c>
       <c r="B402" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5933,7 +5945,7 @@
         <v>402</v>
       </c>
       <c r="B403" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5941,7 +5953,7 @@
         <v>403</v>
       </c>
       <c r="B404" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5949,7 +5961,7 @@
         <v>404</v>
       </c>
       <c r="B405" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5957,7 +5969,7 @@
         <v>405</v>
       </c>
       <c r="B406" s="1">
-        <v>600</v>
+        <v>980</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5965,7 +5977,7 @@
         <v>406</v>
       </c>
       <c r="B407" s="1">
-        <v>760</v>
+        <v>920</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5973,7 +5985,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5981,7 +5993,7 @@
         <v>408</v>
       </c>
       <c r="B409" s="1">
-        <v>620</v>
+        <v>760</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -5989,7 +6001,7 @@
         <v>409</v>
       </c>
       <c r="B410" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -5997,7 +6009,7 @@
         <v>410</v>
       </c>
       <c r="B411" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -6005,7 +6017,7 @@
         <v>411</v>
       </c>
       <c r="B412" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -6013,7 +6025,7 @@
         <v>412</v>
       </c>
       <c r="B413" s="1">
-        <v>640</v>
+        <v>860</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -6021,7 +6033,7 @@
         <v>413</v>
       </c>
       <c r="B414" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -6029,7 +6041,7 @@
         <v>414</v>
       </c>
       <c r="B415" s="1">
-        <v>820</v>
+        <v>640</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -6037,7 +6049,7 @@
         <v>415</v>
       </c>
       <c r="B416" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -6045,7 +6057,7 @@
         <v>416</v>
       </c>
       <c r="B417" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -6053,7 +6065,7 @@
         <v>417</v>
       </c>
       <c r="B418" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -6061,7 +6073,7 @@
         <v>418</v>
       </c>
       <c r="B419" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -6069,7 +6081,7 @@
         <v>419</v>
       </c>
       <c r="B420" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -6077,7 +6089,7 @@
         <v>420</v>
       </c>
       <c r="B421" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -6085,7 +6097,7 @@
         <v>421</v>
       </c>
       <c r="B422" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -6093,7 +6105,7 @@
         <v>422</v>
       </c>
       <c r="B423" s="1">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -6101,7 +6113,7 @@
         <v>423</v>
       </c>
       <c r="B424" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6109,7 +6121,7 @@
         <v>424</v>
       </c>
       <c r="B425" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6117,7 +6129,7 @@
         <v>425</v>
       </c>
       <c r="B426" s="1">
-        <v>840</v>
+        <v>640</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6125,7 +6137,7 @@
         <v>426</v>
       </c>
       <c r="B427" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6133,7 +6145,7 @@
         <v>427</v>
       </c>
       <c r="B428" s="1">
-        <v>480</v>
+        <v>840</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6141,7 +6153,7 @@
         <v>428</v>
       </c>
       <c r="B429" s="1">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6149,7 +6161,7 @@
         <v>429</v>
       </c>
       <c r="B430" s="1">
-        <v>780</v>
+        <v>480</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6157,7 +6169,7 @@
         <v>430</v>
       </c>
       <c r="B431" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6165,7 +6177,7 @@
         <v>431</v>
       </c>
       <c r="B432" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6173,7 +6185,7 @@
         <v>432</v>
       </c>
       <c r="B433" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6181,7 +6193,7 @@
         <v>433</v>
       </c>
       <c r="B434" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6189,7 +6201,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6197,7 +6209,7 @@
         <v>435</v>
       </c>
       <c r="B436" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6205,7 +6217,7 @@
         <v>436</v>
       </c>
       <c r="B437" s="1">
-        <v>480</v>
+        <v>780</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6213,7 +6225,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6221,7 +6233,7 @@
         <v>438</v>
       </c>
       <c r="B439" s="1">
-        <v>660</v>
+        <v>480</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6229,7 +6241,7 @@
         <v>439</v>
       </c>
       <c r="B440" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6237,7 +6249,7 @@
         <v>440</v>
       </c>
       <c r="B441" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6245,7 +6257,7 @@
         <v>441</v>
       </c>
       <c r="B442" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6253,7 +6265,7 @@
         <v>442</v>
       </c>
       <c r="B443" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6261,7 +6273,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="1">
-        <v>880</v>
+        <v>440</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6269,7 +6281,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6277,7 +6289,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6285,7 +6297,7 @@
         <v>446</v>
       </c>
       <c r="B447" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6293,7 +6305,7 @@
         <v>447</v>
       </c>
       <c r="B448" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6301,7 +6313,7 @@
         <v>448</v>
       </c>
       <c r="B449" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6309,7 +6321,7 @@
         <v>449</v>
       </c>
       <c r="B450" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6317,7 +6329,7 @@
         <v>450</v>
       </c>
       <c r="B451" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6325,7 +6337,7 @@
         <v>451</v>
       </c>
       <c r="B452" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6333,7 +6345,7 @@
         <v>452</v>
       </c>
       <c r="B453" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6341,7 +6353,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6349,7 +6361,7 @@
         <v>454</v>
       </c>
       <c r="B455" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6357,7 +6369,7 @@
         <v>455</v>
       </c>
       <c r="B456" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6365,7 +6377,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6373,7 +6385,7 @@
         <v>457</v>
       </c>
       <c r="B458" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6381,7 +6393,7 @@
         <v>458</v>
       </c>
       <c r="B459" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6389,7 +6401,7 @@
         <v>459</v>
       </c>
       <c r="B460" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6397,7 +6409,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6405,7 +6417,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6413,7 +6425,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6421,7 +6433,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6429,7 +6441,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6437,7 +6449,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6445,7 +6457,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6453,7 +6465,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="1">
-        <v>880</v>
+        <v>620</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6461,7 +6473,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6469,7 +6481,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="1">
-        <v>800</v>
+        <v>880</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6485,7 +6497,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6493,7 +6505,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6501,7 +6513,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6509,7 +6521,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6517,7 +6529,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6525,7 +6537,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="1">
-        <v>790</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6533,7 +6545,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6541,7 +6553,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6549,7 +6561,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6557,7 +6569,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6565,7 +6577,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6573,7 +6585,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6581,7 +6593,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6605,7 +6617,7 @@
         <v>486</v>
       </c>
       <c r="B487" s="1">
-        <v>920</v>
+        <v>820</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6613,7 +6625,7 @@
         <v>487</v>
       </c>
       <c r="B488" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6621,7 +6633,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6629,7 +6641,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="1">
-        <v>640</v>
+        <v>600</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6637,7 +6649,7 @@
         <v>490</v>
       </c>
       <c r="B491" s="1">
-        <v>700</v>
+        <v>880</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6645,7 +6657,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6653,7 +6665,7 @@
         <v>492</v>
       </c>
       <c r="B493" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6661,7 +6673,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6669,7 +6681,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6677,7 +6689,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6685,7 +6697,7 @@
         <v>496</v>
       </c>
       <c r="B497" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6693,7 +6705,7 @@
         <v>497</v>
       </c>
       <c r="B498" s="1">
-        <v>960</v>
+        <v>840</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6701,7 +6713,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6709,7 +6721,7 @@
         <v>499</v>
       </c>
       <c r="B500" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6717,7 +6729,7 @@
         <v>500</v>
       </c>
       <c r="B501" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6725,7 +6737,7 @@
         <v>501</v>
       </c>
       <c r="B502" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6733,7 +6745,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="1">
-        <v>920</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6741,7 +6753,7 @@
         <v>503</v>
       </c>
       <c r="B504" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6749,7 +6761,7 @@
         <v>504</v>
       </c>
       <c r="B505" s="1">
-        <v>580</v>
+        <v>920</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6757,7 +6769,7 @@
         <v>505</v>
       </c>
       <c r="B506" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6765,7 +6777,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6773,7 +6785,7 @@
         <v>507</v>
       </c>
       <c r="B508" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6781,7 +6793,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6789,7 +6801,7 @@
         <v>509</v>
       </c>
       <c r="B510" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6797,7 +6809,7 @@
         <v>510</v>
       </c>
       <c r="B511" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6805,7 +6817,7 @@
         <v>511</v>
       </c>
       <c r="B512" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6813,7 +6825,7 @@
         <v>512</v>
       </c>
       <c r="B513" s="1">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6821,7 +6833,7 @@
         <v>513</v>
       </c>
       <c r="B514" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6829,7 +6841,7 @@
         <v>514</v>
       </c>
       <c r="B515" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6837,7 +6849,7 @@
         <v>515</v>
       </c>
       <c r="B516" s="1">
-        <v>540</v>
+        <v>720</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6845,7 +6857,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="1">
-        <v>1100</v>
+        <v>780</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6853,7 +6865,7 @@
         <v>517</v>
       </c>
       <c r="B518" s="1">
-        <v>1060</v>
+        <v>540</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6869,7 +6881,7 @@
         <v>519</v>
       </c>
       <c r="B520" s="1">
-        <v>1100</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6877,7 +6889,7 @@
         <v>520</v>
       </c>
       <c r="B521" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6885,7 +6897,7 @@
         <v>521</v>
       </c>
       <c r="B522" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -6893,7 +6905,7 @@
         <v>522</v>
       </c>
       <c r="B523" s="1">
-        <v>560</v>
+        <v>840</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6901,7 +6913,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6909,7 +6921,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6917,7 +6929,7 @@
         <v>525</v>
       </c>
       <c r="B526" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6925,7 +6937,7 @@
         <v>526</v>
       </c>
       <c r="B527" s="1">
-        <v>980</v>
+        <v>620</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6933,7 +6945,7 @@
         <v>527</v>
       </c>
       <c r="B528" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6941,7 +6953,7 @@
         <v>528</v>
       </c>
       <c r="B529" s="1">
-        <v>760</v>
+        <v>980</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6949,7 +6961,7 @@
         <v>529</v>
       </c>
       <c r="B530" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6957,7 +6969,7 @@
         <v>530</v>
       </c>
       <c r="B531" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6973,7 +6985,7 @@
         <v>532</v>
       </c>
       <c r="B533" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6981,7 +6993,7 @@
         <v>533</v>
       </c>
       <c r="B534" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -6989,7 +7001,7 @@
         <v>534</v>
       </c>
       <c r="B535" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -6997,7 +7009,7 @@
         <v>535</v>
       </c>
       <c r="B536" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -7005,7 +7017,7 @@
         <v>536</v>
       </c>
       <c r="B537" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -7021,7 +7033,7 @@
         <v>538</v>
       </c>
       <c r="B539" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -7029,7 +7041,7 @@
         <v>539</v>
       </c>
       <c r="B540" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -7037,7 +7049,7 @@
         <v>540</v>
       </c>
       <c r="B541" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -7045,7 +7057,7 @@
         <v>541</v>
       </c>
       <c r="B542" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -7061,7 +7073,7 @@
         <v>543</v>
       </c>
       <c r="B544" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -7069,7 +7081,7 @@
         <v>544</v>
       </c>
       <c r="B545" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -7085,7 +7097,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -7093,7 +7105,7 @@
         <v>547</v>
       </c>
       <c r="B548" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -7101,7 +7113,7 @@
         <v>548</v>
       </c>
       <c r="B549" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7109,7 +7121,7 @@
         <v>549</v>
       </c>
       <c r="B550" s="1">
-        <v>720</v>
+        <v>820</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7117,7 +7129,7 @@
         <v>550</v>
       </c>
       <c r="B551" s="1">
-        <v>1400</v>
+        <v>760</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7133,7 +7145,7 @@
         <v>552</v>
       </c>
       <c r="B553" s="1">
-        <v>660</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7141,7 +7153,7 @@
         <v>553</v>
       </c>
       <c r="B554" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7149,7 +7161,7 @@
         <v>554</v>
       </c>
       <c r="B555" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7157,7 +7169,7 @@
         <v>555</v>
       </c>
       <c r="B556" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7165,7 +7177,7 @@
         <v>556</v>
       </c>
       <c r="B557" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7173,7 +7185,7 @@
         <v>557</v>
       </c>
       <c r="B558" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7181,7 +7193,7 @@
         <v>558</v>
       </c>
       <c r="B559" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7189,7 +7201,7 @@
         <v>559</v>
       </c>
       <c r="B560" s="1">
-        <v>760</v>
+        <v>900</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7197,7 +7209,7 @@
         <v>560</v>
       </c>
       <c r="B561" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7213,7 +7225,7 @@
         <v>562</v>
       </c>
       <c r="B563" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7229,7 +7241,7 @@
         <v>564</v>
       </c>
       <c r="B565" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7253,7 +7265,7 @@
         <v>567</v>
       </c>
       <c r="B568" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7261,7 +7273,7 @@
         <v>568</v>
       </c>
       <c r="B569" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7269,7 +7281,7 @@
         <v>569</v>
       </c>
       <c r="B570" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7277,7 +7289,7 @@
         <v>570</v>
       </c>
       <c r="B571" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7285,7 +7297,7 @@
         <v>571</v>
       </c>
       <c r="B572" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7293,7 +7305,7 @@
         <v>572</v>
       </c>
       <c r="B573" s="1">
-        <v>660</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7301,7 +7313,7 @@
         <v>573</v>
       </c>
       <c r="B574" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7309,7 +7321,7 @@
         <v>574</v>
       </c>
       <c r="B575" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7317,7 +7329,7 @@
         <v>575</v>
       </c>
       <c r="B576" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7325,7 +7337,7 @@
         <v>576</v>
       </c>
       <c r="B577" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7333,7 +7345,7 @@
         <v>577</v>
       </c>
       <c r="B578" s="1">
-        <v>540</v>
+        <v>680</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7341,7 +7353,7 @@
         <v>578</v>
       </c>
       <c r="B579" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7349,7 +7361,7 @@
         <v>579</v>
       </c>
       <c r="B580" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7357,7 +7369,7 @@
         <v>580</v>
       </c>
       <c r="B581" s="1">
-        <v>860</v>
+        <v>540</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7365,7 +7377,7 @@
         <v>581</v>
       </c>
       <c r="B582" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7373,7 +7385,7 @@
         <v>582</v>
       </c>
       <c r="B583" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7381,7 +7393,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7389,7 +7401,7 @@
         <v>584</v>
       </c>
       <c r="B585" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7405,7 +7417,7 @@
         <v>586</v>
       </c>
       <c r="B587" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7413,7 +7425,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7421,7 +7433,7 @@
         <v>588</v>
       </c>
       <c r="B589" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7429,7 +7441,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7437,7 +7449,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="1">
-        <v>1020</v>
+        <v>680</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7453,7 +7465,7 @@
         <v>592</v>
       </c>
       <c r="B593" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7461,7 +7473,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="1">
-        <v>700</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7469,7 +7481,7 @@
         <v>594</v>
       </c>
       <c r="B595" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7477,7 +7489,7 @@
         <v>595</v>
       </c>
       <c r="B596" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7485,7 +7497,7 @@
         <v>596</v>
       </c>
       <c r="B597" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7501,7 +7513,7 @@
         <v>598</v>
       </c>
       <c r="B599" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7509,7 +7521,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7517,7 +7529,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7525,7 +7537,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7533,7 +7545,7 @@
         <v>602</v>
       </c>
       <c r="B603" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7541,7 +7553,7 @@
         <v>603</v>
       </c>
       <c r="B604" s="1">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7549,7 +7561,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="1">
-        <v>800</v>
+        <v>740</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7557,7 +7569,7 @@
         <v>605</v>
       </c>
       <c r="B606" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7565,7 +7577,7 @@
         <v>606</v>
       </c>
       <c r="B607" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7573,7 +7585,7 @@
         <v>607</v>
       </c>
       <c r="B608" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7581,7 +7593,7 @@
         <v>608</v>
       </c>
       <c r="B609" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7589,7 +7601,7 @@
         <v>609</v>
       </c>
       <c r="B610" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7597,7 +7609,7 @@
         <v>610</v>
       </c>
       <c r="B611" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7605,7 +7617,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7621,7 +7633,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7629,7 +7641,7 @@
         <v>614</v>
       </c>
       <c r="B615" s="1">
-        <v>640</v>
+        <v>960</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7637,7 +7649,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -7645,7 +7657,7 @@
         <v>616</v>
       </c>
       <c r="B617" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -7653,7 +7665,7 @@
         <v>617</v>
       </c>
       <c r="B618" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -7661,7 +7673,7 @@
         <v>618</v>
       </c>
       <c r="B619" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7669,7 +7681,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7677,7 +7689,7 @@
         <v>620</v>
       </c>
       <c r="B621" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -7693,7 +7705,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -7701,7 +7713,7 @@
         <v>623</v>
       </c>
       <c r="B624" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -7709,7 +7721,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -7717,7 +7729,7 @@
         <v>625</v>
       </c>
       <c r="B626" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -7725,7 +7737,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -7741,7 +7753,7 @@
         <v>628</v>
       </c>
       <c r="B629" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -7749,7 +7761,7 @@
         <v>629</v>
       </c>
       <c r="B630" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -7757,7 +7769,7 @@
         <v>630</v>
       </c>
       <c r="B631" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -7765,7 +7777,7 @@
         <v>631</v>
       </c>
       <c r="B632" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -7773,7 +7785,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -7781,7 +7793,7 @@
         <v>633</v>
       </c>
       <c r="B634" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -7789,7 +7801,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -7797,7 +7809,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -7805,7 +7817,7 @@
         <v>636</v>
       </c>
       <c r="B637" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -7813,7 +7825,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -7821,7 +7833,7 @@
         <v>638</v>
       </c>
       <c r="B639" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -7829,7 +7841,7 @@
         <v>639</v>
       </c>
       <c r="B640" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -7837,7 +7849,7 @@
         <v>640</v>
       </c>
       <c r="B641" s="1">
-        <v>900</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -7845,7 +7857,7 @@
         <v>641</v>
       </c>
       <c r="B642" s="1">
-        <v>920</v>
+        <v>820</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -7861,7 +7873,7 @@
         <v>643</v>
       </c>
       <c r="B644" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -7869,7 +7881,7 @@
         <v>644</v>
       </c>
       <c r="B645" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -7877,7 +7889,7 @@
         <v>645</v>
       </c>
       <c r="B646" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -7885,7 +7897,7 @@
         <v>646</v>
       </c>
       <c r="B647" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="648" spans="1:2">
@@ -7893,7 +7905,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -7901,7 +7913,7 @@
         <v>648</v>
       </c>
       <c r="B649" s="1">
-        <v>660</v>
+        <v>880</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -7909,7 +7921,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -7917,7 +7929,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -7925,7 +7937,7 @@
         <v>651</v>
       </c>
       <c r="B652" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -7933,7 +7945,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -7949,7 +7961,7 @@
         <v>654</v>
       </c>
       <c r="B655" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -7957,7 +7969,7 @@
         <v>655</v>
       </c>
       <c r="B656" s="1">
-        <v>800</v>
+        <v>660</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -7965,7 +7977,7 @@
         <v>656</v>
       </c>
       <c r="B657" s="1">
-        <v>720</v>
+        <v>440</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -7973,7 +7985,7 @@
         <v>657</v>
       </c>
       <c r="B658" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -7981,7 +7993,7 @@
         <v>658</v>
       </c>
       <c r="B659" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -7989,7 +8001,7 @@
         <v>659</v>
       </c>
       <c r="B660" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -7997,7 +8009,7 @@
         <v>660</v>
       </c>
       <c r="B661" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -8005,7 +8017,7 @@
         <v>661</v>
       </c>
       <c r="B662" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -8013,7 +8025,7 @@
         <v>662</v>
       </c>
       <c r="B663" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -8021,7 +8033,7 @@
         <v>663</v>
       </c>
       <c r="B664" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -8029,7 +8041,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -8037,7 +8049,7 @@
         <v>665</v>
       </c>
       <c r="B666" s="1">
-        <v>940</v>
+        <v>800</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -8045,7 +8057,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="1">
-        <v>980</v>
+        <v>780</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -8061,7 +8073,7 @@
         <v>668</v>
       </c>
       <c r="B669" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -8069,7 +8081,7 @@
         <v>669</v>
       </c>
       <c r="B670" s="1">
-        <v>860</v>
+        <v>940</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8077,7 +8089,7 @@
         <v>670</v>
       </c>
       <c r="B671" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -8085,7 +8097,7 @@
         <v>671</v>
       </c>
       <c r="B672" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -8093,7 +8105,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8101,7 +8113,7 @@
         <v>673</v>
       </c>
       <c r="B674" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -8109,7 +8121,7 @@
         <v>674</v>
       </c>
       <c r="B675" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8117,7 +8129,7 @@
         <v>675</v>
       </c>
       <c r="B676" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8125,7 +8137,7 @@
         <v>676</v>
       </c>
       <c r="B677" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8133,7 +8145,7 @@
         <v>677</v>
       </c>
       <c r="B678" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8141,7 +8153,7 @@
         <v>678</v>
       </c>
       <c r="B679" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8149,7 +8161,7 @@
         <v>679</v>
       </c>
       <c r="B680" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8157,7 +8169,7 @@
         <v>680</v>
       </c>
       <c r="B681" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8165,7 +8177,7 @@
         <v>681</v>
       </c>
       <c r="B682" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8173,7 +8185,7 @@
         <v>682</v>
       </c>
       <c r="B683" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8181,7 +8193,7 @@
         <v>683</v>
       </c>
       <c r="B684" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8197,7 +8209,7 @@
         <v>685</v>
       </c>
       <c r="B686" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8205,7 +8217,7 @@
         <v>686</v>
       </c>
       <c r="B687" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8213,7 +8225,7 @@
         <v>687</v>
       </c>
       <c r="B688" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8221,7 +8233,7 @@
         <v>688</v>
       </c>
       <c r="B689" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8229,7 +8241,7 @@
         <v>689</v>
       </c>
       <c r="B690" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8237,7 +8249,7 @@
         <v>690</v>
       </c>
       <c r="B691" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8245,7 +8257,7 @@
         <v>691</v>
       </c>
       <c r="B692" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8253,7 +8265,7 @@
         <v>692</v>
       </c>
       <c r="B693" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8261,7 +8273,7 @@
         <v>693</v>
       </c>
       <c r="B694" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8269,7 +8281,7 @@
         <v>694</v>
       </c>
       <c r="B695" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8277,7 +8289,7 @@
         <v>695</v>
       </c>
       <c r="B696" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8285,7 +8297,7 @@
         <v>696</v>
       </c>
       <c r="B697" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8293,7 +8305,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8301,7 +8313,7 @@
         <v>698</v>
       </c>
       <c r="B699" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8309,7 +8321,7 @@
         <v>699</v>
       </c>
       <c r="B700" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8317,7 +8329,7 @@
         <v>700</v>
       </c>
       <c r="B701" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8325,7 +8337,7 @@
         <v>701</v>
       </c>
       <c r="B702" s="1">
-        <v>920</v>
+        <v>600</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8333,7 +8345,7 @@
         <v>702</v>
       </c>
       <c r="B703" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8341,7 +8353,7 @@
         <v>703</v>
       </c>
       <c r="B704" s="1">
-        <v>1040</v>
+        <v>500</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8349,7 +8361,7 @@
         <v>704</v>
       </c>
       <c r="B705" s="1">
-        <v>940</v>
+        <v>760</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8357,7 +8369,7 @@
         <v>705</v>
       </c>
       <c r="B706" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8365,7 +8377,7 @@
         <v>706</v>
       </c>
       <c r="B707" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8373,7 +8385,7 @@
         <v>707</v>
       </c>
       <c r="B708" s="1">
-        <v>1100</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8381,7 +8393,7 @@
         <v>708</v>
       </c>
       <c r="B709" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8389,7 +8401,7 @@
         <v>709</v>
       </c>
       <c r="B710" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8397,7 +8409,7 @@
         <v>710</v>
       </c>
       <c r="B711" s="1">
-        <v>1100</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8405,7 +8417,7 @@
         <v>711</v>
       </c>
       <c r="B712" s="1">
-        <v>740</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8413,7 +8425,7 @@
         <v>712</v>
       </c>
       <c r="B713" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8421,7 +8433,7 @@
         <v>713</v>
       </c>
       <c r="B714" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8429,7 +8441,7 @@
         <v>714</v>
       </c>
       <c r="B715" s="1">
-        <v>500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8437,7 +8449,7 @@
         <v>715</v>
       </c>
       <c r="B716" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8445,7 +8457,7 @@
         <v>716</v>
       </c>
       <c r="B717" s="1">
-        <v>560</v>
+        <v>820</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8453,7 +8465,7 @@
         <v>717</v>
       </c>
       <c r="B718" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8461,7 +8473,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8469,7 +8481,7 @@
         <v>719</v>
       </c>
       <c r="B720" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8477,7 +8489,7 @@
         <v>720</v>
       </c>
       <c r="B721" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8485,7 +8497,7 @@
         <v>721</v>
       </c>
       <c r="B722" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8493,7 +8505,7 @@
         <v>722</v>
       </c>
       <c r="B723" s="1">
-        <v>400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8501,7 +8513,7 @@
         <v>723</v>
       </c>
       <c r="B724" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8509,7 +8521,7 @@
         <v>724</v>
       </c>
       <c r="B725" s="1">
-        <v>380</v>
+        <v>760</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8517,7 +8529,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8525,7 +8537,7 @@
         <v>726</v>
       </c>
       <c r="B727" s="1">
-        <v>520</v>
+        <v>400</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8533,7 +8545,7 @@
         <v>727</v>
       </c>
       <c r="B728" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8541,7 +8553,7 @@
         <v>728</v>
       </c>
       <c r="B729" s="1">
-        <v>860</v>
+        <v>380</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8549,7 +8561,7 @@
         <v>729</v>
       </c>
       <c r="B730" s="1">
-        <v>680</v>
+        <v>380</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8557,7 +8569,7 @@
         <v>730</v>
       </c>
       <c r="B731" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8565,7 +8577,7 @@
         <v>731</v>
       </c>
       <c r="B732" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -8573,7 +8585,7 @@
         <v>732</v>
       </c>
       <c r="B733" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -8581,7 +8593,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -8589,7 +8601,7 @@
         <v>734</v>
       </c>
       <c r="B735" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -8597,7 +8609,7 @@
         <v>735</v>
       </c>
       <c r="B736" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -8605,7 +8617,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -8613,7 +8625,7 @@
         <v>737</v>
       </c>
       <c r="B738" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="739" spans="1:2">
@@ -8621,7 +8633,7 @@
         <v>738</v>
       </c>
       <c r="B739" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -8629,7 +8641,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -8637,7 +8649,7 @@
         <v>740</v>
       </c>
       <c r="B741" s="1">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -8645,7 +8657,7 @@
         <v>741</v>
       </c>
       <c r="B742" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -8653,7 +8665,7 @@
         <v>742</v>
       </c>
       <c r="B743" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="744" spans="1:2">
@@ -8661,7 +8673,7 @@
         <v>743</v>
       </c>
       <c r="B744" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -8669,7 +8681,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -8677,7 +8689,7 @@
         <v>745</v>
       </c>
       <c r="B746" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -8685,7 +8697,7 @@
         <v>746</v>
       </c>
       <c r="B747" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -8693,7 +8705,7 @@
         <v>747</v>
       </c>
       <c r="B748" s="1">
-        <v>1100</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -8701,7 +8713,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -8709,7 +8721,7 @@
         <v>749</v>
       </c>
       <c r="B750" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="751" spans="1:2">
@@ -8717,7 +8729,7 @@
         <v>750</v>
       </c>
       <c r="B751" s="1">
-        <v>1100</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -8725,7 +8737,7 @@
         <v>751</v>
       </c>
       <c r="B752" s="1">
-        <v>740</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -8733,7 +8745,7 @@
         <v>752</v>
       </c>
       <c r="B753" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="754" spans="1:2">
@@ -8741,7 +8753,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -8749,7 +8761,7 @@
         <v>754</v>
       </c>
       <c r="B755" s="1">
-        <v>500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="756" spans="1:2">
@@ -8757,7 +8769,7 @@
         <v>755</v>
       </c>
       <c r="B756" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -8765,7 +8777,7 @@
         <v>756</v>
       </c>
       <c r="B757" s="1">
-        <v>560</v>
+        <v>820</v>
       </c>
     </row>
     <row r="758" spans="1:2">
@@ -8773,7 +8785,7 @@
         <v>757</v>
       </c>
       <c r="B758" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="759" spans="1:2">
@@ -8781,7 +8793,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -8789,7 +8801,7 @@
         <v>759</v>
       </c>
       <c r="B760" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="761" spans="1:2">
@@ -8797,7 +8809,7 @@
         <v>760</v>
       </c>
       <c r="B761" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="762" spans="1:2">
@@ -8805,7 +8817,7 @@
         <v>761</v>
       </c>
       <c r="B762" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="763" spans="1:2">
@@ -8813,7 +8825,7 @@
         <v>762</v>
       </c>
       <c r="B763" s="1">
-        <v>480</v>
+        <v>820</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -8821,7 +8833,7 @@
         <v>763</v>
       </c>
       <c r="B764" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="765" spans="1:2">
@@ -8829,7 +8841,7 @@
         <v>764</v>
       </c>
       <c r="B765" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -8837,7 +8849,7 @@
         <v>765</v>
       </c>
       <c r="B766" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -8845,7 +8857,7 @@
         <v>766</v>
       </c>
       <c r="B767" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="768" spans="1:2">
@@ -8853,7 +8865,7 @@
         <v>767</v>
       </c>
       <c r="B768" s="1">
-        <v>440</v>
+        <v>480</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -8861,7 +8873,7 @@
         <v>768</v>
       </c>
       <c r="B769" s="1">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -8869,7 +8881,7 @@
         <v>769</v>
       </c>
       <c r="B770" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="771" spans="1:2">
@@ -8877,7 +8889,7 @@
         <v>770</v>
       </c>
       <c r="B771" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="772" spans="1:2">
@@ -8885,7 +8897,7 @@
         <v>771</v>
       </c>
       <c r="B772" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -8893,7 +8905,7 @@
         <v>772</v>
       </c>
       <c r="B773" s="1">
-        <v>660</v>
+        <v>420</v>
       </c>
     </row>
     <row r="774" spans="1:2">
@@ -8901,7 +8913,7 @@
         <v>773</v>
       </c>
       <c r="B774" s="1">
-        <v>580</v>
+        <v>380</v>
       </c>
     </row>
     <row r="775" spans="1:2">
@@ -8909,7 +8921,7 @@
         <v>774</v>
       </c>
       <c r="B775" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="776" spans="1:2">
@@ -8917,7 +8929,7 @@
         <v>775</v>
       </c>
       <c r="B776" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="777" spans="1:2">
@@ -8925,7 +8937,7 @@
         <v>776</v>
       </c>
       <c r="B777" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="778" spans="1:2">
@@ -8933,7 +8945,7 @@
         <v>777</v>
       </c>
       <c r="B778" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="779" spans="1:2">
@@ -8941,6 +8953,38 @@
         <v>778</v>
       </c>
       <c r="B779" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2">
+      <c r="A780" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="B780" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2">
+      <c r="A781" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="B781" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2">
+      <c r="A782" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B782" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2">
+      <c r="A783" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="B783" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="787">
   <si>
     <t>Наименование</t>
   </si>
@@ -347,6 +347,9 @@
     <t>GAMBRINUS PREMIUM, розлив</t>
   </si>
   <si>
+    <t>Ganza - Ascension (NEIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Ganza - Sour Incident (Sour), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -668,6 +671,9 @@
     <t>Plan B  "Солнечный ветер"  (APA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Plan B  -  Delta Seeker  (AIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Plan B  -  Misty Standard  (NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1526,6 +1532,9 @@
     <t>вынос_Dieta  - Властелины Лапулина (DIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Ganza - Ascension (NEIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Ganza - Sour Incident (Sour), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1692,6 +1701,9 @@
   </si>
   <si>
     <t>вынос_Plague Brew - Saltlake (Gose), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Plan B  -  Delta Seeker  (AIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
     <t>вынос_Plan B  - Static Cloud (NEIPA), РОЗЛИВ, Россия</t>
@@ -2717,7 +2729,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B783"/>
+  <dimension ref="A1:B787"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -3601,7 +3613,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3609,7 +3621,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3617,7 +3629,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3625,7 +3637,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>420</v>
+        <v>680</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3633,7 +3645,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3641,7 +3653,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3649,7 +3661,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3657,7 +3669,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3665,7 +3677,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3673,7 +3685,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>580</v>
+        <v>740</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3681,7 +3693,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3689,7 +3701,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3697,7 +3709,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -3705,7 +3717,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -3713,7 +3725,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -3721,7 +3733,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -3729,7 +3741,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>900</v>
+        <v>960</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -3737,7 +3749,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -3745,7 +3757,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -3753,7 +3765,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -3761,7 +3773,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>500</v>
+        <v>780</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -3769,7 +3781,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>580</v>
+        <v>500</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -3777,7 +3789,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -3785,7 +3797,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -3793,7 +3805,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>1100</v>
+        <v>520</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -3801,7 +3813,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>1060</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -3809,7 +3821,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>1100</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -3825,7 +3837,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -3833,12 +3845,12 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B140" s="1">
         <v>840</v>
@@ -3849,7 +3861,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="1">
-        <v>420</v>
+        <v>840</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -3857,7 +3869,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="1">
-        <v>520</v>
+        <v>420</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -3865,7 +3877,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -3873,7 +3885,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="1">
-        <v>460</v>
+        <v>720</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -3881,7 +3893,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="1">
-        <v>560</v>
+        <v>460</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -3889,7 +3901,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -3897,7 +3909,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3905,7 +3917,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -3913,7 +3925,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -3921,7 +3933,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="1">
-        <v>980</v>
+        <v>520</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -3929,7 +3941,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="1">
-        <v>540</v>
+        <v>980</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3937,7 +3949,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3945,7 +3957,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3953,7 +3965,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -3961,7 +3973,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="1">
-        <v>560</v>
+        <v>760</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -3969,7 +3981,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -3993,7 +4005,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4001,7 +4013,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -4009,7 +4021,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -4017,7 +4029,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -4025,7 +4037,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -4049,7 +4061,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4057,7 +4069,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -4065,7 +4077,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4073,7 +4085,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4081,7 +4093,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -4089,7 +4101,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="1">
-        <v>460</v>
+        <v>700</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4097,7 +4109,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4105,7 +4117,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4113,7 +4125,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4121,7 +4133,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4129,7 +4141,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4145,7 +4157,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4161,7 +4173,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4169,7 +4181,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4177,7 +4189,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4185,7 +4197,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4193,7 +4205,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4201,7 +4213,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="1">
-        <v>740</v>
+        <v>400</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4209,7 +4221,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4217,7 +4229,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4225,7 +4237,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4233,7 +4245,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4241,7 +4253,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4249,7 +4261,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4265,7 +4277,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4273,7 +4285,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4281,7 +4293,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4297,7 +4309,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4305,7 +4317,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4313,7 +4325,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4321,7 +4333,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4329,7 +4341,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4337,7 +4349,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4345,7 +4357,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4353,7 +4365,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4361,7 +4373,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4369,7 +4381,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4377,7 +4389,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4385,7 +4397,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="1">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4393,7 +4405,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="1">
-        <v>480</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4401,7 +4413,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4409,7 +4421,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4417,7 +4429,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4425,7 +4437,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4433,7 +4445,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4441,7 +4453,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4449,7 +4461,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4457,7 +4469,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4465,7 +4477,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="1">
-        <v>660</v>
+        <v>520</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4473,7 +4485,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="1">
-        <v>620</v>
+        <v>900</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4481,7 +4493,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4497,7 +4509,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4505,7 +4517,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4513,7 +4525,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4521,7 +4533,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4529,7 +4541,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4537,7 +4549,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4545,7 +4557,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4569,7 +4581,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4585,7 +4597,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4601,7 +4613,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -4617,7 +4629,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4625,7 +4637,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4633,7 +4645,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4641,7 +4653,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="1">
-        <v>500</v>
+        <v>640</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4649,7 +4661,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="1">
-        <v>758</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4657,7 +4669,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="1">
-        <v>2273</v>
+        <v>500</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4665,7 +4677,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="1">
-        <v>1515</v>
+        <v>758</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4673,7 +4685,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="1">
-        <v>520</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4681,7 +4693,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="1">
-        <v>800</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4689,7 +4701,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="1">
-        <v>4000</v>
+        <v>520</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4697,7 +4709,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4705,7 +4717,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="1">
-        <v>480</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4713,7 +4725,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4721,7 +4733,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4729,7 +4741,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4737,7 +4749,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4745,7 +4757,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4753,7 +4765,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="1">
-        <v>520</v>
+        <v>700</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4761,7 +4773,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="1">
-        <v>680</v>
+        <v>580</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -4769,7 +4781,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4777,7 +4789,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4785,7 +4797,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4793,7 +4805,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="1">
-        <v>380</v>
+        <v>580</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4801,7 +4813,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="1">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4809,7 +4821,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="1">
-        <v>540</v>
+        <v>380</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4817,7 +4829,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="1">
-        <v>520</v>
+        <v>660</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4825,7 +4837,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="1">
-        <v>660</v>
+        <v>540</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4833,7 +4845,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4841,7 +4853,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="1">
-        <v>460</v>
+        <v>660</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4849,7 +4861,7 @@
         <v>265</v>
       </c>
       <c r="B266" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4857,7 +4869,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4865,7 +4877,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="1">
-        <v>860</v>
+        <v>520</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4873,7 +4885,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4881,7 +4893,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4897,7 +4909,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4905,7 +4917,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4913,7 +4925,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="1">
-        <v>1000</v>
+        <v>560</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4921,7 +4933,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4929,7 +4941,7 @@
         <v>275</v>
       </c>
       <c r="B276" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4937,7 +4949,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -4945,7 +4957,7 @@
         <v>277</v>
       </c>
       <c r="B278" s="1">
-        <v>1000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4953,7 +4965,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="1">
-        <v>840</v>
+        <v>680</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4969,7 +4981,7 @@
         <v>280</v>
       </c>
       <c r="B281" s="1">
-        <v>1020</v>
+        <v>840</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4985,7 +4997,7 @@
         <v>282</v>
       </c>
       <c r="B283" s="1">
-        <v>680</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -4993,7 +5005,7 @@
         <v>283</v>
       </c>
       <c r="B284" s="1">
-        <v>520</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5001,7 +5013,7 @@
         <v>284</v>
       </c>
       <c r="B285" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5009,7 +5021,7 @@
         <v>285</v>
       </c>
       <c r="B286" s="1">
-        <v>800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5017,7 +5029,7 @@
         <v>286</v>
       </c>
       <c r="B287" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5025,7 +5037,7 @@
         <v>287</v>
       </c>
       <c r="B288" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5033,7 +5045,7 @@
         <v>288</v>
       </c>
       <c r="B289" s="1">
-        <v>580</v>
+        <v>660</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5041,7 +5053,7 @@
         <v>289</v>
       </c>
       <c r="B290" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5049,7 +5061,7 @@
         <v>290</v>
       </c>
       <c r="B291" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5057,7 +5069,7 @@
         <v>291</v>
       </c>
       <c r="B292" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5065,7 +5077,7 @@
         <v>292</v>
       </c>
       <c r="B293" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5081,7 +5093,7 @@
         <v>294</v>
       </c>
       <c r="B295" s="1">
-        <v>880</v>
+        <v>640</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5089,7 +5101,7 @@
         <v>295</v>
       </c>
       <c r="B296" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5097,7 +5109,7 @@
         <v>296</v>
       </c>
       <c r="B297" s="1">
-        <v>520</v>
+        <v>880</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5105,7 +5117,7 @@
         <v>297</v>
       </c>
       <c r="B298" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5113,7 +5125,7 @@
         <v>298</v>
       </c>
       <c r="B299" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5121,7 +5133,7 @@
         <v>299</v>
       </c>
       <c r="B300" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5137,7 +5149,7 @@
         <v>301</v>
       </c>
       <c r="B302" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5145,7 +5157,7 @@
         <v>302</v>
       </c>
       <c r="B303" s="1">
-        <v>520</v>
+        <v>600</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5153,7 +5165,7 @@
         <v>303</v>
       </c>
       <c r="B304" s="1">
-        <v>320</v>
+        <v>380</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5161,7 +5173,7 @@
         <v>304</v>
       </c>
       <c r="B305" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5169,7 +5181,7 @@
         <v>305</v>
       </c>
       <c r="B306" s="1">
-        <v>560</v>
+        <v>320</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5177,7 +5189,7 @@
         <v>306</v>
       </c>
       <c r="B307" s="1">
-        <v>480</v>
+        <v>540</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5185,7 +5197,7 @@
         <v>307</v>
       </c>
       <c r="B308" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5193,7 +5205,7 @@
         <v>308</v>
       </c>
       <c r="B309" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5201,7 +5213,7 @@
         <v>309</v>
       </c>
       <c r="B310" s="1">
-        <v>500</v>
+        <v>480</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5209,7 +5221,7 @@
         <v>310</v>
       </c>
       <c r="B311" s="1">
-        <v>800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5217,7 +5229,7 @@
         <v>311</v>
       </c>
       <c r="B312" s="1">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5233,7 +5245,7 @@
         <v>313</v>
       </c>
       <c r="B314" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5241,7 +5253,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="1">
-        <v>380</v>
+        <v>800</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5249,7 +5261,7 @@
         <v>315</v>
       </c>
       <c r="B316" s="1">
-        <v>440</v>
+        <v>520</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5257,7 +5269,7 @@
         <v>316</v>
       </c>
       <c r="B317" s="1">
-        <v>900</v>
+        <v>380</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5265,7 +5277,7 @@
         <v>317</v>
       </c>
       <c r="B318" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5273,7 +5285,7 @@
         <v>318</v>
       </c>
       <c r="B319" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5281,7 +5293,7 @@
         <v>319</v>
       </c>
       <c r="B320" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5289,7 +5301,7 @@
         <v>320</v>
       </c>
       <c r="B321" s="1">
-        <v>960</v>
+        <v>780</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5297,7 +5309,7 @@
         <v>321</v>
       </c>
       <c r="B322" s="1">
-        <v>1020</v>
+        <v>720</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5305,7 +5317,7 @@
         <v>322</v>
       </c>
       <c r="B323" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5313,7 +5325,7 @@
         <v>323</v>
       </c>
       <c r="B324" s="1">
-        <v>700</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5321,7 +5333,7 @@
         <v>324</v>
       </c>
       <c r="B325" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5329,7 +5341,7 @@
         <v>325</v>
       </c>
       <c r="B326" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5337,7 +5349,7 @@
         <v>326</v>
       </c>
       <c r="B327" s="1">
-        <v>1020</v>
+        <v>640</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5353,7 +5365,7 @@
         <v>328</v>
       </c>
       <c r="B329" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5361,7 +5373,7 @@
         <v>329</v>
       </c>
       <c r="B330" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5369,7 +5381,7 @@
         <v>330</v>
       </c>
       <c r="B331" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5377,7 +5389,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5385,7 +5397,7 @@
         <v>332</v>
       </c>
       <c r="B333" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5393,7 +5405,7 @@
         <v>333</v>
       </c>
       <c r="B334" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5401,7 +5413,7 @@
         <v>334</v>
       </c>
       <c r="B335" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5417,7 +5429,7 @@
         <v>336</v>
       </c>
       <c r="B337" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5425,7 +5437,7 @@
         <v>337</v>
       </c>
       <c r="B338" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5433,7 +5445,7 @@
         <v>338</v>
       </c>
       <c r="B339" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5441,7 +5453,7 @@
         <v>339</v>
       </c>
       <c r="B340" s="1">
-        <v>480</v>
+        <v>740</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5449,7 +5461,7 @@
         <v>340</v>
       </c>
       <c r="B341" s="1">
-        <v>640</v>
+        <v>680</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5457,7 +5469,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="1">
-        <v>1000</v>
+        <v>480</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5465,7 +5477,7 @@
         <v>342</v>
       </c>
       <c r="B343" s="1">
-        <v>920</v>
+        <v>640</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5473,7 +5485,7 @@
         <v>343</v>
       </c>
       <c r="B344" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5481,7 +5493,7 @@
         <v>344</v>
       </c>
       <c r="B345" s="1">
-        <v>520</v>
+        <v>920</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5489,7 +5501,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="1">
-        <v>540</v>
+        <v>860</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5497,7 +5509,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="1">
-        <v>700</v>
+        <v>520</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5505,7 +5517,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5513,7 +5525,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="1">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5529,7 +5541,7 @@
         <v>350</v>
       </c>
       <c r="B351" s="1">
-        <v>720</v>
+        <v>420</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5537,7 +5549,7 @@
         <v>351</v>
       </c>
       <c r="B352" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5545,7 +5557,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5553,7 +5565,7 @@
         <v>353</v>
       </c>
       <c r="B354" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5561,7 +5573,7 @@
         <v>354</v>
       </c>
       <c r="B355" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5569,7 +5581,7 @@
         <v>355</v>
       </c>
       <c r="B356" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5577,7 +5589,7 @@
         <v>356</v>
       </c>
       <c r="B357" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5585,7 +5597,7 @@
         <v>357</v>
       </c>
       <c r="B358" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5593,7 +5605,7 @@
         <v>358</v>
       </c>
       <c r="B359" s="1">
-        <v>440</v>
+        <v>720</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -5601,7 +5613,7 @@
         <v>359</v>
       </c>
       <c r="B360" s="1">
-        <v>1100</v>
+        <v>620</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5609,7 +5621,7 @@
         <v>360</v>
       </c>
       <c r="B361" s="1">
-        <v>320</v>
+        <v>440</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5617,7 +5629,7 @@
         <v>361</v>
       </c>
       <c r="B362" s="1">
-        <v>320</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5625,7 +5637,7 @@
         <v>362</v>
       </c>
       <c r="B363" s="1">
-        <v>820</v>
+        <v>320</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5633,7 +5645,7 @@
         <v>363</v>
       </c>
       <c r="B364" s="1">
-        <v>1000</v>
+        <v>320</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5641,7 +5653,7 @@
         <v>364</v>
       </c>
       <c r="B365" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5649,7 +5661,7 @@
         <v>365</v>
       </c>
       <c r="B366" s="1">
-        <v>580</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5657,7 +5669,7 @@
         <v>366</v>
       </c>
       <c r="B367" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5673,7 +5685,7 @@
         <v>368</v>
       </c>
       <c r="B369" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5681,7 +5693,7 @@
         <v>369</v>
       </c>
       <c r="B370" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5689,7 +5701,7 @@
         <v>370</v>
       </c>
       <c r="B371" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5697,7 +5709,7 @@
         <v>371</v>
       </c>
       <c r="B372" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5705,7 +5717,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5713,7 +5725,7 @@
         <v>373</v>
       </c>
       <c r="B374" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5721,7 +5733,7 @@
         <v>374</v>
       </c>
       <c r="B375" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5737,7 +5749,7 @@
         <v>376</v>
       </c>
       <c r="B377" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5745,7 +5757,7 @@
         <v>377</v>
       </c>
       <c r="B378" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5753,7 +5765,7 @@
         <v>378</v>
       </c>
       <c r="B379" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5761,7 +5773,7 @@
         <v>379</v>
       </c>
       <c r="B380" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5769,7 +5781,7 @@
         <v>380</v>
       </c>
       <c r="B381" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5777,7 +5789,7 @@
         <v>381</v>
       </c>
       <c r="B382" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5785,7 +5797,7 @@
         <v>382</v>
       </c>
       <c r="B383" s="1">
-        <v>440</v>
+        <v>680</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5793,7 +5805,7 @@
         <v>383</v>
       </c>
       <c r="B384" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5801,7 +5813,7 @@
         <v>384</v>
       </c>
       <c r="B385" s="1">
-        <v>900</v>
+        <v>440</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5809,7 +5821,7 @@
         <v>385</v>
       </c>
       <c r="B386" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5817,7 +5829,7 @@
         <v>386</v>
       </c>
       <c r="B387" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5825,7 +5837,7 @@
         <v>387</v>
       </c>
       <c r="B388" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5833,7 +5845,7 @@
         <v>388</v>
       </c>
       <c r="B389" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5841,7 +5853,7 @@
         <v>389</v>
       </c>
       <c r="B390" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5849,7 +5861,7 @@
         <v>390</v>
       </c>
       <c r="B391" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5857,7 +5869,7 @@
         <v>391</v>
       </c>
       <c r="B392" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5865,7 +5877,7 @@
         <v>392</v>
       </c>
       <c r="B393" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5873,7 +5885,7 @@
         <v>393</v>
       </c>
       <c r="B394" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5881,7 +5893,7 @@
         <v>394</v>
       </c>
       <c r="B395" s="1">
-        <v>680</v>
+        <v>620</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5889,7 +5901,7 @@
         <v>395</v>
       </c>
       <c r="B396" s="1">
-        <v>480</v>
+        <v>720</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5897,7 +5909,7 @@
         <v>396</v>
       </c>
       <c r="B397" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5905,7 +5917,7 @@
         <v>397</v>
       </c>
       <c r="B398" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5913,7 +5925,7 @@
         <v>398</v>
       </c>
       <c r="B399" s="1">
-        <v>880</v>
+        <v>480</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5929,7 +5941,7 @@
         <v>400</v>
       </c>
       <c r="B401" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5937,7 +5949,7 @@
         <v>401</v>
       </c>
       <c r="B402" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5945,7 +5957,7 @@
         <v>402</v>
       </c>
       <c r="B403" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5953,7 +5965,7 @@
         <v>403</v>
       </c>
       <c r="B404" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5961,7 +5973,7 @@
         <v>404</v>
       </c>
       <c r="B405" s="1">
-        <v>940</v>
+        <v>740</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5969,7 +5981,7 @@
         <v>405</v>
       </c>
       <c r="B406" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5977,7 +5989,7 @@
         <v>406</v>
       </c>
       <c r="B407" s="1">
-        <v>920</v>
+        <v>940</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5985,7 +5997,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="1">
-        <v>600</v>
+        <v>980</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -5993,7 +6005,7 @@
         <v>408</v>
       </c>
       <c r="B409" s="1">
-        <v>760</v>
+        <v>920</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -6001,7 +6013,7 @@
         <v>409</v>
       </c>
       <c r="B410" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -6009,7 +6021,7 @@
         <v>410</v>
       </c>
       <c r="B411" s="1">
-        <v>620</v>
+        <v>760</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -6017,7 +6029,7 @@
         <v>411</v>
       </c>
       <c r="B412" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -6025,7 +6037,7 @@
         <v>412</v>
       </c>
       <c r="B413" s="1">
-        <v>860</v>
+        <v>620</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -6033,7 +6045,7 @@
         <v>413</v>
       </c>
       <c r="B414" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -6041,7 +6053,7 @@
         <v>414</v>
       </c>
       <c r="B415" s="1">
-        <v>640</v>
+        <v>860</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -6049,7 +6061,7 @@
         <v>415</v>
       </c>
       <c r="B416" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -6057,7 +6069,7 @@
         <v>416</v>
       </c>
       <c r="B417" s="1">
-        <v>820</v>
+        <v>640</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -6065,7 +6077,7 @@
         <v>417</v>
       </c>
       <c r="B418" s="1">
-        <v>960</v>
+        <v>680</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -6073,7 +6085,7 @@
         <v>418</v>
       </c>
       <c r="B419" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -6081,7 +6093,7 @@
         <v>419</v>
       </c>
       <c r="B420" s="1">
-        <v>1000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -6089,7 +6101,7 @@
         <v>420</v>
       </c>
       <c r="B421" s="1">
-        <v>640</v>
+        <v>740</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -6097,7 +6109,7 @@
         <v>421</v>
       </c>
       <c r="B422" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -6105,7 +6117,7 @@
         <v>422</v>
       </c>
       <c r="B423" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -6113,7 +6125,7 @@
         <v>423</v>
       </c>
       <c r="B424" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6121,7 +6133,7 @@
         <v>424</v>
       </c>
       <c r="B425" s="1">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6129,7 +6141,7 @@
         <v>425</v>
       </c>
       <c r="B426" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6137,7 +6149,7 @@
         <v>426</v>
       </c>
       <c r="B427" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6145,7 +6157,7 @@
         <v>427</v>
       </c>
       <c r="B428" s="1">
-        <v>840</v>
+        <v>640</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6153,7 +6165,7 @@
         <v>428</v>
       </c>
       <c r="B429" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6161,7 +6173,7 @@
         <v>429</v>
       </c>
       <c r="B430" s="1">
-        <v>480</v>
+        <v>840</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6169,7 +6181,7 @@
         <v>430</v>
       </c>
       <c r="B431" s="1">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6177,7 +6189,7 @@
         <v>431</v>
       </c>
       <c r="B432" s="1">
-        <v>780</v>
+        <v>480</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6185,7 +6197,7 @@
         <v>432</v>
       </c>
       <c r="B433" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6193,7 +6205,7 @@
         <v>433</v>
       </c>
       <c r="B434" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6201,7 +6213,7 @@
         <v>434</v>
       </c>
       <c r="B435" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6209,7 +6221,7 @@
         <v>435</v>
       </c>
       <c r="B436" s="1">
-        <v>740</v>
+        <v>820</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6217,7 +6229,7 @@
         <v>436</v>
       </c>
       <c r="B437" s="1">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6225,7 +6237,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6233,7 +6245,7 @@
         <v>438</v>
       </c>
       <c r="B439" s="1">
-        <v>480</v>
+        <v>780</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6241,7 +6253,7 @@
         <v>439</v>
       </c>
       <c r="B440" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6249,7 +6261,7 @@
         <v>440</v>
       </c>
       <c r="B441" s="1">
-        <v>660</v>
+        <v>480</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6257,7 +6269,7 @@
         <v>441</v>
       </c>
       <c r="B442" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6265,7 +6277,7 @@
         <v>442</v>
       </c>
       <c r="B443" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6273,7 +6285,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="1">
-        <v>440</v>
+        <v>700</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6281,7 +6293,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="1">
-        <v>740</v>
+        <v>440</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6289,7 +6301,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="1">
-        <v>880</v>
+        <v>440</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6297,7 +6309,7 @@
         <v>446</v>
       </c>
       <c r="B447" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6305,7 +6317,7 @@
         <v>447</v>
       </c>
       <c r="B448" s="1">
-        <v>760</v>
+        <v>880</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6313,7 +6325,7 @@
         <v>448</v>
       </c>
       <c r="B449" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6321,7 +6333,7 @@
         <v>449</v>
       </c>
       <c r="B450" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6329,7 +6341,7 @@
         <v>450</v>
       </c>
       <c r="B451" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6337,7 +6349,7 @@
         <v>451</v>
       </c>
       <c r="B452" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6345,7 +6357,7 @@
         <v>452</v>
       </c>
       <c r="B453" s="1">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6353,7 +6365,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6361,7 +6373,7 @@
         <v>454</v>
       </c>
       <c r="B455" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6369,7 +6381,7 @@
         <v>455</v>
       </c>
       <c r="B456" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6377,7 +6389,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6385,7 +6397,7 @@
         <v>457</v>
       </c>
       <c r="B458" s="1">
-        <v>840</v>
+        <v>660</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6393,7 +6405,7 @@
         <v>458</v>
       </c>
       <c r="B459" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6401,7 +6413,7 @@
         <v>459</v>
       </c>
       <c r="B460" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6409,7 +6421,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6417,7 +6429,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6425,7 +6437,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6433,7 +6445,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="1">
-        <v>600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6441,7 +6453,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6449,7 +6461,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="1">
-        <v>660</v>
+        <v>600</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6457,7 +6469,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6465,7 +6477,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6473,7 +6485,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6481,7 +6493,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="1">
-        <v>880</v>
+        <v>620</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6489,7 +6501,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="1">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6497,7 +6509,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="1">
-        <v>800</v>
+        <v>880</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6513,7 +6525,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6521,7 +6533,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6529,7 +6541,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6537,7 +6549,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6545,7 +6557,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6553,7 +6565,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="1">
-        <v>780</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6561,7 +6573,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6569,7 +6581,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6577,7 +6589,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6585,7 +6597,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6593,7 +6605,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="1">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6601,7 +6613,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6609,7 +6621,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6633,7 +6645,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="1">
-        <v>920</v>
+        <v>820</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6641,7 +6653,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="1">
-        <v>600</v>
+        <v>760</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6649,7 +6661,7 @@
         <v>490</v>
       </c>
       <c r="B491" s="1">
-        <v>880</v>
+        <v>920</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6657,7 +6669,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="1">
-        <v>640</v>
+        <v>600</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6665,7 +6677,7 @@
         <v>492</v>
       </c>
       <c r="B493" s="1">
-        <v>700</v>
+        <v>880</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6673,7 +6685,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6681,7 +6693,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="1">
-        <v>560</v>
+        <v>700</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -6689,7 +6701,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6697,7 +6709,7 @@
         <v>496</v>
       </c>
       <c r="B497" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6705,7 +6717,7 @@
         <v>497</v>
       </c>
       <c r="B498" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6713,7 +6725,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6721,7 +6733,7 @@
         <v>499</v>
       </c>
       <c r="B500" s="1">
-        <v>960</v>
+        <v>840</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6729,7 +6741,7 @@
         <v>500</v>
       </c>
       <c r="B501" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6737,7 +6749,7 @@
         <v>501</v>
       </c>
       <c r="B502" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6745,7 +6757,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6753,7 +6765,7 @@
         <v>503</v>
       </c>
       <c r="B504" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6761,7 +6773,7 @@
         <v>504</v>
       </c>
       <c r="B505" s="1">
-        <v>920</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6769,7 +6781,7 @@
         <v>505</v>
       </c>
       <c r="B506" s="1">
-        <v>680</v>
+        <v>940</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6777,7 +6789,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6785,7 +6797,7 @@
         <v>507</v>
       </c>
       <c r="B508" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6793,7 +6805,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="1">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6801,7 +6813,7 @@
         <v>509</v>
       </c>
       <c r="B510" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6809,7 +6821,7 @@
         <v>510</v>
       </c>
       <c r="B511" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6817,7 +6829,7 @@
         <v>511</v>
       </c>
       <c r="B512" s="1">
-        <v>700</v>
+        <v>620</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6825,7 +6837,7 @@
         <v>512</v>
       </c>
       <c r="B513" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6833,7 +6845,7 @@
         <v>513</v>
       </c>
       <c r="B514" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6841,7 +6853,7 @@
         <v>514</v>
       </c>
       <c r="B515" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6849,7 +6861,7 @@
         <v>515</v>
       </c>
       <c r="B516" s="1">
-        <v>720</v>
+        <v>960</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6857,7 +6869,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6865,7 +6877,7 @@
         <v>517</v>
       </c>
       <c r="B518" s="1">
-        <v>540</v>
+        <v>600</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6873,7 +6885,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6881,7 +6893,7 @@
         <v>519</v>
       </c>
       <c r="B520" s="1">
-        <v>1060</v>
+        <v>780</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6889,7 +6901,7 @@
         <v>520</v>
       </c>
       <c r="B521" s="1">
-        <v>1100</v>
+        <v>540</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6905,7 +6917,7 @@
         <v>522</v>
       </c>
       <c r="B523" s="1">
-        <v>840</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6913,7 +6925,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6921,7 +6933,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6929,7 +6941,7 @@
         <v>525</v>
       </c>
       <c r="B526" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6937,7 +6949,7 @@
         <v>526</v>
       </c>
       <c r="B527" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6945,7 +6957,7 @@
         <v>527</v>
       </c>
       <c r="B528" s="1">
-        <v>860</v>
+        <v>560</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6953,7 +6965,7 @@
         <v>528</v>
       </c>
       <c r="B529" s="1">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6961,7 +6973,7 @@
         <v>529</v>
       </c>
       <c r="B530" s="1">
-        <v>740</v>
+        <v>620</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6969,7 +6981,7 @@
         <v>530</v>
       </c>
       <c r="B531" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6977,7 +6989,7 @@
         <v>531</v>
       </c>
       <c r="B532" s="1">
-        <v>1100</v>
+        <v>980</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6985,7 +6997,7 @@
         <v>532</v>
       </c>
       <c r="B533" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -6993,7 +7005,7 @@
         <v>533</v>
       </c>
       <c r="B534" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -7001,7 +7013,7 @@
         <v>534</v>
       </c>
       <c r="B535" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -7009,7 +7021,7 @@
         <v>535</v>
       </c>
       <c r="B536" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -7017,7 +7029,7 @@
         <v>536</v>
       </c>
       <c r="B537" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -7025,7 +7037,7 @@
         <v>537</v>
       </c>
       <c r="B538" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -7033,7 +7045,7 @@
         <v>538</v>
       </c>
       <c r="B539" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -7041,7 +7053,7 @@
         <v>539</v>
       </c>
       <c r="B540" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -7049,7 +7061,7 @@
         <v>540</v>
       </c>
       <c r="B541" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -7057,7 +7069,7 @@
         <v>541</v>
       </c>
       <c r="B542" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -7065,7 +7077,7 @@
         <v>542</v>
       </c>
       <c r="B543" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -7081,7 +7093,7 @@
         <v>544</v>
       </c>
       <c r="B545" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -7089,7 +7101,7 @@
         <v>545</v>
       </c>
       <c r="B546" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -7097,7 +7109,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -7105,7 +7117,7 @@
         <v>547</v>
       </c>
       <c r="B548" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -7113,7 +7125,7 @@
         <v>548</v>
       </c>
       <c r="B549" s="1">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7121,7 +7133,7 @@
         <v>549</v>
       </c>
       <c r="B550" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7129,7 +7141,7 @@
         <v>550</v>
       </c>
       <c r="B551" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7137,7 +7149,7 @@
         <v>551</v>
       </c>
       <c r="B552" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7145,7 +7157,7 @@
         <v>552</v>
       </c>
       <c r="B553" s="1">
-        <v>1400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7153,7 +7165,7 @@
         <v>553</v>
       </c>
       <c r="B554" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7161,7 +7173,7 @@
         <v>554</v>
       </c>
       <c r="B555" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7169,7 +7181,7 @@
         <v>555</v>
       </c>
       <c r="B556" s="1">
-        <v>700</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7177,7 +7189,7 @@
         <v>556</v>
       </c>
       <c r="B557" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7185,7 +7197,7 @@
         <v>557</v>
       </c>
       <c r="B558" s="1">
-        <v>720</v>
+        <v>660</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7193,7 +7205,7 @@
         <v>558</v>
       </c>
       <c r="B559" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7201,7 +7213,7 @@
         <v>559</v>
       </c>
       <c r="B560" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7209,7 +7221,7 @@
         <v>560</v>
       </c>
       <c r="B561" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7225,7 +7237,7 @@
         <v>562</v>
       </c>
       <c r="B563" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7233,7 +7245,7 @@
         <v>563</v>
       </c>
       <c r="B564" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7241,7 +7253,7 @@
         <v>564</v>
       </c>
       <c r="B565" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7257,7 +7269,7 @@
         <v>566</v>
       </c>
       <c r="B567" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7273,7 +7285,7 @@
         <v>568</v>
       </c>
       <c r="B569" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7281,7 +7293,7 @@
         <v>569</v>
       </c>
       <c r="B570" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7289,7 +7301,7 @@
         <v>570</v>
       </c>
       <c r="B571" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7297,7 +7309,7 @@
         <v>571</v>
       </c>
       <c r="B572" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7305,7 +7317,7 @@
         <v>572</v>
       </c>
       <c r="B573" s="1">
-        <v>4000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7313,7 +7325,7 @@
         <v>573</v>
       </c>
       <c r="B574" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7321,7 +7333,7 @@
         <v>574</v>
       </c>
       <c r="B575" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7329,7 +7341,7 @@
         <v>575</v>
       </c>
       <c r="B576" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7337,7 +7349,7 @@
         <v>576</v>
       </c>
       <c r="B577" s="1">
-        <v>700</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7345,7 +7357,7 @@
         <v>577</v>
       </c>
       <c r="B578" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7353,7 +7365,7 @@
         <v>578</v>
       </c>
       <c r="B579" s="1">
-        <v>640</v>
+        <v>720</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7369,7 +7381,7 @@
         <v>580</v>
       </c>
       <c r="B581" s="1">
-        <v>540</v>
+        <v>700</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7377,7 +7389,7 @@
         <v>581</v>
       </c>
       <c r="B582" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7385,7 +7397,7 @@
         <v>582</v>
       </c>
       <c r="B583" s="1">
-        <v>580</v>
+        <v>640</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7393,7 +7405,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7401,7 +7413,7 @@
         <v>584</v>
       </c>
       <c r="B585" s="1">
-        <v>900</v>
+        <v>540</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7409,7 +7421,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7417,7 +7429,7 @@
         <v>586</v>
       </c>
       <c r="B587" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7425,7 +7437,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7441,7 +7453,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7449,7 +7461,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7465,7 +7477,7 @@
         <v>592</v>
       </c>
       <c r="B593" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7473,7 +7485,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="1">
-        <v>1020</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7481,7 +7493,7 @@
         <v>594</v>
       </c>
       <c r="B595" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7489,7 +7501,7 @@
         <v>595</v>
       </c>
       <c r="B596" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7497,7 +7509,7 @@
         <v>596</v>
       </c>
       <c r="B597" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7505,7 +7517,7 @@
         <v>597</v>
       </c>
       <c r="B598" s="1">
-        <v>640</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7513,7 +7525,7 @@
         <v>598</v>
       </c>
       <c r="B599" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7521,7 +7533,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7529,7 +7541,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7537,7 +7549,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7545,7 +7557,7 @@
         <v>602</v>
       </c>
       <c r="B603" s="1">
-        <v>880</v>
+        <v>740</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7553,7 +7565,7 @@
         <v>603</v>
       </c>
       <c r="B604" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7561,7 +7573,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7569,7 +7581,7 @@
         <v>605</v>
       </c>
       <c r="B606" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7577,7 +7589,7 @@
         <v>606</v>
       </c>
       <c r="B607" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7585,7 +7597,7 @@
         <v>607</v>
       </c>
       <c r="B608" s="1">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7593,7 +7605,7 @@
         <v>608</v>
       </c>
       <c r="B609" s="1">
-        <v>800</v>
+        <v>740</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7601,7 +7613,7 @@
         <v>609</v>
       </c>
       <c r="B610" s="1">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7609,7 +7621,7 @@
         <v>610</v>
       </c>
       <c r="B611" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7617,7 +7629,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7625,7 +7637,7 @@
         <v>612</v>
       </c>
       <c r="B613" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7633,7 +7645,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7641,7 +7653,7 @@
         <v>614</v>
       </c>
       <c r="B615" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7649,7 +7661,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -7665,7 +7677,7 @@
         <v>617</v>
       </c>
       <c r="B618" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -7673,7 +7685,7 @@
         <v>618</v>
       </c>
       <c r="B619" s="1">
-        <v>640</v>
+        <v>960</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7681,7 +7693,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7689,7 +7701,7 @@
         <v>620</v>
       </c>
       <c r="B621" s="1">
-        <v>1020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -7697,7 +7709,7 @@
         <v>621</v>
       </c>
       <c r="B622" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -7705,7 +7717,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -7713,7 +7725,7 @@
         <v>623</v>
       </c>
       <c r="B624" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="625" spans="1:2">
@@ -7721,7 +7733,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -7737,7 +7749,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -7745,7 +7757,7 @@
         <v>627</v>
       </c>
       <c r="B628" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -7753,7 +7765,7 @@
         <v>628</v>
       </c>
       <c r="B629" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -7761,7 +7773,7 @@
         <v>629</v>
       </c>
       <c r="B630" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -7769,7 +7781,7 @@
         <v>630</v>
       </c>
       <c r="B631" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -7785,7 +7797,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -7793,7 +7805,7 @@
         <v>633</v>
       </c>
       <c r="B634" s="1">
-        <v>920</v>
+        <v>680</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -7801,7 +7813,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -7809,7 +7821,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -7817,7 +7829,7 @@
         <v>636</v>
       </c>
       <c r="B637" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="638" spans="1:2">
@@ -7825,7 +7837,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -7833,7 +7845,7 @@
         <v>638</v>
       </c>
       <c r="B639" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -7841,7 +7853,7 @@
         <v>639</v>
       </c>
       <c r="B640" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -7849,7 +7861,7 @@
         <v>640</v>
       </c>
       <c r="B641" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -7857,7 +7869,7 @@
         <v>641</v>
       </c>
       <c r="B642" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -7865,7 +7877,7 @@
         <v>642</v>
       </c>
       <c r="B643" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -7873,7 +7885,7 @@
         <v>643</v>
       </c>
       <c r="B644" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -7881,7 +7893,7 @@
         <v>644</v>
       </c>
       <c r="B645" s="1">
-        <v>900</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -7889,7 +7901,7 @@
         <v>645</v>
       </c>
       <c r="B646" s="1">
-        <v>920</v>
+        <v>820</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -7905,7 +7917,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -7913,7 +7925,7 @@
         <v>648</v>
       </c>
       <c r="B649" s="1">
-        <v>880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -7921,7 +7933,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -7929,7 +7941,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="1">
-        <v>780</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -7937,7 +7949,7 @@
         <v>651</v>
       </c>
       <c r="B652" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -7945,7 +7957,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="1">
-        <v>660</v>
+        <v>880</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -7953,7 +7965,7 @@
         <v>653</v>
       </c>
       <c r="B654" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -7961,7 +7973,7 @@
         <v>654</v>
       </c>
       <c r="B655" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -7969,7 +7981,7 @@
         <v>655</v>
       </c>
       <c r="B656" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -7977,7 +7989,7 @@
         <v>656</v>
       </c>
       <c r="B657" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -7993,7 +8005,7 @@
         <v>658</v>
       </c>
       <c r="B659" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -8001,7 +8013,7 @@
         <v>659</v>
       </c>
       <c r="B660" s="1">
-        <v>800</v>
+        <v>660</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -8009,7 +8021,7 @@
         <v>660</v>
       </c>
       <c r="B661" s="1">
-        <v>720</v>
+        <v>440</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -8017,7 +8029,7 @@
         <v>661</v>
       </c>
       <c r="B662" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -8025,7 +8037,7 @@
         <v>662</v>
       </c>
       <c r="B663" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -8033,7 +8045,7 @@
         <v>663</v>
       </c>
       <c r="B664" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -8041,7 +8053,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="1">
-        <v>880</v>
+        <v>720</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -8049,7 +8061,7 @@
         <v>665</v>
       </c>
       <c r="B666" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -8057,7 +8069,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -8065,7 +8077,7 @@
         <v>667</v>
       </c>
       <c r="B668" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -8073,7 +8085,7 @@
         <v>668</v>
       </c>
       <c r="B669" s="1">
-        <v>740</v>
+        <v>880</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -8081,7 +8093,7 @@
         <v>669</v>
       </c>
       <c r="B670" s="1">
-        <v>940</v>
+        <v>800</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8089,7 +8101,7 @@
         <v>670</v>
       </c>
       <c r="B671" s="1">
-        <v>980</v>
+        <v>780</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -8105,7 +8117,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8113,7 +8125,7 @@
         <v>673</v>
       </c>
       <c r="B674" s="1">
-        <v>860</v>
+        <v>940</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -8121,7 +8133,7 @@
         <v>674</v>
       </c>
       <c r="B675" s="1">
-        <v>920</v>
+        <v>980</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8129,7 +8141,7 @@
         <v>675</v>
       </c>
       <c r="B676" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8137,7 +8149,7 @@
         <v>676</v>
       </c>
       <c r="B677" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8145,7 +8157,7 @@
         <v>677</v>
       </c>
       <c r="B678" s="1">
-        <v>960</v>
+        <v>860</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8153,7 +8165,7 @@
         <v>678</v>
       </c>
       <c r="B679" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8161,7 +8173,7 @@
         <v>679</v>
       </c>
       <c r="B680" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8169,7 +8181,7 @@
         <v>680</v>
       </c>
       <c r="B681" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8177,7 +8189,7 @@
         <v>681</v>
       </c>
       <c r="B682" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8185,7 +8197,7 @@
         <v>682</v>
       </c>
       <c r="B683" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="684" spans="1:2">
@@ -8193,7 +8205,7 @@
         <v>683</v>
       </c>
       <c r="B684" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8201,7 +8213,7 @@
         <v>684</v>
       </c>
       <c r="B685" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8209,7 +8221,7 @@
         <v>685</v>
       </c>
       <c r="B686" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8217,7 +8229,7 @@
         <v>686</v>
       </c>
       <c r="B687" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8225,7 +8237,7 @@
         <v>687</v>
       </c>
       <c r="B688" s="1">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8241,7 +8253,7 @@
         <v>689</v>
       </c>
       <c r="B690" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8249,7 +8261,7 @@
         <v>690</v>
       </c>
       <c r="B691" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8257,7 +8269,7 @@
         <v>691</v>
       </c>
       <c r="B692" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8265,7 +8277,7 @@
         <v>692</v>
       </c>
       <c r="B693" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8273,7 +8285,7 @@
         <v>693</v>
       </c>
       <c r="B694" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8281,7 +8293,7 @@
         <v>694</v>
       </c>
       <c r="B695" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8289,7 +8301,7 @@
         <v>695</v>
       </c>
       <c r="B696" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8297,7 +8309,7 @@
         <v>696</v>
       </c>
       <c r="B697" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8305,7 +8317,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8313,7 +8325,7 @@
         <v>698</v>
       </c>
       <c r="B699" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8321,7 +8333,7 @@
         <v>699</v>
       </c>
       <c r="B700" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8329,7 +8341,7 @@
         <v>700</v>
       </c>
       <c r="B701" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8337,7 +8349,7 @@
         <v>701</v>
       </c>
       <c r="B702" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="703" spans="1:2">
@@ -8345,7 +8357,7 @@
         <v>702</v>
       </c>
       <c r="B703" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="704" spans="1:2">
@@ -8353,7 +8365,7 @@
         <v>703</v>
       </c>
       <c r="B704" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8361,7 +8373,7 @@
         <v>704</v>
       </c>
       <c r="B705" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8369,7 +8381,7 @@
         <v>705</v>
       </c>
       <c r="B706" s="1">
-        <v>920</v>
+        <v>600</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8377,7 +8389,7 @@
         <v>706</v>
       </c>
       <c r="B707" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8385,7 +8397,7 @@
         <v>707</v>
       </c>
       <c r="B708" s="1">
-        <v>1040</v>
+        <v>500</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8393,7 +8405,7 @@
         <v>708</v>
       </c>
       <c r="B709" s="1">
-        <v>940</v>
+        <v>760</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8401,7 +8413,7 @@
         <v>709</v>
       </c>
       <c r="B710" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8409,7 +8421,7 @@
         <v>710</v>
       </c>
       <c r="B711" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8417,7 +8429,7 @@
         <v>711</v>
       </c>
       <c r="B712" s="1">
-        <v>1100</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8425,7 +8437,7 @@
         <v>712</v>
       </c>
       <c r="B713" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8433,7 +8445,7 @@
         <v>713</v>
       </c>
       <c r="B714" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8441,7 +8453,7 @@
         <v>714</v>
       </c>
       <c r="B715" s="1">
-        <v>1100</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8449,7 +8461,7 @@
         <v>715</v>
       </c>
       <c r="B716" s="1">
-        <v>740</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8457,7 +8469,7 @@
         <v>716</v>
       </c>
       <c r="B717" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8465,7 +8477,7 @@
         <v>717</v>
       </c>
       <c r="B718" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8473,7 +8485,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="1">
-        <v>500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8481,7 +8493,7 @@
         <v>719</v>
       </c>
       <c r="B720" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8489,7 +8501,7 @@
         <v>720</v>
       </c>
       <c r="B721" s="1">
-        <v>560</v>
+        <v>820</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8497,7 +8509,7 @@
         <v>721</v>
       </c>
       <c r="B722" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8505,7 +8517,7 @@
         <v>722</v>
       </c>
       <c r="B723" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8513,7 +8525,7 @@
         <v>723</v>
       </c>
       <c r="B724" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8521,7 +8533,7 @@
         <v>724</v>
       </c>
       <c r="B725" s="1">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8529,7 +8541,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8537,7 +8549,7 @@
         <v>726</v>
       </c>
       <c r="B727" s="1">
-        <v>400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8545,7 +8557,7 @@
         <v>727</v>
       </c>
       <c r="B728" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8553,7 +8565,7 @@
         <v>728</v>
       </c>
       <c r="B729" s="1">
-        <v>380</v>
+        <v>760</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8561,7 +8573,7 @@
         <v>729</v>
       </c>
       <c r="B730" s="1">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8569,7 +8581,7 @@
         <v>730</v>
       </c>
       <c r="B731" s="1">
-        <v>520</v>
+        <v>400</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8577,7 +8589,7 @@
         <v>731</v>
       </c>
       <c r="B732" s="1">
-        <v>700</v>
+        <v>380</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -8585,7 +8597,7 @@
         <v>732</v>
       </c>
       <c r="B733" s="1">
-        <v>860</v>
+        <v>380</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -8593,7 +8605,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="1">
-        <v>680</v>
+        <v>380</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -8601,7 +8613,7 @@
         <v>734</v>
       </c>
       <c r="B735" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -8609,7 +8621,7 @@
         <v>735</v>
       </c>
       <c r="B736" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -8617,7 +8629,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -8625,7 +8637,7 @@
         <v>737</v>
       </c>
       <c r="B738" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="739" spans="1:2">
@@ -8633,7 +8645,7 @@
         <v>738</v>
       </c>
       <c r="B739" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -8641,7 +8653,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -8649,7 +8661,7 @@
         <v>740</v>
       </c>
       <c r="B741" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -8657,7 +8669,7 @@
         <v>741</v>
       </c>
       <c r="B742" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -8665,7 +8677,7 @@
         <v>742</v>
       </c>
       <c r="B743" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="744" spans="1:2">
@@ -8673,7 +8685,7 @@
         <v>743</v>
       </c>
       <c r="B744" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -8681,7 +8693,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="1">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -8689,7 +8701,7 @@
         <v>745</v>
       </c>
       <c r="B746" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -8697,7 +8709,7 @@
         <v>746</v>
       </c>
       <c r="B747" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -8705,7 +8717,7 @@
         <v>747</v>
       </c>
       <c r="B748" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -8713,7 +8725,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="1">
-        <v>940</v>
+        <v>900</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -8721,7 +8733,7 @@
         <v>749</v>
       </c>
       <c r="B750" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="751" spans="1:2">
@@ -8729,7 +8741,7 @@
         <v>750</v>
       </c>
       <c r="B751" s="1">
-        <v>1040</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -8737,7 +8749,7 @@
         <v>751</v>
       </c>
       <c r="B752" s="1">
-        <v>1100</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -8745,7 +8757,7 @@
         <v>752</v>
       </c>
       <c r="B753" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="754" spans="1:2">
@@ -8753,7 +8765,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -8761,7 +8773,7 @@
         <v>754</v>
       </c>
       <c r="B755" s="1">
-        <v>1100</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="756" spans="1:2">
@@ -8769,7 +8781,7 @@
         <v>755</v>
       </c>
       <c r="B756" s="1">
-        <v>740</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -8777,7 +8789,7 @@
         <v>756</v>
       </c>
       <c r="B757" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="758" spans="1:2">
@@ -8785,7 +8797,7 @@
         <v>757</v>
       </c>
       <c r="B758" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="759" spans="1:2">
@@ -8793,7 +8805,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="1">
-        <v>500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -8801,7 +8813,7 @@
         <v>759</v>
       </c>
       <c r="B760" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="761" spans="1:2">
@@ -8809,7 +8821,7 @@
         <v>760</v>
       </c>
       <c r="B761" s="1">
-        <v>560</v>
+        <v>820</v>
       </c>
     </row>
     <row r="762" spans="1:2">
@@ -8817,7 +8829,7 @@
         <v>761</v>
       </c>
       <c r="B762" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="763" spans="1:2">
@@ -8825,7 +8837,7 @@
         <v>762</v>
       </c>
       <c r="B763" s="1">
-        <v>820</v>
+        <v>500</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -8833,7 +8845,7 @@
         <v>763</v>
       </c>
       <c r="B764" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="765" spans="1:2">
@@ -8841,7 +8853,7 @@
         <v>764</v>
       </c>
       <c r="B765" s="1">
-        <v>380</v>
+        <v>560</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -8849,7 +8861,7 @@
         <v>765</v>
       </c>
       <c r="B766" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -8857,7 +8869,7 @@
         <v>766</v>
       </c>
       <c r="B767" s="1">
-        <v>480</v>
+        <v>820</v>
       </c>
     </row>
     <row r="768" spans="1:2">
@@ -8865,7 +8877,7 @@
         <v>767</v>
       </c>
       <c r="B768" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -8873,7 +8885,7 @@
         <v>768</v>
       </c>
       <c r="B769" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -8881,7 +8893,7 @@
         <v>769</v>
       </c>
       <c r="B770" s="1">
-        <v>520</v>
+        <v>380</v>
       </c>
     </row>
     <row r="771" spans="1:2">
@@ -8889,7 +8901,7 @@
         <v>770</v>
       </c>
       <c r="B771" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="772" spans="1:2">
@@ -8897,7 +8909,7 @@
         <v>771</v>
       </c>
       <c r="B772" s="1">
-        <v>440</v>
+        <v>480</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -8905,7 +8917,7 @@
         <v>772</v>
       </c>
       <c r="B773" s="1">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row r="774" spans="1:2">
@@ -8913,7 +8925,7 @@
         <v>773</v>
       </c>
       <c r="B774" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="775" spans="1:2">
@@ -8921,7 +8933,7 @@
         <v>774</v>
       </c>
       <c r="B775" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="776" spans="1:2">
@@ -8929,7 +8941,7 @@
         <v>775</v>
       </c>
       <c r="B776" s="1">
-        <v>820</v>
+        <v>440</v>
       </c>
     </row>
     <row r="777" spans="1:2">
@@ -8937,7 +8949,7 @@
         <v>776</v>
       </c>
       <c r="B777" s="1">
-        <v>660</v>
+        <v>420</v>
       </c>
     </row>
     <row r="778" spans="1:2">
@@ -8945,7 +8957,7 @@
         <v>777</v>
       </c>
       <c r="B778" s="1">
-        <v>580</v>
+        <v>380</v>
       </c>
     </row>
     <row r="779" spans="1:2">
@@ -8953,7 +8965,7 @@
         <v>778</v>
       </c>
       <c r="B779" s="1">
-        <v>560</v>
+        <v>600</v>
       </c>
     </row>
     <row r="780" spans="1:2">
@@ -8961,7 +8973,7 @@
         <v>779</v>
       </c>
       <c r="B780" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="781" spans="1:2">
@@ -8969,7 +8981,7 @@
         <v>780</v>
       </c>
       <c r="B781" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="782" spans="1:2">
@@ -8977,7 +8989,7 @@
         <v>781</v>
       </c>
       <c r="B782" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="783" spans="1:2">
@@ -8985,6 +8997,38 @@
         <v>782</v>
       </c>
       <c r="B783" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2">
+      <c r="A784" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="B784" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2">
+      <c r="A785" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B785" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2">
+      <c r="A786" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="B786" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2">
+      <c r="A787" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="B787" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="798">
   <si>
     <t>Наименование</t>
   </si>
@@ -137,6 +137,9 @@
     <t>BIERBANK - SOOTHING YOU (AIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Big Village - All Cats Are Cute (NE Pale Ale), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Big Village - Big Kid's Toy (Sour), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -155,6 +158,9 @@
     <t>Big Village - LUMINBLOOM (NEPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Big Village - Magical Place (DDH NEDIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Big Village - Mission Red (DIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -176,6 +182,9 @@
     <t>Big Village - Village Kolsch (Kolsch), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Big Village - Вспять (WC APA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Big Village - ПЕРИФЕРИЯ (NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -425,6 +434,9 @@
     <t>Jungle - Body Flow (IPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Jungle - Citra One Love (Session NEIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Jungle - Hired Gun (APA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -485,6 +497,9 @@
     <t>Maisel`S Weisse ORIGINAL, Розлив, Германия</t>
   </si>
   <si>
+    <t>Malanka - Bliskaviza: Motueka (NEIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Malanka - Imhla: Galaxy (NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -860,6 +875,9 @@
     <t>Saliwa - Гора Коврижка (NZ Pils), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>Saliwa - Змей Ушиныч (NZ Pils), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>Saliwa - Михалыч (DIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1415,6 +1433,9 @@
     <t>вынос_Bakunin - Рука Бога (Golden ale), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Big Village - All Cats Are Cute (NE Pale Ale), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Big Village - Big Kid's Toy (Sour), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1433,6 +1454,9 @@
     <t>вынос_Big Village - LUMINBLOOM (NEPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Big Village - Magical Place (DDH NEDIPA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Big Village - Pacification (NE Pale Ale), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1448,6 +1472,9 @@
     <t>вынос_Big Village - Village Kolsch (Kolsch), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Big Village - Вспять (WC APA), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Big Village - ПЕРИФЕРИЯ (NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1805,6 +1832,9 @@
     <t>вынос_Saliwa - Волгоградский Скоростной Траммяу (NEPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
+    <t>вынос_Saliwa - Змей Ушиныч (NZ Pils), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
     <t>вынос_Saliwa - Михалыч (DIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -2202,6 +2232,9 @@
   </si>
   <si>
     <t xml:space="preserve">Заповедник - Абанамат (Сухой Сидр), РОЗЛИВ, Россия </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Как С Куста - Полусухой, РОЗЛИВ, Россия </t>
   </si>
   <si>
     <t>Кафедра Сидороделия- АНАНАС, Розлив , Россия</t>
@@ -2729,7 +2762,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B787"/>
+  <dimension ref="A1:B798"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -3053,7 +3086,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3061,7 +3094,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="1">
-        <v>660</v>
+        <v>800</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3069,7 +3102,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3077,7 +3110,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="1">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3085,7 +3118,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="1">
-        <v>840</v>
+        <v>620</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3093,7 +3126,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3101,7 +3134,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="1">
-        <v>720</v>
+        <v>880</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3109,7 +3142,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>860</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3117,7 +3150,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -3133,7 +3166,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>480</v>
+        <v>800</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3141,7 +3174,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>760</v>
+        <v>860</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -3149,7 +3182,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -3157,7 +3190,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3165,7 +3198,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -3181,7 +3214,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>580</v>
+        <v>900</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -3189,7 +3222,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -3197,7 +3230,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>560</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3205,7 +3238,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>780</v>
+        <v>580</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -3213,7 +3246,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -3221,7 +3254,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>800</v>
+        <v>560</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -3229,7 +3262,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -3237,7 +3270,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -3245,7 +3278,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -3261,7 +3294,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="1">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -3277,7 +3310,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -3285,7 +3318,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -3293,7 +3326,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -3301,7 +3334,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -3309,7 +3342,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -3317,7 +3350,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -3325,7 +3358,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -3333,7 +3366,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3341,7 +3374,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>880</v>
+        <v>760</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -3349,7 +3382,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>640</v>
+        <v>920</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -3357,7 +3390,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -3365,7 +3398,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -3373,7 +3406,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -3381,7 +3414,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -3389,7 +3422,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -3397,7 +3430,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>620</v>
+        <v>700</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -3405,7 +3438,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -3413,7 +3446,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>560</v>
+        <v>840</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -3421,7 +3454,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>480</v>
+        <v>620</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -3437,7 +3470,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3445,7 +3478,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3453,7 +3486,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>540</v>
+        <v>560</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3461,7 +3494,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>860</v>
+        <v>480</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3469,7 +3502,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3477,7 +3510,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>720</v>
+        <v>540</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3485,7 +3518,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>440</v>
+        <v>860</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3493,7 +3526,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>560</v>
+        <v>840</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3501,7 +3534,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>460</v>
+        <v>720</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3509,7 +3542,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>460</v>
+        <v>440</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3517,7 +3550,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>960</v>
+        <v>560</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3525,7 +3558,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>940</v>
+        <v>460</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3533,7 +3566,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="1">
-        <v>1040</v>
+        <v>460</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3541,7 +3574,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>1040</v>
+        <v>960</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3549,7 +3582,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>660</v>
+        <v>940</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3557,7 +3590,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>480</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3565,7 +3598,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="1">
-        <v>400</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3573,7 +3606,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>720</v>
+        <v>660</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3581,7 +3614,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3589,7 +3622,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -3597,7 +3630,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>760</v>
+        <v>720</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3605,7 +3638,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>500</v>
+        <v>560</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3613,7 +3646,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>940</v>
+        <v>500</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3621,7 +3654,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3629,7 +3662,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>920</v>
+        <v>500</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3637,7 +3670,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>680</v>
+        <v>940</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3645,7 +3678,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>420</v>
+        <v>900</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3653,7 +3686,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>560</v>
+        <v>920</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3661,7 +3694,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3669,7 +3702,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>520</v>
+        <v>420</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3685,7 +3718,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3693,7 +3726,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3701,7 +3734,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3709,7 +3742,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -3717,7 +3750,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -3725,7 +3758,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -3733,7 +3766,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>700</v>
+        <v>620</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -3741,7 +3774,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -3749,7 +3782,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>900</v>
+        <v>780</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -3757,7 +3790,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -3765,7 +3798,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>720</v>
+        <v>960</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -3773,7 +3806,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -3781,7 +3814,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -3789,7 +3822,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -3797,7 +3830,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>540</v>
+        <v>780</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -3805,7 +3838,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>520</v>
+        <v>500</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -3813,7 +3846,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>1100</v>
+        <v>580</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -3821,7 +3854,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>1060</v>
+        <v>540</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -3829,7 +3862,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>1100</v>
+        <v>520</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -3845,7 +3878,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>560</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -3853,39 +3886,39 @@
         <v>140</v>
       </c>
       <c r="B140" s="1">
-        <v>840</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>840</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B142" s="1">
-        <v>420</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -3893,7 +3926,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="1">
-        <v>460</v>
+        <v>840</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -3901,7 +3934,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="1">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -3909,7 +3942,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3917,7 +3950,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -3925,7 +3958,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="1">
-        <v>620</v>
+        <v>460</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -3933,7 +3966,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -3941,7 +3974,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="1">
-        <v>980</v>
+        <v>580</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3949,7 +3982,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="1">
-        <v>540</v>
+        <v>740</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3957,7 +3990,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="1">
-        <v>580</v>
+        <v>620</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3965,7 +3998,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="1">
-        <v>740</v>
+        <v>520</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -3973,7 +4006,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="1">
-        <v>760</v>
+        <v>980</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -3981,7 +4014,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -3989,7 +4022,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="1">
-        <v>1100</v>
+        <v>580</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -3997,7 +4030,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -4005,7 +4038,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4021,7 +4054,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="1">
-        <v>640</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -4029,7 +4062,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -4037,7 +4070,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="1">
-        <v>900</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -4045,7 +4078,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="1">
-        <v>920</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -4053,7 +4086,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="1">
-        <v>920</v>
+        <v>560</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4061,7 +4094,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="1">
-        <v>920</v>
+        <v>640</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4069,7 +4102,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="1">
-        <v>720</v>
+        <v>560</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -4077,7 +4110,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4085,7 +4118,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4093,7 +4126,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -4101,7 +4134,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="1">
-        <v>700</v>
+        <v>920</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4109,7 +4142,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="1">
-        <v>460</v>
+        <v>720</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4117,7 +4150,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4125,7 +4158,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4133,7 +4166,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="1">
-        <v>660</v>
+        <v>840</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4141,7 +4174,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4149,7 +4182,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="1">
-        <v>260</v>
+        <v>460</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4157,7 +4190,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="1">
-        <v>260</v>
+        <v>580</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4165,7 +4198,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="1">
-        <v>440</v>
+        <v>720</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4173,7 +4206,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="1">
-        <v>440</v>
+        <v>660</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4181,7 +4214,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4189,7 +4222,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="1">
-        <v>740</v>
+        <v>260</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4197,7 +4230,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="1">
-        <v>720</v>
+        <v>260</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4205,7 +4238,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="1">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4213,7 +4246,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="1">
-        <v>400</v>
+        <v>440</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4221,7 +4254,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4229,7 +4262,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4237,7 +4270,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4245,7 +4278,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="1">
-        <v>620</v>
+        <v>500</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4253,7 +4286,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="1">
-        <v>640</v>
+        <v>400</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4261,7 +4294,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4269,7 +4302,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4277,7 +4310,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="1">
-        <v>580</v>
+        <v>780</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4293,7 +4326,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="1">
-        <v>520</v>
+        <v>640</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4301,7 +4334,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4317,7 +4350,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4325,7 +4358,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4333,7 +4366,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4341,7 +4374,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4357,7 +4390,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4365,7 +4398,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4373,7 +4406,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="1">
-        <v>820</v>
+        <v>560</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4381,7 +4414,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="1">
-        <v>760</v>
+        <v>520</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4389,7 +4422,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4397,7 +4430,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="1">
-        <v>600</v>
+        <v>540</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4405,7 +4438,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="1">
-        <v>1400</v>
+        <v>700</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4413,7 +4446,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="1">
-        <v>480</v>
+        <v>820</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4421,7 +4454,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4429,7 +4462,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4445,7 +4478,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="1">
-        <v>700</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4453,7 +4486,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="1">
-        <v>740</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4469,7 +4502,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4477,7 +4510,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="1">
-        <v>520</v>
+        <v>600</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4485,7 +4518,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4493,7 +4526,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4501,7 +4534,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="1">
-        <v>620</v>
+        <v>720</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4509,7 +4542,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4517,7 +4550,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="1">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4525,7 +4558,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="1">
-        <v>620</v>
+        <v>900</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4533,7 +4566,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4541,7 +4574,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4549,7 +4582,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4557,7 +4590,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="1">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4565,7 +4598,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4573,7 +4606,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4581,7 +4614,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4589,7 +4622,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -4597,7 +4630,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -4605,7 +4638,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -4621,7 +4654,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -4629,7 +4662,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="1">
-        <v>560</v>
+        <v>780</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -4637,7 +4670,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -4645,7 +4678,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -4653,7 +4686,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -4661,7 +4694,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -4669,7 +4702,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="1">
-        <v>500</v>
+        <v>560</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -4677,7 +4710,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="1">
-        <v>758</v>
+        <v>780</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -4685,7 +4718,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="1">
-        <v>2273</v>
+        <v>640</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -4693,7 +4726,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="1">
-        <v>1515</v>
+        <v>640</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -4701,7 +4734,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="1">
-        <v>520</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -4709,7 +4742,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -4717,7 +4750,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="1">
-        <v>4000</v>
+        <v>758</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -4725,7 +4758,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="1">
-        <v>560</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -4733,7 +4766,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="1">
-        <v>480</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -4741,7 +4774,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -4749,7 +4782,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -4757,7 +4790,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="1">
-        <v>660</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -4765,7 +4798,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="1">
-        <v>700</v>
+        <v>560</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -4773,7 +4806,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="1">
-        <v>580</v>
+        <v>480</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -4781,7 +4814,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="1">
-        <v>520</v>
+        <v>720</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -4789,7 +4822,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -4797,7 +4830,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -4805,7 +4838,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="1">
-        <v>580</v>
+        <v>700</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -4813,7 +4846,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -4821,7 +4854,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -4829,7 +4862,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -4837,7 +4870,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="1">
-        <v>540</v>
+        <v>640</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -4845,7 +4878,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -4853,7 +4886,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="1">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -4861,7 +4894,7 @@
         <v>265</v>
       </c>
       <c r="B266" s="1">
-        <v>580</v>
+        <v>380</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -4869,7 +4902,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="1">
-        <v>460</v>
+        <v>660</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -4877,7 +4910,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -4885,7 +4918,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -4893,7 +4926,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -4901,7 +4934,7 @@
         <v>270</v>
       </c>
       <c r="B271" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -4909,7 +4942,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="1">
-        <v>900</v>
+        <v>460</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -4917,7 +4950,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="1">
-        <v>900</v>
+        <v>520</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -4925,7 +4958,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="1">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -4933,7 +4966,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="1">
-        <v>560</v>
+        <v>860</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -4941,7 +4974,7 @@
         <v>275</v>
       </c>
       <c r="B276" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -4957,7 +4990,7 @@
         <v>277</v>
       </c>
       <c r="B278" s="1">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -4965,7 +4998,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="1">
-        <v>680</v>
+        <v>560</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -4973,7 +5006,7 @@
         <v>279</v>
       </c>
       <c r="B280" s="1">
-        <v>1000</v>
+        <v>560</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -4981,7 +5014,7 @@
         <v>280</v>
       </c>
       <c r="B281" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -4989,7 +5022,7 @@
         <v>281</v>
       </c>
       <c r="B282" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -4997,7 +5030,7 @@
         <v>282</v>
       </c>
       <c r="B283" s="1">
-        <v>1020</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5005,7 +5038,7 @@
         <v>283</v>
       </c>
       <c r="B284" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -5013,7 +5046,7 @@
         <v>284</v>
       </c>
       <c r="B285" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -5021,7 +5054,7 @@
         <v>285</v>
       </c>
       <c r="B286" s="1">
-        <v>520</v>
+        <v>840</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -5029,7 +5062,7 @@
         <v>286</v>
       </c>
       <c r="B287" s="1">
-        <v>640</v>
+        <v>860</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -5037,7 +5070,7 @@
         <v>287</v>
       </c>
       <c r="B288" s="1">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5045,7 +5078,7 @@
         <v>288</v>
       </c>
       <c r="B289" s="1">
-        <v>660</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5053,7 +5086,7 @@
         <v>289</v>
       </c>
       <c r="B290" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -5061,7 +5094,7 @@
         <v>290</v>
       </c>
       <c r="B291" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5069,7 +5102,7 @@
         <v>291</v>
       </c>
       <c r="B292" s="1">
-        <v>640</v>
+        <v>520</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5077,7 +5110,7 @@
         <v>292</v>
       </c>
       <c r="B293" s="1">
-        <v>740</v>
+        <v>640</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5085,7 +5118,7 @@
         <v>293</v>
       </c>
       <c r="B294" s="1">
-        <v>720</v>
+        <v>800</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5093,7 +5126,7 @@
         <v>294</v>
       </c>
       <c r="B295" s="1">
-        <v>640</v>
+        <v>660</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5101,7 +5134,7 @@
         <v>295</v>
       </c>
       <c r="B296" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5109,7 +5142,7 @@
         <v>296</v>
       </c>
       <c r="B297" s="1">
-        <v>880</v>
+        <v>580</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5117,7 +5150,7 @@
         <v>297</v>
       </c>
       <c r="B298" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5125,7 +5158,7 @@
         <v>298</v>
       </c>
       <c r="B299" s="1">
-        <v>520</v>
+        <v>740</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5133,7 +5166,7 @@
         <v>299</v>
       </c>
       <c r="B300" s="1">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -5141,7 +5174,7 @@
         <v>300</v>
       </c>
       <c r="B301" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5149,7 +5182,7 @@
         <v>301</v>
       </c>
       <c r="B302" s="1">
-        <v>820</v>
+        <v>720</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5157,7 +5190,7 @@
         <v>302</v>
       </c>
       <c r="B303" s="1">
-        <v>600</v>
+        <v>880</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5165,7 +5198,7 @@
         <v>303</v>
       </c>
       <c r="B304" s="1">
-        <v>380</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -5181,7 +5214,7 @@
         <v>305</v>
       </c>
       <c r="B306" s="1">
-        <v>320</v>
+        <v>740</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5189,7 +5222,7 @@
         <v>306</v>
       </c>
       <c r="B307" s="1">
-        <v>540</v>
+        <v>600</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5197,7 +5230,7 @@
         <v>307</v>
       </c>
       <c r="B308" s="1">
-        <v>560</v>
+        <v>820</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5205,7 +5238,7 @@
         <v>308</v>
       </c>
       <c r="B309" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5213,7 +5246,7 @@
         <v>309</v>
       </c>
       <c r="B310" s="1">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5229,7 +5262,7 @@
         <v>311</v>
       </c>
       <c r="B312" s="1">
-        <v>500</v>
+        <v>320</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5237,7 +5270,7 @@
         <v>312</v>
       </c>
       <c r="B313" s="1">
-        <v>800</v>
+        <v>540</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5245,7 +5278,7 @@
         <v>313</v>
       </c>
       <c r="B314" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5253,7 +5286,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="1">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5261,7 +5294,7 @@
         <v>315</v>
       </c>
       <c r="B316" s="1">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -5269,7 +5302,7 @@
         <v>316</v>
       </c>
       <c r="B317" s="1">
-        <v>380</v>
+        <v>520</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5277,7 +5310,7 @@
         <v>317</v>
       </c>
       <c r="B318" s="1">
-        <v>440</v>
+        <v>500</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5285,7 +5318,7 @@
         <v>318</v>
       </c>
       <c r="B319" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5293,7 +5326,7 @@
         <v>319</v>
       </c>
       <c r="B320" s="1">
-        <v>900</v>
+        <v>480</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5301,7 +5334,7 @@
         <v>320</v>
       </c>
       <c r="B321" s="1">
-        <v>780</v>
+        <v>800</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5309,7 +5342,7 @@
         <v>321</v>
       </c>
       <c r="B322" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5317,7 +5350,7 @@
         <v>322</v>
       </c>
       <c r="B323" s="1">
-        <v>960</v>
+        <v>380</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5325,7 +5358,7 @@
         <v>323</v>
       </c>
       <c r="B324" s="1">
-        <v>1020</v>
+        <v>440</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5333,7 +5366,7 @@
         <v>324</v>
       </c>
       <c r="B325" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5341,7 +5374,7 @@
         <v>325</v>
       </c>
       <c r="B326" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5349,7 +5382,7 @@
         <v>326</v>
       </c>
       <c r="B327" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5357,7 +5390,7 @@
         <v>327</v>
       </c>
       <c r="B328" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -5365,7 +5398,7 @@
         <v>328</v>
       </c>
       <c r="B329" s="1">
-        <v>1020</v>
+        <v>960</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5373,7 +5406,7 @@
         <v>329</v>
       </c>
       <c r="B330" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5381,7 +5414,7 @@
         <v>330</v>
       </c>
       <c r="B331" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5389,7 +5422,7 @@
         <v>331</v>
       </c>
       <c r="B332" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5397,7 +5430,7 @@
         <v>332</v>
       </c>
       <c r="B333" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5413,7 +5446,7 @@
         <v>334</v>
       </c>
       <c r="B335" s="1">
-        <v>720</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5421,7 +5454,7 @@
         <v>335</v>
       </c>
       <c r="B336" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5429,7 +5462,7 @@
         <v>336</v>
       </c>
       <c r="B337" s="1">
-        <v>760</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5437,7 +5470,7 @@
         <v>337</v>
       </c>
       <c r="B338" s="1">
-        <v>680</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5445,7 +5478,7 @@
         <v>338</v>
       </c>
       <c r="B339" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5453,7 +5486,7 @@
         <v>339</v>
       </c>
       <c r="B340" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5461,7 +5494,7 @@
         <v>340</v>
       </c>
       <c r="B341" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5469,7 +5502,7 @@
         <v>341</v>
       </c>
       <c r="B342" s="1">
-        <v>480</v>
+        <v>680</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5477,7 +5510,7 @@
         <v>342</v>
       </c>
       <c r="B343" s="1">
-        <v>640</v>
+        <v>760</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5485,7 +5518,7 @@
         <v>343</v>
       </c>
       <c r="B344" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5493,7 +5526,7 @@
         <v>344</v>
       </c>
       <c r="B345" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5501,7 +5534,7 @@
         <v>345</v>
       </c>
       <c r="B346" s="1">
-        <v>860</v>
+        <v>740</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5509,7 +5542,7 @@
         <v>346</v>
       </c>
       <c r="B347" s="1">
-        <v>520</v>
+        <v>680</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5517,7 +5550,7 @@
         <v>347</v>
       </c>
       <c r="B348" s="1">
-        <v>540</v>
+        <v>480</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5525,7 +5558,7 @@
         <v>348</v>
       </c>
       <c r="B349" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5533,7 +5566,7 @@
         <v>349</v>
       </c>
       <c r="B350" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5541,7 +5574,7 @@
         <v>350</v>
       </c>
       <c r="B351" s="1">
-        <v>420</v>
+        <v>920</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5549,7 +5582,7 @@
         <v>351</v>
       </c>
       <c r="B352" s="1">
-        <v>700</v>
+        <v>860</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5557,7 +5590,7 @@
         <v>352</v>
       </c>
       <c r="B353" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5565,7 +5598,7 @@
         <v>353</v>
       </c>
       <c r="B354" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5573,7 +5606,7 @@
         <v>354</v>
       </c>
       <c r="B355" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5581,7 +5614,7 @@
         <v>355</v>
       </c>
       <c r="B356" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5589,7 +5622,7 @@
         <v>356</v>
       </c>
       <c r="B357" s="1">
-        <v>920</v>
+        <v>420</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -5597,7 +5630,7 @@
         <v>357</v>
       </c>
       <c r="B358" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -5613,7 +5646,7 @@
         <v>359</v>
       </c>
       <c r="B360" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -5621,7 +5654,7 @@
         <v>360</v>
       </c>
       <c r="B361" s="1">
-        <v>440</v>
+        <v>740</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -5629,7 +5662,7 @@
         <v>361</v>
       </c>
       <c r="B362" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -5637,7 +5670,7 @@
         <v>362</v>
       </c>
       <c r="B363" s="1">
-        <v>320</v>
+        <v>920</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -5645,7 +5678,7 @@
         <v>363</v>
       </c>
       <c r="B364" s="1">
-        <v>320</v>
+        <v>840</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -5653,7 +5686,7 @@
         <v>364</v>
       </c>
       <c r="B365" s="1">
-        <v>820</v>
+        <v>720</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -5661,7 +5694,7 @@
         <v>365</v>
       </c>
       <c r="B366" s="1">
-        <v>1000</v>
+        <v>620</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -5669,7 +5702,7 @@
         <v>366</v>
       </c>
       <c r="B367" s="1">
-        <v>580</v>
+        <v>440</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -5677,7 +5710,7 @@
         <v>367</v>
       </c>
       <c r="B368" s="1">
-        <v>580</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -5685,7 +5718,7 @@
         <v>368</v>
       </c>
       <c r="B369" s="1">
-        <v>900</v>
+        <v>320</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -5693,7 +5726,7 @@
         <v>369</v>
       </c>
       <c r="B370" s="1">
-        <v>580</v>
+        <v>320</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -5701,7 +5734,7 @@
         <v>370</v>
       </c>
       <c r="B371" s="1">
-        <v>580</v>
+        <v>820</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -5709,7 +5742,7 @@
         <v>371</v>
       </c>
       <c r="B372" s="1">
-        <v>620</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -5717,7 +5750,7 @@
         <v>372</v>
       </c>
       <c r="B373" s="1">
-        <v>900</v>
+        <v>580</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -5725,7 +5758,7 @@
         <v>373</v>
       </c>
       <c r="B374" s="1">
-        <v>920</v>
+        <v>580</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -5733,7 +5766,7 @@
         <v>374</v>
       </c>
       <c r="B375" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -5741,7 +5774,7 @@
         <v>375</v>
       </c>
       <c r="B376" s="1">
-        <v>780</v>
+        <v>580</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -5749,7 +5782,7 @@
         <v>376</v>
       </c>
       <c r="B377" s="1">
-        <v>880</v>
+        <v>580</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -5757,7 +5790,7 @@
         <v>377</v>
       </c>
       <c r="B378" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -5765,7 +5798,7 @@
         <v>378</v>
       </c>
       <c r="B379" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -5773,7 +5806,7 @@
         <v>379</v>
       </c>
       <c r="B380" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -5781,7 +5814,7 @@
         <v>380</v>
       </c>
       <c r="B381" s="1">
-        <v>660</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -5789,7 +5822,7 @@
         <v>381</v>
       </c>
       <c r="B382" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -5797,7 +5830,7 @@
         <v>382</v>
       </c>
       <c r="B383" s="1">
-        <v>680</v>
+        <v>880</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -5805,7 +5838,7 @@
         <v>383</v>
       </c>
       <c r="B384" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -5813,7 +5846,7 @@
         <v>384</v>
       </c>
       <c r="B385" s="1">
-        <v>440</v>
+        <v>780</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -5821,7 +5854,7 @@
         <v>385</v>
       </c>
       <c r="B386" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -5829,7 +5862,7 @@
         <v>386</v>
       </c>
       <c r="B387" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -5837,7 +5870,7 @@
         <v>387</v>
       </c>
       <c r="B388" s="1">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -5845,7 +5878,7 @@
         <v>388</v>
       </c>
       <c r="B389" s="1">
-        <v>560</v>
+        <v>680</v>
       </c>
     </row>
     <row r="390" spans="1:2">
@@ -5853,7 +5886,7 @@
         <v>389</v>
       </c>
       <c r="B390" s="1">
-        <v>760</v>
+        <v>660</v>
       </c>
     </row>
     <row r="391" spans="1:2">
@@ -5861,7 +5894,7 @@
         <v>390</v>
       </c>
       <c r="B391" s="1">
-        <v>780</v>
+        <v>440</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -5869,7 +5902,7 @@
         <v>391</v>
       </c>
       <c r="B392" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -5877,7 +5910,7 @@
         <v>392</v>
       </c>
       <c r="B393" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -5885,7 +5918,7 @@
         <v>393</v>
       </c>
       <c r="B394" s="1">
-        <v>560</v>
+        <v>800</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -5893,7 +5926,7 @@
         <v>394</v>
       </c>
       <c r="B395" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -5901,7 +5934,7 @@
         <v>395</v>
       </c>
       <c r="B396" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -5909,7 +5942,7 @@
         <v>396</v>
       </c>
       <c r="B397" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -5917,7 +5950,7 @@
         <v>397</v>
       </c>
       <c r="B398" s="1">
-        <v>480</v>
+        <v>720</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -5925,7 +5958,7 @@
         <v>398</v>
       </c>
       <c r="B399" s="1">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -5933,7 +5966,7 @@
         <v>399</v>
       </c>
       <c r="B400" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -5941,7 +5974,7 @@
         <v>400</v>
       </c>
       <c r="B401" s="1">
-        <v>880</v>
+        <v>620</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -5949,7 +5982,7 @@
         <v>401</v>
       </c>
       <c r="B402" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -5957,7 +5990,7 @@
         <v>402</v>
       </c>
       <c r="B403" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -5965,7 +5998,7 @@
         <v>403</v>
       </c>
       <c r="B404" s="1">
-        <v>920</v>
+        <v>480</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -5973,7 +6006,7 @@
         <v>404</v>
       </c>
       <c r="B405" s="1">
-        <v>740</v>
+        <v>480</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -5981,7 +6014,7 @@
         <v>405</v>
       </c>
       <c r="B406" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -5989,7 +6022,7 @@
         <v>406</v>
       </c>
       <c r="B407" s="1">
-        <v>940</v>
+        <v>880</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -5997,7 +6030,7 @@
         <v>407</v>
       </c>
       <c r="B408" s="1">
-        <v>980</v>
+        <v>900</v>
       </c>
     </row>
     <row r="409" spans="1:2">
@@ -6005,7 +6038,7 @@
         <v>408</v>
       </c>
       <c r="B409" s="1">
-        <v>920</v>
+        <v>780</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -6013,7 +6046,7 @@
         <v>409</v>
       </c>
       <c r="B410" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -6021,7 +6054,7 @@
         <v>410</v>
       </c>
       <c r="B411" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -6029,7 +6062,7 @@
         <v>411</v>
       </c>
       <c r="B412" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -6037,7 +6070,7 @@
         <v>412</v>
       </c>
       <c r="B413" s="1">
-        <v>620</v>
+        <v>940</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -6045,7 +6078,7 @@
         <v>413</v>
       </c>
       <c r="B414" s="1">
-        <v>620</v>
+        <v>980</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -6053,7 +6086,7 @@
         <v>414</v>
       </c>
       <c r="B415" s="1">
-        <v>860</v>
+        <v>920</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -6061,7 +6094,7 @@
         <v>415</v>
       </c>
       <c r="B416" s="1">
-        <v>920</v>
+        <v>600</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -6069,7 +6102,7 @@
         <v>416</v>
       </c>
       <c r="B417" s="1">
-        <v>640</v>
+        <v>760</v>
       </c>
     </row>
     <row r="418" spans="1:2">
@@ -6077,7 +6110,7 @@
         <v>417</v>
       </c>
       <c r="B418" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -6085,7 +6118,7 @@
         <v>418</v>
       </c>
       <c r="B419" s="1">
-        <v>820</v>
+        <v>620</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -6093,7 +6126,7 @@
         <v>419</v>
       </c>
       <c r="B420" s="1">
-        <v>960</v>
+        <v>620</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -6101,7 +6134,7 @@
         <v>420</v>
       </c>
       <c r="B421" s="1">
-        <v>740</v>
+        <v>860</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -6109,7 +6142,7 @@
         <v>421</v>
       </c>
       <c r="B422" s="1">
-        <v>1000</v>
+        <v>920</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -6125,7 +6158,7 @@
         <v>423</v>
       </c>
       <c r="B424" s="1">
-        <v>860</v>
+        <v>680</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6133,7 +6166,7 @@
         <v>424</v>
       </c>
       <c r="B425" s="1">
-        <v>560</v>
+        <v>820</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6141,7 +6174,7 @@
         <v>425</v>
       </c>
       <c r="B426" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6149,7 +6182,7 @@
         <v>426</v>
       </c>
       <c r="B427" s="1">
-        <v>660</v>
+        <v>740</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6157,7 +6190,7 @@
         <v>427</v>
       </c>
       <c r="B428" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6165,7 +6198,7 @@
         <v>428</v>
       </c>
       <c r="B429" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6173,7 +6206,7 @@
         <v>429</v>
       </c>
       <c r="B430" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6181,7 +6214,7 @@
         <v>430</v>
       </c>
       <c r="B431" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6189,7 +6222,7 @@
         <v>431</v>
       </c>
       <c r="B432" s="1">
-        <v>480</v>
+        <v>780</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6197,7 +6230,7 @@
         <v>432</v>
       </c>
       <c r="B433" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6205,7 +6238,7 @@
         <v>433</v>
       </c>
       <c r="B434" s="1">
-        <v>780</v>
+        <v>640</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6221,7 +6254,7 @@
         <v>435</v>
       </c>
       <c r="B436" s="1">
-        <v>820</v>
+        <v>840</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6229,7 +6262,7 @@
         <v>436</v>
       </c>
       <c r="B437" s="1">
-        <v>760</v>
+        <v>520</v>
       </c>
     </row>
     <row r="438" spans="1:2">
@@ -6237,7 +6270,7 @@
         <v>437</v>
       </c>
       <c r="B438" s="1">
-        <v>740</v>
+        <v>480</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6245,7 +6278,7 @@
         <v>438</v>
       </c>
       <c r="B439" s="1">
-        <v>780</v>
+        <v>620</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6253,7 +6286,7 @@
         <v>439</v>
       </c>
       <c r="B440" s="1">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6261,7 +6294,7 @@
         <v>440</v>
       </c>
       <c r="B441" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6269,7 +6302,7 @@
         <v>441</v>
       </c>
       <c r="B442" s="1">
-        <v>840</v>
+        <v>820</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6277,7 +6310,7 @@
         <v>442</v>
       </c>
       <c r="B443" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6285,7 +6318,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="1">
-        <v>700</v>
+        <v>740</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6293,7 +6326,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="1">
-        <v>440</v>
+        <v>780</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6301,7 +6334,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="1">
-        <v>440</v>
+        <v>600</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6309,7 +6342,7 @@
         <v>446</v>
       </c>
       <c r="B447" s="1">
-        <v>740</v>
+        <v>480</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6317,7 +6350,7 @@
         <v>447</v>
       </c>
       <c r="B448" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6325,7 +6358,7 @@
         <v>448</v>
       </c>
       <c r="B449" s="1">
-        <v>880</v>
+        <v>660</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6333,7 +6366,7 @@
         <v>449</v>
       </c>
       <c r="B450" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6341,7 +6374,7 @@
         <v>450</v>
       </c>
       <c r="B451" s="1">
-        <v>840</v>
+        <v>440</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6349,7 +6382,7 @@
         <v>451</v>
       </c>
       <c r="B452" s="1">
-        <v>660</v>
+        <v>440</v>
       </c>
     </row>
     <row r="453" spans="1:2">
@@ -6357,7 +6390,7 @@
         <v>452</v>
       </c>
       <c r="B453" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6365,7 +6398,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="1">
-        <v>840</v>
+        <v>880</v>
       </c>
     </row>
     <row r="455" spans="1:2">
@@ -6373,7 +6406,7 @@
         <v>454</v>
       </c>
       <c r="B455" s="1">
-        <v>700</v>
+        <v>880</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6389,7 +6422,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="1">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6405,7 +6438,7 @@
         <v>458</v>
       </c>
       <c r="B459" s="1">
-        <v>660</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="460" spans="1:2">
@@ -6421,7 +6454,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6437,7 +6470,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="1">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6445,7 +6478,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6453,7 +6486,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6461,7 +6494,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="1">
-        <v>600</v>
+        <v>840</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6469,7 +6502,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="1">
-        <v>800</v>
+        <v>740</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6477,7 +6510,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6485,7 +6518,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6493,7 +6526,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="1">
-        <v>620</v>
+        <v>860</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6501,7 +6534,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="1">
-        <v>840</v>
+        <v>600</v>
       </c>
     </row>
     <row r="472" spans="1:2">
@@ -6509,7 +6542,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6517,7 +6550,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="1">
-        <v>860</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6533,7 +6566,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="1">
-        <v>860</v>
+        <v>660</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6541,7 +6574,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="1">
-        <v>760</v>
+        <v>600</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6549,7 +6582,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="1">
-        <v>720</v>
+        <v>620</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6557,7 +6590,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="1">
-        <v>900</v>
+        <v>840</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6565,7 +6598,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="1">
-        <v>1100</v>
+        <v>880</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6573,7 +6606,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="1">
-        <v>1000</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6581,7 +6614,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="1">
-        <v>780</v>
+        <v>860</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6589,7 +6622,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="1">
-        <v>640</v>
+        <v>800</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -6597,7 +6630,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="1">
-        <v>800</v>
+        <v>860</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -6605,7 +6638,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="1">
-        <v>660</v>
+        <v>760</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -6613,7 +6646,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -6621,7 +6654,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -6629,7 +6662,7 @@
         <v>486</v>
       </c>
       <c r="B487" s="1">
-        <v>820</v>
+        <v>900</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -6637,7 +6670,7 @@
         <v>487</v>
       </c>
       <c r="B488" s="1">
-        <v>760</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="489" spans="1:2">
@@ -6645,7 +6678,7 @@
         <v>488</v>
       </c>
       <c r="B489" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -6653,7 +6686,7 @@
         <v>489</v>
       </c>
       <c r="B490" s="1">
-        <v>760</v>
+        <v>780</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -6661,7 +6694,7 @@
         <v>490</v>
       </c>
       <c r="B491" s="1">
-        <v>920</v>
+        <v>640</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -6669,7 +6702,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -6677,7 +6710,7 @@
         <v>492</v>
       </c>
       <c r="B493" s="1">
-        <v>880</v>
+        <v>660</v>
       </c>
     </row>
     <row r="494" spans="1:2">
@@ -6685,7 +6718,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="1">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -6701,7 +6734,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="1">
-        <v>600</v>
+        <v>820</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -6709,7 +6742,7 @@
         <v>496</v>
       </c>
       <c r="B497" s="1">
-        <v>560</v>
+        <v>760</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -6717,7 +6750,7 @@
         <v>497</v>
       </c>
       <c r="B498" s="1">
-        <v>560</v>
+        <v>820</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -6725,7 +6758,7 @@
         <v>498</v>
       </c>
       <c r="B499" s="1">
-        <v>860</v>
+        <v>760</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -6733,7 +6766,7 @@
         <v>499</v>
       </c>
       <c r="B500" s="1">
-        <v>840</v>
+        <v>920</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -6741,7 +6774,7 @@
         <v>500</v>
       </c>
       <c r="B501" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -6749,7 +6782,7 @@
         <v>501</v>
       </c>
       <c r="B502" s="1">
-        <v>960</v>
+        <v>880</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -6757,7 +6790,7 @@
         <v>502</v>
       </c>
       <c r="B503" s="1">
-        <v>940</v>
+        <v>640</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -6765,7 +6798,7 @@
         <v>503</v>
       </c>
       <c r="B504" s="1">
-        <v>1040</v>
+        <v>700</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -6773,7 +6806,7 @@
         <v>504</v>
       </c>
       <c r="B505" s="1">
-        <v>1040</v>
+        <v>600</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -6781,7 +6814,7 @@
         <v>505</v>
       </c>
       <c r="B506" s="1">
-        <v>940</v>
+        <v>560</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -6789,7 +6822,7 @@
         <v>506</v>
       </c>
       <c r="B507" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -6797,7 +6830,7 @@
         <v>507</v>
       </c>
       <c r="B508" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -6805,7 +6838,7 @@
         <v>508</v>
       </c>
       <c r="B509" s="1">
-        <v>680</v>
+        <v>840</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -6813,7 +6846,7 @@
         <v>509</v>
       </c>
       <c r="B510" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -6821,7 +6854,7 @@
         <v>510</v>
       </c>
       <c r="B511" s="1">
-        <v>820</v>
+        <v>960</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -6829,7 +6862,7 @@
         <v>511</v>
       </c>
       <c r="B512" s="1">
-        <v>620</v>
+        <v>940</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -6837,7 +6870,7 @@
         <v>512</v>
       </c>
       <c r="B513" s="1">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -6845,7 +6878,7 @@
         <v>513</v>
       </c>
       <c r="B514" s="1">
-        <v>780</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -6853,7 +6886,7 @@
         <v>514</v>
       </c>
       <c r="B515" s="1">
-        <v>700</v>
+        <v>940</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -6861,7 +6894,7 @@
         <v>515</v>
       </c>
       <c r="B516" s="1">
-        <v>960</v>
+        <v>900</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -6869,7 +6902,7 @@
         <v>516</v>
       </c>
       <c r="B517" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -6877,7 +6910,7 @@
         <v>517</v>
       </c>
       <c r="B518" s="1">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -6885,7 +6918,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -6893,7 +6926,7 @@
         <v>519</v>
       </c>
       <c r="B520" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -6901,7 +6934,7 @@
         <v>520</v>
       </c>
       <c r="B521" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -6909,7 +6942,7 @@
         <v>521</v>
       </c>
       <c r="B522" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="523" spans="1:2">
@@ -6917,7 +6950,7 @@
         <v>522</v>
       </c>
       <c r="B523" s="1">
-        <v>1060</v>
+        <v>780</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -6925,7 +6958,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="1">
-        <v>1100</v>
+        <v>700</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -6933,7 +6966,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1">
-        <v>1100</v>
+        <v>960</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -6941,7 +6974,7 @@
         <v>525</v>
       </c>
       <c r="B526" s="1">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -6949,7 +6982,7 @@
         <v>526</v>
       </c>
       <c r="B527" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -6957,7 +6990,7 @@
         <v>527</v>
       </c>
       <c r="B528" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -6965,7 +6998,7 @@
         <v>528</v>
       </c>
       <c r="B529" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -6973,7 +7006,7 @@
         <v>529</v>
       </c>
       <c r="B530" s="1">
-        <v>620</v>
+        <v>540</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -6981,7 +7014,7 @@
         <v>530</v>
       </c>
       <c r="B531" s="1">
-        <v>860</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -6989,7 +7022,7 @@
         <v>531</v>
       </c>
       <c r="B532" s="1">
-        <v>980</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="533" spans="1:2">
@@ -6997,7 +7030,7 @@
         <v>532</v>
       </c>
       <c r="B533" s="1">
-        <v>740</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -7005,7 +7038,7 @@
         <v>533</v>
       </c>
       <c r="B534" s="1">
-        <v>760</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -7013,7 +7046,7 @@
         <v>534</v>
       </c>
       <c r="B535" s="1">
-        <v>1100</v>
+        <v>840</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -7021,7 +7054,7 @@
         <v>535</v>
       </c>
       <c r="B536" s="1">
-        <v>1100</v>
+        <v>720</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -7029,7 +7062,7 @@
         <v>536</v>
       </c>
       <c r="B537" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -7037,7 +7070,7 @@
         <v>537</v>
       </c>
       <c r="B538" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -7045,7 +7078,7 @@
         <v>538</v>
       </c>
       <c r="B539" s="1">
-        <v>920</v>
+        <v>620</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -7053,7 +7086,7 @@
         <v>539</v>
       </c>
       <c r="B540" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -7061,7 +7094,7 @@
         <v>540</v>
       </c>
       <c r="B541" s="1">
-        <v>700</v>
+        <v>980</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -7069,7 +7102,7 @@
         <v>541</v>
       </c>
       <c r="B542" s="1">
-        <v>840</v>
+        <v>740</v>
       </c>
     </row>
     <row r="543" spans="1:2">
@@ -7077,7 +7110,7 @@
         <v>542</v>
       </c>
       <c r="B543" s="1">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -7085,7 +7118,7 @@
         <v>543</v>
       </c>
       <c r="B544" s="1">
-        <v>720</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -7093,7 +7126,7 @@
         <v>544</v>
       </c>
       <c r="B545" s="1">
-        <v>800</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="546" spans="1:2">
@@ -7101,7 +7134,7 @@
         <v>545</v>
       </c>
       <c r="B546" s="1">
-        <v>740</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -7109,7 +7142,7 @@
         <v>546</v>
       </c>
       <c r="B547" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -7117,7 +7150,7 @@
         <v>547</v>
       </c>
       <c r="B548" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -7125,7 +7158,7 @@
         <v>548</v>
       </c>
       <c r="B549" s="1">
-        <v>680</v>
+        <v>720</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7133,7 +7166,7 @@
         <v>549</v>
       </c>
       <c r="B550" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7141,7 +7174,7 @@
         <v>550</v>
       </c>
       <c r="B551" s="1">
-        <v>680</v>
+        <v>840</v>
       </c>
     </row>
     <row r="552" spans="1:2">
@@ -7157,7 +7190,7 @@
         <v>552</v>
       </c>
       <c r="B553" s="1">
-        <v>820</v>
+        <v>720</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7165,7 +7198,7 @@
         <v>553</v>
       </c>
       <c r="B554" s="1">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7173,7 +7206,7 @@
         <v>554</v>
       </c>
       <c r="B555" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7181,7 +7214,7 @@
         <v>555</v>
       </c>
       <c r="B556" s="1">
-        <v>1400</v>
+        <v>720</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7189,7 +7222,7 @@
         <v>556</v>
       </c>
       <c r="B557" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7197,7 +7230,7 @@
         <v>557</v>
       </c>
       <c r="B558" s="1">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7205,7 +7238,7 @@
         <v>558</v>
       </c>
       <c r="B559" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7213,7 +7246,7 @@
         <v>559</v>
       </c>
       <c r="B560" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7221,7 +7254,7 @@
         <v>560</v>
       </c>
       <c r="B561" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="562" spans="1:2">
@@ -7229,7 +7262,7 @@
         <v>561</v>
       </c>
       <c r="B562" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7237,7 +7270,7 @@
         <v>562</v>
       </c>
       <c r="B563" s="1">
-        <v>900</v>
+        <v>760</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7245,7 +7278,7 @@
         <v>563</v>
       </c>
       <c r="B564" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7253,7 +7286,7 @@
         <v>564</v>
       </c>
       <c r="B565" s="1">
-        <v>600</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7261,7 +7294,7 @@
         <v>565</v>
       </c>
       <c r="B566" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7269,7 +7302,7 @@
         <v>566</v>
       </c>
       <c r="B567" s="1">
-        <v>720</v>
+        <v>660</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7277,7 +7310,7 @@
         <v>567</v>
       </c>
       <c r="B568" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7285,7 +7318,7 @@
         <v>568</v>
       </c>
       <c r="B569" s="1">
-        <v>900</v>
+        <v>740</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7293,7 +7326,7 @@
         <v>569</v>
       </c>
       <c r="B570" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="571" spans="1:2">
@@ -7309,7 +7342,7 @@
         <v>571</v>
       </c>
       <c r="B572" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7317,7 +7350,7 @@
         <v>572</v>
       </c>
       <c r="B573" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7325,7 +7358,7 @@
         <v>573</v>
       </c>
       <c r="B574" s="1">
-        <v>640</v>
+        <v>600</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7333,7 +7366,7 @@
         <v>574</v>
       </c>
       <c r="B575" s="1">
-        <v>640</v>
+        <v>780</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7341,7 +7374,7 @@
         <v>575</v>
       </c>
       <c r="B576" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7349,7 +7382,7 @@
         <v>576</v>
       </c>
       <c r="B577" s="1">
-        <v>4000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7357,7 +7390,7 @@
         <v>577</v>
       </c>
       <c r="B578" s="1">
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7365,7 +7398,7 @@
         <v>578</v>
       </c>
       <c r="B579" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7373,7 +7406,7 @@
         <v>579</v>
       </c>
       <c r="B580" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7381,7 +7414,7 @@
         <v>580</v>
       </c>
       <c r="B581" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7389,7 +7422,7 @@
         <v>581</v>
       </c>
       <c r="B582" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7405,7 +7438,7 @@
         <v>583</v>
       </c>
       <c r="B584" s="1">
-        <v>660</v>
+        <v>640</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7413,7 +7446,7 @@
         <v>584</v>
       </c>
       <c r="B585" s="1">
-        <v>540</v>
+        <v>800</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7421,7 +7454,7 @@
         <v>585</v>
       </c>
       <c r="B586" s="1">
-        <v>660</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7429,7 +7462,7 @@
         <v>586</v>
       </c>
       <c r="B587" s="1">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7437,7 +7470,7 @@
         <v>587</v>
       </c>
       <c r="B588" s="1">
-        <v>860</v>
+        <v>720</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7445,7 +7478,7 @@
         <v>588</v>
       </c>
       <c r="B589" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7453,7 +7486,7 @@
         <v>589</v>
       </c>
       <c r="B590" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7461,7 +7494,7 @@
         <v>590</v>
       </c>
       <c r="B591" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7469,7 +7502,7 @@
         <v>591</v>
       </c>
       <c r="B592" s="1">
-        <v>1000</v>
+        <v>640</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7477,7 +7510,7 @@
         <v>592</v>
       </c>
       <c r="B593" s="1">
-        <v>900</v>
+        <v>660</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7485,7 +7518,7 @@
         <v>593</v>
       </c>
       <c r="B594" s="1">
-        <v>1040</v>
+        <v>540</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7493,7 +7526,7 @@
         <v>594</v>
       </c>
       <c r="B595" s="1">
-        <v>680</v>
+        <v>660</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7501,7 +7534,7 @@
         <v>595</v>
       </c>
       <c r="B596" s="1">
-        <v>1000</v>
+        <v>580</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7509,7 +7542,7 @@
         <v>596</v>
       </c>
       <c r="B597" s="1">
-        <v>1000</v>
+        <v>860</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7517,7 +7550,7 @@
         <v>597</v>
       </c>
       <c r="B598" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7525,7 +7558,7 @@
         <v>598</v>
       </c>
       <c r="B599" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7533,7 +7566,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="1">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7541,7 +7574,7 @@
         <v>600</v>
       </c>
       <c r="B601" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -7549,7 +7582,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="1">
-        <v>640</v>
+        <v>900</v>
       </c>
     </row>
     <row r="603" spans="1:2">
@@ -7557,7 +7590,7 @@
         <v>602</v>
       </c>
       <c r="B603" s="1">
-        <v>740</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="604" spans="1:2">
@@ -7565,7 +7598,7 @@
         <v>603</v>
       </c>
       <c r="B604" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="605" spans="1:2">
@@ -7573,7 +7606,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="1">
-        <v>640</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="606" spans="1:2">
@@ -7581,7 +7614,7 @@
         <v>605</v>
       </c>
       <c r="B606" s="1">
-        <v>720</v>
+        <v>860</v>
       </c>
     </row>
     <row r="607" spans="1:2">
@@ -7589,7 +7622,7 @@
         <v>606</v>
       </c>
       <c r="B607" s="1">
-        <v>880</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="608" spans="1:2">
@@ -7597,7 +7630,7 @@
         <v>607</v>
       </c>
       <c r="B608" s="1">
-        <v>1000</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -7605,7 +7638,7 @@
         <v>608</v>
       </c>
       <c r="B609" s="1">
-        <v>740</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="610" spans="1:2">
@@ -7613,7 +7646,7 @@
         <v>609</v>
       </c>
       <c r="B610" s="1">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="611" spans="1:2">
@@ -7621,7 +7654,7 @@
         <v>610</v>
       </c>
       <c r="B611" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -7629,7 +7662,7 @@
         <v>611</v>
       </c>
       <c r="B612" s="1">
-        <v>600</v>
+        <v>640</v>
       </c>
     </row>
     <row r="613" spans="1:2">
@@ -7637,7 +7670,7 @@
         <v>612</v>
       </c>
       <c r="B613" s="1">
-        <v>800</v>
+        <v>740</v>
       </c>
     </row>
     <row r="614" spans="1:2">
@@ -7645,7 +7678,7 @@
         <v>613</v>
       </c>
       <c r="B614" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="615" spans="1:2">
@@ -7653,7 +7686,7 @@
         <v>614</v>
       </c>
       <c r="B615" s="1">
-        <v>900</v>
+        <v>640</v>
       </c>
     </row>
     <row r="616" spans="1:2">
@@ -7661,7 +7694,7 @@
         <v>615</v>
       </c>
       <c r="B616" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="617" spans="1:2">
@@ -7669,7 +7702,7 @@
         <v>616</v>
       </c>
       <c r="B617" s="1">
-        <v>780</v>
+        <v>880</v>
       </c>
     </row>
     <row r="618" spans="1:2">
@@ -7677,7 +7710,7 @@
         <v>617</v>
       </c>
       <c r="B618" s="1">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="619" spans="1:2">
@@ -7685,7 +7718,7 @@
         <v>618</v>
       </c>
       <c r="B619" s="1">
-        <v>960</v>
+        <v>740</v>
       </c>
     </row>
     <row r="620" spans="1:2">
@@ -7693,7 +7726,7 @@
         <v>619</v>
       </c>
       <c r="B620" s="1">
-        <v>1020</v>
+        <v>600</v>
       </c>
     </row>
     <row r="621" spans="1:2">
@@ -7701,7 +7734,7 @@
         <v>620</v>
       </c>
       <c r="B621" s="1">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="622" spans="1:2">
@@ -7709,7 +7742,7 @@
         <v>621</v>
       </c>
       <c r="B622" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="623" spans="1:2">
@@ -7717,7 +7750,7 @@
         <v>622</v>
       </c>
       <c r="B623" s="1">
-        <v>640</v>
+        <v>800</v>
       </c>
     </row>
     <row r="624" spans="1:2">
@@ -7733,7 +7766,7 @@
         <v>624</v>
       </c>
       <c r="B625" s="1">
-        <v>1020</v>
+        <v>900</v>
       </c>
     </row>
     <row r="626" spans="1:2">
@@ -7741,7 +7774,7 @@
         <v>625</v>
       </c>
       <c r="B626" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="627" spans="1:2">
@@ -7749,7 +7782,7 @@
         <v>626</v>
       </c>
       <c r="B627" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="628" spans="1:2">
@@ -7757,7 +7790,7 @@
         <v>627</v>
       </c>
       <c r="B628" s="1">
-        <v>1000</v>
+        <v>720</v>
       </c>
     </row>
     <row r="629" spans="1:2">
@@ -7765,7 +7798,7 @@
         <v>628</v>
       </c>
       <c r="B629" s="1">
-        <v>780</v>
+        <v>960</v>
       </c>
     </row>
     <row r="630" spans="1:2">
@@ -7773,7 +7806,7 @@
         <v>629</v>
       </c>
       <c r="B630" s="1">
-        <v>780</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="631" spans="1:2">
@@ -7781,7 +7814,7 @@
         <v>630</v>
       </c>
       <c r="B631" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="632" spans="1:2">
@@ -7789,7 +7822,7 @@
         <v>631</v>
       </c>
       <c r="B632" s="1">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="633" spans="1:2">
@@ -7797,7 +7830,7 @@
         <v>632</v>
       </c>
       <c r="B633" s="1">
-        <v>760</v>
+        <v>640</v>
       </c>
     </row>
     <row r="634" spans="1:2">
@@ -7805,7 +7838,7 @@
         <v>633</v>
       </c>
       <c r="B634" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="635" spans="1:2">
@@ -7813,7 +7846,7 @@
         <v>634</v>
       </c>
       <c r="B635" s="1">
-        <v>740</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="636" spans="1:2">
@@ -7821,7 +7854,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="1">
-        <v>680</v>
+        <v>780</v>
       </c>
     </row>
     <row r="637" spans="1:2">
@@ -7837,7 +7870,7 @@
         <v>637</v>
       </c>
       <c r="B638" s="1">
-        <v>920</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="639" spans="1:2">
@@ -7845,7 +7878,7 @@
         <v>638</v>
       </c>
       <c r="B639" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
     </row>
     <row r="640" spans="1:2">
@@ -7853,7 +7886,7 @@
         <v>639</v>
       </c>
       <c r="B640" s="1">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="641" spans="1:2">
@@ -7861,7 +7894,7 @@
         <v>640</v>
       </c>
       <c r="B641" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="642" spans="1:2">
@@ -7869,7 +7902,7 @@
         <v>641</v>
       </c>
       <c r="B642" s="1">
-        <v>740</v>
+        <v>680</v>
       </c>
     </row>
     <row r="643" spans="1:2">
@@ -7877,7 +7910,7 @@
         <v>642</v>
       </c>
       <c r="B643" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="644" spans="1:2">
@@ -7885,7 +7918,7 @@
         <v>643</v>
       </c>
       <c r="B644" s="1">
-        <v>720</v>
+        <v>680</v>
       </c>
     </row>
     <row r="645" spans="1:2">
@@ -7893,7 +7926,7 @@
         <v>644</v>
       </c>
       <c r="B645" s="1">
-        <v>1100</v>
+        <v>740</v>
       </c>
     </row>
     <row r="646" spans="1:2">
@@ -7901,7 +7934,7 @@
         <v>645</v>
       </c>
       <c r="B646" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="647" spans="1:2">
@@ -7917,7 +7950,7 @@
         <v>647</v>
       </c>
       <c r="B648" s="1">
-        <v>900</v>
+        <v>920</v>
       </c>
     </row>
     <row r="649" spans="1:2">
@@ -7925,7 +7958,7 @@
         <v>648</v>
       </c>
       <c r="B649" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="650" spans="1:2">
@@ -7933,7 +7966,7 @@
         <v>649</v>
       </c>
       <c r="B650" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="651" spans="1:2">
@@ -7941,7 +7974,7 @@
         <v>650</v>
       </c>
       <c r="B651" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="652" spans="1:2">
@@ -7949,7 +7982,7 @@
         <v>651</v>
       </c>
       <c r="B652" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="653" spans="1:2">
@@ -7957,7 +7990,7 @@
         <v>652</v>
       </c>
       <c r="B653" s="1">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="654" spans="1:2">
@@ -7965,7 +7998,7 @@
         <v>653</v>
       </c>
       <c r="B654" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="655" spans="1:2">
@@ -7973,7 +8006,7 @@
         <v>654</v>
       </c>
       <c r="B655" s="1">
-        <v>780</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="656" spans="1:2">
@@ -7981,7 +8014,7 @@
         <v>655</v>
       </c>
       <c r="B656" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="657" spans="1:2">
@@ -7989,7 +8022,7 @@
         <v>656</v>
       </c>
       <c r="B657" s="1">
-        <v>660</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="658" spans="1:2">
@@ -7997,7 +8030,7 @@
         <v>657</v>
       </c>
       <c r="B658" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="659" spans="1:2">
@@ -8005,7 +8038,7 @@
         <v>658</v>
       </c>
       <c r="B659" s="1">
-        <v>680</v>
+        <v>900</v>
       </c>
     </row>
     <row r="660" spans="1:2">
@@ -8013,7 +8046,7 @@
         <v>659</v>
       </c>
       <c r="B660" s="1">
-        <v>660</v>
+        <v>920</v>
       </c>
     </row>
     <row r="661" spans="1:2">
@@ -8021,7 +8054,7 @@
         <v>660</v>
       </c>
       <c r="B661" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="662" spans="1:2">
@@ -8029,7 +8062,7 @@
         <v>661</v>
       </c>
       <c r="B662" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="663" spans="1:2">
@@ -8037,7 +8070,7 @@
         <v>662</v>
       </c>
       <c r="B663" s="1">
-        <v>900</v>
+        <v>880</v>
       </c>
     </row>
     <row r="664" spans="1:2">
@@ -8045,7 +8078,7 @@
         <v>663</v>
       </c>
       <c r="B664" s="1">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="665" spans="1:2">
@@ -8053,7 +8086,7 @@
         <v>664</v>
       </c>
       <c r="B665" s="1">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row r="666" spans="1:2">
@@ -8061,7 +8094,7 @@
         <v>665</v>
       </c>
       <c r="B666" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="667" spans="1:2">
@@ -8069,7 +8102,7 @@
         <v>666</v>
       </c>
       <c r="B667" s="1">
-        <v>560</v>
+        <v>660</v>
       </c>
     </row>
     <row r="668" spans="1:2">
@@ -8077,7 +8110,7 @@
         <v>667</v>
       </c>
       <c r="B668" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row r="669" spans="1:2">
@@ -8085,7 +8118,7 @@
         <v>668</v>
       </c>
       <c r="B669" s="1">
-        <v>880</v>
+        <v>680</v>
       </c>
     </row>
     <row r="670" spans="1:2">
@@ -8093,7 +8126,7 @@
         <v>669</v>
       </c>
       <c r="B670" s="1">
-        <v>800</v>
+        <v>660</v>
       </c>
     </row>
     <row r="671" spans="1:2">
@@ -8101,7 +8134,7 @@
         <v>670</v>
       </c>
       <c r="B671" s="1">
-        <v>780</v>
+        <v>440</v>
       </c>
     </row>
     <row r="672" spans="1:2">
@@ -8109,7 +8142,7 @@
         <v>671</v>
       </c>
       <c r="B672" s="1">
-        <v>920</v>
+        <v>700</v>
       </c>
     </row>
     <row r="673" spans="1:2">
@@ -8117,7 +8150,7 @@
         <v>672</v>
       </c>
       <c r="B673" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="674" spans="1:2">
@@ -8125,7 +8158,7 @@
         <v>673</v>
       </c>
       <c r="B674" s="1">
-        <v>940</v>
+        <v>800</v>
       </c>
     </row>
     <row r="675" spans="1:2">
@@ -8133,7 +8166,7 @@
         <v>674</v>
       </c>
       <c r="B675" s="1">
-        <v>980</v>
+        <v>720</v>
       </c>
     </row>
     <row r="676" spans="1:2">
@@ -8141,7 +8174,7 @@
         <v>675</v>
       </c>
       <c r="B676" s="1">
-        <v>920</v>
+        <v>600</v>
       </c>
     </row>
     <row r="677" spans="1:2">
@@ -8149,7 +8182,7 @@
         <v>676</v>
       </c>
       <c r="B677" s="1">
-        <v>780</v>
+        <v>560</v>
       </c>
     </row>
     <row r="678" spans="1:2">
@@ -8157,7 +8190,7 @@
         <v>677</v>
       </c>
       <c r="B678" s="1">
-        <v>860</v>
+        <v>900</v>
       </c>
     </row>
     <row r="679" spans="1:2">
@@ -8165,7 +8198,7 @@
         <v>678</v>
       </c>
       <c r="B679" s="1">
-        <v>920</v>
+        <v>880</v>
       </c>
     </row>
     <row r="680" spans="1:2">
@@ -8173,7 +8206,7 @@
         <v>679</v>
       </c>
       <c r="B680" s="1">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="681" spans="1:2">
@@ -8181,7 +8214,7 @@
         <v>680</v>
       </c>
       <c r="B681" s="1">
-        <v>820</v>
+        <v>780</v>
       </c>
     </row>
     <row r="682" spans="1:2">
@@ -8189,7 +8222,7 @@
         <v>681</v>
       </c>
       <c r="B682" s="1">
-        <v>960</v>
+        <v>920</v>
       </c>
     </row>
     <row r="683" spans="1:2">
@@ -8205,7 +8238,7 @@
         <v>683</v>
       </c>
       <c r="B684" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
     </row>
     <row r="685" spans="1:2">
@@ -8213,7 +8246,7 @@
         <v>684</v>
       </c>
       <c r="B685" s="1">
-        <v>860</v>
+        <v>980</v>
       </c>
     </row>
     <row r="686" spans="1:2">
@@ -8221,7 +8254,7 @@
         <v>685</v>
       </c>
       <c r="B686" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="687" spans="1:2">
@@ -8229,7 +8262,7 @@
         <v>686</v>
       </c>
       <c r="B687" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="688" spans="1:2">
@@ -8237,7 +8270,7 @@
         <v>687</v>
       </c>
       <c r="B688" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="689" spans="1:2">
@@ -8245,7 +8278,7 @@
         <v>688</v>
       </c>
       <c r="B689" s="1">
-        <v>780</v>
+        <v>920</v>
       </c>
     </row>
     <row r="690" spans="1:2">
@@ -8253,7 +8286,7 @@
         <v>689</v>
       </c>
       <c r="B690" s="1">
-        <v>820</v>
+        <v>680</v>
       </c>
     </row>
     <row r="691" spans="1:2">
@@ -8261,7 +8294,7 @@
         <v>690</v>
       </c>
       <c r="B691" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="692" spans="1:2">
@@ -8269,7 +8302,7 @@
         <v>691</v>
       </c>
       <c r="B692" s="1">
-        <v>740</v>
+        <v>960</v>
       </c>
     </row>
     <row r="693" spans="1:2">
@@ -8277,7 +8310,7 @@
         <v>692</v>
       </c>
       <c r="B693" s="1">
-        <v>780</v>
+        <v>740</v>
       </c>
     </row>
     <row r="694" spans="1:2">
@@ -8285,7 +8318,7 @@
         <v>693</v>
       </c>
       <c r="B694" s="1">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="695" spans="1:2">
@@ -8293,7 +8326,7 @@
         <v>694</v>
       </c>
       <c r="B695" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="696" spans="1:2">
@@ -8301,7 +8334,7 @@
         <v>695</v>
       </c>
       <c r="B696" s="1">
-        <v>660</v>
+        <v>780</v>
       </c>
     </row>
     <row r="697" spans="1:2">
@@ -8309,7 +8342,7 @@
         <v>696</v>
       </c>
       <c r="B697" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
     </row>
     <row r="698" spans="1:2">
@@ -8317,7 +8350,7 @@
         <v>697</v>
       </c>
       <c r="B698" s="1">
-        <v>760</v>
+        <v>840</v>
       </c>
     </row>
     <row r="699" spans="1:2">
@@ -8325,7 +8358,7 @@
         <v>698</v>
       </c>
       <c r="B699" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="700" spans="1:2">
@@ -8333,7 +8366,7 @@
         <v>699</v>
       </c>
       <c r="B700" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="701" spans="1:2">
@@ -8341,7 +8374,7 @@
         <v>700</v>
       </c>
       <c r="B701" s="1">
-        <v>680</v>
+        <v>760</v>
       </c>
     </row>
     <row r="702" spans="1:2">
@@ -8365,7 +8398,7 @@
         <v>703</v>
       </c>
       <c r="B704" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="705" spans="1:2">
@@ -8373,7 +8406,7 @@
         <v>704</v>
       </c>
       <c r="B705" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="706" spans="1:2">
@@ -8381,7 +8414,7 @@
         <v>705</v>
       </c>
       <c r="B706" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="707" spans="1:2">
@@ -8389,7 +8422,7 @@
         <v>706</v>
       </c>
       <c r="B707" s="1">
-        <v>600</v>
+        <v>740</v>
       </c>
     </row>
     <row r="708" spans="1:2">
@@ -8397,7 +8430,7 @@
         <v>707</v>
       </c>
       <c r="B708" s="1">
-        <v>500</v>
+        <v>760</v>
       </c>
     </row>
     <row r="709" spans="1:2">
@@ -8405,7 +8438,7 @@
         <v>708</v>
       </c>
       <c r="B709" s="1">
-        <v>760</v>
+        <v>700</v>
       </c>
     </row>
     <row r="710" spans="1:2">
@@ -8413,7 +8446,7 @@
         <v>709</v>
       </c>
       <c r="B710" s="1">
-        <v>920</v>
+        <v>860</v>
       </c>
     </row>
     <row r="711" spans="1:2">
@@ -8421,7 +8454,7 @@
         <v>710</v>
       </c>
       <c r="B711" s="1">
-        <v>1000</v>
+        <v>680</v>
       </c>
     </row>
     <row r="712" spans="1:2">
@@ -8429,7 +8462,7 @@
         <v>711</v>
       </c>
       <c r="B712" s="1">
-        <v>1040</v>
+        <v>740</v>
       </c>
     </row>
     <row r="713" spans="1:2">
@@ -8437,7 +8470,7 @@
         <v>712</v>
       </c>
       <c r="B713" s="1">
-        <v>940</v>
+        <v>780</v>
       </c>
     </row>
     <row r="714" spans="1:2">
@@ -8445,7 +8478,7 @@
         <v>713</v>
       </c>
       <c r="B714" s="1">
-        <v>900</v>
+        <v>720</v>
       </c>
     </row>
     <row r="715" spans="1:2">
@@ -8453,7 +8486,7 @@
         <v>714</v>
       </c>
       <c r="B715" s="1">
-        <v>1040</v>
+        <v>720</v>
       </c>
     </row>
     <row r="716" spans="1:2">
@@ -8461,7 +8494,7 @@
         <v>715</v>
       </c>
       <c r="B716" s="1">
-        <v>1100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="717" spans="1:2">
@@ -8469,7 +8502,7 @@
         <v>716</v>
       </c>
       <c r="B717" s="1">
-        <v>1000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="718" spans="1:2">
@@ -8477,7 +8510,7 @@
         <v>717</v>
       </c>
       <c r="B718" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="719" spans="1:2">
@@ -8485,7 +8518,7 @@
         <v>718</v>
       </c>
       <c r="B719" s="1">
-        <v>1100</v>
+        <v>760</v>
       </c>
     </row>
     <row r="720" spans="1:2">
@@ -8493,7 +8526,7 @@
         <v>719</v>
       </c>
       <c r="B720" s="1">
-        <v>740</v>
+        <v>920</v>
       </c>
     </row>
     <row r="721" spans="1:2">
@@ -8501,7 +8534,7 @@
         <v>720</v>
       </c>
       <c r="B721" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="722" spans="1:2">
@@ -8509,7 +8542,7 @@
         <v>721</v>
       </c>
       <c r="B722" s="1">
-        <v>440</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="723" spans="1:2">
@@ -8517,7 +8550,7 @@
         <v>722</v>
       </c>
       <c r="B723" s="1">
-        <v>500</v>
+        <v>940</v>
       </c>
     </row>
     <row r="724" spans="1:2">
@@ -8525,7 +8558,7 @@
         <v>723</v>
       </c>
       <c r="B724" s="1">
-        <v>440</v>
+        <v>900</v>
       </c>
     </row>
     <row r="725" spans="1:2">
@@ -8533,7 +8566,7 @@
         <v>724</v>
       </c>
       <c r="B725" s="1">
-        <v>560</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="726" spans="1:2">
@@ -8541,7 +8574,7 @@
         <v>725</v>
       </c>
       <c r="B726" s="1">
-        <v>500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="727" spans="1:2">
@@ -8549,7 +8582,7 @@
         <v>726</v>
       </c>
       <c r="B727" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="728" spans="1:2">
@@ -8557,7 +8590,7 @@
         <v>727</v>
       </c>
       <c r="B728" s="1">
-        <v>820</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="729" spans="1:2">
@@ -8565,7 +8598,7 @@
         <v>728</v>
       </c>
       <c r="B729" s="1">
-        <v>760</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="730" spans="1:2">
@@ -8573,7 +8606,7 @@
         <v>729</v>
       </c>
       <c r="B730" s="1">
-        <v>400</v>
+        <v>740</v>
       </c>
     </row>
     <row r="731" spans="1:2">
@@ -8581,7 +8614,7 @@
         <v>730</v>
       </c>
       <c r="B731" s="1">
-        <v>400</v>
+        <v>820</v>
       </c>
     </row>
     <row r="732" spans="1:2">
@@ -8589,7 +8622,7 @@
         <v>731</v>
       </c>
       <c r="B732" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="733" spans="1:2">
@@ -8597,7 +8630,7 @@
         <v>732</v>
       </c>
       <c r="B733" s="1">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="734" spans="1:2">
@@ -8605,7 +8638,7 @@
         <v>733</v>
       </c>
       <c r="B734" s="1">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="735" spans="1:2">
@@ -8613,7 +8646,7 @@
         <v>734</v>
       </c>
       <c r="B735" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="736" spans="1:2">
@@ -8621,7 +8654,7 @@
         <v>735</v>
       </c>
       <c r="B736" s="1">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row r="737" spans="1:2">
@@ -8629,7 +8662,7 @@
         <v>736</v>
       </c>
       <c r="B737" s="1">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="738" spans="1:2">
@@ -8637,7 +8670,7 @@
         <v>737</v>
       </c>
       <c r="B738" s="1">
-        <v>680</v>
+        <v>820</v>
       </c>
     </row>
     <row r="739" spans="1:2">
@@ -8645,7 +8678,7 @@
         <v>738</v>
       </c>
       <c r="B739" s="1">
-        <v>740</v>
+        <v>760</v>
       </c>
     </row>
     <row r="740" spans="1:2">
@@ -8653,7 +8686,7 @@
         <v>739</v>
       </c>
       <c r="B740" s="1">
-        <v>780</v>
+        <v>840</v>
       </c>
     </row>
     <row r="741" spans="1:2">
@@ -8661,7 +8694,7 @@
         <v>740</v>
       </c>
       <c r="B741" s="1">
-        <v>720</v>
+        <v>400</v>
       </c>
     </row>
     <row r="742" spans="1:2">
@@ -8669,7 +8702,7 @@
         <v>741</v>
       </c>
       <c r="B742" s="1">
-        <v>720</v>
+        <v>400</v>
       </c>
     </row>
     <row r="743" spans="1:2">
@@ -8677,7 +8710,7 @@
         <v>742</v>
       </c>
       <c r="B743" s="1">
-        <v>600</v>
+        <v>380</v>
       </c>
     </row>
     <row r="744" spans="1:2">
@@ -8685,7 +8718,7 @@
         <v>743</v>
       </c>
       <c r="B744" s="1">
-        <v>600</v>
+        <v>380</v>
       </c>
     </row>
     <row r="745" spans="1:2">
@@ -8693,7 +8726,7 @@
         <v>744</v>
       </c>
       <c r="B745" s="1">
-        <v>500</v>
+        <v>380</v>
       </c>
     </row>
     <row r="746" spans="1:2">
@@ -8701,7 +8734,7 @@
         <v>745</v>
       </c>
       <c r="B746" s="1">
-        <v>760</v>
+        <v>520</v>
       </c>
     </row>
     <row r="747" spans="1:2">
@@ -8709,7 +8742,7 @@
         <v>746</v>
       </c>
       <c r="B747" s="1">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="748" spans="1:2">
@@ -8717,7 +8750,7 @@
         <v>747</v>
       </c>
       <c r="B748" s="1">
-        <v>900</v>
+        <v>860</v>
       </c>
     </row>
     <row r="749" spans="1:2">
@@ -8725,7 +8758,7 @@
         <v>748</v>
       </c>
       <c r="B749" s="1">
-        <v>900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="750" spans="1:2">
@@ -8733,7 +8766,7 @@
         <v>749</v>
       </c>
       <c r="B750" s="1">
-        <v>920</v>
+        <v>740</v>
       </c>
     </row>
     <row r="751" spans="1:2">
@@ -8741,7 +8774,7 @@
         <v>750</v>
       </c>
       <c r="B751" s="1">
-        <v>1000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="752" spans="1:2">
@@ -8749,7 +8782,7 @@
         <v>751</v>
       </c>
       <c r="B752" s="1">
-        <v>1040</v>
+        <v>720</v>
       </c>
     </row>
     <row r="753" spans="1:2">
@@ -8757,7 +8790,7 @@
         <v>752</v>
       </c>
       <c r="B753" s="1">
-        <v>940</v>
+        <v>720</v>
       </c>
     </row>
     <row r="754" spans="1:2">
@@ -8765,7 +8798,7 @@
         <v>753</v>
       </c>
       <c r="B754" s="1">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="755" spans="1:2">
@@ -8773,7 +8806,7 @@
         <v>754</v>
       </c>
       <c r="B755" s="1">
-        <v>1040</v>
+        <v>600</v>
       </c>
     </row>
     <row r="756" spans="1:2">
@@ -8781,7 +8814,7 @@
         <v>755</v>
       </c>
       <c r="B756" s="1">
-        <v>1100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="757" spans="1:2">
@@ -8789,7 +8822,7 @@
         <v>756</v>
       </c>
       <c r="B757" s="1">
-        <v>1000</v>
+        <v>760</v>
       </c>
     </row>
     <row r="758" spans="1:2">
@@ -8797,7 +8830,7 @@
         <v>757</v>
       </c>
       <c r="B758" s="1">
-        <v>1000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="759" spans="1:2">
@@ -8805,7 +8838,7 @@
         <v>758</v>
       </c>
       <c r="B759" s="1">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="760" spans="1:2">
@@ -8813,7 +8846,7 @@
         <v>759</v>
       </c>
       <c r="B760" s="1">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="761" spans="1:2">
@@ -8821,7 +8854,7 @@
         <v>760</v>
       </c>
       <c r="B761" s="1">
-        <v>820</v>
+        <v>920</v>
       </c>
     </row>
     <row r="762" spans="1:2">
@@ -8829,7 +8862,7 @@
         <v>761</v>
       </c>
       <c r="B762" s="1">
-        <v>440</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="763" spans="1:2">
@@ -8837,7 +8870,7 @@
         <v>762</v>
       </c>
       <c r="B763" s="1">
-        <v>500</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="764" spans="1:2">
@@ -8845,7 +8878,7 @@
         <v>763</v>
       </c>
       <c r="B764" s="1">
-        <v>440</v>
+        <v>940</v>
       </c>
     </row>
     <row r="765" spans="1:2">
@@ -8853,7 +8886,7 @@
         <v>764</v>
       </c>
       <c r="B765" s="1">
-        <v>560</v>
+        <v>900</v>
       </c>
     </row>
     <row r="766" spans="1:2">
@@ -8861,7 +8894,7 @@
         <v>765</v>
       </c>
       <c r="B766" s="1">
-        <v>500</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="767" spans="1:2">
@@ -8869,7 +8902,7 @@
         <v>766</v>
       </c>
       <c r="B767" s="1">
-        <v>820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="768" spans="1:2">
@@ -8877,7 +8910,7 @@
         <v>767</v>
       </c>
       <c r="B768" s="1">
-        <v>380</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="769" spans="1:2">
@@ -8885,7 +8918,7 @@
         <v>768</v>
       </c>
       <c r="B769" s="1">
-        <v>380</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="770" spans="1:2">
@@ -8893,7 +8926,7 @@
         <v>769</v>
       </c>
       <c r="B770" s="1">
-        <v>380</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="771" spans="1:2">
@@ -8901,7 +8934,7 @@
         <v>770</v>
       </c>
       <c r="B771" s="1">
-        <v>480</v>
+        <v>740</v>
       </c>
     </row>
     <row r="772" spans="1:2">
@@ -8909,7 +8942,7 @@
         <v>771</v>
       </c>
       <c r="B772" s="1">
-        <v>480</v>
+        <v>820</v>
       </c>
     </row>
     <row r="773" spans="1:2">
@@ -8917,7 +8950,7 @@
         <v>772</v>
       </c>
       <c r="B773" s="1">
-        <v>480</v>
+        <v>440</v>
       </c>
     </row>
     <row r="774" spans="1:2">
@@ -8925,7 +8958,7 @@
         <v>773</v>
       </c>
       <c r="B774" s="1">
-        <v>520</v>
+        <v>500</v>
       </c>
     </row>
     <row r="775" spans="1:2">
@@ -8933,7 +8966,7 @@
         <v>774</v>
       </c>
       <c r="B775" s="1">
-        <v>520</v>
+        <v>440</v>
       </c>
     </row>
     <row r="776" spans="1:2">
@@ -8941,7 +8974,7 @@
         <v>775</v>
       </c>
       <c r="B776" s="1">
-        <v>440</v>
+        <v>560</v>
       </c>
     </row>
     <row r="777" spans="1:2">
@@ -8949,7 +8982,7 @@
         <v>776</v>
       </c>
       <c r="B777" s="1">
-        <v>420</v>
+        <v>500</v>
       </c>
     </row>
     <row r="778" spans="1:2">
@@ -8957,7 +8990,7 @@
         <v>777</v>
       </c>
       <c r="B778" s="1">
-        <v>380</v>
+        <v>820</v>
       </c>
     </row>
     <row r="779" spans="1:2">
@@ -8965,7 +8998,7 @@
         <v>778</v>
       </c>
       <c r="B779" s="1">
-        <v>600</v>
+        <v>380</v>
       </c>
     </row>
     <row r="780" spans="1:2">
@@ -8973,7 +9006,7 @@
         <v>779</v>
       </c>
       <c r="B780" s="1">
-        <v>820</v>
+        <v>380</v>
       </c>
     </row>
     <row r="781" spans="1:2">
@@ -8981,7 +9014,7 @@
         <v>780</v>
       </c>
       <c r="B781" s="1">
-        <v>660</v>
+        <v>380</v>
       </c>
     </row>
     <row r="782" spans="1:2">
@@ -8989,7 +9022,7 @@
         <v>781</v>
       </c>
       <c r="B782" s="1">
-        <v>580</v>
+        <v>480</v>
       </c>
     </row>
     <row r="783" spans="1:2">
@@ -8997,7 +9030,7 @@
         <v>782</v>
       </c>
       <c r="B783" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="784" spans="1:2">
@@ -9005,7 +9038,7 @@
         <v>783</v>
       </c>
       <c r="B784" s="1">
-        <v>580</v>
+        <v>480</v>
       </c>
     </row>
     <row r="785" spans="1:2">
@@ -9013,7 +9046,7 @@
         <v>784</v>
       </c>
       <c r="B785" s="1">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="786" spans="1:2">
@@ -9021,7 +9054,7 @@
         <v>785</v>
       </c>
       <c r="B786" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="787" spans="1:2">
@@ -9029,6 +9062,94 @@
         <v>786</v>
       </c>
       <c r="B787" s="1">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2">
+      <c r="A788" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="B788" s="1">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2">
+      <c r="A789" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="B789" s="1">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2">
+      <c r="A790" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="B790" s="1">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2">
+      <c r="A791" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B791" s="1">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2">
+      <c r="A792" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="B792" s="1">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2">
+      <c r="A793" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B793" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2">
+      <c r="A794" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B794" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2">
+      <c r="A795" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="B795" s="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2">
+      <c r="A796" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="B796" s="1">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2">
+      <c r="A797" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="B797" s="1">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2">
+      <c r="A798" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="B798" s="1">
         <v>560</v>
       </c>
     </row>

--- a/src/data/rozliv.xlsx
+++ b/src/data/rozliv.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="802">
   <si>
     <t>Наименование</t>
   </si>
@@ -236,6 +236,9 @@
     <t>BOON Kriek Lambic, РОЗЛИВ</t>
   </si>
   <si>
+    <t>Borodachy Brewery - Синтез (IPL), Розлив, Беларусь</t>
+  </si>
+  <si>
     <t>Boxing Wizard - Maythorn (APA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1121,6 +1124,9 @@
     <t>Valaduta Brovar - TripWave (NEDIIPA), РОЗИВ</t>
   </si>
   <si>
+    <t>Valaduta Brovar - Vibe: Simcoe, El Dorado &amp; Green Bullet (NEDIPA), РОЗИВ</t>
+  </si>
+  <si>
     <t>Velka Morava  "Золотой ярлык"  (Lager), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1376,6 +1382,9 @@
     <t xml:space="preserve">Бродилка - Сухой Сидр, РОЗЛИВ, Россия </t>
   </si>
   <si>
+    <t>вынос-Valaduta Brovar - Vibe: Simcoe, El Dorado &amp; Green Bullet (NEDIPA), РОЗИВ</t>
+  </si>
+  <si>
     <t>вынос_15 лет Velka Morava - Салива Коллаб. XV Velka Saliwa (NEIPA), РОЗЛИВ, Россия</t>
   </si>
   <si>
@@ -1500,6 +1509,9 @@
   </si>
   <si>
     <t>вынос_Black Cat - Say Lore To the Black Cat (Sour), РОЗЛИВ, Россия</t>
+  </si>
+  <si>
+    <t>вынос_Borodachy Brewery - Синтез (IPL), Розлив, Беларусь</t>
   </si>
   <si>
     <t>вынос_Boxing Wizard - Maythorn (APA), РОЗЛИВ, Россия</t>
@@ -2762,7 +2774,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B798"/>
+  <dimension ref="A1:B802"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="122.541504" bestFit="true" customWidth="true" style="0"/>
@@ -3350,7 +3362,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="1">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -3358,7 +3370,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -3366,7 +3378,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="1">
-        <v>820</v>
+        <v>760</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3374,7 +3386,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -3382,7 +3394,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="1">
-        <v>920</v>
+        <v>760</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -3390,7 +3402,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="1">
-        <v>600</v>
+        <v>920</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -3398,7 +3410,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="1">
-        <v>880</v>
+        <v>600</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -3406,7 +3418,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="1">
-        <v>640</v>
+        <v>880</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -3414,7 +3426,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="1">
-        <v>700</v>
+        <v>640</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -3422,7 +3434,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -3430,7 +3442,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -3438,7 +3450,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="1">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -3446,7 +3458,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="1">
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -3454,7 +3466,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="1">
-        <v>620</v>
+        <v>840</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -3462,7 +3474,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -3478,7 +3490,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3486,7 +3498,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3494,7 +3506,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1">
-        <v>480</v>
+        <v>560</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3502,7 +3514,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="1">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3510,7 +3522,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="1">
-        <v>540</v>
+        <v>560</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3518,7 +3530,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="1">
-        <v>860</v>
+        <v>540</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3526,7 +3538,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="1">
-        <v>840</v>
+        <v>860</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3534,7 +3546,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="1">
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3542,7 +3554,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="1">
-        <v>440</v>
+        <v>720</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3550,7 +3562,7 @@
         <v>98</v>
       </c>
       <c r="B98" s="1">
-        <v>560</v>
+        <v>440</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3558,7 +3570,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="1">
-        <v>460</v>
+        <v>560</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3574,7 +3586,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="1">
-        <v>960</v>
+        <v>460</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3582,7 +3594,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="1">
-        <v>940</v>
+        <v>960</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3590,7 +3602,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="1">
-        <v>1040</v>
+        <v>940</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3606,7 +3618,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="1">
-        <v>660</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3614,7 +3626,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1">
-        <v>480</v>
+        <v>660</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3622,7 +3634,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="1">
-        <v>400</v>
+        <v>480</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -3630,7 +3642,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="1">
-        <v>720</v>
+        <v>400</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -3638,7 +3650,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="1">
-        <v>560</v>
+        <v>720</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -3646,7 +3658,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="1">
-        <v>500</v>
+        <v>560</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -3654,7 +3666,7 @@
         <v>111</v>
       </c>
       <c r="B111" s="1">
-        <v>760</v>
+        <v>500</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -3662,7 +3674,7 @@
         <v>112</v>
       </c>
       <c r="B112" s="1">
-        <v>500</v>
+        <v>760</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -3670,7 +3682,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="1">
-        <v>940</v>
+        <v>500</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -3678,7 +3690,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="1">
-        <v>900</v>
+        <v>940</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3686,7 +3698,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -3694,7 +3706,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="1">
-        <v>680</v>
+        <v>920</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -3702,7 +3714,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="1">
-        <v>420</v>
+        <v>680</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -3710,7 +3722,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="1">
-        <v>560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -3718,7 +3730,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -3726,7 +3738,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="1">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -3734,7 +3746,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="1">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -3742,7 +3754,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="1">
-        <v>740</v>
+        <v>560</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -3750,7 +3762,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="1">
-        <v>580</v>
+        <v>740</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -3758,7 +3770,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="1">
-        <v>820</v>
+        <v>580</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -3766,7 +3778,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="1">
-        <v>620</v>
+        <v>820</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -3774,7 +3786,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="1">
-        <v>900</v>
+        <v>620</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -3782,7 +3794,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="1">
-        <v>780</v>
+        <v>900</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -3790,7 +3802,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="1">
-        <v>700</v>
+        <v>780</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -3798,7 +3810,7 @@
         <v>129</v>
       </c>
       <c r="B129" s="1">
-        <v>960</v>
+        <v>700</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -3806,7 +3818,7 @@
         <v>130</v>
       </c>
       <c r="B130" s="1">
-        <v>900</v>
+        <v>960</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -3814,7 +3826,7 @@
         <v>131</v>
       </c>
       <c r="B131" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -3822,7 +3834,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="1">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -3830,7 +3842,7 @@
         <v>133</v>
       </c>
       <c r="B133" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -3838,7 +3850,7 @@
         <v>134</v>
       </c>
       <c r="B134" s="1">
-        <v>500</v>
+        <v>780</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -3846,7 +3858,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="1">
-        <v>580</v>
+        <v>500</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -3854,7 +3866,7 @@
         <v>136</v>
       </c>
       <c r="B136" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -3862,7 +3874,7 @@
         <v>137</v>
       </c>
       <c r="B137" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -3870,7 +3882,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="1">
-        <v>1100</v>
+        <v>520</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -3878,7 +3890,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1">
-        <v>1060</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -3894,7 +3906,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="1">
-        <v>1100</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -3910,7 +3922,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -3918,12 +3930,12 @@
         <v>144</v>
       </c>
       <c r="B144" s="1">
-        <v>840</v>
+        <v>560</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B145" s="1">
         <v>840</v>
@@ -3934,7 +3946,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="1">
-        <v>420</v>
+        <v>840</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -3942,7 +3954,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="1">
-        <v>520</v>
+        <v>420</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -3950,7 +3962,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="1">
-        <v>720</v>
+        <v>520</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -3958,7 +3970,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="1">
-        <v>460</v>
+        <v>720</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -3966,7 +3978,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="1">
-        <v>560</v>
+        <v>460</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -3974,7 +3986,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -3982,7 +3994,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -3990,7 +4002,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="1">
-        <v>620</v>
+        <v>740</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -3998,7 +4010,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -4006,7 +4018,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="1">
-        <v>980</v>
+        <v>520</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -4014,7 +4026,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="1">
-        <v>540</v>
+        <v>980</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -4022,7 +4034,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="1">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -4030,7 +4042,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="1">
-        <v>740</v>
+        <v>580</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -4038,7 +4050,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="1">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4046,7 +4058,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="1">
-        <v>560</v>
+        <v>760</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -4054,7 +4066,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="1">
-        <v>1100</v>
+        <v>560</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -4086,7 +4098,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="1">
-        <v>560</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4094,7 +4106,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="1">
-        <v>640</v>
+        <v>560</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4102,7 +4114,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="1">
-        <v>560</v>
+        <v>640</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -4110,7 +4122,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="1">
-        <v>900</v>
+        <v>560</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4118,7 +4130,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="1">
-        <v>920</v>
+        <v>900</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4142,7 +4154,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="1">
-        <v>720</v>
+        <v>920</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4150,7 +4162,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="1">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4158,7 +4170,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4166,7 +4178,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="1">
-        <v>840</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4174,7 +4186,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="1">
-        <v>700</v>
+        <v>840</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4182,7 +4194,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="1">
-        <v>460</v>
+        <v>700</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4190,7 +4202,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="1">
-        <v>580</v>
+        <v>460</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4198,7 +4210,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="1">
-        <v>720</v>
+        <v>580</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4206,7 +4218,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -4214,7 +4226,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="1">
-        <v>780</v>
+        <v>660</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4222,7 +4234,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="1">
-        <v>260</v>
+        <v>780</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4238,7 +4250,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="1">
-        <v>440</v>
+        <v>260</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -4254,7 +4266,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="1">
-        <v>800</v>
+        <v>440</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4262,7 +4274,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="1">
-        <v>740</v>
+        <v>800</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4270,7 +4282,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4278,7 +4290,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="1">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4286,7 +4298,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4294,7 +4306,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="1">
-        <v>740</v>
+        <v>400</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4302,7 +4314,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="1">
-        <v>680</v>
+        <v>740</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4310,7 +4322,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="1">
-        <v>780</v>
+        <v>680</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4318,7 +4330,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="1">
-        <v>620</v>
+        <v>780</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4326,7 +4338,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="1">
-        <v>640</v>
+        <v>620</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -4334,7 +4346,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="1">
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4342,7 +4354,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="1">
-        <v>580</v>
+        <v>680</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4358,7 +4370,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4366,7 +4378,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="1">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4374,7 +4386,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4390,7 +4402,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="1">
-        <v>620</v>
+        <v>580</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4398,7 +4410,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="1">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4406,7 +4418,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="1">
-        <v>560</v>
+        <v>540</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4414,7 +4426,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="1">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4422,7 +4434,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="1">
-        <v>580</v>
+        <v>520</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4430,7 +4442,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="1">
-        <v>540</v>
+        <v>580</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4438,7 +4450,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="1">
-        <v>700</v>
+        <v>540</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4446,7 +4458,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="1">
-        <v>820</v>
+        <v>700</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4454,7 +4466,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="1">
-        <v>760</v>
+        <v>820</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4462,7 +4474,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="1">
-        <v>720</v>
+        <v>760</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4470,7 +4482,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="1">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4478,7 +4490,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="1">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4486,7 +4498,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="1">
-        <v>480</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4494,7 +4506,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="1">
-        <v>720</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4502,7 +4514,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="1">
-        <v>660</v>
+        <v>720</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4510,7 +4522,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="1">
-        <v>600</v>
+        <v>660</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4518,7 +4530,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -4526,7 +4538,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="1">
-        <v>740</v>
+        <v>700</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -4534,7 +4546,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4542,7 +4554,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4550,7 +4562,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4558,7 +4570,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="1">
-        <v>900</v>
+        <v>520</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4566,7 +4578,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="1">
-        <v>660</v>
+        <v>900</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4574,7 +4586,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="1">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4582,7 +4594,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="1">
-        <v>560</v>
+        <v>620</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4590,7 +4602,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="1">
-        <v>620</v>
+        <v>560</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4606,7 